--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -6263,10 +6263,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120944647</v>
+        <v>120944646</v>
       </c>
       <c r="B48" t="n">
-        <v>91092</v>
+        <v>98071</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6275,25 +6275,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>693266</v>
+        <v>693387</v>
       </c>
       <c r="R48" t="n">
-        <v>6553907</v>
+        <v>6554088</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6375,10 +6375,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120944646</v>
+        <v>120944647</v>
       </c>
       <c r="B49" t="n">
-        <v>98071</v>
+        <v>91092</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6387,25 +6387,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6415,10 +6415,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>693387</v>
+        <v>693266</v>
       </c>
       <c r="R49" t="n">
-        <v>6554088</v>
+        <v>6553907</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6873,10 +6873,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121124048</v>
+        <v>121124073</v>
       </c>
       <c r="B53" t="n">
-        <v>110208</v>
+        <v>90652</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6889,21 +6889,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219711</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6913,10 +6913,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>693677</v>
+        <v>693439</v>
       </c>
       <c r="R53" t="n">
-        <v>6553911</v>
+        <v>6553651</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6985,10 +6985,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121124073</v>
+        <v>121124048</v>
       </c>
       <c r="B54" t="n">
-        <v>90652</v>
+        <v>110208</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7001,21 +7001,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>219711</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>693439</v>
+        <v>693677</v>
       </c>
       <c r="R54" t="n">
-        <v>6553651</v>
+        <v>6553911</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7070,7 +7070,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8078,10 +8078,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121124059</v>
+        <v>121124053</v>
       </c>
       <c r="B63" t="n">
-        <v>89743</v>
+        <v>91370</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8090,25 +8090,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1962</v>
+        <v>3298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8118,10 +8118,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>693491</v>
+        <v>693628</v>
       </c>
       <c r="R63" t="n">
-        <v>6553751</v>
+        <v>6553797</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8177,17 +8177,22 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL63" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies # Stående död gran.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8205,10 +8210,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121124053</v>
+        <v>121124059</v>
       </c>
       <c r="B64" t="n">
-        <v>91370</v>
+        <v>89743</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8217,25 +8222,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3298</v>
+        <v>1962</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8245,10 +8250,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>693628</v>
+        <v>693491</v>
       </c>
       <c r="R64" t="n">
-        <v>6553797</v>
+        <v>6553751</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8280,7 +8285,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8290,7 +8295,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8304,22 +8309,17 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL64" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död gran.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -11355,10 +11355,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121231794</v>
+        <v>121231773</v>
       </c>
       <c r="B89" t="n">
-        <v>94594</v>
+        <v>98071</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11367,38 +11367,47 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2818</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>693674</v>
+        <v>693495</v>
       </c>
       <c r="R89" t="n">
-        <v>6553897</v>
+        <v>6553900</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11430,7 +11439,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11440,7 +11449,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11452,24 +11461,9 @@
       <c r="AG89" t="b">
         <v>0</v>
       </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL89" t="inlineStr">
-        <is>
-          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>Sluttning med tallskog</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11480,17 +11474,17 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121231773</v>
+        <v>121231794</v>
       </c>
       <c r="B90" t="n">
-        <v>98071</v>
+        <v>94594</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11499,47 +11493,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>2818</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>693495</v>
+        <v>693674</v>
       </c>
       <c r="R90" t="n">
-        <v>6553900</v>
+        <v>6553897</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11571,7 +11556,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11581,7 +11566,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11593,9 +11578,24 @@
       <c r="AG90" t="b">
         <v>0</v>
       </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>Sluttning med tallskog</t>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL90" t="inlineStr">
+        <is>
+          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11606,7 +11606,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -4362,10 +4362,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120944662</v>
+        <v>120944654</v>
       </c>
       <c r="B32" t="n">
-        <v>90707</v>
+        <v>94604</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4374,25 +4374,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>2818</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>693541</v>
+        <v>693326</v>
       </c>
       <c r="R32" t="n">
-        <v>6553901</v>
+        <v>6553834</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4458,21 +4458,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4489,10 +4474,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120944669</v>
+        <v>120944670</v>
       </c>
       <c r="B33" t="n">
-        <v>110208</v>
+        <v>83177</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4505,34 +4490,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219711</v>
+        <v>1444</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Sarcoscypha coccinea s.lat.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Jacq.:Fr.) Lambotte</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>693696</v>
+        <v>693691</v>
       </c>
       <c r="R33" t="n">
-        <v>6553895</v>
+        <v>6553897</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4564,7 +4552,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4574,7 +4562,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4583,6 +4571,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4601,10 +4590,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120944645</v>
+        <v>120944660</v>
       </c>
       <c r="B34" t="n">
-        <v>98071</v>
+        <v>100347</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4613,25 +4602,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4641,10 +4630,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>693400</v>
+        <v>693463</v>
       </c>
       <c r="R34" t="n">
-        <v>6554080</v>
+        <v>6553888</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4676,7 +4665,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4686,7 +4675,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4713,10 +4702,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120944652</v>
+        <v>120944668</v>
       </c>
       <c r="B35" t="n">
-        <v>5189</v>
+        <v>43707</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4729,21 +4718,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>105930</v>
+        <v>101735</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4758,10 +4747,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>693267</v>
+        <v>693684</v>
       </c>
       <c r="R35" t="n">
-        <v>6553784</v>
+        <v>6553982</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4793,7 +4782,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4803,7 +4792,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4814,6 +4803,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>Fnöskticka på björk</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius # Fnöskticka på björk</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4830,10 +4839,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120944644</v>
+        <v>120944659</v>
       </c>
       <c r="B36" t="n">
-        <v>98071</v>
+        <v>110218</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4842,25 +4851,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4870,10 +4879,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>693429</v>
+        <v>693460</v>
       </c>
       <c r="R36" t="n">
-        <v>6554092</v>
+        <v>6553882</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4905,7 +4914,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4915,7 +4924,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4942,10 +4951,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120944649</v>
+        <v>120944653</v>
       </c>
       <c r="B37" t="n">
-        <v>109843</v>
+        <v>109853</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4976,16 +4985,21 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>693290</v>
+        <v>693271</v>
       </c>
       <c r="R37" t="n">
-        <v>6553793</v>
+        <v>6553781</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5017,7 +5031,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5027,7 +5041,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5054,10 +5068,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120944659</v>
+        <v>120944652</v>
       </c>
       <c r="B38" t="n">
-        <v>110208</v>
+        <v>5189</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5070,34 +5084,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219711</v>
+        <v>105930</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>693460</v>
+        <v>693267</v>
       </c>
       <c r="R38" t="n">
-        <v>6553882</v>
+        <v>6553784</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5129,7 +5148,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5139,7 +5158,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5166,10 +5185,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120944651</v>
+        <v>120944672</v>
       </c>
       <c r="B39" t="n">
-        <v>100337</v>
+        <v>57370</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5182,34 +5201,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>102977</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>693262</v>
+        <v>693659</v>
       </c>
       <c r="R39" t="n">
-        <v>6553782</v>
+        <v>6553831</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5241,7 +5265,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5251,7 +5275,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5278,10 +5302,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120944663</v>
+        <v>120944651</v>
       </c>
       <c r="B40" t="n">
-        <v>8432</v>
+        <v>100347</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5294,39 +5318,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>693555</v>
+        <v>693262</v>
       </c>
       <c r="R40" t="n">
-        <v>6553910</v>
+        <v>6553782</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5358,7 +5377,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5368,7 +5387,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5379,26 +5398,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL40" t="inlineStr">
-        <is>
-          <t>Äldre tallåga</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Äldre tallåga</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5415,10 +5414,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120944654</v>
+        <v>120944675</v>
       </c>
       <c r="B41" t="n">
-        <v>94594</v>
+        <v>5169</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5431,34 +5430,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>693326</v>
+        <v>693463</v>
       </c>
       <c r="R41" t="n">
-        <v>6553834</v>
+        <v>6553650</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5490,7 +5494,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5500,7 +5504,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5511,6 +5515,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>Klen granlåga</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen granlåga</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5527,10 +5551,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120944675</v>
+        <v>120944644</v>
       </c>
       <c r="B42" t="n">
-        <v>5169</v>
+        <v>98081</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5539,43 +5563,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>693463</v>
+        <v>693429</v>
       </c>
       <c r="R42" t="n">
-        <v>6553650</v>
+        <v>6554092</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5607,7 +5626,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5617,7 +5636,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5628,26 +5647,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL42" t="inlineStr">
-        <is>
-          <t>Klen granlåga</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen granlåga</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5664,10 +5663,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120944660</v>
+        <v>120944645</v>
       </c>
       <c r="B43" t="n">
-        <v>100337</v>
+        <v>98081</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5676,25 +5675,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5704,10 +5703,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>693463</v>
+        <v>693400</v>
       </c>
       <c r="R43" t="n">
-        <v>6553888</v>
+        <v>6554080</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5739,7 +5738,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5749,7 +5748,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5776,10 +5775,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120944670</v>
+        <v>120944669</v>
       </c>
       <c r="B44" t="n">
-        <v>83174</v>
+        <v>110218</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5792,37 +5791,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1444</v>
+        <v>219711</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Scharlakansvårskål agg.</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcoscypha coccinea s.lat.</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Jacq.:Fr.) Lambotte</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>693691</v>
+        <v>693696</v>
       </c>
       <c r="R44" t="n">
-        <v>6553897</v>
+        <v>6553895</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5854,7 +5850,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5864,7 +5860,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5873,7 +5869,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5892,10 +5887,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120944653</v>
+        <v>120944647</v>
       </c>
       <c r="B45" t="n">
-        <v>109843</v>
+        <v>91102</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5904,43 +5899,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222776</v>
+        <v>5420</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>693271</v>
+        <v>693266</v>
       </c>
       <c r="R45" t="n">
-        <v>6553781</v>
+        <v>6553907</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5972,7 +5962,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5982,7 +5972,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6009,10 +5999,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120944668</v>
+        <v>120944676</v>
       </c>
       <c r="B46" t="n">
-        <v>43704</v>
+        <v>5189</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6025,39 +6015,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>101735</v>
+        <v>105930</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>693684</v>
+        <v>693463</v>
       </c>
       <c r="R46" t="n">
-        <v>6553982</v>
+        <v>6553650</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6089,7 +6074,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6099,7 +6084,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6113,22 +6098,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk</t>
+          <t>Klen granlåga</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Fomes fomentarius # Fnöskticka på björk</t>
+          <t>Picea abies # Klen granlåga</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6146,10 +6131,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120944672</v>
+        <v>120944646</v>
       </c>
       <c r="B47" t="n">
-        <v>57367</v>
+        <v>98081</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6158,43 +6143,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102977</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>693659</v>
+        <v>693387</v>
       </c>
       <c r="R47" t="n">
-        <v>6553831</v>
+        <v>6554088</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6226,7 +6206,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6236,7 +6216,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6263,10 +6243,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120944646</v>
+        <v>120944663</v>
       </c>
       <c r="B48" t="n">
-        <v>98071</v>
+        <v>8432</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6275,38 +6255,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>693387</v>
+        <v>693555</v>
       </c>
       <c r="R48" t="n">
-        <v>6554088</v>
+        <v>6553910</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6338,7 +6323,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6348,7 +6333,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6359,6 +6344,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>Äldre tallåga</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Äldre tallåga</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6375,10 +6380,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120944647</v>
+        <v>120944662</v>
       </c>
       <c r="B49" t="n">
-        <v>91092</v>
+        <v>90717</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6387,25 +6392,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6415,10 +6420,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>693266</v>
+        <v>693541</v>
       </c>
       <c r="R49" t="n">
-        <v>6553907</v>
+        <v>6553901</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6450,7 +6455,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6460,7 +6465,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6471,6 +6476,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6487,10 +6507,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120944676</v>
+        <v>120944649</v>
       </c>
       <c r="B50" t="n">
-        <v>5189</v>
+        <v>109853</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6499,25 +6519,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>105930</v>
+        <v>222776</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6527,10 +6547,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>693463</v>
+        <v>693290</v>
       </c>
       <c r="R50" t="n">
-        <v>6553650</v>
+        <v>6553793</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6562,7 +6582,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6572,7 +6592,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6583,26 +6603,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL50" t="inlineStr">
-        <is>
-          <t>Klen granlåga</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen granlåga</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6622,7 +6622,7 @@
         <v>120944657</v>
       </c>
       <c r="B51" t="n">
-        <v>94594</v>
+        <v>94604</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6731,10 +6731,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121124066</v>
+        <v>121124074</v>
       </c>
       <c r="B52" t="n">
-        <v>4766</v>
+        <v>5168</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6743,47 +6743,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100299</v>
+        <v>102204</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>693536</v>
+        <v>693455</v>
       </c>
       <c r="R52" t="n">
-        <v>6553680</v>
+        <v>6553651</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6815,7 +6811,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6825,7 +6821,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6834,7 +6830,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6850,12 +6845,12 @@
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>Stående död gran.</t>
+          <t>Gren långt ner på gammal tall.</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död gran.</t>
+          <t>Picea abies # Gren långt ner på gammal tall.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6873,10 +6868,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121124073</v>
+        <v>121124071</v>
       </c>
       <c r="B53" t="n">
-        <v>90652</v>
+        <v>94604</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6889,21 +6884,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6913,10 +6908,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>693439</v>
+        <v>693461</v>
       </c>
       <c r="R53" t="n">
-        <v>6553651</v>
+        <v>6553671</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6948,7 +6943,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6958,7 +6953,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6969,6 +6964,26 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies # Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6985,10 +7000,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121124048</v>
+        <v>121124073</v>
       </c>
       <c r="B54" t="n">
-        <v>110208</v>
+        <v>90662</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7001,21 +7016,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219711</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7025,10 +7040,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>693677</v>
+        <v>693439</v>
       </c>
       <c r="R54" t="n">
-        <v>6553911</v>
+        <v>6553651</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7060,7 +7075,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7070,7 +7085,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7097,10 +7112,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121124055</v>
+        <v>121124080</v>
       </c>
       <c r="B55" t="n">
-        <v>91998</v>
+        <v>5169</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7109,38 +7124,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5966</v>
+        <v>100526</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>693466</v>
+        <v>693426</v>
       </c>
       <c r="R55" t="n">
-        <v>6553741</v>
+        <v>6553560</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7172,7 +7192,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7182,7 +7202,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7193,6 +7213,26 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>Klen låga.</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen låga.</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7209,10 +7249,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121124047</v>
+        <v>121124066</v>
       </c>
       <c r="B56" t="n">
-        <v>110208</v>
+        <v>4766</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7225,34 +7265,43 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219711</v>
+        <v>100299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>693691</v>
+        <v>693536</v>
       </c>
       <c r="R56" t="n">
-        <v>6553924</v>
+        <v>6553680</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7284,7 +7333,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7294,7 +7343,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7303,8 +7352,29 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död gran.</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7321,10 +7391,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121124067</v>
+        <v>121124061</v>
       </c>
       <c r="B57" t="n">
-        <v>94594</v>
+        <v>94854</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7337,21 +7407,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2818</v>
+        <v>2180</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7361,10 +7431,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>693537</v>
+        <v>693526</v>
       </c>
       <c r="R57" t="n">
-        <v>6553673</v>
+        <v>6553740</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7396,7 +7466,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7406,7 +7476,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7433,10 +7503,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121124071</v>
+        <v>121124067</v>
       </c>
       <c r="B58" t="n">
-        <v>94594</v>
+        <v>94604</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7473,10 +7543,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>693461</v>
+        <v>693537</v>
       </c>
       <c r="R58" t="n">
-        <v>6553671</v>
+        <v>6553673</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7508,7 +7578,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7518,7 +7588,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7529,26 +7599,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL58" t="inlineStr">
-        <is>
-          <t>Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies # Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7565,10 +7615,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121124058</v>
+        <v>121124055</v>
       </c>
       <c r="B59" t="n">
-        <v>94844</v>
+        <v>92008</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7577,25 +7627,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7605,10 +7655,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>693480</v>
+        <v>693466</v>
       </c>
       <c r="R59" t="n">
-        <v>6553749</v>
+        <v>6553741</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7640,7 +7690,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7650,7 +7700,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7677,10 +7727,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121124070</v>
+        <v>121124081</v>
       </c>
       <c r="B60" t="n">
-        <v>94690</v>
+        <v>5168</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7689,38 +7739,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>210</v>
+        <v>102204</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>693461</v>
+        <v>693426</v>
       </c>
       <c r="R60" t="n">
-        <v>6553671</v>
+        <v>6553560</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7752,7 +7807,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7762,7 +7817,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7786,12 +7841,12 @@
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
+          <t>Klen låga.</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
+          <t>Picea abies # Klen låga.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7809,10 +7864,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121124082</v>
+        <v>121124058</v>
       </c>
       <c r="B61" t="n">
-        <v>89743</v>
+        <v>94854</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7821,25 +7876,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1962</v>
+        <v>2180</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7849,10 +7904,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>693411</v>
+        <v>693480</v>
       </c>
       <c r="R61" t="n">
-        <v>6553549</v>
+        <v>6553749</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7884,7 +7939,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7894,7 +7949,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7905,26 +7960,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL61" t="inlineStr">
-        <is>
-          <t>På undersidan av tallved.</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # På undersidan av tallved.</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7941,10 +7976,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121124080</v>
+        <v>121124053</v>
       </c>
       <c r="B62" t="n">
-        <v>5169</v>
+        <v>91380</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7957,39 +7992,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100526</v>
+        <v>3298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>693426</v>
+        <v>693628</v>
       </c>
       <c r="R62" t="n">
-        <v>6553560</v>
+        <v>6553797</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8021,7 +8051,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8031,7 +8061,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8055,12 +8085,12 @@
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>Klen låga.</t>
+          <t>Stående död gran.</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Picea abies # Klen låga.</t>
+          <t>Picea abies # Stående död gran.</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8078,10 +8108,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121124053</v>
+        <v>121124059</v>
       </c>
       <c r="B63" t="n">
-        <v>91370</v>
+        <v>89753</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8090,25 +8120,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3298</v>
+        <v>1962</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8118,10 +8148,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>693628</v>
+        <v>693491</v>
       </c>
       <c r="R63" t="n">
-        <v>6553797</v>
+        <v>6553751</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8153,7 +8183,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8163,7 +8193,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8177,22 +8207,17 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL63" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död gran.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8210,10 +8235,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121124059</v>
+        <v>121124047</v>
       </c>
       <c r="B64" t="n">
-        <v>89743</v>
+        <v>110218</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8222,25 +8247,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1962</v>
+        <v>219711</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8250,10 +8275,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>693491</v>
+        <v>693691</v>
       </c>
       <c r="R64" t="n">
-        <v>6553751</v>
+        <v>6553924</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8285,7 +8310,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8295,7 +8320,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8306,21 +8331,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8337,10 +8347,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121124081</v>
+        <v>121124056</v>
       </c>
       <c r="B65" t="n">
-        <v>5168</v>
+        <v>94854</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8349,43 +8359,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102204</v>
+        <v>2180</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>693426</v>
+        <v>693482</v>
       </c>
       <c r="R65" t="n">
-        <v>6553560</v>
+        <v>6553750</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8417,7 +8422,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8427,7 +8432,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8438,26 +8443,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL65" t="inlineStr">
-        <is>
-          <t>Klen låga.</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen låga.</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8474,10 +8459,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121124065</v>
+        <v>121124060</v>
       </c>
       <c r="B66" t="n">
-        <v>5168</v>
+        <v>57367</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8490,39 +8475,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>102204</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>693560</v>
+        <v>693507</v>
       </c>
       <c r="R66" t="n">
-        <v>6553691</v>
+        <v>6553745</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8554,7 +8534,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8564,7 +8544,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8575,26 +8555,6 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL66" t="inlineStr">
-        <is>
-          <t>Klen granlåga</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen granlåga</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8611,10 +8571,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121124056</v>
+        <v>121124065</v>
       </c>
       <c r="B67" t="n">
-        <v>94844</v>
+        <v>5168</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8623,38 +8583,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2180</v>
+        <v>102204</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>693482</v>
+        <v>693560</v>
       </c>
       <c r="R67" t="n">
-        <v>6553750</v>
+        <v>6553691</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8686,7 +8651,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8696,7 +8661,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8707,6 +8672,26 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL67" t="inlineStr">
+        <is>
+          <t>Klen granlåga</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen granlåga</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8723,10 +8708,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121124061</v>
+        <v>121124077</v>
       </c>
       <c r="B68" t="n">
-        <v>94844</v>
+        <v>5168</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8735,38 +8720,47 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2180</v>
+        <v>102204</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>693526</v>
+        <v>693453</v>
       </c>
       <c r="R68" t="n">
-        <v>6553740</v>
+        <v>6553587</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8798,7 +8792,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8808,7 +8802,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8817,8 +8811,29 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL68" t="inlineStr">
+        <is>
+          <t>Klen granlåga</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen granlåga</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8835,10 +8850,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121124077</v>
+        <v>121124082</v>
       </c>
       <c r="B69" t="n">
-        <v>5168</v>
+        <v>89753</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8851,43 +8866,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102204</v>
+        <v>1962</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>693453</v>
+        <v>693411</v>
       </c>
       <c r="R69" t="n">
-        <v>6553587</v>
+        <v>6553549</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8919,7 +8925,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8929,7 +8935,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8938,28 +8944,27 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>Klen granlåga</t>
+          <t>På undersidan av tallved.</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Picea abies # Klen granlåga</t>
+          <t>Pinus sylvestris # På undersidan av tallved.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8977,10 +8982,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121124074</v>
+        <v>121124070</v>
       </c>
       <c r="B70" t="n">
-        <v>5168</v>
+        <v>94700</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8989,43 +8994,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102204</v>
+        <v>210</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>693455</v>
+        <v>693461</v>
       </c>
       <c r="R70" t="n">
-        <v>6553651</v>
+        <v>6553671</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9057,7 +9057,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9091,12 +9091,12 @@
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>Gren långt ner på gammal tall.</t>
+          <t>Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Picea abies # Gren långt ner på gammal tall.</t>
+          <t>Picea abies # Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9114,10 +9114,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121124045</v>
+        <v>121124079</v>
       </c>
       <c r="B71" t="n">
-        <v>110208</v>
+        <v>5189</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9130,34 +9130,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219711</v>
+        <v>105930</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>693689</v>
+        <v>693431</v>
       </c>
       <c r="R71" t="n">
-        <v>6553935</v>
+        <v>6553573</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9189,7 +9194,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9199,12 +9204,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Mycket rikligt.</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9215,6 +9215,26 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL71" t="inlineStr">
+        <is>
+          <t>Klen låga.</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen låga.</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9231,10 +9251,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121124060</v>
+        <v>121124048</v>
       </c>
       <c r="B72" t="n">
-        <v>57364</v>
+        <v>110218</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9243,25 +9263,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9271,10 +9291,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>693507</v>
+        <v>693677</v>
       </c>
       <c r="R72" t="n">
-        <v>6553745</v>
+        <v>6553911</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9306,7 +9326,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9316,7 +9336,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9343,10 +9363,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121124079</v>
+        <v>121124045</v>
       </c>
       <c r="B73" t="n">
-        <v>5189</v>
+        <v>110218</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9359,39 +9379,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>105930</v>
+        <v>219711</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>693431</v>
+        <v>693689</v>
       </c>
       <c r="R73" t="n">
-        <v>6553573</v>
+        <v>6553935</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9423,7 +9438,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9433,7 +9448,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Mycket rikligt.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9444,26 +9464,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL73" t="inlineStr">
-        <is>
-          <t>Klen låga.</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen låga.</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9480,10 +9480,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121124051</v>
+        <v>121124052</v>
       </c>
       <c r="B74" t="n">
-        <v>94594</v>
+        <v>94700</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9496,21 +9496,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9612,10 +9612,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121124052</v>
+        <v>121124051</v>
       </c>
       <c r="B75" t="n">
-        <v>94690</v>
+        <v>94604</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9628,21 +9628,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9744,10 +9744,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121222341</v>
+        <v>121221017</v>
       </c>
       <c r="B76" t="n">
-        <v>8421</v>
+        <v>57367</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9756,50 +9756,46 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Breviksnäs, Srm</t>
+          <t>Kolnäsviken, Kolnäsviken, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>693587</v>
+        <v>693644</v>
       </c>
       <c r="R76" t="n">
-        <v>6553902</v>
+        <v>6554031</v>
       </c>
       <c r="S76" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9828,7 +9824,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9838,7 +9834,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9853,22 +9849,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121224726</v>
+        <v>121224119</v>
       </c>
       <c r="B77" t="n">
-        <v>97025</v>
+        <v>97035</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9909,10 +9905,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>693312</v>
+        <v>693407</v>
       </c>
       <c r="R77" t="n">
-        <v>6553808</v>
+        <v>6553843</v>
       </c>
       <c r="S77" t="n">
         <v>13</v>
@@ -9944,7 +9940,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9954,7 +9950,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9981,10 +9977,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121221017</v>
+        <v>121224447</v>
       </c>
       <c r="B78" t="n">
-        <v>57364</v>
+        <v>100347</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9993,46 +9989,45 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kolnäsviken, Kolnäsviken, Srm</t>
+          <t>Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>693644</v>
+        <v>693195</v>
       </c>
       <c r="R78" t="n">
-        <v>6554031</v>
+        <v>6553768</v>
       </c>
       <c r="S78" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10061,7 +10056,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10071,7 +10066,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10086,22 +10081,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121224447</v>
+        <v>121222341</v>
       </c>
       <c r="B79" t="n">
-        <v>100337</v>
+        <v>8421</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10114,41 +10109,46 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Sandkärr, Srm</t>
+          <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>693195</v>
+        <v>693587</v>
       </c>
       <c r="R79" t="n">
-        <v>6553768</v>
+        <v>6553902</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10326,10 +10326,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121224119</v>
+        <v>121224726</v>
       </c>
       <c r="B81" t="n">
-        <v>97025</v>
+        <v>97035</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10370,10 +10370,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>693407</v>
+        <v>693312</v>
       </c>
       <c r="R81" t="n">
-        <v>6553843</v>
+        <v>6553808</v>
       </c>
       <c r="S81" t="n">
         <v>13</v>
@@ -10405,7 +10405,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10442,10 +10442,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121231771</v>
+        <v>121231789</v>
       </c>
       <c r="B82" t="n">
-        <v>4772</v>
+        <v>91102</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10458,21 +10458,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>102306</v>
+        <v>5420</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10482,10 +10482,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>693494</v>
+        <v>693670</v>
       </c>
       <c r="R82" t="n">
-        <v>6553917</v>
+        <v>6553974</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10517,7 +10517,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10527,7 +10527,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10541,22 +10541,22 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL82" t="inlineStr">
         <is>
-          <t>Äldre grov gran</t>
+          <t>Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grov gran</t>
+          <t>Pinus sylvestris # Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10574,10 +10574,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121231764</v>
+        <v>121231782</v>
       </c>
       <c r="B83" t="n">
-        <v>5189</v>
+        <v>57367</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10586,20 +10586,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -10608,16 +10608,21 @@
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>693261</v>
+        <v>693709</v>
       </c>
       <c r="R83" t="n">
-        <v>6553742</v>
+        <v>6553983</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10649,7 +10654,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10659,7 +10664,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Födosökshack vid basen av stående död tall.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10670,26 +10680,6 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL83" t="inlineStr">
-        <is>
-          <t>Klen gran i område med många fallna granar</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen gran i område med många fallna granar</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10706,10 +10696,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121231785</v>
+        <v>121231762</v>
       </c>
       <c r="B84" t="n">
-        <v>90707</v>
+        <v>110218</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10718,25 +10708,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5442</v>
+        <v>219711</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10746,10 +10736,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>693675</v>
+        <v>693313</v>
       </c>
       <c r="R84" t="n">
-        <v>6553972</v>
+        <v>6553812</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10781,7 +10771,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10791,7 +10781,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10802,26 +10792,6 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL84" t="inlineStr">
-        <is>
-          <t>Äldre tall</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Äldre tall</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10838,10 +10808,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121231795</v>
+        <v>121231765</v>
       </c>
       <c r="B85" t="n">
-        <v>94690</v>
+        <v>100347</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10854,43 +10824,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>693674</v>
+        <v>693309</v>
       </c>
       <c r="R85" t="n">
-        <v>6553897</v>
+        <v>6553789</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10922,7 +10883,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10932,7 +10893,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10943,26 +10904,6 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL85" t="inlineStr">
-        <is>
-          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10972,17 +10913,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121231792</v>
+        <v>121231764</v>
       </c>
       <c r="B86" t="n">
-        <v>94594</v>
+        <v>5189</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10995,21 +10936,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2818</v>
+        <v>105930</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -11019,10 +10960,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>693674</v>
+        <v>693261</v>
       </c>
       <c r="R86" t="n">
-        <v>6553894</v>
+        <v>6553742</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11054,7 +10995,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11064,7 +11005,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11088,12 +11029,12 @@
       </c>
       <c r="AL86" t="inlineStr">
         <is>
-          <t>Kraftigt nedbruten granlåga</t>
+          <t>Klen gran i område med många fallna granar</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftigt nedbruten granlåga</t>
+          <t>Picea abies # Klen gran i område med många fallna granar</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11104,17 +11045,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121231781</v>
+        <v>121231792</v>
       </c>
       <c r="B87" t="n">
-        <v>5189</v>
+        <v>94604</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11127,39 +11068,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>105930</v>
+        <v>2818</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>693639</v>
+        <v>693674</v>
       </c>
       <c r="R87" t="n">
-        <v>6553969</v>
+        <v>6553894</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11191,7 +11127,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11201,7 +11137,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11223,9 +11159,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL87" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten granlåga</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Kraftigt nedbruten granlåga</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11236,17 +11177,17 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121231762</v>
+        <v>121231773</v>
       </c>
       <c r="B88" t="n">
-        <v>110208</v>
+        <v>98081</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11255,38 +11196,47 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>693313</v>
+        <v>693495</v>
       </c>
       <c r="R88" t="n">
-        <v>6553812</v>
+        <v>6553900</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11318,7 +11268,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11328,7 +11278,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11339,6 +11289,11 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>Sluttning med tallskog</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -11355,10 +11310,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121231773</v>
+        <v>121231771</v>
       </c>
       <c r="B89" t="n">
-        <v>98071</v>
+        <v>4772</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11367,47 +11322,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>693495</v>
+        <v>693494</v>
       </c>
       <c r="R89" t="n">
-        <v>6553900</v>
+        <v>6553917</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11439,7 +11385,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11449,7 +11395,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11461,9 +11407,24 @@
       <c r="AG89" t="b">
         <v>0</v>
       </c>
-      <c r="AI89" t="inlineStr">
-        <is>
-          <t>Sluttning med tallskog</t>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL89" t="inlineStr">
+        <is>
+          <t>Äldre grov gran</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grov gran</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11481,10 +11442,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121231794</v>
+        <v>121231781</v>
       </c>
       <c r="B90" t="n">
-        <v>94594</v>
+        <v>5189</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11497,34 +11458,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2818</v>
+        <v>105930</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>693674</v>
+        <v>693639</v>
       </c>
       <c r="R90" t="n">
-        <v>6553897</v>
+        <v>6553969</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11556,7 +11522,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11566,7 +11532,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11588,14 +11554,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL90" t="inlineStr">
-        <is>
-          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
-        </is>
-      </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11606,7 +11567,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -11616,7 +11577,7 @@
         <v>121231793</v>
       </c>
       <c r="B91" t="n">
-        <v>94690</v>
+        <v>94700</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11754,10 +11715,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121231767</v>
+        <v>121231775</v>
       </c>
       <c r="B92" t="n">
-        <v>94690</v>
+        <v>8432</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11770,31 +11731,27 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>210</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -11803,10 +11760,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>693436</v>
+        <v>693555</v>
       </c>
       <c r="R92" t="n">
-        <v>6553861</v>
+        <v>6553905</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11838,7 +11795,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11848,7 +11805,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11862,22 +11819,17 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL92" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten grov granlåga</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftigt nedbruten grov granlåga</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11895,10 +11847,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121231774</v>
+        <v>121231794</v>
       </c>
       <c r="B93" t="n">
-        <v>105137</v>
+        <v>94604</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11907,47 +11859,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>340</v>
+        <v>2818</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>693495</v>
+        <v>693674</v>
       </c>
       <c r="R93" t="n">
-        <v>6553900</v>
+        <v>6553897</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11979,7 +11922,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11989,12 +11932,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Två av skotten hade frökapslar.</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12006,9 +11944,24 @@
       <c r="AG93" t="b">
         <v>0</v>
       </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>Sluttning med tallskog</t>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL93" t="inlineStr">
+        <is>
+          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12019,17 +11972,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121231789</v>
+        <v>121231795</v>
       </c>
       <c r="B94" t="n">
-        <v>91092</v>
+        <v>94700</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12042,34 +11995,43 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5420</v>
+        <v>210</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>693670</v>
+        <v>693674</v>
       </c>
       <c r="R94" t="n">
-        <v>6553974</v>
+        <v>6553897</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12101,7 +12063,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12111,7 +12073,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12125,22 +12087,22 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL94" t="inlineStr">
         <is>
-          <t>Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
+          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
+          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12151,17 +12113,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121231782</v>
+        <v>121231785</v>
       </c>
       <c r="B95" t="n">
-        <v>57364</v>
+        <v>90717</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12174,39 +12136,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>693709</v>
+        <v>693675</v>
       </c>
       <c r="R95" t="n">
-        <v>6553983</v>
+        <v>6553972</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12238,7 +12195,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12248,12 +12205,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Födosökshack vid basen av stående död tall.</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12264,6 +12216,26 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL95" t="inlineStr">
+        <is>
+          <t>Äldre tall</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Äldre tall</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -12280,10 +12252,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121231775</v>
+        <v>121231774</v>
       </c>
       <c r="B96" t="n">
-        <v>8432</v>
+        <v>105147</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12292,31 +12264,35 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>340</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -12325,10 +12301,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>693555</v>
+        <v>693495</v>
       </c>
       <c r="R96" t="n">
-        <v>6553905</v>
+        <v>6553900</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12360,7 +12336,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12370,7 +12346,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Två av skotten hade frökapslar.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12382,19 +12363,9 @@
       <c r="AG96" t="b">
         <v>0</v>
       </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>Sluttning med tallskog</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12412,10 +12383,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121231765</v>
+        <v>121231767</v>
       </c>
       <c r="B97" t="n">
-        <v>100337</v>
+        <v>94700</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12428,34 +12399,43 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>693309</v>
+        <v>693436</v>
       </c>
       <c r="R97" t="n">
-        <v>6553789</v>
+        <v>6553861</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12487,7 +12467,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12497,7 +12477,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12508,6 +12488,26 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL97" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten grov granlåga</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Picea abies # Kraftigt nedbruten grov granlåga</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -12527,7 +12527,7 @@
         <v>121231766</v>
       </c>
       <c r="B98" t="n">
-        <v>94594</v>
+        <v>94604</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>121231768</v>
       </c>
       <c r="B99" t="n">
-        <v>94690</v>
+        <v>94700</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12797,10 +12797,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121231788</v>
+        <v>121231786</v>
       </c>
       <c r="B100" t="n">
-        <v>94573</v>
+        <v>94090</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12813,24 +12813,28 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2667</v>
+        <v>2362</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
@@ -12891,6 +12895,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -12914,10 +12919,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121231787</v>
+        <v>121231776</v>
       </c>
       <c r="B101" t="n">
-        <v>94367</v>
+        <v>94604</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12930,21 +12935,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2779</v>
+        <v>2818</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12954,10 +12959,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>693670</v>
+        <v>693581</v>
       </c>
       <c r="R101" t="n">
-        <v>6553974</v>
+        <v>6553897</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12989,7 +12994,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12999,7 +13004,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13010,11 +13015,6 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Vid basen av lodvägg</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -13031,10 +13031,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121231776</v>
+        <v>121231787</v>
       </c>
       <c r="B102" t="n">
-        <v>94594</v>
+        <v>94377</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13047,21 +13047,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2818</v>
+        <v>2779</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -13071,10 +13071,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>693581</v>
+        <v>693670</v>
       </c>
       <c r="R102" t="n">
-        <v>6553897</v>
+        <v>6553974</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13106,7 +13106,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13127,6 +13127,11 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Vid basen av lodvägg</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -13143,10 +13148,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121231786</v>
+        <v>121231788</v>
       </c>
       <c r="B103" t="n">
-        <v>94080</v>
+        <v>94583</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13159,28 +13164,24 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2362</v>
+        <v>2667</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Blek stjärnmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Mnium stellare</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
@@ -13241,7 +13242,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -13268,7 +13268,7 @@
         <v>121330721</v>
       </c>
       <c r="B104" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13390,37 +13390,37 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121231778</v>
+        <v>121231770</v>
       </c>
       <c r="B105" t="n">
-        <v>95657</v>
+        <v>95944</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2590</v>
+        <v>990</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -13434,10 +13434,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>693588</v>
+        <v>693478</v>
       </c>
       <c r="R105" t="n">
-        <v>6553885</v>
+        <v>6553857</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13469,7 +13469,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13479,7 +13479,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13494,22 +13494,22 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr">
         <is>
-          <t>Tallåga i kärr</t>
+          <t>Granlåga i blockig sluttning</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Tallåga i kärr</t>
+          <t>Picea abies # Granlåga i blockig sluttning</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -13527,37 +13527,37 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121231770</v>
+        <v>121231778</v>
       </c>
       <c r="B106" t="n">
-        <v>95934</v>
+        <v>95667</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>990</v>
+        <v>2590</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -13571,10 +13571,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>693478</v>
+        <v>693588</v>
       </c>
       <c r="R106" t="n">
-        <v>6553857</v>
+        <v>6553885</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13606,7 +13606,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13631,22 +13631,22 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL106" t="inlineStr">
         <is>
-          <t>Granlåga i blockig sluttning</t>
+          <t>Tallåga i kärr</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga i blockig sluttning</t>
+          <t>Pinus sylvestris # Tallåga i kärr</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -9114,10 +9114,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121124079</v>
+        <v>121124048</v>
       </c>
       <c r="B71" t="n">
-        <v>5189</v>
+        <v>110218</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9130,39 +9130,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>105930</v>
+        <v>219711</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>693431</v>
+        <v>693677</v>
       </c>
       <c r="R71" t="n">
-        <v>6553573</v>
+        <v>6553911</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9194,7 +9189,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9204,7 +9199,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9215,26 +9210,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL71" t="inlineStr">
-        <is>
-          <t>Klen låga.</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen låga.</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9251,7 +9226,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121124048</v>
+        <v>121124045</v>
       </c>
       <c r="B72" t="n">
         <v>110218</v>
@@ -9291,10 +9266,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>693677</v>
+        <v>693689</v>
       </c>
       <c r="R72" t="n">
-        <v>6553911</v>
+        <v>6553935</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9326,7 +9301,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9336,7 +9311,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Mycket rikligt.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9363,10 +9343,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121124045</v>
+        <v>121124079</v>
       </c>
       <c r="B73" t="n">
-        <v>110218</v>
+        <v>5189</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9379,34 +9359,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219711</v>
+        <v>105930</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>693689</v>
+        <v>693431</v>
       </c>
       <c r="R73" t="n">
-        <v>6553935</v>
+        <v>6553573</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9438,7 +9423,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9448,12 +9433,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Mycket rikligt.</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9464,6 +9444,26 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL73" t="inlineStr">
+        <is>
+          <t>Klen låga.</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen låga.</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9480,10 +9480,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121124052</v>
+        <v>121124051</v>
       </c>
       <c r="B74" t="n">
-        <v>94700</v>
+        <v>94604</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9496,21 +9496,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9612,10 +9612,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121124051</v>
+        <v>121124052</v>
       </c>
       <c r="B75" t="n">
-        <v>94604</v>
+        <v>94700</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9628,21 +9628,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -11184,10 +11184,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121231773</v>
+        <v>121231771</v>
       </c>
       <c r="B88" t="n">
-        <v>98081</v>
+        <v>4772</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11196,47 +11196,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>693495</v>
+        <v>693494</v>
       </c>
       <c r="R88" t="n">
-        <v>6553900</v>
+        <v>6553917</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11268,7 +11259,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11278,7 +11269,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11290,9 +11281,24 @@
       <c r="AG88" t="b">
         <v>0</v>
       </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>Sluttning med tallskog</t>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL88" t="inlineStr">
+        <is>
+          <t>Äldre grov gran</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grov gran</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11310,10 +11316,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121231771</v>
+        <v>121231781</v>
       </c>
       <c r="B89" t="n">
-        <v>4772</v>
+        <v>5189</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11326,34 +11332,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>693494</v>
+        <v>693639</v>
       </c>
       <c r="R89" t="n">
-        <v>6553917</v>
+        <v>6553969</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11385,7 +11396,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11395,7 +11406,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11417,14 +11428,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL89" t="inlineStr">
-        <is>
-          <t>Äldre grov gran</t>
-        </is>
-      </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grov gran</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11442,10 +11448,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121231781</v>
+        <v>121231773</v>
       </c>
       <c r="B90" t="n">
-        <v>5189</v>
+        <v>98081</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11454,31 +11460,35 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -11487,10 +11497,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>693639</v>
+        <v>693495</v>
       </c>
       <c r="R90" t="n">
-        <v>6553969</v>
+        <v>6553900</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11522,7 +11532,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11532,7 +11542,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11544,19 +11554,9 @@
       <c r="AG90" t="b">
         <v>0</v>
       </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>Sluttning med tallskog</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11715,10 +11715,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121231775</v>
+        <v>121231794</v>
       </c>
       <c r="B92" t="n">
-        <v>8432</v>
+        <v>94604</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11731,39 +11731,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>2818</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>693555</v>
+        <v>693674</v>
       </c>
       <c r="R92" t="n">
-        <v>6553905</v>
+        <v>6553897</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11795,7 +11790,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11805,7 +11800,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11819,17 +11814,22 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL92" t="inlineStr">
+        <is>
+          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11840,17 +11840,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121231794</v>
+        <v>121231775</v>
       </c>
       <c r="B93" t="n">
-        <v>94604</v>
+        <v>8432</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11863,34 +11863,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2818</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>693674</v>
+        <v>693555</v>
       </c>
       <c r="R93" t="n">
-        <v>6553897</v>
+        <v>6553905</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11922,7 +11927,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11932,7 +11937,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11946,22 +11951,17 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL93" t="inlineStr">
-        <is>
-          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -12120,10 +12120,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121231785</v>
+        <v>121231774</v>
       </c>
       <c r="B95" t="n">
-        <v>90717</v>
+        <v>105147</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12132,38 +12132,47 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5442</v>
+        <v>340</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>693675</v>
+        <v>693495</v>
       </c>
       <c r="R95" t="n">
-        <v>6553972</v>
+        <v>6553900</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12195,7 +12204,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12205,7 +12214,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Två av skotten hade frökapslar.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12217,24 +12231,9 @@
       <c r="AG95" t="b">
         <v>0</v>
       </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL95" t="inlineStr">
-        <is>
-          <t>Äldre tall</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Äldre tall</t>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>Sluttning med tallskog</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12252,10 +12251,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121231774</v>
+        <v>121231785</v>
       </c>
       <c r="B96" t="n">
-        <v>105147</v>
+        <v>90717</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12264,47 +12263,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>340</v>
+        <v>5442</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>693495</v>
+        <v>693675</v>
       </c>
       <c r="R96" t="n">
-        <v>6553900</v>
+        <v>6553972</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12336,7 +12326,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12346,12 +12336,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Två av skotten hade frökapslar.</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12363,9 +12348,24 @@
       <c r="AG96" t="b">
         <v>0</v>
       </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>Sluttning med tallskog</t>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL96" t="inlineStr">
+        <is>
+          <t>Äldre tall</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Äldre tall</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -4362,10 +4362,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120944654</v>
+        <v>120944660</v>
       </c>
       <c r="B32" t="n">
-        <v>94604</v>
+        <v>100347</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4378,21 +4378,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>693326</v>
+        <v>693463</v>
       </c>
       <c r="R32" t="n">
-        <v>6553834</v>
+        <v>6553888</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4474,10 +4474,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120944670</v>
+        <v>120944654</v>
       </c>
       <c r="B33" t="n">
-        <v>83177</v>
+        <v>94604</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4490,37 +4490,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1444</v>
+        <v>2818</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Scharlakansvårskål agg.</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcoscypha coccinea s.lat.</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Jacq.:Fr.) Lambotte</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>693691</v>
+        <v>693326</v>
       </c>
       <c r="R33" t="n">
-        <v>6553897</v>
+        <v>6553834</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4552,7 +4549,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4562,7 +4559,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4571,7 +4568,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4590,10 +4586,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120944660</v>
+        <v>120944670</v>
       </c>
       <c r="B34" t="n">
-        <v>100347</v>
+        <v>83177</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4606,34 +4602,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>1444</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcoscypha coccinea s.lat.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Jacq.:Fr.) Lambotte</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>693463</v>
+        <v>693691</v>
       </c>
       <c r="R34" t="n">
-        <v>6553888</v>
+        <v>6553897</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4665,7 +4664,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4675,7 +4674,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4684,6 +4683,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4702,10 +4702,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120944668</v>
+        <v>120944659</v>
       </c>
       <c r="B35" t="n">
-        <v>43707</v>
+        <v>110218</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4718,39 +4718,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>101735</v>
+        <v>219711</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>693684</v>
+        <v>693460</v>
       </c>
       <c r="R35" t="n">
-        <v>6553982</v>
+        <v>6553882</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4782,7 +4777,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4792,7 +4787,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4803,26 +4798,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AL35" t="inlineStr">
-        <is>
-          <t>Fnöskticka på björk</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius # Fnöskticka på björk</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4839,10 +4814,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120944659</v>
+        <v>120944668</v>
       </c>
       <c r="B36" t="n">
-        <v>110218</v>
+        <v>43707</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4855,34 +4830,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219711</v>
+        <v>101735</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>693460</v>
+        <v>693684</v>
       </c>
       <c r="R36" t="n">
-        <v>6553882</v>
+        <v>6553982</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4914,7 +4894,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4924,7 +4904,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4935,6 +4915,26 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>Fnöskticka på björk</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius # Fnöskticka på björk</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5185,10 +5185,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120944672</v>
+        <v>120944675</v>
       </c>
       <c r="B39" t="n">
-        <v>57370</v>
+        <v>5169</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5201,27 +5201,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102977</v>
+        <v>100526</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>693659</v>
+        <v>693463</v>
       </c>
       <c r="R39" t="n">
-        <v>6553831</v>
+        <v>6553650</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5286,6 +5286,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>Klen granlåga</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen granlåga</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5302,10 +5322,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120944651</v>
+        <v>120944672</v>
       </c>
       <c r="B40" t="n">
-        <v>100347</v>
+        <v>57370</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5318,34 +5338,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>102977</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>693262</v>
+        <v>693659</v>
       </c>
       <c r="R40" t="n">
-        <v>6553782</v>
+        <v>6553831</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5377,7 +5402,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5387,7 +5412,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5414,10 +5439,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120944675</v>
+        <v>120944651</v>
       </c>
       <c r="B41" t="n">
-        <v>5169</v>
+        <v>100347</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5430,39 +5455,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>693463</v>
+        <v>693262</v>
       </c>
       <c r="R41" t="n">
-        <v>6553650</v>
+        <v>6553782</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5494,7 +5514,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5504,7 +5524,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5515,26 +5535,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>Klen granlåga</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen granlåga</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -9114,10 +9114,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121124048</v>
+        <v>121124079</v>
       </c>
       <c r="B71" t="n">
-        <v>110218</v>
+        <v>5189</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9130,34 +9130,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219711</v>
+        <v>105930</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>693677</v>
+        <v>693431</v>
       </c>
       <c r="R71" t="n">
-        <v>6553911</v>
+        <v>6553573</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9189,7 +9194,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9199,7 +9204,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9210,6 +9215,26 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL71" t="inlineStr">
+        <is>
+          <t>Klen låga.</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen låga.</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9226,7 +9251,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121124045</v>
+        <v>121124048</v>
       </c>
       <c r="B72" t="n">
         <v>110218</v>
@@ -9266,10 +9291,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>693689</v>
+        <v>693677</v>
       </c>
       <c r="R72" t="n">
-        <v>6553935</v>
+        <v>6553911</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9301,7 +9326,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9311,12 +9336,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Mycket rikligt.</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9343,10 +9363,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121124079</v>
+        <v>121124045</v>
       </c>
       <c r="B73" t="n">
-        <v>5189</v>
+        <v>110218</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9359,39 +9379,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>105930</v>
+        <v>219711</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>693431</v>
+        <v>693689</v>
       </c>
       <c r="R73" t="n">
-        <v>6553573</v>
+        <v>6553935</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9423,7 +9438,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9433,7 +9448,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Mycket rikligt.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9444,26 +9464,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL73" t="inlineStr">
-        <is>
-          <t>Klen låga.</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen låga.</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9480,10 +9480,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121124051</v>
+        <v>121124052</v>
       </c>
       <c r="B74" t="n">
-        <v>94604</v>
+        <v>94700</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9496,21 +9496,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9612,10 +9612,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121124052</v>
+        <v>121124051</v>
       </c>
       <c r="B75" t="n">
-        <v>94700</v>
+        <v>94604</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9628,21 +9628,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -10808,10 +10808,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121231765</v>
+        <v>121231764</v>
       </c>
       <c r="B85" t="n">
-        <v>100347</v>
+        <v>5189</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10824,21 +10824,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10848,10 +10848,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>693309</v>
+        <v>693261</v>
       </c>
       <c r="R85" t="n">
-        <v>6553789</v>
+        <v>6553742</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10904,6 +10904,26 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL85" t="inlineStr">
+        <is>
+          <t>Klen gran i område med många fallna granar</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen gran i område med många fallna granar</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10920,10 +10940,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121231764</v>
+        <v>121231765</v>
       </c>
       <c r="B86" t="n">
-        <v>5189</v>
+        <v>100347</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10936,21 +10956,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10960,10 +10980,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>693261</v>
+        <v>693309</v>
       </c>
       <c r="R86" t="n">
-        <v>6553742</v>
+        <v>6553789</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10995,7 +11015,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11005,7 +11025,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11016,26 +11036,6 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL86" t="inlineStr">
-        <is>
-          <t>Klen gran i område med många fallna granar</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen gran i område med många fallna granar</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -11715,10 +11715,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121231794</v>
+        <v>121231775</v>
       </c>
       <c r="B92" t="n">
-        <v>94604</v>
+        <v>8432</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11731,34 +11731,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2818</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>693674</v>
+        <v>693555</v>
       </c>
       <c r="R92" t="n">
-        <v>6553897</v>
+        <v>6553905</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11790,7 +11795,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11800,7 +11805,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11814,22 +11819,17 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL92" t="inlineStr">
-        <is>
-          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11840,17 +11840,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121231775</v>
+        <v>121231794</v>
       </c>
       <c r="B93" t="n">
-        <v>8432</v>
+        <v>94604</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11863,39 +11863,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>2818</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>693555</v>
+        <v>693674</v>
       </c>
       <c r="R93" t="n">
-        <v>6553905</v>
+        <v>6553897</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11927,7 +11922,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11937,7 +11932,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11951,17 +11946,22 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL93" t="inlineStr">
+        <is>
+          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -4362,10 +4362,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120944660</v>
+        <v>120944668</v>
       </c>
       <c r="B32" t="n">
-        <v>100347</v>
+        <v>43707</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4378,34 +4378,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>101735</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>693463</v>
+        <v>693684</v>
       </c>
       <c r="R32" t="n">
-        <v>6553888</v>
+        <v>6553982</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4437,7 +4442,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4447,7 +4452,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4458,6 +4463,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>Fnöskticka på björk</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius # Fnöskticka på björk</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4474,10 +4499,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120944654</v>
+        <v>120944647</v>
       </c>
       <c r="B33" t="n">
-        <v>94604</v>
+        <v>91102</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4490,21 +4515,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2818</v>
+        <v>5420</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4514,10 +4539,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>693326</v>
+        <v>693266</v>
       </c>
       <c r="R33" t="n">
-        <v>6553834</v>
+        <v>6553907</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4549,7 +4574,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4559,7 +4584,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4702,10 +4727,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120944659</v>
+        <v>120944652</v>
       </c>
       <c r="B35" t="n">
-        <v>110218</v>
+        <v>5189</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4718,34 +4743,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219711</v>
+        <v>105930</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>693460</v>
+        <v>693267</v>
       </c>
       <c r="R35" t="n">
-        <v>6553882</v>
+        <v>6553784</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4777,7 +4807,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4787,7 +4817,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4814,10 +4844,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120944668</v>
+        <v>120944676</v>
       </c>
       <c r="B36" t="n">
-        <v>43707</v>
+        <v>5189</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4830,39 +4860,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>101735</v>
+        <v>105930</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>693684</v>
+        <v>693463</v>
       </c>
       <c r="R36" t="n">
-        <v>6553982</v>
+        <v>6553650</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4894,7 +4919,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4904,7 +4929,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4918,22 +4943,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk</t>
+          <t>Klen granlåga</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Fomes fomentarius # Fnöskticka på björk</t>
+          <t>Picea abies # Klen granlåga</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4951,10 +4976,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120944653</v>
+        <v>120944644</v>
       </c>
       <c r="B37" t="n">
-        <v>109853</v>
+        <v>98081</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4963,43 +4988,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222776</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>693271</v>
+        <v>693429</v>
       </c>
       <c r="R37" t="n">
-        <v>6553781</v>
+        <v>6554092</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5031,7 +5051,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5041,7 +5061,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5068,10 +5088,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120944652</v>
+        <v>120944660</v>
       </c>
       <c r="B38" t="n">
-        <v>5189</v>
+        <v>100347</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5084,39 +5104,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>693267</v>
+        <v>693463</v>
       </c>
       <c r="R38" t="n">
-        <v>6553784</v>
+        <v>6553888</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5148,7 +5163,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5158,7 +5173,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5185,10 +5200,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120944675</v>
+        <v>120944662</v>
       </c>
       <c r="B39" t="n">
-        <v>5169</v>
+        <v>90717</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5197,43 +5212,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>693463</v>
+        <v>693541</v>
       </c>
       <c r="R39" t="n">
-        <v>6553650</v>
+        <v>6553901</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5265,7 +5275,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5275,7 +5285,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5289,22 +5299,17 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL39" t="inlineStr">
-        <is>
-          <t>Klen granlåga</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies # Klen granlåga</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5322,10 +5327,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120944672</v>
+        <v>120944669</v>
       </c>
       <c r="B40" t="n">
-        <v>57370</v>
+        <v>110218</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5338,39 +5343,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102977</v>
+        <v>219711</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>693659</v>
+        <v>693696</v>
       </c>
       <c r="R40" t="n">
-        <v>6553831</v>
+        <v>6553895</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5439,10 +5439,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120944651</v>
+        <v>120944663</v>
       </c>
       <c r="B41" t="n">
-        <v>100347</v>
+        <v>8432</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5455,34 +5455,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>693262</v>
+        <v>693555</v>
       </c>
       <c r="R41" t="n">
-        <v>6553782</v>
+        <v>6553910</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5514,7 +5519,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5524,7 +5529,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5535,6 +5540,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>Äldre tallåga</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Äldre tallåga</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5551,10 +5576,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120944644</v>
+        <v>120944651</v>
       </c>
       <c r="B42" t="n">
-        <v>98081</v>
+        <v>100347</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5563,25 +5588,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5591,10 +5616,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>693429</v>
+        <v>693262</v>
       </c>
       <c r="R42" t="n">
-        <v>6554092</v>
+        <v>6553782</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5626,7 +5651,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5636,7 +5661,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5663,10 +5688,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120944645</v>
+        <v>120944659</v>
       </c>
       <c r="B43" t="n">
-        <v>98081</v>
+        <v>110218</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5675,25 +5700,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5703,10 +5728,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>693400</v>
+        <v>693460</v>
       </c>
       <c r="R43" t="n">
-        <v>6554080</v>
+        <v>6553882</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5738,7 +5763,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5748,7 +5773,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5775,10 +5800,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120944669</v>
+        <v>120944649</v>
       </c>
       <c r="B44" t="n">
-        <v>110218</v>
+        <v>109853</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5787,20 +5812,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219711</v>
+        <v>222776</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5815,10 +5840,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>693696</v>
+        <v>693290</v>
       </c>
       <c r="R44" t="n">
-        <v>6553895</v>
+        <v>6553793</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5850,7 +5875,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5860,7 +5885,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5887,10 +5912,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120944647</v>
+        <v>120944646</v>
       </c>
       <c r="B45" t="n">
-        <v>91102</v>
+        <v>98081</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5899,25 +5924,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5927,10 +5952,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>693266</v>
+        <v>693387</v>
       </c>
       <c r="R45" t="n">
-        <v>6553907</v>
+        <v>6554088</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5962,7 +5987,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5972,7 +5997,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5999,10 +6024,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120944676</v>
+        <v>120944645</v>
       </c>
       <c r="B46" t="n">
-        <v>5189</v>
+        <v>98081</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6011,25 +6036,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6039,10 +6064,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>693463</v>
+        <v>693400</v>
       </c>
       <c r="R46" t="n">
-        <v>6553650</v>
+        <v>6554080</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6074,7 +6099,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6084,7 +6109,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6095,26 +6120,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL46" t="inlineStr">
-        <is>
-          <t>Klen granlåga</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen granlåga</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6131,10 +6136,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120944646</v>
+        <v>120944654</v>
       </c>
       <c r="B47" t="n">
-        <v>98081</v>
+        <v>94604</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6143,25 +6148,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>2818</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6171,10 +6176,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>693387</v>
+        <v>693326</v>
       </c>
       <c r="R47" t="n">
-        <v>6554088</v>
+        <v>6553834</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6206,7 +6211,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6216,7 +6221,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6243,10 +6248,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120944663</v>
+        <v>120944672</v>
       </c>
       <c r="B48" t="n">
-        <v>8432</v>
+        <v>57370</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6259,27 +6264,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>102977</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6288,10 +6293,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>693555</v>
+        <v>693659</v>
       </c>
       <c r="R48" t="n">
-        <v>6553910</v>
+        <v>6553831</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6323,7 +6328,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6333,7 +6338,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6344,26 +6349,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>Äldre tallåga</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Äldre tallåga</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6380,10 +6365,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120944662</v>
+        <v>120944675</v>
       </c>
       <c r="B49" t="n">
-        <v>90717</v>
+        <v>5169</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6392,38 +6377,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>693541</v>
+        <v>693463</v>
       </c>
       <c r="R49" t="n">
-        <v>6553901</v>
+        <v>6553650</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6455,7 +6445,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6465,7 +6455,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6479,17 +6469,22 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>Klen granlåga</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies # Klen granlåga</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6507,7 +6502,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120944649</v>
+        <v>120944653</v>
       </c>
       <c r="B50" t="n">
         <v>109853</v>
@@ -6541,16 +6536,21 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>693290</v>
+        <v>693271</v>
       </c>
       <c r="R50" t="n">
-        <v>6553793</v>
+        <v>6553781</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6731,10 +6731,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121124074</v>
+        <v>121124060</v>
       </c>
       <c r="B52" t="n">
-        <v>5168</v>
+        <v>57367</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6747,39 +6747,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102204</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>693455</v>
+        <v>693507</v>
       </c>
       <c r="R52" t="n">
-        <v>6553651</v>
+        <v>6553745</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6811,7 +6806,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6821,7 +6816,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6832,26 +6827,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL52" t="inlineStr">
-        <is>
-          <t>Gren långt ner på gammal tall.</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Picea abies # Gren långt ner på gammal tall.</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6868,10 +6843,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121124071</v>
+        <v>121124070</v>
       </c>
       <c r="B53" t="n">
-        <v>94604</v>
+        <v>94700</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6884,21 +6859,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7000,10 +6975,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121124073</v>
+        <v>121124077</v>
       </c>
       <c r="B54" t="n">
-        <v>90662</v>
+        <v>5168</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7012,38 +6987,47 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>102204</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>693439</v>
+        <v>693453</v>
       </c>
       <c r="R54" t="n">
-        <v>6553651</v>
+        <v>6553587</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7075,7 +7059,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7085,7 +7069,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7094,8 +7078,29 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>Klen granlåga</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen granlåga</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7112,10 +7117,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121124080</v>
+        <v>121124055</v>
       </c>
       <c r="B55" t="n">
-        <v>5169</v>
+        <v>92008</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7124,43 +7129,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100526</v>
+        <v>5966</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>693426</v>
+        <v>693466</v>
       </c>
       <c r="R55" t="n">
-        <v>6553560</v>
+        <v>6553741</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7192,7 +7192,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7213,26 +7213,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL55" t="inlineStr">
-        <is>
-          <t>Klen låga.</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen låga.</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7249,10 +7229,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121124066</v>
+        <v>121124056</v>
       </c>
       <c r="B56" t="n">
-        <v>4766</v>
+        <v>94854</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7265,43 +7245,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100299</v>
+        <v>2180</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>693536</v>
+        <v>693482</v>
       </c>
       <c r="R56" t="n">
-        <v>6553680</v>
+        <v>6553750</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7333,7 +7304,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7343,7 +7314,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7352,29 +7323,8 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL56" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7391,10 +7341,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121124061</v>
+        <v>121124079</v>
       </c>
       <c r="B57" t="n">
-        <v>94854</v>
+        <v>5189</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7407,34 +7357,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2180</v>
+        <v>105930</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>693526</v>
+        <v>693431</v>
       </c>
       <c r="R57" t="n">
-        <v>6553740</v>
+        <v>6553573</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7466,7 +7421,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7476,7 +7431,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7487,6 +7442,26 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>Klen låga.</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen låga.</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7503,10 +7478,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121124067</v>
+        <v>121124082</v>
       </c>
       <c r="B58" t="n">
-        <v>94604</v>
+        <v>89753</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7515,25 +7490,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2818</v>
+        <v>1962</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7543,10 +7518,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>693537</v>
+        <v>693411</v>
       </c>
       <c r="R58" t="n">
-        <v>6553673</v>
+        <v>6553549</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7578,7 +7553,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7588,7 +7563,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7599,6 +7574,26 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>På undersidan av tallved.</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # På undersidan av tallved.</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7615,10 +7610,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121124055</v>
+        <v>121124065</v>
       </c>
       <c r="B59" t="n">
-        <v>92008</v>
+        <v>5168</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7631,34 +7626,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5966</v>
+        <v>102204</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>693466</v>
+        <v>693560</v>
       </c>
       <c r="R59" t="n">
-        <v>6553741</v>
+        <v>6553691</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7700,7 +7700,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7711,6 +7711,26 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL59" t="inlineStr">
+        <is>
+          <t>Klen granlåga</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen granlåga</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7727,10 +7747,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121124081</v>
+        <v>121124045</v>
       </c>
       <c r="B60" t="n">
-        <v>5168</v>
+        <v>110218</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7739,43 +7759,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102204</v>
+        <v>219711</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>693426</v>
+        <v>693689</v>
       </c>
       <c r="R60" t="n">
-        <v>6553560</v>
+        <v>6553935</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7807,7 +7822,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7817,7 +7832,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Mycket rikligt.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7828,26 +7848,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL60" t="inlineStr">
-        <is>
-          <t>Klen låga.</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen låga.</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7864,10 +7864,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121124058</v>
+        <v>121124053</v>
       </c>
       <c r="B61" t="n">
-        <v>94854</v>
+        <v>91380</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7880,21 +7880,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2180</v>
+        <v>3298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7904,10 +7904,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>693480</v>
+        <v>693628</v>
       </c>
       <c r="R61" t="n">
-        <v>6553749</v>
+        <v>6553797</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7960,6 +7960,26 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död gran.</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7976,10 +7996,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121124053</v>
+        <v>121124067</v>
       </c>
       <c r="B62" t="n">
-        <v>91380</v>
+        <v>94604</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7992,21 +8012,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3298</v>
+        <v>2818</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8016,10 +8036,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>693628</v>
+        <v>693537</v>
       </c>
       <c r="R62" t="n">
-        <v>6553797</v>
+        <v>6553673</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8051,7 +8071,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8061,7 +8081,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8072,26 +8092,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL62" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -8108,10 +8108,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121124059</v>
+        <v>121124061</v>
       </c>
       <c r="B63" t="n">
-        <v>89753</v>
+        <v>94854</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8120,25 +8120,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1962</v>
+        <v>2180</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>693491</v>
+        <v>693526</v>
       </c>
       <c r="R63" t="n">
-        <v>6553751</v>
+        <v>6553740</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8183,7 +8183,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8204,21 +8204,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -8235,10 +8220,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121124047</v>
+        <v>121124081</v>
       </c>
       <c r="B64" t="n">
-        <v>110218</v>
+        <v>5168</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8247,38 +8232,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219711</v>
+        <v>102204</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>693691</v>
+        <v>693426</v>
       </c>
       <c r="R64" t="n">
-        <v>6553924</v>
+        <v>6553560</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8310,7 +8300,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8320,7 +8310,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8331,6 +8321,26 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL64" t="inlineStr">
+        <is>
+          <t>Klen låga.</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen låga.</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8347,7 +8357,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121124056</v>
+        <v>121124058</v>
       </c>
       <c r="B65" t="n">
         <v>94854</v>
@@ -8387,10 +8397,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>693482</v>
+        <v>693480</v>
       </c>
       <c r="R65" t="n">
-        <v>6553750</v>
+        <v>6553749</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8422,7 +8432,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8432,7 +8442,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8459,10 +8469,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121124060</v>
+        <v>121124059</v>
       </c>
       <c r="B66" t="n">
-        <v>57367</v>
+        <v>89753</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8475,21 +8485,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>1962</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8499,10 +8509,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>693507</v>
+        <v>693491</v>
       </c>
       <c r="R66" t="n">
-        <v>6553745</v>
+        <v>6553751</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8534,7 +8544,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8544,7 +8554,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8555,6 +8565,21 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8571,10 +8596,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121124065</v>
+        <v>121124080</v>
       </c>
       <c r="B67" t="n">
-        <v>5168</v>
+        <v>5169</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8583,25 +8608,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102204</v>
+        <v>100526</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8616,10 +8641,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>693560</v>
+        <v>693426</v>
       </c>
       <c r="R67" t="n">
-        <v>6553691</v>
+        <v>6553560</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8651,7 +8676,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8661,7 +8686,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8685,12 +8710,12 @@
       </c>
       <c r="AL67" t="inlineStr">
         <is>
-          <t>Klen granlåga</t>
+          <t>Klen låga.</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Picea abies # Klen granlåga</t>
+          <t>Picea abies # Klen låga.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8708,10 +8733,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121124077</v>
+        <v>121124066</v>
       </c>
       <c r="B68" t="n">
-        <v>5168</v>
+        <v>4766</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8720,25 +8745,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102204</v>
+        <v>100299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8757,10 +8782,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>693453</v>
+        <v>693536</v>
       </c>
       <c r="R68" t="n">
-        <v>6553587</v>
+        <v>6553680</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8792,7 +8817,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8802,7 +8827,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8827,12 +8852,12 @@
       </c>
       <c r="AL68" t="inlineStr">
         <is>
-          <t>Klen granlåga</t>
+          <t>Stående död gran.</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Picea abies # Klen granlåga</t>
+          <t>Picea abies # Stående död gran.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8850,10 +8875,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121124082</v>
+        <v>121124074</v>
       </c>
       <c r="B69" t="n">
-        <v>89753</v>
+        <v>5168</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8866,34 +8891,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1962</v>
+        <v>102204</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>693411</v>
+        <v>693455</v>
       </c>
       <c r="R69" t="n">
-        <v>6553549</v>
+        <v>6553651</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8925,7 +8955,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8935,7 +8965,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8949,22 +8979,22 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>På undersidan av tallved.</t>
+          <t>Gren långt ner på gammal tall.</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # På undersidan av tallved.</t>
+          <t>Picea abies # Gren långt ner på gammal tall.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8982,10 +9012,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121124070</v>
+        <v>121124071</v>
       </c>
       <c r="B70" t="n">
-        <v>94700</v>
+        <v>94604</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8998,21 +9028,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9114,10 +9144,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121124079</v>
+        <v>121124073</v>
       </c>
       <c r="B71" t="n">
-        <v>5189</v>
+        <v>90662</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9130,39 +9160,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>693431</v>
+        <v>693439</v>
       </c>
       <c r="R71" t="n">
-        <v>6553573</v>
+        <v>6553651</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9194,7 +9219,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9204,7 +9229,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9215,26 +9240,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL71" t="inlineStr">
-        <is>
-          <t>Klen låga.</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen låga.</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9251,7 +9256,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121124048</v>
+        <v>121124047</v>
       </c>
       <c r="B72" t="n">
         <v>110218</v>
@@ -9291,10 +9296,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>693677</v>
+        <v>693691</v>
       </c>
       <c r="R72" t="n">
-        <v>6553911</v>
+        <v>6553924</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9326,7 +9331,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9336,7 +9341,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9363,7 +9368,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121124045</v>
+        <v>121124048</v>
       </c>
       <c r="B73" t="n">
         <v>110218</v>
@@ -9403,10 +9408,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>693689</v>
+        <v>693677</v>
       </c>
       <c r="R73" t="n">
-        <v>6553935</v>
+        <v>6553911</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9438,7 +9443,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9448,12 +9453,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Mycket rikligt.</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9480,10 +9480,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121124052</v>
+        <v>121124051</v>
       </c>
       <c r="B74" t="n">
-        <v>94700</v>
+        <v>94604</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9496,21 +9496,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9612,10 +9612,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121124051</v>
+        <v>121124052</v>
       </c>
       <c r="B75" t="n">
-        <v>94604</v>
+        <v>94700</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9628,21 +9628,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9744,10 +9744,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121221017</v>
+        <v>121224119</v>
       </c>
       <c r="B76" t="n">
-        <v>57367</v>
+        <v>97035</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9756,46 +9756,45 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kolnäsviken, Kolnäsviken, Srm</t>
+          <t>Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>693644</v>
+        <v>693407</v>
       </c>
       <c r="R76" t="n">
-        <v>6554031</v>
+        <v>6553843</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9824,7 +9823,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9834,7 +9833,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9849,22 +9848,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121224119</v>
+        <v>121224447</v>
       </c>
       <c r="B77" t="n">
-        <v>97035</v>
+        <v>100347</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9877,21 +9876,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9905,13 +9904,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>693407</v>
+        <v>693195</v>
       </c>
       <c r="R77" t="n">
-        <v>6553843</v>
+        <v>6553768</v>
       </c>
       <c r="S77" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9940,7 +9939,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9950,7 +9949,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9977,10 +9976,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121224447</v>
+        <v>121222341</v>
       </c>
       <c r="B78" t="n">
-        <v>100347</v>
+        <v>8421</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9993,41 +9992,46 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sandkärr, Srm</t>
+          <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>693195</v>
+        <v>693587</v>
       </c>
       <c r="R78" t="n">
-        <v>6553768</v>
+        <v>6553902</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10056,7 +10060,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10066,7 +10070,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10093,10 +10097,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121222341</v>
+        <v>121224726</v>
       </c>
       <c r="B79" t="n">
-        <v>8421</v>
+        <v>97035</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10109,43 +10113,38 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Breviksnäs, Srm</t>
+          <t>Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>693587</v>
+        <v>693312</v>
       </c>
       <c r="R79" t="n">
-        <v>6553902</v>
+        <v>6553808</v>
       </c>
       <c r="S79" t="n">
         <v>13</v>
@@ -10177,7 +10176,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10187,7 +10186,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10326,10 +10325,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121224726</v>
+        <v>121221017</v>
       </c>
       <c r="B81" t="n">
-        <v>97035</v>
+        <v>57367</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10338,45 +10337,46 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sandkärr, Srm</t>
+          <t>Kolnäsviken, Kolnäsviken, Srm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>693312</v>
+        <v>693644</v>
       </c>
       <c r="R81" t="n">
-        <v>6553808</v>
+        <v>6554031</v>
       </c>
       <c r="S81" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10430,22 +10430,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121231789</v>
+        <v>121231771</v>
       </c>
       <c r="B82" t="n">
-        <v>91102</v>
+        <v>4772</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10458,21 +10458,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5420</v>
+        <v>102306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10482,10 +10482,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>693670</v>
+        <v>693494</v>
       </c>
       <c r="R82" t="n">
-        <v>6553974</v>
+        <v>6553917</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10517,7 +10517,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10527,7 +10527,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10541,22 +10541,22 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL82" t="inlineStr">
         <is>
-          <t>Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
+          <t>Äldre grov gran</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
+          <t>Picea abies # Äldre grov gran</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10574,10 +10574,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121231782</v>
+        <v>121231765</v>
       </c>
       <c r="B83" t="n">
-        <v>57367</v>
+        <v>100347</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10586,43 +10586,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>693709</v>
+        <v>693309</v>
       </c>
       <c r="R83" t="n">
-        <v>6553983</v>
+        <v>6553789</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10654,7 +10649,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10664,12 +10659,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Födosökshack vid basen av stående död tall.</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10696,10 +10686,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121231762</v>
+        <v>121231792</v>
       </c>
       <c r="B84" t="n">
-        <v>110218</v>
+        <v>94604</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10712,21 +10702,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>219711</v>
+        <v>2818</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10736,10 +10726,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>693313</v>
+        <v>693674</v>
       </c>
       <c r="R84" t="n">
-        <v>6553812</v>
+        <v>6553894</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10771,7 +10761,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10781,7 +10771,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10792,6 +10782,26 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL84" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten granlåga</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Picea abies # Kraftigt nedbruten granlåga</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10801,17 +10811,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121231764</v>
+        <v>121231789</v>
       </c>
       <c r="B85" t="n">
-        <v>5189</v>
+        <v>91102</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10824,21 +10834,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>105930</v>
+        <v>5420</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10848,10 +10858,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>693261</v>
+        <v>693670</v>
       </c>
       <c r="R85" t="n">
-        <v>6553742</v>
+        <v>6553974</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10883,7 +10893,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10893,7 +10903,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10907,22 +10917,22 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL85" t="inlineStr">
         <is>
-          <t>Klen gran i område med många fallna granar</t>
+          <t>Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Picea abies # Klen gran i område med många fallna granar</t>
+          <t>Pinus sylvestris # Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10940,10 +10950,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121231765</v>
+        <v>121231775</v>
       </c>
       <c r="B86" t="n">
-        <v>100347</v>
+        <v>8432</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10956,34 +10966,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>222498</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>693309</v>
+        <v>693555</v>
       </c>
       <c r="R86" t="n">
-        <v>6553789</v>
+        <v>6553905</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11015,7 +11030,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11025,7 +11040,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11036,6 +11051,21 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -11052,7 +11082,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121231792</v>
+        <v>121231794</v>
       </c>
       <c r="B87" t="n">
         <v>94604</v>
@@ -11095,7 +11125,7 @@
         <v>693674</v>
       </c>
       <c r="R87" t="n">
-        <v>6553894</v>
+        <v>6553897</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11127,7 +11157,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11137,7 +11167,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11161,12 +11191,12 @@
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>Kraftigt nedbruten granlåga</t>
+          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftigt nedbruten granlåga</t>
+          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11184,10 +11214,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121231771</v>
+        <v>121231773</v>
       </c>
       <c r="B88" t="n">
-        <v>4772</v>
+        <v>98081</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11196,38 +11226,47 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>693494</v>
+        <v>693495</v>
       </c>
       <c r="R88" t="n">
-        <v>6553917</v>
+        <v>6553900</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11259,7 +11298,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11269,7 +11308,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11281,24 +11320,9 @@
       <c r="AG88" t="b">
         <v>0</v>
       </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL88" t="inlineStr">
-        <is>
-          <t>Äldre grov gran</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre grov gran</t>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>Sluttning med tallskog</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11316,10 +11340,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121231781</v>
+        <v>121231785</v>
       </c>
       <c r="B89" t="n">
-        <v>5189</v>
+        <v>90717</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11328,43 +11352,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>105930</v>
+        <v>5442</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>693639</v>
+        <v>693675</v>
       </c>
       <c r="R89" t="n">
-        <v>6553969</v>
+        <v>6553972</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11396,7 +11415,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11406,7 +11425,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11420,17 +11439,22 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL89" t="inlineStr">
+        <is>
+          <t>Äldre tall</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris # Äldre tall</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11448,10 +11472,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121231773</v>
+        <v>121231764</v>
       </c>
       <c r="B90" t="n">
-        <v>98081</v>
+        <v>5189</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11460,47 +11484,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>693495</v>
+        <v>693261</v>
       </c>
       <c r="R90" t="n">
-        <v>6553900</v>
+        <v>6553742</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11532,7 +11547,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11542,7 +11557,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11554,9 +11569,24 @@
       <c r="AG90" t="b">
         <v>0</v>
       </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>Sluttning med tallskog</t>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL90" t="inlineStr">
+        <is>
+          <t>Klen gran i område med många fallna granar</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen gran i område med många fallna granar</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11574,7 +11604,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121231793</v>
+        <v>121231767</v>
       </c>
       <c r="B91" t="n">
         <v>94700</v>
@@ -11609,7 +11639,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11623,10 +11653,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>693674</v>
+        <v>693436</v>
       </c>
       <c r="R91" t="n">
-        <v>6553894</v>
+        <v>6553861</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11658,7 +11688,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11668,7 +11698,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11692,12 +11722,12 @@
       </c>
       <c r="AL91" t="inlineStr">
         <is>
-          <t>Kraftigt nedbruten granlåga</t>
+          <t>Kraftigt nedbruten grov granlåga</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftigt nedbruten granlåga</t>
+          <t>Picea abies # Kraftigt nedbruten grov granlåga</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11708,17 +11738,17 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121231775</v>
+        <v>121231795</v>
       </c>
       <c r="B92" t="n">
-        <v>8432</v>
+        <v>94700</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11731,27 +11761,31 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>210</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -11760,10 +11794,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>693555</v>
+        <v>693674</v>
       </c>
       <c r="R92" t="n">
-        <v>6553905</v>
+        <v>6553897</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11795,7 +11829,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11805,7 +11839,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11819,17 +11853,22 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL92" t="inlineStr">
+        <is>
+          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11840,17 +11879,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121231794</v>
+        <v>121231762</v>
       </c>
       <c r="B93" t="n">
-        <v>94604</v>
+        <v>110218</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11863,21 +11902,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2818</v>
+        <v>219711</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11887,10 +11926,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>693674</v>
+        <v>693313</v>
       </c>
       <c r="R93" t="n">
-        <v>6553897</v>
+        <v>6553812</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11922,7 +11961,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11932,7 +11971,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11943,26 +11982,6 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL93" t="inlineStr">
-        <is>
-          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11972,17 +11991,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121231795</v>
+        <v>121231774</v>
       </c>
       <c r="B94" t="n">
-        <v>94700</v>
+        <v>105147</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11991,35 +12010,35 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>210</v>
+        <v>340</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) W. P. C. Barton</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -12028,10 +12047,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>693674</v>
+        <v>693495</v>
       </c>
       <c r="R94" t="n">
-        <v>6553897</v>
+        <v>6553900</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12063,7 +12082,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12073,7 +12092,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Två av skotten hade frökapslar.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12085,24 +12109,9 @@
       <c r="AG94" t="b">
         <v>0</v>
       </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL94" t="inlineStr">
-        <is>
-          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>Sluttning med tallskog</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12113,17 +12122,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121231774</v>
+        <v>121231782</v>
       </c>
       <c r="B95" t="n">
-        <v>105147</v>
+        <v>57367</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12132,35 +12141,31 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>340</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -12169,10 +12174,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>693495</v>
+        <v>693709</v>
       </c>
       <c r="R95" t="n">
-        <v>6553900</v>
+        <v>6553983</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12204,7 +12209,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12214,12 +12219,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Två av skotten hade frökapslar.</t>
+          <t>Födosökshack vid basen av stående död tall.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12230,11 +12235,6 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>Sluttning med tallskog</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -12251,10 +12251,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121231785</v>
+        <v>121231781</v>
       </c>
       <c r="B96" t="n">
-        <v>90717</v>
+        <v>5189</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12263,38 +12263,43 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5442</v>
+        <v>105930</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>693675</v>
+        <v>693639</v>
       </c>
       <c r="R96" t="n">
-        <v>6553972</v>
+        <v>6553969</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12326,7 +12331,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12336,7 +12341,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12350,22 +12355,17 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL96" t="inlineStr">
-        <is>
-          <t>Äldre tall</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Äldre tall</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12383,7 +12383,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121231767</v>
+        <v>121231793</v>
       </c>
       <c r="B97" t="n">
         <v>94700</v>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -12432,10 +12432,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>693436</v>
+        <v>693674</v>
       </c>
       <c r="R97" t="n">
-        <v>6553861</v>
+        <v>6553894</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12467,7 +12467,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>Kraftigt nedbruten grov granlåga</t>
+          <t>Kraftigt nedbruten granlåga</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftigt nedbruten grov granlåga</t>
+          <t>Picea abies # Kraftigt nedbruten granlåga</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -12517,7 +12517,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -12656,10 +12656,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121231768</v>
+        <v>121231788</v>
       </c>
       <c r="B99" t="n">
-        <v>94700</v>
+        <v>94583</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12672,43 +12672,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>210</v>
+        <v>2667</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>693478</v>
+        <v>693670</v>
       </c>
       <c r="R99" t="n">
-        <v>6553857</v>
+        <v>6553974</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12740,7 +12731,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12750,7 +12741,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12762,24 +12753,9 @@
       <c r="AG99" t="b">
         <v>0</v>
       </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL99" t="inlineStr">
-        <is>
-          <t>Granlåga i blockig sluttning</t>
-        </is>
-      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga i blockig sluttning</t>
+          <t>Vid basen av lodvägg</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -12797,10 +12773,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121231786</v>
+        <v>121231768</v>
       </c>
       <c r="B100" t="n">
-        <v>94090</v>
+        <v>94700</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12813,38 +12789,43 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2362</v>
+        <v>210</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blek stjärnmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Mnium stellare</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>693670</v>
+        <v>693478</v>
       </c>
       <c r="R100" t="n">
-        <v>6553974</v>
+        <v>6553857</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12876,7 +12857,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12886,7 +12867,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12895,13 +12876,27 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL100" t="inlineStr">
+        <is>
+          <t>Granlåga i blockig sluttning</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>Vid basen av lodvägg</t>
+          <t>Picea abies # Granlåga i blockig sluttning</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -12919,10 +12914,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121231776</v>
+        <v>121231786</v>
       </c>
       <c r="B101" t="n">
-        <v>94604</v>
+        <v>94090</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12935,34 +12930,38 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2818</v>
+        <v>2362</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>693581</v>
+        <v>693670</v>
       </c>
       <c r="R101" t="n">
-        <v>6553897</v>
+        <v>6553974</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12994,7 +12993,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -13004,7 +13003,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13013,8 +13012,14 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Vid basen av lodvägg</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -13031,10 +13036,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121231787</v>
+        <v>121231776</v>
       </c>
       <c r="B102" t="n">
-        <v>94377</v>
+        <v>94604</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13047,21 +13052,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2779</v>
+        <v>2818</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -13071,10 +13076,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>693670</v>
+        <v>693581</v>
       </c>
       <c r="R102" t="n">
-        <v>6553974</v>
+        <v>6553897</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13106,7 +13111,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13116,7 +13121,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13127,11 +13132,6 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Vid basen av lodvägg</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -13148,10 +13148,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121231788</v>
+        <v>121231787</v>
       </c>
       <c r="B103" t="n">
-        <v>94583</v>
+        <v>94377</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13164,21 +13164,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -13390,37 +13390,37 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121231770</v>
+        <v>121231778</v>
       </c>
       <c r="B105" t="n">
-        <v>95944</v>
+        <v>95667</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>990</v>
+        <v>2590</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -13434,10 +13434,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>693478</v>
+        <v>693588</v>
       </c>
       <c r="R105" t="n">
-        <v>6553857</v>
+        <v>6553885</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13469,7 +13469,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13479,7 +13479,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13494,22 +13494,22 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr">
         <is>
-          <t>Granlåga i blockig sluttning</t>
+          <t>Tallåga i kärr</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga i blockig sluttning</t>
+          <t>Pinus sylvestris # Tallåga i kärr</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -13527,37 +13527,37 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121231778</v>
+        <v>121231770</v>
       </c>
       <c r="B106" t="n">
-        <v>95667</v>
+        <v>95944</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2590</v>
+        <v>990</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -13571,10 +13571,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>693588</v>
+        <v>693478</v>
       </c>
       <c r="R106" t="n">
-        <v>6553885</v>
+        <v>6553857</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13606,7 +13606,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13631,22 +13631,22 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL106" t="inlineStr">
         <is>
-          <t>Tallåga i kärr</t>
+          <t>Granlåga i blockig sluttning</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Tallåga i kärr</t>
+          <t>Picea abies # Granlåga i blockig sluttning</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -4499,10 +4499,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120944647</v>
+        <v>120944652</v>
       </c>
       <c r="B33" t="n">
-        <v>91102</v>
+        <v>5189</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4515,34 +4515,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5420</v>
+        <v>105930</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>693266</v>
+        <v>693267</v>
       </c>
       <c r="R33" t="n">
-        <v>6553907</v>
+        <v>6553784</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4574,7 +4579,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4584,7 +4589,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4727,10 +4732,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120944652</v>
+        <v>120944647</v>
       </c>
       <c r="B35" t="n">
-        <v>5189</v>
+        <v>91102</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4743,39 +4748,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>105930</v>
+        <v>5420</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>693267</v>
+        <v>693266</v>
       </c>
       <c r="R35" t="n">
-        <v>6553784</v>
+        <v>6553907</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4807,7 +4807,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5800,10 +5800,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120944649</v>
+        <v>120944646</v>
       </c>
       <c r="B44" t="n">
-        <v>109853</v>
+        <v>98081</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5812,25 +5812,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222776</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5840,10 +5840,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>693290</v>
+        <v>693387</v>
       </c>
       <c r="R44" t="n">
-        <v>6553793</v>
+        <v>6554088</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5912,7 +5912,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120944646</v>
+        <v>120944645</v>
       </c>
       <c r="B45" t="n">
         <v>98081</v>
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>693387</v>
+        <v>693400</v>
       </c>
       <c r="R45" t="n">
-        <v>6554088</v>
+        <v>6554080</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5987,7 +5987,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6024,10 +6024,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120944645</v>
+        <v>120944649</v>
       </c>
       <c r="B46" t="n">
-        <v>98081</v>
+        <v>109853</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6036,25 +6036,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>222776</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6064,10 +6064,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>693400</v>
+        <v>693290</v>
       </c>
       <c r="R46" t="n">
-        <v>6554080</v>
+        <v>6553793</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -7341,10 +7341,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121124079</v>
+        <v>121124082</v>
       </c>
       <c r="B57" t="n">
-        <v>5189</v>
+        <v>89753</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7353,43 +7353,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>105930</v>
+        <v>1962</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>693431</v>
+        <v>693411</v>
       </c>
       <c r="R57" t="n">
-        <v>6553573</v>
+        <v>6553549</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7421,7 +7416,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7431,7 +7426,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7445,22 +7440,22 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>Klen låga.</t>
+          <t>På undersidan av tallved.</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies # Klen låga.</t>
+          <t>Pinus sylvestris # På undersidan av tallved.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7478,10 +7473,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121124082</v>
+        <v>121124065</v>
       </c>
       <c r="B58" t="n">
-        <v>89753</v>
+        <v>5168</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7494,34 +7489,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1962</v>
+        <v>102204</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>693411</v>
+        <v>693560</v>
       </c>
       <c r="R58" t="n">
-        <v>6553549</v>
+        <v>6553691</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7553,7 +7553,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7577,22 +7577,22 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL58" t="inlineStr">
         <is>
-          <t>På undersidan av tallved.</t>
+          <t>Klen granlåga</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # På undersidan av tallved.</t>
+          <t>Picea abies # Klen granlåga</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7610,10 +7610,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121124065</v>
+        <v>121124079</v>
       </c>
       <c r="B59" t="n">
-        <v>5168</v>
+        <v>5189</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7622,25 +7622,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102204</v>
+        <v>105930</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7655,10 +7655,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>693560</v>
+        <v>693431</v>
       </c>
       <c r="R59" t="n">
-        <v>6553691</v>
+        <v>6553573</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7700,7 +7700,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7724,12 +7724,12 @@
       </c>
       <c r="AL59" t="inlineStr">
         <is>
-          <t>Klen granlåga</t>
+          <t>Klen låga.</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Picea abies # Klen granlåga</t>
+          <t>Picea abies # Klen låga.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -10574,10 +10574,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121231765</v>
+        <v>121231792</v>
       </c>
       <c r="B83" t="n">
-        <v>100347</v>
+        <v>94604</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10590,21 +10590,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10614,10 +10614,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>693309</v>
+        <v>693674</v>
       </c>
       <c r="R83" t="n">
-        <v>6553789</v>
+        <v>6553894</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10659,7 +10659,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10670,6 +10670,26 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL83" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten granlåga</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Picea abies # Kraftigt nedbruten granlåga</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10679,17 +10699,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121231792</v>
+        <v>121231765</v>
       </c>
       <c r="B84" t="n">
-        <v>94604</v>
+        <v>100347</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10702,21 +10722,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10726,10 +10746,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>693674</v>
+        <v>693309</v>
       </c>
       <c r="R84" t="n">
-        <v>6553894</v>
+        <v>6553789</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10761,7 +10781,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10771,7 +10791,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10782,26 +10802,6 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL84" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten granlåga</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Picea abies # Kraftigt nedbruten granlåga</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10811,7 +10811,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -6622,7 +6622,7 @@
         <v>120944657</v>
       </c>
       <c r="B51" t="n">
-        <v>94604</v>
+        <v>94616</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6731,10 +6731,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121124060</v>
+        <v>121124056</v>
       </c>
       <c r="B52" t="n">
-        <v>57367</v>
+        <v>94866</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6743,25 +6743,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>693507</v>
+        <v>693482</v>
       </c>
       <c r="R52" t="n">
-        <v>6553745</v>
+        <v>6553750</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6843,10 +6843,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121124070</v>
+        <v>121124066</v>
       </c>
       <c r="B53" t="n">
-        <v>94700</v>
+        <v>4766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6859,34 +6859,43 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>210</v>
+        <v>100299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>693461</v>
+        <v>693536</v>
       </c>
       <c r="R53" t="n">
-        <v>6553671</v>
+        <v>6553680</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6918,7 +6927,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6928,7 +6937,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6937,6 +6946,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6952,12 +6962,12 @@
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
+          <t>Stående död gran.</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
+          <t>Picea abies # Stående död gran.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6975,10 +6985,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121124077</v>
+        <v>121124060</v>
       </c>
       <c r="B54" t="n">
-        <v>5168</v>
+        <v>57367</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6991,43 +7001,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>102204</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>693453</v>
+        <v>693507</v>
       </c>
       <c r="R54" t="n">
-        <v>6553587</v>
+        <v>6553745</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7059,7 +7060,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7069,7 +7070,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7078,29 +7079,8 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL54" t="inlineStr">
-        <is>
-          <t>Klen granlåga</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen granlåga</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7117,10 +7097,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121124055</v>
+        <v>121124082</v>
       </c>
       <c r="B55" t="n">
-        <v>92008</v>
+        <v>89760</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7133,21 +7113,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5966</v>
+        <v>1962</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7157,10 +7137,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>693466</v>
+        <v>693411</v>
       </c>
       <c r="R55" t="n">
-        <v>6553741</v>
+        <v>6553549</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7192,7 +7172,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7202,7 +7182,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7213,6 +7193,26 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>På undersidan av tallved.</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # På undersidan av tallved.</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7229,10 +7229,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121124056</v>
+        <v>121124070</v>
       </c>
       <c r="B56" t="n">
-        <v>94854</v>
+        <v>94712</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7245,21 +7245,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2180</v>
+        <v>210</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7269,10 +7269,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>693482</v>
+        <v>693461</v>
       </c>
       <c r="R56" t="n">
-        <v>6553750</v>
+        <v>6553671</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7325,6 +7325,26 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Picea abies # Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7341,10 +7361,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121124082</v>
+        <v>121124047</v>
       </c>
       <c r="B57" t="n">
-        <v>89753</v>
+        <v>110231</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7353,25 +7373,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1962</v>
+        <v>219711</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7381,10 +7401,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>693411</v>
+        <v>693691</v>
       </c>
       <c r="R57" t="n">
-        <v>6553549</v>
+        <v>6553924</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7416,7 +7436,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7426,7 +7446,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7437,26 +7457,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL57" t="inlineStr">
-        <is>
-          <t>På undersidan av tallved.</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # På undersidan av tallved.</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7473,10 +7473,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121124065</v>
+        <v>121124058</v>
       </c>
       <c r="B58" t="n">
-        <v>5168</v>
+        <v>94866</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7485,43 +7485,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>102204</v>
+        <v>2180</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>693560</v>
+        <v>693480</v>
       </c>
       <c r="R58" t="n">
-        <v>6553691</v>
+        <v>6553749</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7553,7 +7548,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7563,7 +7558,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7574,26 +7569,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL58" t="inlineStr">
-        <is>
-          <t>Klen granlåga</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen granlåga</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7610,10 +7585,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121124079</v>
+        <v>121124074</v>
       </c>
       <c r="B59" t="n">
-        <v>5189</v>
+        <v>5168</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7622,25 +7597,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>105930</v>
+        <v>102204</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7655,10 +7630,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>693431</v>
+        <v>693455</v>
       </c>
       <c r="R59" t="n">
-        <v>6553573</v>
+        <v>6553651</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7690,7 +7665,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7700,7 +7675,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7724,12 +7699,12 @@
       </c>
       <c r="AL59" t="inlineStr">
         <is>
-          <t>Klen låga.</t>
+          <t>Gren långt ner på gammal tall.</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Picea abies # Klen låga.</t>
+          <t>Picea abies # Gren långt ner på gammal tall.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7747,10 +7722,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121124045</v>
+        <v>121124080</v>
       </c>
       <c r="B60" t="n">
-        <v>110218</v>
+        <v>5169</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7763,34 +7738,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219711</v>
+        <v>100526</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>693689</v>
+        <v>693426</v>
       </c>
       <c r="R60" t="n">
-        <v>6553935</v>
+        <v>6553560</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7822,7 +7802,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7832,12 +7812,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Mycket rikligt.</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7848,6 +7823,26 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>Klen låga.</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen låga.</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7864,10 +7859,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121124053</v>
+        <v>121124081</v>
       </c>
       <c r="B61" t="n">
-        <v>91380</v>
+        <v>5168</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7876,38 +7871,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3298</v>
+        <v>102204</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>693628</v>
+        <v>693426</v>
       </c>
       <c r="R61" t="n">
-        <v>6553797</v>
+        <v>6553560</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>Stående död gran.</t>
+          <t>Klen låga.</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död gran.</t>
+          <t>Picea abies # Klen låga.</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7996,10 +7996,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121124067</v>
+        <v>121124048</v>
       </c>
       <c r="B62" t="n">
-        <v>94604</v>
+        <v>110231</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8012,21 +8012,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2818</v>
+        <v>219711</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8036,10 +8036,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>693537</v>
+        <v>693677</v>
       </c>
       <c r="R62" t="n">
-        <v>6553673</v>
+        <v>6553911</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8108,10 +8108,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121124061</v>
+        <v>121124077</v>
       </c>
       <c r="B63" t="n">
-        <v>94854</v>
+        <v>5168</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8120,38 +8120,47 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2180</v>
+        <v>102204</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>693526</v>
+        <v>693453</v>
       </c>
       <c r="R63" t="n">
-        <v>6553740</v>
+        <v>6553587</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8183,7 +8192,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8193,7 +8202,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8202,8 +8211,29 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL63" t="inlineStr">
+        <is>
+          <t>Klen granlåga</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen granlåga</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -8220,10 +8250,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121124081</v>
+        <v>121124055</v>
       </c>
       <c r="B64" t="n">
-        <v>5168</v>
+        <v>92020</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8236,39 +8266,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102204</v>
+        <v>5966</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>693426</v>
+        <v>693466</v>
       </c>
       <c r="R64" t="n">
-        <v>6553560</v>
+        <v>6553741</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8300,7 +8325,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8310,7 +8335,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8321,26 +8346,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL64" t="inlineStr">
-        <is>
-          <t>Klen låga.</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen låga.</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8357,10 +8362,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121124058</v>
+        <v>121124045</v>
       </c>
       <c r="B65" t="n">
-        <v>94854</v>
+        <v>110231</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8373,21 +8378,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2180</v>
+        <v>219711</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8397,10 +8402,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>693480</v>
+        <v>693689</v>
       </c>
       <c r="R65" t="n">
-        <v>6553749</v>
+        <v>6553935</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8432,7 +8437,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8442,7 +8447,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Mycket rikligt.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8469,10 +8479,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121124059</v>
+        <v>121124053</v>
       </c>
       <c r="B66" t="n">
-        <v>89753</v>
+        <v>91392</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8481,25 +8491,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1962</v>
+        <v>3298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8509,10 +8519,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>693491</v>
+        <v>693628</v>
       </c>
       <c r="R66" t="n">
-        <v>6553751</v>
+        <v>6553797</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8544,7 +8554,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8554,7 +8564,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8568,17 +8578,22 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL66" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies # Stående död gran.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8596,10 +8611,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121124080</v>
+        <v>121124073</v>
       </c>
       <c r="B67" t="n">
-        <v>5169</v>
+        <v>90674</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8612,39 +8627,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>693426</v>
+        <v>693439</v>
       </c>
       <c r="R67" t="n">
-        <v>6553560</v>
+        <v>6553651</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8676,7 +8686,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8686,7 +8696,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8697,26 +8707,6 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL67" t="inlineStr">
-        <is>
-          <t>Klen låga.</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen låga.</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8733,10 +8723,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121124066</v>
+        <v>121124071</v>
       </c>
       <c r="B68" t="n">
-        <v>4766</v>
+        <v>94616</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8749,43 +8739,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100299</v>
+        <v>2818</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>693536</v>
+        <v>693461</v>
       </c>
       <c r="R68" t="n">
-        <v>6553680</v>
+        <v>6553671</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8817,7 +8798,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8827,7 +8808,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8836,7 +8817,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8852,12 +8832,12 @@
       </c>
       <c r="AL68" t="inlineStr">
         <is>
-          <t>Stående död gran.</t>
+          <t>Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död gran.</t>
+          <t>Picea abies # Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8875,10 +8855,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121124074</v>
+        <v>121124067</v>
       </c>
       <c r="B69" t="n">
-        <v>5168</v>
+        <v>94616</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8887,43 +8867,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102204</v>
+        <v>2818</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>693455</v>
+        <v>693537</v>
       </c>
       <c r="R69" t="n">
-        <v>6553651</v>
+        <v>6553673</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8955,7 +8930,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8965,7 +8940,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8976,26 +8951,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL69" t="inlineStr">
-        <is>
-          <t>Gren långt ner på gammal tall.</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Picea abies # Gren långt ner på gammal tall.</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -9012,10 +8967,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121124071</v>
+        <v>121124061</v>
       </c>
       <c r="B70" t="n">
-        <v>94604</v>
+        <v>94866</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9028,21 +8983,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2818</v>
+        <v>2180</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9052,10 +9007,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>693461</v>
+        <v>693526</v>
       </c>
       <c r="R70" t="n">
-        <v>6553671</v>
+        <v>6553740</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9087,7 +9042,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9097,7 +9052,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9108,26 +9063,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL70" t="inlineStr">
-        <is>
-          <t>Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Picea abies # Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -9144,10 +9079,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121124073</v>
+        <v>121124065</v>
       </c>
       <c r="B71" t="n">
-        <v>90662</v>
+        <v>5168</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9156,38 +9091,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5447</v>
+        <v>102204</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>693439</v>
+        <v>693560</v>
       </c>
       <c r="R71" t="n">
-        <v>6553651</v>
+        <v>6553691</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9219,7 +9159,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9229,7 +9169,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9240,6 +9180,26 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL71" t="inlineStr">
+        <is>
+          <t>Klen granlåga</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen granlåga</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9256,10 +9216,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121124047</v>
+        <v>121124079</v>
       </c>
       <c r="B72" t="n">
-        <v>110218</v>
+        <v>5189</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9272,34 +9232,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219711</v>
+        <v>105930</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>693691</v>
+        <v>693431</v>
       </c>
       <c r="R72" t="n">
-        <v>6553924</v>
+        <v>6553573</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9331,7 +9296,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9341,7 +9306,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9352,6 +9317,26 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL72" t="inlineStr">
+        <is>
+          <t>Klen låga.</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen låga.</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -9368,10 +9353,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121124048</v>
+        <v>121124059</v>
       </c>
       <c r="B73" t="n">
-        <v>110218</v>
+        <v>89760</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9380,25 +9365,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219711</v>
+        <v>1962</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9408,10 +9393,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>693677</v>
+        <v>693491</v>
       </c>
       <c r="R73" t="n">
-        <v>6553911</v>
+        <v>6553751</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9443,7 +9428,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9453,7 +9438,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9464,6 +9449,21 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9483,7 +9483,7 @@
         <v>121124051</v>
       </c>
       <c r="B74" t="n">
-        <v>94604</v>
+        <v>94616</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>121124052</v>
       </c>
       <c r="B75" t="n">
-        <v>94700</v>
+        <v>94712</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9744,10 +9744,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121224119</v>
+        <v>121224447</v>
       </c>
       <c r="B76" t="n">
-        <v>97035</v>
+        <v>100360</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9760,21 +9760,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>693407</v>
+        <v>693195</v>
       </c>
       <c r="R76" t="n">
-        <v>6553843</v>
+        <v>6553768</v>
       </c>
       <c r="S76" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9860,10 +9860,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121224447</v>
+        <v>121222341</v>
       </c>
       <c r="B77" t="n">
-        <v>100347</v>
+        <v>8421</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9876,41 +9876,46 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sandkärr, Srm</t>
+          <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>693195</v>
+        <v>693587</v>
       </c>
       <c r="R77" t="n">
-        <v>6553768</v>
+        <v>6553902</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9939,7 +9944,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9949,7 +9954,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9976,10 +9981,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121222341</v>
+        <v>121224002</v>
       </c>
       <c r="B78" t="n">
-        <v>8421</v>
+        <v>5189</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9992,46 +9997,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Breviksnäs, Srm</t>
+          <t>Sandkärr, Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>693587</v>
+        <v>693430</v>
       </c>
       <c r="R78" t="n">
-        <v>6553902</v>
+        <v>6553864</v>
       </c>
       <c r="S78" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10060,7 +10056,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10070,7 +10066,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10085,22 +10081,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121224726</v>
+        <v>121221017</v>
       </c>
       <c r="B79" t="n">
-        <v>97035</v>
+        <v>57367</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10109,45 +10105,46 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Sandkärr, Srm</t>
+          <t>Kolnäsviken, Kolnäsviken, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>693312</v>
+        <v>693644</v>
       </c>
       <c r="R79" t="n">
-        <v>6553808</v>
+        <v>6554031</v>
       </c>
       <c r="S79" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10176,7 +10173,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10186,7 +10183,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10201,22 +10198,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121224002</v>
+        <v>121224119</v>
       </c>
       <c r="B80" t="n">
-        <v>5189</v>
+        <v>97048</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10229,37 +10226,41 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>105930</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Sandkärr, Sandkärr, Srm</t>
+          <t>Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>693430</v>
+        <v>693407</v>
       </c>
       <c r="R80" t="n">
-        <v>6553864</v>
+        <v>6553843</v>
       </c>
       <c r="S80" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10288,7 +10289,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10298,7 +10299,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10313,22 +10314,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121221017</v>
+        <v>121224726</v>
       </c>
       <c r="B81" t="n">
-        <v>57367</v>
+        <v>97048</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10337,46 +10338,45 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kolnäsviken, Kolnäsviken, Srm</t>
+          <t>Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>693644</v>
+        <v>693312</v>
       </c>
       <c r="R81" t="n">
-        <v>6554031</v>
+        <v>6553808</v>
       </c>
       <c r="S81" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10430,22 +10430,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121231771</v>
+        <v>121231794</v>
       </c>
       <c r="B82" t="n">
-        <v>4772</v>
+        <v>94616</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10458,21 +10458,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>102306</v>
+        <v>2818</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10482,10 +10482,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>693494</v>
+        <v>693674</v>
       </c>
       <c r="R82" t="n">
-        <v>6553917</v>
+        <v>6553897</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10517,7 +10517,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10527,7 +10527,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="AL82" t="inlineStr">
         <is>
-          <t>Äldre grov gran</t>
+          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grov gran</t>
+          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10567,17 +10567,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121231792</v>
+        <v>121231789</v>
       </c>
       <c r="B83" t="n">
-        <v>94604</v>
+        <v>91114</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10590,21 +10590,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2818</v>
+        <v>5420</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10614,10 +10614,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>693674</v>
+        <v>693670</v>
       </c>
       <c r="R83" t="n">
-        <v>6553894</v>
+        <v>6553974</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10659,7 +10659,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10673,22 +10673,22 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL83" t="inlineStr">
         <is>
-          <t>Kraftigt nedbruten granlåga</t>
+          <t>Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftigt nedbruten granlåga</t>
+          <t>Pinus sylvestris # Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10699,17 +10699,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121231765</v>
+        <v>121231792</v>
       </c>
       <c r="B84" t="n">
-        <v>100347</v>
+        <v>94616</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10722,21 +10722,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10746,10 +10746,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>693309</v>
+        <v>693674</v>
       </c>
       <c r="R84" t="n">
-        <v>6553789</v>
+        <v>6553894</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10802,6 +10802,26 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL84" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten granlåga</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Picea abies # Kraftigt nedbruten granlåga</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10811,17 +10831,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121231789</v>
+        <v>121231781</v>
       </c>
       <c r="B85" t="n">
-        <v>91102</v>
+        <v>5189</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10834,34 +10854,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5420</v>
+        <v>105930</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>693670</v>
+        <v>693639</v>
       </c>
       <c r="R85" t="n">
-        <v>6553974</v>
+        <v>6553969</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10893,7 +10918,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10903,7 +10928,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10917,22 +10942,17 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL85" t="inlineStr">
-        <is>
-          <t>Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11082,10 +11102,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121231794</v>
+        <v>121231785</v>
       </c>
       <c r="B87" t="n">
-        <v>94604</v>
+        <v>90729</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11094,25 +11114,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2818</v>
+        <v>5442</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -11122,10 +11142,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>693674</v>
+        <v>693675</v>
       </c>
       <c r="R87" t="n">
-        <v>6553897</v>
+        <v>6553972</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11157,7 +11177,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11167,7 +11187,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11181,22 +11201,22 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+          <t>Äldre tall</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+          <t>Pinus sylvestris # Äldre tall</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11207,17 +11227,17 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121231773</v>
+        <v>121231767</v>
       </c>
       <c r="B88" t="n">
-        <v>98081</v>
+        <v>94712</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11226,25 +11246,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -11254,7 +11274,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -11263,10 +11283,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>693495</v>
+        <v>693436</v>
       </c>
       <c r="R88" t="n">
-        <v>6553900</v>
+        <v>6553861</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11298,7 +11318,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11308,7 +11328,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11320,9 +11340,24 @@
       <c r="AG88" t="b">
         <v>0</v>
       </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>Sluttning med tallskog</t>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL88" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten grov granlåga</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Picea abies # Kraftigt nedbruten grov granlåga</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11340,10 +11375,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121231785</v>
+        <v>121231782</v>
       </c>
       <c r="B89" t="n">
-        <v>90717</v>
+        <v>57367</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11356,34 +11391,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>693675</v>
+        <v>693709</v>
       </c>
       <c r="R89" t="n">
-        <v>6553972</v>
+        <v>6553983</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11415,7 +11455,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11425,7 +11465,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Födosökshack vid basen av stående död tall.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11436,26 +11481,6 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL89" t="inlineStr">
-        <is>
-          <t>Äldre tall</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Äldre tall</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -11472,10 +11497,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121231764</v>
+        <v>121231774</v>
       </c>
       <c r="B90" t="n">
-        <v>5189</v>
+        <v>105160</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11484,38 +11509,47 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>105930</v>
+        <v>340</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>693261</v>
+        <v>693495</v>
       </c>
       <c r="R90" t="n">
-        <v>6553742</v>
+        <v>6553900</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11547,7 +11581,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11557,7 +11591,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Två av skotten hade frökapslar.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11569,24 +11608,9 @@
       <c r="AG90" t="b">
         <v>0</v>
       </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL90" t="inlineStr">
-        <is>
-          <t>Klen gran i område med många fallna granar</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen gran i område med många fallna granar</t>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>Sluttning med tallskog</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11604,10 +11628,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121231767</v>
+        <v>121231771</v>
       </c>
       <c r="B91" t="n">
-        <v>94700</v>
+        <v>4772</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11620,43 +11644,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>210</v>
+        <v>102306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>693436</v>
+        <v>693494</v>
       </c>
       <c r="R91" t="n">
-        <v>6553861</v>
+        <v>6553917</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11688,7 +11703,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11698,7 +11713,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11722,12 +11737,12 @@
       </c>
       <c r="AL91" t="inlineStr">
         <is>
-          <t>Kraftigt nedbruten grov granlåga</t>
+          <t>Äldre grov gran</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftigt nedbruten grov granlåga</t>
+          <t>Picea abies # Äldre grov gran</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11745,10 +11760,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121231795</v>
+        <v>121231762</v>
       </c>
       <c r="B92" t="n">
-        <v>94700</v>
+        <v>110231</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11761,43 +11776,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>210</v>
+        <v>219711</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>693674</v>
+        <v>693313</v>
       </c>
       <c r="R92" t="n">
-        <v>6553897</v>
+        <v>6553812</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11829,7 +11835,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11839,7 +11845,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11850,26 +11856,6 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL92" t="inlineStr">
-        <is>
-          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -11879,17 +11865,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121231762</v>
+        <v>121231764</v>
       </c>
       <c r="B93" t="n">
-        <v>110218</v>
+        <v>5189</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11902,21 +11888,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219711</v>
+        <v>105930</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11926,10 +11912,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>693313</v>
+        <v>693261</v>
       </c>
       <c r="R93" t="n">
-        <v>6553812</v>
+        <v>6553742</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11961,7 +11947,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11971,7 +11957,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11982,6 +11968,26 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL93" t="inlineStr">
+        <is>
+          <t>Klen gran i område med många fallna granar</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen gran i område med många fallna granar</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11998,10 +12004,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121231774</v>
+        <v>121231793</v>
       </c>
       <c r="B94" t="n">
-        <v>105147</v>
+        <v>94712</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12010,35 +12016,35 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>340</v>
+        <v>210</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -12047,10 +12053,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>693495</v>
+        <v>693674</v>
       </c>
       <c r="R94" t="n">
-        <v>6553900</v>
+        <v>6553894</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12082,7 +12088,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12092,12 +12098,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Två av skotten hade frökapslar.</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12109,9 +12110,24 @@
       <c r="AG94" t="b">
         <v>0</v>
       </c>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>Sluttning med tallskog</t>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL94" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten granlåga</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Picea abies # Kraftigt nedbruten granlåga</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12122,17 +12138,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121231782</v>
+        <v>121231795</v>
       </c>
       <c r="B95" t="n">
-        <v>57367</v>
+        <v>94712</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12141,31 +12157,35 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -12174,10 +12194,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>693709</v>
+        <v>693674</v>
       </c>
       <c r="R95" t="n">
-        <v>6553983</v>
+        <v>6553897</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12209,7 +12229,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12219,12 +12239,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Födosökshack vid basen av stående död tall.</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12235,6 +12250,26 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL95" t="inlineStr">
+        <is>
+          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -12244,17 +12279,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121231781</v>
+        <v>121231765</v>
       </c>
       <c r="B96" t="n">
-        <v>5189</v>
+        <v>100360</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12267,39 +12302,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>693639</v>
+        <v>693309</v>
       </c>
       <c r="R96" t="n">
-        <v>6553969</v>
+        <v>6553789</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12331,7 +12361,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12341,7 +12371,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12352,21 +12382,6 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -12383,10 +12398,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121231793</v>
+        <v>121231773</v>
       </c>
       <c r="B97" t="n">
-        <v>94700</v>
+        <v>98094</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12395,35 +12410,35 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -12432,10 +12447,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>693674</v>
+        <v>693495</v>
       </c>
       <c r="R97" t="n">
-        <v>6553894</v>
+        <v>6553900</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12467,7 +12482,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12477,7 +12492,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12489,24 +12504,9 @@
       <c r="AG97" t="b">
         <v>0</v>
       </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL97" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten granlåga</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Picea abies # Kraftigt nedbruten granlåga</t>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>Sluttning med tallskog</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -12517,7 +12517,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -12527,7 +12527,7 @@
         <v>121231766</v>
       </c>
       <c r="B98" t="n">
-        <v>94604</v>
+        <v>94616</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12656,10 +12656,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121231788</v>
+        <v>121231776</v>
       </c>
       <c r="B99" t="n">
-        <v>94583</v>
+        <v>94616</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12672,21 +12672,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2667</v>
+        <v>2818</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -12696,10 +12696,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>693670</v>
+        <v>693581</v>
       </c>
       <c r="R99" t="n">
-        <v>6553974</v>
+        <v>6553897</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12731,7 +12731,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12741,7 +12741,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12752,11 +12752,6 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Vid basen av lodvägg</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -12773,10 +12768,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121231768</v>
+        <v>121231786</v>
       </c>
       <c r="B100" t="n">
-        <v>94700</v>
+        <v>94102</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12789,43 +12784,38 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>210</v>
+        <v>2362</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>693478</v>
+        <v>693670</v>
       </c>
       <c r="R100" t="n">
-        <v>6553857</v>
+        <v>6553974</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12857,7 +12847,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12867,7 +12857,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12876,27 +12866,13 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL100" t="inlineStr">
-        <is>
-          <t>Granlåga i blockig sluttning</t>
-        </is>
-      </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga i blockig sluttning</t>
+          <t>Vid basen av lodvägg</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -12914,10 +12890,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121231786</v>
+        <v>121231787</v>
       </c>
       <c r="B101" t="n">
-        <v>94090</v>
+        <v>94389</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12930,28 +12906,24 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2362</v>
+        <v>2779</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blek stjärnmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Mnium stellare</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
@@ -13012,7 +12984,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -13036,10 +13007,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121231776</v>
+        <v>121231788</v>
       </c>
       <c r="B102" t="n">
-        <v>94604</v>
+        <v>94595</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13052,21 +13023,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2818</v>
+        <v>2667</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -13076,10 +13047,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>693581</v>
+        <v>693670</v>
       </c>
       <c r="R102" t="n">
-        <v>6553897</v>
+        <v>6553974</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13111,7 +13082,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13121,7 +13092,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13132,6 +13103,11 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Vid basen av lodvägg</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -13148,10 +13124,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121231787</v>
+        <v>121231768</v>
       </c>
       <c r="B103" t="n">
-        <v>94377</v>
+        <v>94712</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13164,34 +13140,43 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2779</v>
+        <v>210</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>693670</v>
+        <v>693478</v>
       </c>
       <c r="R103" t="n">
-        <v>6553974</v>
+        <v>6553857</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13223,7 +13208,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13233,7 +13218,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13245,9 +13230,24 @@
       <c r="AG103" t="b">
         <v>0</v>
       </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL103" t="inlineStr">
+        <is>
+          <t>Granlåga i blockig sluttning</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>Vid basen av lodvägg</t>
+          <t>Picea abies # Granlåga i blockig sluttning</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -13268,7 +13268,7 @@
         <v>121330721</v>
       </c>
       <c r="B104" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>121231778</v>
       </c>
       <c r="B105" t="n">
-        <v>95667</v>
+        <v>95680</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
         <v>121231770</v>
       </c>
       <c r="B106" t="n">
-        <v>95944</v>
+        <v>95957</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -6622,7 +6622,7 @@
         <v>120944657</v>
       </c>
       <c r="B51" t="n">
-        <v>94616</v>
+        <v>94617</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6731,10 +6731,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121124056</v>
+        <v>121124059</v>
       </c>
       <c r="B52" t="n">
-        <v>94866</v>
+        <v>89761</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6743,25 +6743,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2180</v>
+        <v>1962</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>693482</v>
+        <v>693491</v>
       </c>
       <c r="R52" t="n">
-        <v>6553750</v>
+        <v>6553751</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6827,6 +6827,21 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6843,10 +6858,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121124066</v>
+        <v>121124079</v>
       </c>
       <c r="B53" t="n">
-        <v>4766</v>
+        <v>5189</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6859,43 +6874,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>693536</v>
+        <v>693431</v>
       </c>
       <c r="R53" t="n">
-        <v>6553680</v>
+        <v>6553573</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6927,7 +6938,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6937,7 +6948,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6946,7 +6957,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6962,12 +6972,12 @@
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>Stående död gran.</t>
+          <t>Klen låga.</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död gran.</t>
+          <t>Picea abies # Klen låga.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6985,10 +6995,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121124060</v>
+        <v>121124071</v>
       </c>
       <c r="B54" t="n">
-        <v>57367</v>
+        <v>94617</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6997,25 +7007,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7025,10 +7035,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>693507</v>
+        <v>693461</v>
       </c>
       <c r="R54" t="n">
-        <v>6553745</v>
+        <v>6553671</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7060,7 +7070,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7070,7 +7080,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7081,6 +7091,26 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies # Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7097,10 +7127,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121124082</v>
+        <v>121124055</v>
       </c>
       <c r="B55" t="n">
-        <v>89760</v>
+        <v>92021</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7113,21 +7143,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1962</v>
+        <v>5966</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7137,10 +7167,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>693411</v>
+        <v>693466</v>
       </c>
       <c r="R55" t="n">
-        <v>6553549</v>
+        <v>6553741</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7172,7 +7202,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7182,7 +7212,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7193,26 +7223,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL55" t="inlineStr">
-        <is>
-          <t>På undersidan av tallved.</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # På undersidan av tallved.</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7229,10 +7239,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121124070</v>
+        <v>121124060</v>
       </c>
       <c r="B56" t="n">
-        <v>94712</v>
+        <v>57367</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7241,25 +7251,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7269,10 +7279,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>693461</v>
+        <v>693507</v>
       </c>
       <c r="R56" t="n">
-        <v>6553671</v>
+        <v>6553745</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7304,7 +7314,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7314,7 +7324,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7325,26 +7335,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL56" t="inlineStr">
-        <is>
-          <t>Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Picea abies # Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7361,10 +7351,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121124047</v>
+        <v>121124065</v>
       </c>
       <c r="B57" t="n">
-        <v>110231</v>
+        <v>5168</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7373,38 +7363,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219711</v>
+        <v>102204</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>693691</v>
+        <v>693560</v>
       </c>
       <c r="R57" t="n">
-        <v>6553924</v>
+        <v>6553691</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7436,7 +7431,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7446,7 +7441,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7457,6 +7452,26 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>Klen granlåga</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen granlåga</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7473,10 +7488,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121124058</v>
+        <v>121124053</v>
       </c>
       <c r="B58" t="n">
-        <v>94866</v>
+        <v>91393</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7489,21 +7504,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2180</v>
+        <v>3298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7513,10 +7528,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>693480</v>
+        <v>693628</v>
       </c>
       <c r="R58" t="n">
-        <v>6553749</v>
+        <v>6553797</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7548,7 +7563,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7558,7 +7573,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7569,6 +7584,26 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död gran.</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7585,10 +7620,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121124074</v>
+        <v>121124073</v>
       </c>
       <c r="B59" t="n">
-        <v>5168</v>
+        <v>90675</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7597,40 +7632,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102204</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>693455</v>
+        <v>693439</v>
       </c>
       <c r="R59" t="n">
         <v>6553651</v>
@@ -7665,7 +7695,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7675,7 +7705,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7686,26 +7716,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL59" t="inlineStr">
-        <is>
-          <t>Gren långt ner på gammal tall.</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies # Gren långt ner på gammal tall.</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7722,10 +7732,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121124080</v>
+        <v>121124077</v>
       </c>
       <c r="B60" t="n">
-        <v>5169</v>
+        <v>5168</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7734,43 +7744,47 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100526</v>
+        <v>102204</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>693426</v>
+        <v>693453</v>
       </c>
       <c r="R60" t="n">
-        <v>6553560</v>
+        <v>6553587</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7802,7 +7816,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7812,7 +7826,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7821,6 +7835,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7836,12 +7851,12 @@
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>Klen låga.</t>
+          <t>Klen granlåga</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Picea abies # Klen låga.</t>
+          <t>Picea abies # Klen granlåga</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7859,10 +7874,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121124081</v>
+        <v>121124070</v>
       </c>
       <c r="B61" t="n">
-        <v>5168</v>
+        <v>94713</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7871,43 +7886,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>102204</v>
+        <v>210</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>693426</v>
+        <v>693461</v>
       </c>
       <c r="R61" t="n">
-        <v>6553560</v>
+        <v>6553671</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7939,7 +7949,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7949,7 +7959,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7973,12 +7983,12 @@
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>Klen låga.</t>
+          <t>Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Picea abies # Klen låga.</t>
+          <t>Picea abies # Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7996,10 +8006,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121124048</v>
+        <v>121124066</v>
       </c>
       <c r="B62" t="n">
-        <v>110231</v>
+        <v>4766</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8012,34 +8022,43 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219711</v>
+        <v>100299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>693677</v>
+        <v>693536</v>
       </c>
       <c r="R62" t="n">
-        <v>6553911</v>
+        <v>6553680</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8071,7 +8090,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8081,7 +8100,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8090,8 +8109,29 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL62" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död gran.</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -8108,10 +8148,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121124077</v>
+        <v>121124080</v>
       </c>
       <c r="B63" t="n">
-        <v>5168</v>
+        <v>5169</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8120,47 +8160,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>102204</v>
+        <v>100526</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>693453</v>
+        <v>693426</v>
       </c>
       <c r="R63" t="n">
-        <v>6553587</v>
+        <v>6553560</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8192,7 +8228,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8202,7 +8238,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8211,7 +8247,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8227,12 +8262,12 @@
       </c>
       <c r="AL63" t="inlineStr">
         <is>
-          <t>Klen granlåga</t>
+          <t>Klen låga.</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Picea abies # Klen granlåga</t>
+          <t>Picea abies # Klen låga.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8250,10 +8285,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121124055</v>
+        <v>121124081</v>
       </c>
       <c r="B64" t="n">
-        <v>92020</v>
+        <v>5168</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8266,34 +8301,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5966</v>
+        <v>102204</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>693466</v>
+        <v>693426</v>
       </c>
       <c r="R64" t="n">
-        <v>6553741</v>
+        <v>6553560</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8325,7 +8365,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8335,7 +8375,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8346,6 +8386,26 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL64" t="inlineStr">
+        <is>
+          <t>Klen låga.</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen låga.</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8365,7 +8425,7 @@
         <v>121124045</v>
       </c>
       <c r="B65" t="n">
-        <v>110231</v>
+        <v>110232</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8479,10 +8539,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121124053</v>
+        <v>121124067</v>
       </c>
       <c r="B66" t="n">
-        <v>91392</v>
+        <v>94617</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8495,21 +8555,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3298</v>
+        <v>2818</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8519,10 +8579,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>693628</v>
+        <v>693537</v>
       </c>
       <c r="R66" t="n">
-        <v>6553797</v>
+        <v>6553673</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8554,7 +8614,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8564,7 +8624,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8575,26 +8635,6 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL66" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8611,10 +8651,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121124073</v>
+        <v>121124061</v>
       </c>
       <c r="B67" t="n">
-        <v>90674</v>
+        <v>94867</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8627,21 +8667,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>2180</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8651,10 +8691,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>693439</v>
+        <v>693526</v>
       </c>
       <c r="R67" t="n">
-        <v>6553651</v>
+        <v>6553740</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8686,7 +8726,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8696,7 +8736,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8723,10 +8763,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121124071</v>
+        <v>121124082</v>
       </c>
       <c r="B68" t="n">
-        <v>94616</v>
+        <v>89761</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8735,25 +8775,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2818</v>
+        <v>1962</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8763,10 +8803,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>693461</v>
+        <v>693411</v>
       </c>
       <c r="R68" t="n">
-        <v>6553671</v>
+        <v>6553549</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8798,7 +8838,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8808,7 +8848,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8822,22 +8862,22 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL68" t="inlineStr">
         <is>
-          <t>Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
+          <t>På undersidan av tallved.</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
+          <t>Pinus sylvestris # På undersidan av tallved.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8855,10 +8895,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121124067</v>
+        <v>121124056</v>
       </c>
       <c r="B69" t="n">
-        <v>94616</v>
+        <v>94867</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8871,21 +8911,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2818</v>
+        <v>2180</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8895,10 +8935,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>693537</v>
+        <v>693482</v>
       </c>
       <c r="R69" t="n">
-        <v>6553673</v>
+        <v>6553750</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8930,7 +8970,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8940,7 +8980,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8967,10 +9007,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121124061</v>
+        <v>121124074</v>
       </c>
       <c r="B70" t="n">
-        <v>94866</v>
+        <v>5168</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8979,38 +9019,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2180</v>
+        <v>102204</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>693526</v>
+        <v>693455</v>
       </c>
       <c r="R70" t="n">
-        <v>6553740</v>
+        <v>6553651</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9042,7 +9087,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9052,7 +9097,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9063,6 +9108,26 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL70" t="inlineStr">
+        <is>
+          <t>Gren långt ner på gammal tall.</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Picea abies # Gren långt ner på gammal tall.</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -9079,10 +9144,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121124065</v>
+        <v>121124047</v>
       </c>
       <c r="B71" t="n">
-        <v>5168</v>
+        <v>110232</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9091,43 +9156,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102204</v>
+        <v>219711</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>693560</v>
+        <v>693691</v>
       </c>
       <c r="R71" t="n">
-        <v>6553691</v>
+        <v>6553924</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9159,7 +9219,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9169,7 +9229,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9180,26 +9240,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL71" t="inlineStr">
-        <is>
-          <t>Klen granlåga</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen granlåga</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9216,10 +9256,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121124079</v>
+        <v>121124058</v>
       </c>
       <c r="B72" t="n">
-        <v>5189</v>
+        <v>94867</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9232,39 +9272,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>105930</v>
+        <v>2180</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>693431</v>
+        <v>693480</v>
       </c>
       <c r="R72" t="n">
-        <v>6553573</v>
+        <v>6553749</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9296,7 +9331,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9306,7 +9341,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9317,26 +9352,6 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL72" t="inlineStr">
-        <is>
-          <t>Klen låga.</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen låga.</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -9353,10 +9368,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121124059</v>
+        <v>121124048</v>
       </c>
       <c r="B73" t="n">
-        <v>89760</v>
+        <v>110232</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9365,25 +9380,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1962</v>
+        <v>219711</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9393,10 +9408,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>693491</v>
+        <v>693677</v>
       </c>
       <c r="R73" t="n">
-        <v>6553751</v>
+        <v>6553911</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9428,7 +9443,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9438,7 +9453,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9449,21 +9464,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9483,7 +9483,7 @@
         <v>121124051</v>
       </c>
       <c r="B74" t="n">
-        <v>94616</v>
+        <v>94617</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>121124052</v>
       </c>
       <c r="B75" t="n">
-        <v>94712</v>
+        <v>94713</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9744,10 +9744,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121224447</v>
+        <v>121221017</v>
       </c>
       <c r="B76" t="n">
-        <v>100360</v>
+        <v>57367</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9756,45 +9756,46 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Sandkärr, Srm</t>
+          <t>Kolnäsviken, Kolnäsviken, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>693195</v>
+        <v>693644</v>
       </c>
       <c r="R76" t="n">
-        <v>6553768</v>
+        <v>6554031</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9823,7 +9824,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9833,7 +9834,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9848,12 +9849,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9981,10 +9982,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121224002</v>
+        <v>121224726</v>
       </c>
       <c r="B78" t="n">
-        <v>5189</v>
+        <v>97049</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9997,37 +9998,41 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>105930</v>
+        <v>221945</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sandkärr, Sandkärr, Srm</t>
+          <t>Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>693430</v>
+        <v>693312</v>
       </c>
       <c r="R78" t="n">
-        <v>6553864</v>
+        <v>6553808</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10056,7 +10061,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10066,7 +10071,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10081,22 +10086,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121221017</v>
+        <v>121224002</v>
       </c>
       <c r="B79" t="n">
-        <v>57367</v>
+        <v>5189</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10105,20 +10110,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -10127,24 +10132,19 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kolnäsviken, Kolnäsviken, Srm</t>
+          <t>Sandkärr, Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>693644</v>
+        <v>693430</v>
       </c>
       <c r="R79" t="n">
-        <v>6554031</v>
+        <v>6553864</v>
       </c>
       <c r="S79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10183,7 +10183,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10210,10 +10210,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121224119</v>
+        <v>121224447</v>
       </c>
       <c r="B80" t="n">
-        <v>97048</v>
+        <v>100361</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10226,21 +10226,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -10254,13 +10254,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>693407</v>
+        <v>693195</v>
       </c>
       <c r="R80" t="n">
-        <v>6553843</v>
+        <v>6553768</v>
       </c>
       <c r="S80" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10326,10 +10326,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121224726</v>
+        <v>121224119</v>
       </c>
       <c r="B81" t="n">
-        <v>97048</v>
+        <v>97049</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10370,10 +10370,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>693312</v>
+        <v>693407</v>
       </c>
       <c r="R81" t="n">
-        <v>6553808</v>
+        <v>6553843</v>
       </c>
       <c r="S81" t="n">
         <v>13</v>
@@ -10405,7 +10405,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10442,10 +10442,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121231794</v>
+        <v>121231773</v>
       </c>
       <c r="B82" t="n">
-        <v>94616</v>
+        <v>98095</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10454,38 +10454,47 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2818</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>693674</v>
+        <v>693495</v>
       </c>
       <c r="R82" t="n">
-        <v>6553897</v>
+        <v>6553900</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10517,7 +10526,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10527,7 +10536,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10539,24 +10548,9 @@
       <c r="AG82" t="b">
         <v>0</v>
       </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL82" t="inlineStr">
-        <is>
-          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Sluttning med tallskog</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10567,17 +10561,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121231789</v>
+        <v>121231782</v>
       </c>
       <c r="B83" t="n">
-        <v>91114</v>
+        <v>57367</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10586,38 +10580,43 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>693670</v>
+        <v>693709</v>
       </c>
       <c r="R83" t="n">
-        <v>6553974</v>
+        <v>6553983</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10649,7 +10648,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10659,7 +10658,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Födosökshack vid basen av stående död tall.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10670,26 +10674,6 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL83" t="inlineStr">
-        <is>
-          <t>Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10706,10 +10690,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121231792</v>
+        <v>121231785</v>
       </c>
       <c r="B84" t="n">
-        <v>94616</v>
+        <v>90730</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10718,25 +10702,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2818</v>
+        <v>5442</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10746,10 +10730,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>693674</v>
+        <v>693675</v>
       </c>
       <c r="R84" t="n">
-        <v>6553894</v>
+        <v>6553972</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10781,7 +10765,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10791,7 +10775,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10805,22 +10789,22 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL84" t="inlineStr">
         <is>
-          <t>Kraftigt nedbruten granlåga</t>
+          <t>Äldre tall</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftigt nedbruten granlåga</t>
+          <t>Pinus sylvestris # Äldre tall</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10831,17 +10815,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Per Flodby, Emilia Blixt, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121231781</v>
+        <v>121231775</v>
       </c>
       <c r="B85" t="n">
-        <v>5189</v>
+        <v>8432</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10854,27 +10838,27 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -10883,10 +10867,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>693639</v>
+        <v>693555</v>
       </c>
       <c r="R85" t="n">
-        <v>6553969</v>
+        <v>6553905</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10918,7 +10902,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10928,7 +10912,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10942,17 +10926,17 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10970,10 +10954,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121231775</v>
+        <v>121231765</v>
       </c>
       <c r="B86" t="n">
-        <v>8432</v>
+        <v>100361</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10986,39 +10970,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>222498</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>693555</v>
+        <v>693309</v>
       </c>
       <c r="R86" t="n">
-        <v>6553905</v>
+        <v>6553789</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11050,7 +11029,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11060,7 +11039,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11071,21 +11050,6 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -11102,10 +11066,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121231785</v>
+        <v>121231771</v>
       </c>
       <c r="B87" t="n">
-        <v>90729</v>
+        <v>4772</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11114,25 +11078,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -11142,10 +11106,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>693675</v>
+        <v>693494</v>
       </c>
       <c r="R87" t="n">
-        <v>6553972</v>
+        <v>6553917</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11177,7 +11141,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11187,7 +11151,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11201,22 +11165,22 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>Äldre tall</t>
+          <t>Äldre grov gran</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Äldre tall</t>
+          <t>Picea abies # Äldre grov gran</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11234,10 +11198,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121231767</v>
+        <v>121231792</v>
       </c>
       <c r="B88" t="n">
-        <v>94712</v>
+        <v>94617</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11250,43 +11214,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>693436</v>
+        <v>693674</v>
       </c>
       <c r="R88" t="n">
-        <v>6553861</v>
+        <v>6553894</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11318,7 +11273,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11328,7 +11283,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11352,12 +11307,12 @@
       </c>
       <c r="AL88" t="inlineStr">
         <is>
-          <t>Kraftigt nedbruten grov granlåga</t>
+          <t>Kraftigt nedbruten granlåga</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftigt nedbruten grov granlåga</t>
+          <t>Picea abies # Kraftigt nedbruten granlåga</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11368,17 +11323,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Cecilia Gottfries, Per Flodby, Emilia Blixt, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121231782</v>
+        <v>121231793</v>
       </c>
       <c r="B89" t="n">
-        <v>57367</v>
+        <v>94713</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11387,31 +11342,35 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -11420,10 +11379,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>693709</v>
+        <v>693674</v>
       </c>
       <c r="R89" t="n">
-        <v>6553983</v>
+        <v>6553894</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11455,7 +11414,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11465,12 +11424,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Födosökshack vid basen av stående död tall.</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11481,6 +11435,26 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL89" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten granlåga</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Picea abies # Kraftigt nedbruten granlåga</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -11490,17 +11464,17 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Cecilia Gottfries, Per Flodby, Emilia Blixt, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121231774</v>
+        <v>121231781</v>
       </c>
       <c r="B90" t="n">
-        <v>105160</v>
+        <v>5189</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11509,35 +11483,31 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>340</v>
+        <v>105930</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -11546,10 +11516,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>693495</v>
+        <v>693639</v>
       </c>
       <c r="R90" t="n">
-        <v>6553900</v>
+        <v>6553969</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11581,7 +11551,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11591,12 +11561,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Två av skotten hade frökapslar.</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11608,9 +11573,19 @@
       <c r="AG90" t="b">
         <v>0</v>
       </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>Sluttning med tallskog</t>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11628,10 +11603,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121231771</v>
+        <v>121231764</v>
       </c>
       <c r="B91" t="n">
-        <v>4772</v>
+        <v>5189</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11644,21 +11619,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11668,10 +11643,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>693494</v>
+        <v>693261</v>
       </c>
       <c r="R91" t="n">
-        <v>6553917</v>
+        <v>6553742</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11703,7 +11678,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11713,7 +11688,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11737,12 +11712,12 @@
       </c>
       <c r="AL91" t="inlineStr">
         <is>
-          <t>Äldre grov gran</t>
+          <t>Klen gran i område med många fallna granar</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grov gran</t>
+          <t>Picea abies # Klen gran i område med många fallna granar</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11760,10 +11735,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121231762</v>
+        <v>121231774</v>
       </c>
       <c r="B92" t="n">
-        <v>110231</v>
+        <v>105161</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11772,38 +11747,47 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219711</v>
+        <v>340</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>693313</v>
+        <v>693495</v>
       </c>
       <c r="R92" t="n">
-        <v>6553812</v>
+        <v>6553900</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11835,7 +11819,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11845,7 +11829,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Två av skotten hade frökapslar.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11856,6 +11845,11 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>Sluttning med tallskog</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -11872,10 +11866,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121231764</v>
+        <v>121231767</v>
       </c>
       <c r="B93" t="n">
-        <v>5189</v>
+        <v>94713</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11888,34 +11882,43 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>105930</v>
+        <v>210</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>693261</v>
+        <v>693436</v>
       </c>
       <c r="R93" t="n">
-        <v>6553742</v>
+        <v>6553861</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11947,7 +11950,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11957,7 +11960,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11981,12 +11984,12 @@
       </c>
       <c r="AL93" t="inlineStr">
         <is>
-          <t>Klen gran i område med många fallna granar</t>
+          <t>Kraftigt nedbruten grov granlåga</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Picea abies # Klen gran i område med många fallna granar</t>
+          <t>Picea abies # Kraftigt nedbruten grov granlåga</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12004,10 +12007,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121231793</v>
+        <v>121231794</v>
       </c>
       <c r="B94" t="n">
-        <v>94712</v>
+        <v>94617</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12020,33 +12023,24 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
@@ -12056,7 +12050,7 @@
         <v>693674</v>
       </c>
       <c r="R94" t="n">
-        <v>6553894</v>
+        <v>6553897</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12088,7 +12082,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12098,7 +12092,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12122,12 +12116,12 @@
       </c>
       <c r="AL94" t="inlineStr">
         <is>
-          <t>Kraftigt nedbruten granlåga</t>
+          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftigt nedbruten granlåga</t>
+          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12138,17 +12132,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Cecilia Gottfries, Per Flodby, Emilia Blixt, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121231795</v>
+        <v>121231789</v>
       </c>
       <c r="B95" t="n">
-        <v>94712</v>
+        <v>91115</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12161,43 +12155,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>210</v>
+        <v>5420</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>693674</v>
+        <v>693670</v>
       </c>
       <c r="R95" t="n">
-        <v>6553897</v>
+        <v>6553974</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12229,7 +12214,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12239,7 +12224,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12253,22 +12238,22 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL95" t="inlineStr">
         <is>
-          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+          <t>Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+          <t>Pinus sylvestris # Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12279,17 +12264,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Per Flodby, Emilia Blixt, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121231765</v>
+        <v>121231795</v>
       </c>
       <c r="B96" t="n">
-        <v>100360</v>
+        <v>94713</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12302,34 +12287,43 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>693309</v>
+        <v>693674</v>
       </c>
       <c r="R96" t="n">
-        <v>6553789</v>
+        <v>6553897</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12361,7 +12355,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12371,7 +12365,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12382,6 +12376,26 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL96" t="inlineStr">
+        <is>
+          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -12391,17 +12405,17 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Cecilia Gottfries, Per Flodby, Emilia Blixt, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121231773</v>
+        <v>121231762</v>
       </c>
       <c r="B97" t="n">
-        <v>98094</v>
+        <v>110232</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12410,47 +12424,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>693495</v>
+        <v>693313</v>
       </c>
       <c r="R97" t="n">
-        <v>6553900</v>
+        <v>6553812</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12482,7 +12487,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12492,7 +12497,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12503,11 +12508,6 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>Sluttning med tallskog</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Per Flodby, Emilia Blixt, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -12527,7 +12527,7 @@
         <v>121231766</v>
       </c>
       <c r="B98" t="n">
-        <v>94616</v>
+        <v>94617</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>121231776</v>
       </c>
       <c r="B99" t="n">
-        <v>94616</v>
+        <v>94617</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12768,10 +12768,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121231786</v>
+        <v>121231787</v>
       </c>
       <c r="B100" t="n">
-        <v>94102</v>
+        <v>94390</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12784,28 +12784,24 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2362</v>
+        <v>2779</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blek stjärnmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Mnium stellare</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
@@ -12866,7 +12862,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -12883,17 +12878,17 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Per Flodby, Emilia Blixt, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121231787</v>
+        <v>121231788</v>
       </c>
       <c r="B101" t="n">
-        <v>94389</v>
+        <v>94596</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12906,21 +12901,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -13000,17 +12995,17 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Per Flodby, Emilia Blixt, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121231788</v>
+        <v>121231768</v>
       </c>
       <c r="B102" t="n">
-        <v>94595</v>
+        <v>94713</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13023,34 +13018,43 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2667</v>
+        <v>210</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>693670</v>
+        <v>693478</v>
       </c>
       <c r="R102" t="n">
-        <v>6553974</v>
+        <v>6553857</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13082,7 +13086,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13092,7 +13096,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13104,9 +13108,24 @@
       <c r="AG102" t="b">
         <v>0</v>
       </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL102" t="inlineStr">
+        <is>
+          <t>Granlåga i blockig sluttning</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Vid basen av lodvägg</t>
+          <t>Picea abies # Granlåga i blockig sluttning</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13124,10 +13143,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121231768</v>
+        <v>121231786</v>
       </c>
       <c r="B103" t="n">
-        <v>94712</v>
+        <v>94103</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13140,43 +13159,38 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>210</v>
+        <v>2362</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>693478</v>
+        <v>693670</v>
       </c>
       <c r="R103" t="n">
-        <v>6553857</v>
+        <v>6553974</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13208,7 +13222,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13218,7 +13232,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13227,27 +13241,13 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL103" t="inlineStr">
-        <is>
-          <t>Granlåga i blockig sluttning</t>
-        </is>
-      </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga i blockig sluttning</t>
+          <t>Vid basen av lodvägg</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -13258,7 +13258,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Per Flodby, Emilia Blixt, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -13268,7 +13268,7 @@
         <v>121330721</v>
       </c>
       <c r="B104" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>121231778</v>
       </c>
       <c r="B105" t="n">
-        <v>95680</v>
+        <v>95681</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
         <v>121231770</v>
       </c>
       <c r="B106" t="n">
-        <v>95957</v>
+        <v>95958</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -6731,10 +6731,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121124059</v>
+        <v>121124048</v>
       </c>
       <c r="B52" t="n">
-        <v>89761</v>
+        <v>110235</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6743,25 +6743,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1962</v>
+        <v>219711</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>693491</v>
+        <v>693677</v>
       </c>
       <c r="R52" t="n">
-        <v>6553751</v>
+        <v>6553911</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6827,21 +6827,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6858,10 +6843,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121124079</v>
+        <v>121124047</v>
       </c>
       <c r="B53" t="n">
-        <v>5189</v>
+        <v>110235</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6874,39 +6859,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>105930</v>
+        <v>219711</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>693431</v>
+        <v>693691</v>
       </c>
       <c r="R53" t="n">
-        <v>6553573</v>
+        <v>6553924</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6938,7 +6918,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6948,7 +6928,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6959,26 +6939,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL53" t="inlineStr">
-        <is>
-          <t>Klen låga.</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen låga.</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6995,10 +6955,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121124071</v>
+        <v>121124070</v>
       </c>
       <c r="B54" t="n">
-        <v>94617</v>
+        <v>94716</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7011,21 +6971,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7127,10 +7087,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121124055</v>
+        <v>121124058</v>
       </c>
       <c r="B55" t="n">
-        <v>92021</v>
+        <v>94870</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7139,25 +7099,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7167,10 +7127,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>693466</v>
+        <v>693480</v>
       </c>
       <c r="R55" t="n">
-        <v>6553741</v>
+        <v>6553749</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7202,7 +7162,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7212,7 +7172,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7239,10 +7199,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121124060</v>
+        <v>121124073</v>
       </c>
       <c r="B56" t="n">
-        <v>57367</v>
+        <v>90678</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7251,25 +7211,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7279,10 +7239,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>693507</v>
+        <v>693439</v>
       </c>
       <c r="R56" t="n">
-        <v>6553745</v>
+        <v>6553651</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7314,7 +7274,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7324,7 +7284,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7351,10 +7311,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121124065</v>
+        <v>121124067</v>
       </c>
       <c r="B57" t="n">
-        <v>5168</v>
+        <v>94620</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7363,43 +7323,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>102204</v>
+        <v>2818</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>693560</v>
+        <v>693537</v>
       </c>
       <c r="R57" t="n">
-        <v>6553691</v>
+        <v>6553673</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7431,7 +7386,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7441,7 +7396,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7452,26 +7407,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL57" t="inlineStr">
-        <is>
-          <t>Klen granlåga</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen granlåga</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7488,10 +7423,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121124053</v>
+        <v>121124061</v>
       </c>
       <c r="B58" t="n">
-        <v>91393</v>
+        <v>94870</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7504,21 +7439,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3298</v>
+        <v>2180</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7528,10 +7463,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>693628</v>
+        <v>693526</v>
       </c>
       <c r="R58" t="n">
-        <v>6553797</v>
+        <v>6553740</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7563,7 +7498,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7573,7 +7508,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7584,26 +7519,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL58" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7620,10 +7535,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121124073</v>
+        <v>121124079</v>
       </c>
       <c r="B59" t="n">
-        <v>90675</v>
+        <v>5192</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7636,34 +7551,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>693439</v>
+        <v>693431</v>
       </c>
       <c r="R59" t="n">
-        <v>6553651</v>
+        <v>6553573</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7695,7 +7615,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7705,7 +7625,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7716,6 +7636,26 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL59" t="inlineStr">
+        <is>
+          <t>Klen låga.</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen låga.</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7732,10 +7672,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121124077</v>
+        <v>121124056</v>
       </c>
       <c r="B60" t="n">
-        <v>5168</v>
+        <v>94870</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7744,47 +7684,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102204</v>
+        <v>2180</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>693453</v>
+        <v>693482</v>
       </c>
       <c r="R60" t="n">
-        <v>6553587</v>
+        <v>6553750</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7816,7 +7747,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7826,7 +7757,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7835,29 +7766,8 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL60" t="inlineStr">
-        <is>
-          <t>Klen granlåga</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen granlåga</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7874,10 +7784,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121124070</v>
+        <v>121124045</v>
       </c>
       <c r="B61" t="n">
-        <v>94713</v>
+        <v>110235</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7890,21 +7800,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>210</v>
+        <v>219711</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7914,10 +7824,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>693461</v>
+        <v>693689</v>
       </c>
       <c r="R61" t="n">
-        <v>6553671</v>
+        <v>6553935</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7949,7 +7859,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7959,7 +7869,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Mycket rikligt.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7970,26 +7885,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL61" t="inlineStr">
-        <is>
-          <t>Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Picea abies # Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -8009,7 +7904,7 @@
         <v>121124066</v>
       </c>
       <c r="B62" t="n">
-        <v>4766</v>
+        <v>4769</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8148,10 +8043,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121124080</v>
+        <v>121124060</v>
       </c>
       <c r="B63" t="n">
-        <v>5169</v>
+        <v>57370</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8160,43 +8055,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>693426</v>
+        <v>693507</v>
       </c>
       <c r="R63" t="n">
-        <v>6553560</v>
+        <v>6553745</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8228,7 +8118,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8238,7 +8128,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8249,26 +8139,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL63" t="inlineStr">
-        <is>
-          <t>Klen låga.</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen låga.</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -8285,10 +8155,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121124081</v>
+        <v>121124082</v>
       </c>
       <c r="B64" t="n">
-        <v>5168</v>
+        <v>89764</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8301,39 +8171,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102204</v>
+        <v>1962</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>693426</v>
+        <v>693411</v>
       </c>
       <c r="R64" t="n">
-        <v>6553560</v>
+        <v>6553549</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8365,7 +8230,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8375,7 +8240,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8389,22 +8254,22 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>Klen låga.</t>
+          <t>På undersidan av tallved.</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Picea abies # Klen låga.</t>
+          <t>Pinus sylvestris # På undersidan av tallved.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8422,10 +8287,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121124045</v>
+        <v>121124077</v>
       </c>
       <c r="B65" t="n">
-        <v>110232</v>
+        <v>5171</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8434,38 +8299,47 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219711</v>
+        <v>102204</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>693689</v>
+        <v>693453</v>
       </c>
       <c r="R65" t="n">
-        <v>6553935</v>
+        <v>6553587</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8497,7 +8371,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8507,12 +8381,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Mycket rikligt.</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8521,8 +8390,29 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL65" t="inlineStr">
+        <is>
+          <t>Klen granlåga</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen granlåga</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8539,10 +8429,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121124067</v>
+        <v>121124071</v>
       </c>
       <c r="B66" t="n">
-        <v>94617</v>
+        <v>94620</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8579,10 +8469,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>693537</v>
+        <v>693461</v>
       </c>
       <c r="R66" t="n">
-        <v>6553673</v>
+        <v>6553671</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8614,7 +8504,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8624,7 +8514,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8635,6 +8525,26 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL66" t="inlineStr">
+        <is>
+          <t>Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Picea abies # Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8651,10 +8561,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121124061</v>
+        <v>121124053</v>
       </c>
       <c r="B67" t="n">
-        <v>94867</v>
+        <v>91396</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8667,21 +8577,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2180</v>
+        <v>3298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8691,10 +8601,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>693526</v>
+        <v>693628</v>
       </c>
       <c r="R67" t="n">
-        <v>6553740</v>
+        <v>6553797</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8726,7 +8636,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8736,7 +8646,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8747,6 +8657,26 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL67" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död gran.</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8763,10 +8693,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121124082</v>
+        <v>121124059</v>
       </c>
       <c r="B68" t="n">
-        <v>89761</v>
+        <v>89764</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8803,10 +8733,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>693411</v>
+        <v>693491</v>
       </c>
       <c r="R68" t="n">
-        <v>6553549</v>
+        <v>6553751</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8838,7 +8768,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8848,7 +8778,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8870,14 +8800,9 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
-      <c r="AL68" t="inlineStr">
-        <is>
-          <t>På undersidan av tallved.</t>
-        </is>
-      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # På undersidan av tallved.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8895,10 +8820,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121124056</v>
+        <v>121124065</v>
       </c>
       <c r="B69" t="n">
-        <v>94867</v>
+        <v>5171</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8907,38 +8832,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2180</v>
+        <v>102204</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>693482</v>
+        <v>693560</v>
       </c>
       <c r="R69" t="n">
-        <v>6553750</v>
+        <v>6553691</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8970,7 +8900,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8980,7 +8910,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8991,6 +8921,26 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL69" t="inlineStr">
+        <is>
+          <t>Klen granlåga</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen granlåga</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -9007,10 +8957,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121124074</v>
+        <v>121124055</v>
       </c>
       <c r="B70" t="n">
-        <v>5168</v>
+        <v>92024</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9023,39 +8973,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102204</v>
+        <v>5966</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>693455</v>
+        <v>693466</v>
       </c>
       <c r="R70" t="n">
-        <v>6553651</v>
+        <v>6553741</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9087,7 +9032,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9097,7 +9042,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9108,26 +9053,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL70" t="inlineStr">
-        <is>
-          <t>Gren långt ner på gammal tall.</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Picea abies # Gren långt ner på gammal tall.</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -9144,10 +9069,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121124047</v>
+        <v>121124074</v>
       </c>
       <c r="B71" t="n">
-        <v>110232</v>
+        <v>5171</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9156,38 +9081,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219711</v>
+        <v>102204</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>693691</v>
+        <v>693455</v>
       </c>
       <c r="R71" t="n">
-        <v>6553924</v>
+        <v>6553651</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9219,7 +9149,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9229,7 +9159,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9240,6 +9170,26 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL71" t="inlineStr">
+        <is>
+          <t>Gren långt ner på gammal tall.</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Picea abies # Gren långt ner på gammal tall.</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9256,10 +9206,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121124058</v>
+        <v>121124081</v>
       </c>
       <c r="B72" t="n">
-        <v>94867</v>
+        <v>5171</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9268,38 +9218,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2180</v>
+        <v>102204</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>693480</v>
+        <v>693426</v>
       </c>
       <c r="R72" t="n">
-        <v>6553749</v>
+        <v>6553560</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9331,7 +9286,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9341,7 +9296,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9352,6 +9307,26 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL72" t="inlineStr">
+        <is>
+          <t>Klen låga.</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen låga.</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -9368,10 +9343,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121124048</v>
+        <v>121124080</v>
       </c>
       <c r="B73" t="n">
-        <v>110232</v>
+        <v>5172</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9384,34 +9359,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219711</v>
+        <v>100526</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>693677</v>
+        <v>693426</v>
       </c>
       <c r="R73" t="n">
-        <v>6553911</v>
+        <v>6553560</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9443,7 +9423,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9453,7 +9433,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9464,6 +9444,26 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL73" t="inlineStr">
+        <is>
+          <t>Klen låga.</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen låga.</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9483,7 +9483,7 @@
         <v>121124051</v>
       </c>
       <c r="B74" t="n">
-        <v>94617</v>
+        <v>94620</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>121124052</v>
       </c>
       <c r="B75" t="n">
-        <v>94713</v>
+        <v>94716</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9744,10 +9744,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121221017</v>
+        <v>121222341</v>
       </c>
       <c r="B76" t="n">
-        <v>57367</v>
+        <v>8424</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9756,46 +9756,50 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kolnäsviken, Kolnäsviken, Srm</t>
+          <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>693644</v>
+        <v>693587</v>
       </c>
       <c r="R76" t="n">
-        <v>6554031</v>
+        <v>6553902</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9824,7 +9828,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9834,7 +9838,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9849,22 +9853,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121222341</v>
+        <v>121224726</v>
       </c>
       <c r="B77" t="n">
-        <v>8421</v>
+        <v>97052</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9877,43 +9881,38 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Breviksnäs, Srm</t>
+          <t>Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>693587</v>
+        <v>693312</v>
       </c>
       <c r="R77" t="n">
-        <v>6553902</v>
+        <v>6553808</v>
       </c>
       <c r="S77" t="n">
         <v>13</v>
@@ -9945,7 +9944,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9955,7 +9954,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9982,10 +9981,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121224726</v>
+        <v>121224119</v>
       </c>
       <c r="B78" t="n">
-        <v>97049</v>
+        <v>97052</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10026,10 +10025,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>693312</v>
+        <v>693407</v>
       </c>
       <c r="R78" t="n">
-        <v>6553808</v>
+        <v>6553843</v>
       </c>
       <c r="S78" t="n">
         <v>13</v>
@@ -10061,7 +10060,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10071,7 +10070,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10098,10 +10097,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121224002</v>
+        <v>121224447</v>
       </c>
       <c r="B79" t="n">
-        <v>5189</v>
+        <v>100364</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10114,37 +10113,41 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Sandkärr, Sandkärr, Srm</t>
+          <t>Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>693430</v>
+        <v>693195</v>
       </c>
       <c r="R79" t="n">
-        <v>6553864</v>
+        <v>6553768</v>
       </c>
       <c r="S79" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10173,7 +10176,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10183,7 +10186,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10198,22 +10201,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121224447</v>
+        <v>121224002</v>
       </c>
       <c r="B80" t="n">
-        <v>100361</v>
+        <v>5192</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10226,41 +10229,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Sandkärr, Srm</t>
+          <t>Sandkärr, Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>693195</v>
+        <v>693430</v>
       </c>
       <c r="R80" t="n">
-        <v>6553768</v>
+        <v>6553864</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10289,7 +10288,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10299,7 +10298,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10314,22 +10313,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121224119</v>
+        <v>121221017</v>
       </c>
       <c r="B81" t="n">
-        <v>97049</v>
+        <v>57370</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10338,45 +10337,46 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sandkärr, Srm</t>
+          <t>Kolnäsviken, Kolnäsviken, Srm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>693407</v>
+        <v>693644</v>
       </c>
       <c r="R81" t="n">
-        <v>6553843</v>
+        <v>6554031</v>
       </c>
       <c r="S81" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10430,22 +10430,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121231773</v>
+        <v>121231775</v>
       </c>
       <c r="B82" t="n">
-        <v>98095</v>
+        <v>8435</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10454,35 +10454,31 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -10491,10 +10487,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>693495</v>
+        <v>693555</v>
       </c>
       <c r="R82" t="n">
-        <v>6553900</v>
+        <v>6553905</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10526,7 +10522,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10536,7 +10532,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10548,9 +10544,19 @@
       <c r="AG82" t="b">
         <v>0</v>
       </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>Sluttning med tallskog</t>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10568,10 +10574,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121231782</v>
+        <v>121231793</v>
       </c>
       <c r="B83" t="n">
-        <v>57367</v>
+        <v>94716</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10580,31 +10586,35 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10613,10 +10623,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>693709</v>
+        <v>693674</v>
       </c>
       <c r="R83" t="n">
-        <v>6553983</v>
+        <v>6553894</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10648,7 +10658,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10658,12 +10668,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Födosökshack vid basen av stående död tall.</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10674,6 +10679,26 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL83" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten granlåga</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Picea abies # Kraftigt nedbruten granlåga</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10683,17 +10708,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121231785</v>
+        <v>121231771</v>
       </c>
       <c r="B84" t="n">
-        <v>90730</v>
+        <v>4775</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10702,25 +10727,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10730,10 +10755,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>693675</v>
+        <v>693494</v>
       </c>
       <c r="R84" t="n">
-        <v>6553972</v>
+        <v>6553917</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10765,7 +10790,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10775,7 +10800,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10789,22 +10814,22 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL84" t="inlineStr">
         <is>
-          <t>Äldre tall</t>
+          <t>Äldre grov gran</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Äldre tall</t>
+          <t>Picea abies # Äldre grov gran</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10815,17 +10840,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Per Flodby, Emilia Blixt, Klas Magnusson</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121231775</v>
+        <v>121231795</v>
       </c>
       <c r="B85" t="n">
-        <v>8432</v>
+        <v>94716</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10838,27 +10863,31 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>210</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -10867,10 +10896,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>693555</v>
+        <v>693674</v>
       </c>
       <c r="R85" t="n">
-        <v>6553905</v>
+        <v>6553897</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10902,7 +10931,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10912,7 +10941,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10926,17 +10955,22 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL85" t="inlineStr">
+        <is>
+          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10947,17 +10981,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121231765</v>
+        <v>121231785</v>
       </c>
       <c r="B86" t="n">
-        <v>100361</v>
+        <v>90733</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10966,25 +11000,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10994,10 +11028,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>693309</v>
+        <v>693675</v>
       </c>
       <c r="R86" t="n">
-        <v>6553789</v>
+        <v>6553972</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11029,7 +11063,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11039,7 +11073,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11050,6 +11084,26 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL86" t="inlineStr">
+        <is>
+          <t>Äldre tall</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Äldre tall</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -11066,10 +11120,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121231771</v>
+        <v>121231773</v>
       </c>
       <c r="B87" t="n">
-        <v>4772</v>
+        <v>98098</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11078,38 +11132,47 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>693494</v>
+        <v>693495</v>
       </c>
       <c r="R87" t="n">
-        <v>6553917</v>
+        <v>6553900</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11141,7 +11204,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11151,7 +11214,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11163,24 +11226,9 @@
       <c r="AG87" t="b">
         <v>0</v>
       </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL87" t="inlineStr">
-        <is>
-          <t>Äldre grov gran</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre grov gran</t>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>Sluttning med tallskog</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11198,10 +11246,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121231792</v>
+        <v>121231781</v>
       </c>
       <c r="B88" t="n">
-        <v>94617</v>
+        <v>5192</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11214,34 +11262,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2818</v>
+        <v>105930</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>693674</v>
+        <v>693639</v>
       </c>
       <c r="R88" t="n">
-        <v>6553894</v>
+        <v>6553969</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11273,7 +11326,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11283,7 +11336,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11305,14 +11358,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL88" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten granlåga</t>
-        </is>
-      </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftigt nedbruten granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11323,17 +11371,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Cecilia Gottfries, Per Flodby, Emilia Blixt, Klas Magnusson</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121231793</v>
+        <v>121231789</v>
       </c>
       <c r="B89" t="n">
-        <v>94713</v>
+        <v>91118</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11346,43 +11394,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>210</v>
+        <v>5420</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>693674</v>
+        <v>693670</v>
       </c>
       <c r="R89" t="n">
-        <v>6553894</v>
+        <v>6553974</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11414,7 +11453,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11424,7 +11463,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11438,22 +11477,22 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL89" t="inlineStr">
         <is>
-          <t>Kraftigt nedbruten granlåga</t>
+          <t>Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftigt nedbruten granlåga</t>
+          <t>Pinus sylvestris # Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11464,17 +11503,17 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Cecilia Gottfries, Per Flodby, Emilia Blixt, Klas Magnusson</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121231781</v>
+        <v>121231774</v>
       </c>
       <c r="B90" t="n">
-        <v>5189</v>
+        <v>105164</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11483,31 +11522,35 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>105930</v>
+        <v>340</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -11516,10 +11559,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>693639</v>
+        <v>693495</v>
       </c>
       <c r="R90" t="n">
-        <v>6553969</v>
+        <v>6553900</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11551,7 +11594,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11561,7 +11604,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Två av skotten hade frökapslar.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11573,19 +11621,9 @@
       <c r="AG90" t="b">
         <v>0</v>
       </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>Sluttning med tallskog</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11606,7 +11644,7 @@
         <v>121231764</v>
       </c>
       <c r="B91" t="n">
-        <v>5189</v>
+        <v>5192</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11735,10 +11773,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121231774</v>
+        <v>121231792</v>
       </c>
       <c r="B92" t="n">
-        <v>105161</v>
+        <v>94620</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11747,47 +11785,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>340</v>
+        <v>2818</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>693495</v>
+        <v>693674</v>
       </c>
       <c r="R92" t="n">
-        <v>6553900</v>
+        <v>6553894</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11819,7 +11848,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11829,12 +11858,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Två av skotten hade frökapslar.</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11846,9 +11870,24 @@
       <c r="AG92" t="b">
         <v>0</v>
       </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>Sluttning med tallskog</t>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL92" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten granlåga</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Picea abies # Kraftigt nedbruten granlåga</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11859,17 +11898,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121231767</v>
+        <v>121231782</v>
       </c>
       <c r="B93" t="n">
-        <v>94713</v>
+        <v>57370</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11878,35 +11917,31 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -11915,10 +11950,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>693436</v>
+        <v>693709</v>
       </c>
       <c r="R93" t="n">
-        <v>6553861</v>
+        <v>6553983</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11950,7 +11985,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11960,7 +11995,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Födosökshack vid basen av stående död tall.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11971,26 +12011,6 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL93" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten grov granlåga</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Picea abies # Kraftigt nedbruten grov granlåga</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -12010,7 +12030,7 @@
         <v>121231794</v>
       </c>
       <c r="B94" t="n">
-        <v>94617</v>
+        <v>94620</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12132,17 +12152,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Cecilia Gottfries, Per Flodby, Emilia Blixt, Klas Magnusson</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121231789</v>
+        <v>121231765</v>
       </c>
       <c r="B95" t="n">
-        <v>91115</v>
+        <v>100364</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12155,21 +12175,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5420</v>
+        <v>222498</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12179,10 +12199,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>693670</v>
+        <v>693309</v>
       </c>
       <c r="R95" t="n">
-        <v>6553974</v>
+        <v>6553789</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12214,7 +12234,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12224,7 +12244,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12235,26 +12255,6 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL95" t="inlineStr">
-        <is>
-          <t>Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -12264,17 +12264,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Per Flodby, Emilia Blixt, Klas Magnusson</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121231795</v>
+        <v>121231767</v>
       </c>
       <c r="B96" t="n">
-        <v>94713</v>
+        <v>94716</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12320,10 +12320,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>693674</v>
+        <v>693436</v>
       </c>
       <c r="R96" t="n">
-        <v>6553897</v>
+        <v>6553861</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="AL96" t="inlineStr">
         <is>
-          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+          <t>Kraftigt nedbruten grov granlåga</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+          <t>Picea abies # Kraftigt nedbruten grov granlåga</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12405,7 +12405,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Cecilia Gottfries, Per Flodby, Emilia Blixt, Klas Magnusson</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -12415,7 +12415,7 @@
         <v>121231762</v>
       </c>
       <c r="B97" t="n">
-        <v>110232</v>
+        <v>110235</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Per Flodby, Emilia Blixt, Klas Magnusson</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -12527,7 +12527,7 @@
         <v>121231766</v>
       </c>
       <c r="B98" t="n">
-        <v>94617</v>
+        <v>94620</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12656,10 +12656,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121231776</v>
+        <v>121231786</v>
       </c>
       <c r="B99" t="n">
-        <v>94617</v>
+        <v>94106</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12672,34 +12672,38 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2818</v>
+        <v>2362</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>693581</v>
+        <v>693670</v>
       </c>
       <c r="R99" t="n">
-        <v>6553897</v>
+        <v>6553974</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12731,7 +12735,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12741,7 +12745,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12750,8 +12754,14 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Vid basen av lodvägg</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -12768,10 +12778,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121231787</v>
+        <v>121231788</v>
       </c>
       <c r="B100" t="n">
-        <v>94390</v>
+        <v>94599</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12784,21 +12794,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -12878,17 +12888,17 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Per Flodby, Emilia Blixt, Klas Magnusson</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121231788</v>
+        <v>121231776</v>
       </c>
       <c r="B101" t="n">
-        <v>94596</v>
+        <v>94620</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12901,21 +12911,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2667</v>
+        <v>2818</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12925,10 +12935,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>693670</v>
+        <v>693581</v>
       </c>
       <c r="R101" t="n">
-        <v>6553974</v>
+        <v>6553897</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12960,7 +12970,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12970,7 +12980,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12981,11 +12991,6 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Vid basen av lodvägg</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -12995,17 +13000,17 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Per Flodby, Emilia Blixt, Klas Magnusson</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121231768</v>
+        <v>121231787</v>
       </c>
       <c r="B102" t="n">
-        <v>94713</v>
+        <v>94393</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13018,43 +13023,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>210</v>
+        <v>2779</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>693478</v>
+        <v>693670</v>
       </c>
       <c r="R102" t="n">
-        <v>6553857</v>
+        <v>6553974</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13086,7 +13082,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13096,7 +13092,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13108,24 +13104,9 @@
       <c r="AG102" t="b">
         <v>0</v>
       </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL102" t="inlineStr">
-        <is>
-          <t>Granlåga i blockig sluttning</t>
-        </is>
-      </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga i blockig sluttning</t>
+          <t>Vid basen av lodvägg</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13143,10 +13124,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121231786</v>
+        <v>121231768</v>
       </c>
       <c r="B103" t="n">
-        <v>94103</v>
+        <v>94716</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13159,38 +13140,43 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2362</v>
+        <v>210</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Blek stjärnmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Mnium stellare</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>693670</v>
+        <v>693478</v>
       </c>
       <c r="R103" t="n">
-        <v>6553974</v>
+        <v>6553857</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13222,7 +13208,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13232,7 +13218,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13241,13 +13227,27 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL103" t="inlineStr">
+        <is>
+          <t>Granlåga i blockig sluttning</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>Vid basen av lodvägg</t>
+          <t>Picea abies # Granlåga i blockig sluttning</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -13258,7 +13258,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Per Flodby, Emilia Blixt, Klas Magnusson</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -13268,7 +13268,7 @@
         <v>121330721</v>
       </c>
       <c r="B104" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>121231778</v>
       </c>
       <c r="B105" t="n">
-        <v>95681</v>
+        <v>95684</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
         <v>121231770</v>
       </c>
       <c r="B106" t="n">
-        <v>95958</v>
+        <v>95961</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -6731,10 +6731,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121124048</v>
+        <v>121124060</v>
       </c>
       <c r="B52" t="n">
-        <v>110235</v>
+        <v>57370</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6743,25 +6743,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>693677</v>
+        <v>693507</v>
       </c>
       <c r="R52" t="n">
-        <v>6553911</v>
+        <v>6553745</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6843,10 +6843,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121124047</v>
+        <v>121124065</v>
       </c>
       <c r="B53" t="n">
-        <v>110235</v>
+        <v>5171</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6855,38 +6855,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219711</v>
+        <v>102204</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>693691</v>
+        <v>693560</v>
       </c>
       <c r="R53" t="n">
-        <v>6553924</v>
+        <v>6553691</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6918,7 +6923,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6928,7 +6933,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6939,6 +6944,26 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>Klen granlåga</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen granlåga</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6955,10 +6980,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121124070</v>
+        <v>121124055</v>
       </c>
       <c r="B54" t="n">
-        <v>94716</v>
+        <v>92024</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6967,25 +6992,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>210</v>
+        <v>5966</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6995,10 +7020,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>693461</v>
+        <v>693466</v>
       </c>
       <c r="R54" t="n">
-        <v>6553671</v>
+        <v>6553741</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7030,7 +7055,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7040,7 +7065,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7051,26 +7076,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL54" t="inlineStr">
-        <is>
-          <t>Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Picea abies # Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7199,10 +7204,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121124073</v>
+        <v>121124082</v>
       </c>
       <c r="B56" t="n">
-        <v>90678</v>
+        <v>89764</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7211,25 +7216,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7239,10 +7244,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>693439</v>
+        <v>693411</v>
       </c>
       <c r="R56" t="n">
-        <v>6553651</v>
+        <v>6553549</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7274,7 +7279,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7284,7 +7289,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7295,6 +7300,26 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>På undersidan av tallved.</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # På undersidan av tallved.</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7311,10 +7336,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121124067</v>
+        <v>121124045</v>
       </c>
       <c r="B57" t="n">
-        <v>94620</v>
+        <v>110235</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7327,21 +7352,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2818</v>
+        <v>219711</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7351,10 +7376,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>693537</v>
+        <v>693689</v>
       </c>
       <c r="R57" t="n">
-        <v>6553673</v>
+        <v>6553935</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7386,7 +7411,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7396,7 +7421,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Mycket rikligt.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7423,10 +7453,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121124061</v>
+        <v>121124048</v>
       </c>
       <c r="B58" t="n">
-        <v>94870</v>
+        <v>110235</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7439,21 +7469,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2180</v>
+        <v>219711</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7463,10 +7493,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>693526</v>
+        <v>693677</v>
       </c>
       <c r="R58" t="n">
-        <v>6553740</v>
+        <v>6553911</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7498,7 +7528,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7508,7 +7538,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7535,10 +7565,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121124079</v>
+        <v>121124061</v>
       </c>
       <c r="B59" t="n">
-        <v>5192</v>
+        <v>94870</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7551,39 +7581,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>105930</v>
+        <v>2180</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>693431</v>
+        <v>693526</v>
       </c>
       <c r="R59" t="n">
-        <v>6553573</v>
+        <v>6553740</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7615,7 +7640,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7625,7 +7650,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7636,26 +7661,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL59" t="inlineStr">
-        <is>
-          <t>Klen låga.</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen låga.</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7672,10 +7677,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121124056</v>
+        <v>121124053</v>
       </c>
       <c r="B60" t="n">
-        <v>94870</v>
+        <v>91396</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7688,21 +7693,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2180</v>
+        <v>3298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7712,10 +7717,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>693482</v>
+        <v>693628</v>
       </c>
       <c r="R60" t="n">
-        <v>6553750</v>
+        <v>6553797</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7747,7 +7752,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7757,7 +7762,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7768,6 +7773,26 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död gran.</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7784,10 +7809,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121124045</v>
+        <v>121124059</v>
       </c>
       <c r="B61" t="n">
-        <v>110235</v>
+        <v>89764</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7796,25 +7821,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219711</v>
+        <v>1962</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7824,10 +7849,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>693689</v>
+        <v>693491</v>
       </c>
       <c r="R61" t="n">
-        <v>6553935</v>
+        <v>6553751</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7859,7 +7884,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7869,12 +7894,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Mycket rikligt.</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7885,6 +7905,21 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7901,10 +7936,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121124066</v>
+        <v>121124077</v>
       </c>
       <c r="B62" t="n">
-        <v>4769</v>
+        <v>5171</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7913,25 +7948,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100299</v>
+        <v>102204</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7950,10 +7985,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>693536</v>
+        <v>693453</v>
       </c>
       <c r="R62" t="n">
-        <v>6553680</v>
+        <v>6553587</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7985,7 +8020,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7995,7 +8030,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8020,12 +8055,12 @@
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>Stående död gran.</t>
+          <t>Klen granlåga</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död gran.</t>
+          <t>Picea abies # Klen granlåga</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8043,10 +8078,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121124060</v>
+        <v>121124067</v>
       </c>
       <c r="B63" t="n">
-        <v>57370</v>
+        <v>94620</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8055,25 +8090,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8083,10 +8118,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>693507</v>
+        <v>693537</v>
       </c>
       <c r="R63" t="n">
-        <v>6553745</v>
+        <v>6553673</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8118,7 +8153,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8128,7 +8163,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8155,10 +8190,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121124082</v>
+        <v>121124066</v>
       </c>
       <c r="B64" t="n">
-        <v>89764</v>
+        <v>4769</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8167,38 +8202,47 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1962</v>
+        <v>100299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>693411</v>
+        <v>693536</v>
       </c>
       <c r="R64" t="n">
-        <v>6553549</v>
+        <v>6553680</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8230,7 +8274,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8240,7 +8284,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8249,27 +8293,28 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>På undersidan av tallved.</t>
+          <t>Stående död gran.</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # På undersidan av tallved.</t>
+          <t>Picea abies # Stående död gran.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8287,7 +8332,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121124077</v>
+        <v>121124081</v>
       </c>
       <c r="B65" t="n">
         <v>5171</v>
@@ -8321,25 +8366,21 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>693453</v>
+        <v>693426</v>
       </c>
       <c r="R65" t="n">
-        <v>6553587</v>
+        <v>6553560</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8371,7 +8412,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8381,7 +8422,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8390,7 +8431,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8406,12 +8446,12 @@
       </c>
       <c r="AL65" t="inlineStr">
         <is>
-          <t>Klen granlåga</t>
+          <t>Klen låga.</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Picea abies # Klen granlåga</t>
+          <t>Picea abies # Klen låga.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8429,10 +8469,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121124071</v>
+        <v>121124074</v>
       </c>
       <c r="B66" t="n">
-        <v>94620</v>
+        <v>5171</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8441,38 +8481,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2818</v>
+        <v>102204</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>693461</v>
+        <v>693455</v>
       </c>
       <c r="R66" t="n">
-        <v>6553671</v>
+        <v>6553651</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8504,7 +8549,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8514,7 +8559,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8538,12 +8583,12 @@
       </c>
       <c r="AL66" t="inlineStr">
         <is>
-          <t>Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
+          <t>Gren långt ner på gammal tall.</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
+          <t>Picea abies # Gren långt ner på gammal tall.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8561,10 +8606,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121124053</v>
+        <v>121124056</v>
       </c>
       <c r="B67" t="n">
-        <v>91396</v>
+        <v>94870</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8577,21 +8622,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3298</v>
+        <v>2180</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8601,10 +8646,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>693628</v>
+        <v>693482</v>
       </c>
       <c r="R67" t="n">
-        <v>6553797</v>
+        <v>6553750</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8636,7 +8681,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8646,7 +8691,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8657,26 +8702,6 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL67" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8693,10 +8718,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121124059</v>
+        <v>121124071</v>
       </c>
       <c r="B68" t="n">
-        <v>89764</v>
+        <v>94620</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8705,25 +8730,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1962</v>
+        <v>2818</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8733,10 +8758,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>693491</v>
+        <v>693461</v>
       </c>
       <c r="R68" t="n">
-        <v>6553751</v>
+        <v>6553671</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8768,7 +8793,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8778,7 +8803,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8792,17 +8817,22 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL68" t="inlineStr">
+        <is>
+          <t>Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies # Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8820,10 +8850,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121124065</v>
+        <v>121124070</v>
       </c>
       <c r="B69" t="n">
-        <v>5171</v>
+        <v>94716</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8832,43 +8862,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102204</v>
+        <v>210</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>693560</v>
+        <v>693461</v>
       </c>
       <c r="R69" t="n">
-        <v>6553691</v>
+        <v>6553671</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8900,7 +8925,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8910,7 +8935,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8934,12 +8959,12 @@
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>Klen granlåga</t>
+          <t>Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Picea abies # Klen granlåga</t>
+          <t>Picea abies # Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8957,10 +8982,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121124055</v>
+        <v>121124073</v>
       </c>
       <c r="B70" t="n">
-        <v>92024</v>
+        <v>90678</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8969,25 +8994,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8997,10 +9022,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>693466</v>
+        <v>693439</v>
       </c>
       <c r="R70" t="n">
-        <v>6553741</v>
+        <v>6553651</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9032,7 +9057,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9042,7 +9067,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9069,10 +9094,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121124074</v>
+        <v>121124047</v>
       </c>
       <c r="B71" t="n">
-        <v>5171</v>
+        <v>110235</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9081,43 +9106,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102204</v>
+        <v>219711</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>693455</v>
+        <v>693691</v>
       </c>
       <c r="R71" t="n">
-        <v>6553651</v>
+        <v>6553924</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9149,7 +9169,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9159,7 +9179,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9170,26 +9190,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL71" t="inlineStr">
-        <is>
-          <t>Gren långt ner på gammal tall.</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Picea abies # Gren långt ner på gammal tall.</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9206,10 +9206,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121124081</v>
+        <v>121124080</v>
       </c>
       <c r="B72" t="n">
-        <v>5171</v>
+        <v>5172</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9218,25 +9218,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>102204</v>
+        <v>100526</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9343,10 +9343,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121124080</v>
+        <v>121124079</v>
       </c>
       <c r="B73" t="n">
-        <v>5172</v>
+        <v>5192</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9359,21 +9359,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>693426</v>
+        <v>693431</v>
       </c>
       <c r="R73" t="n">
-        <v>6553560</v>
+        <v>6553573</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9480,10 +9480,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121124051</v>
+        <v>121124052</v>
       </c>
       <c r="B74" t="n">
-        <v>94620</v>
+        <v>94716</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9496,21 +9496,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9612,10 +9612,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121124052</v>
+        <v>121124051</v>
       </c>
       <c r="B75" t="n">
-        <v>94716</v>
+        <v>94620</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9628,21 +9628,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9865,7 +9865,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121224726</v>
+        <v>121224119</v>
       </c>
       <c r="B77" t="n">
         <v>97052</v>
@@ -9909,10 +9909,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>693312</v>
+        <v>693407</v>
       </c>
       <c r="R77" t="n">
-        <v>6553808</v>
+        <v>6553843</v>
       </c>
       <c r="S77" t="n">
         <v>13</v>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9981,10 +9981,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121224119</v>
+        <v>121224447</v>
       </c>
       <c r="B78" t="n">
-        <v>97052</v>
+        <v>100364</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9997,21 +9997,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10025,13 +10025,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>693407</v>
+        <v>693195</v>
       </c>
       <c r="R78" t="n">
-        <v>6553843</v>
+        <v>6553768</v>
       </c>
       <c r="S78" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10097,10 +10097,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121224447</v>
+        <v>121224002</v>
       </c>
       <c r="B79" t="n">
-        <v>100364</v>
+        <v>5192</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10113,41 +10113,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Sandkärr, Srm</t>
+          <t>Sandkärr, Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>693195</v>
+        <v>693430</v>
       </c>
       <c r="R79" t="n">
-        <v>6553768</v>
+        <v>6553864</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10176,7 +10172,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10186,7 +10182,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10201,22 +10197,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121224002</v>
+        <v>121224726</v>
       </c>
       <c r="B80" t="n">
-        <v>5192</v>
+        <v>97052</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10229,37 +10225,41 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>105930</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Sandkärr, Sandkärr, Srm</t>
+          <t>Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>693430</v>
+        <v>693312</v>
       </c>
       <c r="R80" t="n">
-        <v>6553864</v>
+        <v>6553808</v>
       </c>
       <c r="S80" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10298,7 +10298,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10313,12 +10313,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -10442,10 +10442,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121231775</v>
+        <v>121231762</v>
       </c>
       <c r="B82" t="n">
-        <v>8435</v>
+        <v>110235</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10458,39 +10458,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>219711</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>693555</v>
+        <v>693313</v>
       </c>
       <c r="R82" t="n">
-        <v>6553905</v>
+        <v>6553812</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10522,7 +10517,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10532,7 +10527,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10543,21 +10538,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10574,7 +10554,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121231793</v>
+        <v>121231795</v>
       </c>
       <c r="B83" t="n">
         <v>94716</v>
@@ -10609,7 +10589,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10626,7 +10606,7 @@
         <v>693674</v>
       </c>
       <c r="R83" t="n">
-        <v>6553894</v>
+        <v>6553897</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10658,7 +10638,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10668,7 +10648,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10692,12 +10672,12 @@
       </c>
       <c r="AL83" t="inlineStr">
         <is>
-          <t>Kraftigt nedbruten granlåga</t>
+          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftigt nedbruten granlåga</t>
+          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10715,10 +10695,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121231771</v>
+        <v>121231782</v>
       </c>
       <c r="B84" t="n">
-        <v>4775</v>
+        <v>57370</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10727,38 +10707,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>693494</v>
+        <v>693709</v>
       </c>
       <c r="R84" t="n">
-        <v>6553917</v>
+        <v>6553983</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10790,7 +10775,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10800,7 +10785,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Födosökshack vid basen av stående död tall.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10811,26 +10801,6 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL84" t="inlineStr">
-        <is>
-          <t>Äldre grov gran</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre grov gran</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10847,10 +10817,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121231795</v>
+        <v>121231789</v>
       </c>
       <c r="B85" t="n">
-        <v>94716</v>
+        <v>91118</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10863,43 +10833,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>210</v>
+        <v>5420</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>693674</v>
+        <v>693670</v>
       </c>
       <c r="R85" t="n">
-        <v>6553897</v>
+        <v>6553974</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10931,7 +10892,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10941,7 +10902,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10955,22 +10916,22 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL85" t="inlineStr">
         <is>
-          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+          <t>Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+          <t>Pinus sylvestris # Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10981,17 +10942,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121231785</v>
+        <v>121231775</v>
       </c>
       <c r="B86" t="n">
-        <v>90733</v>
+        <v>8435</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11000,38 +10961,43 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>693675</v>
+        <v>693555</v>
       </c>
       <c r="R86" t="n">
-        <v>6553972</v>
+        <v>6553905</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11063,7 +11029,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11073,7 +11039,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11095,14 +11061,9 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
-      <c r="AL86" t="inlineStr">
-        <is>
-          <t>Äldre tall</t>
-        </is>
-      </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Äldre tall</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11120,10 +11081,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121231773</v>
+        <v>121231774</v>
       </c>
       <c r="B87" t="n">
-        <v>98098</v>
+        <v>105164</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11132,35 +11093,35 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>340</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) W. P. C. Barton</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -11215,6 +11176,11 @@
       <c r="AB87" t="inlineStr">
         <is>
           <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Två av skotten hade frökapslar.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11246,10 +11212,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121231781</v>
+        <v>121231767</v>
       </c>
       <c r="B88" t="n">
-        <v>5192</v>
+        <v>94716</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11262,27 +11228,31 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>105930</v>
+        <v>210</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -11291,10 +11261,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>693639</v>
+        <v>693436</v>
       </c>
       <c r="R88" t="n">
-        <v>6553969</v>
+        <v>6553861</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11326,7 +11296,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11336,7 +11306,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11358,9 +11328,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL88" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten grov granlåga</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Kraftigt nedbruten grov granlåga</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11378,10 +11353,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121231789</v>
+        <v>121231785</v>
       </c>
       <c r="B89" t="n">
-        <v>91118</v>
+        <v>90733</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11390,25 +11365,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -11418,10 +11393,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>693670</v>
+        <v>693675</v>
       </c>
       <c r="R89" t="n">
-        <v>6553974</v>
+        <v>6553972</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11453,7 +11428,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11463,7 +11438,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11487,12 +11462,12 @@
       </c>
       <c r="AL89" t="inlineStr">
         <is>
-          <t>Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
+          <t>Äldre tall</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
+          <t>Pinus sylvestris # Äldre tall</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11510,10 +11485,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121231774</v>
+        <v>121231781</v>
       </c>
       <c r="B90" t="n">
-        <v>105164</v>
+        <v>5192</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11522,35 +11497,31 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>340</v>
+        <v>105930</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -11559,10 +11530,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>693495</v>
+        <v>693639</v>
       </c>
       <c r="R90" t="n">
-        <v>6553900</v>
+        <v>6553969</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11594,7 +11565,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11604,12 +11575,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Två av skotten hade frökapslar.</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11621,9 +11587,19 @@
       <c r="AG90" t="b">
         <v>0</v>
       </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>Sluttning med tallskog</t>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11641,10 +11617,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121231764</v>
+        <v>121231773</v>
       </c>
       <c r="B91" t="n">
-        <v>5192</v>
+        <v>98098</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11653,38 +11629,47 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>693261</v>
+        <v>693495</v>
       </c>
       <c r="R91" t="n">
-        <v>6553742</v>
+        <v>6553900</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11716,7 +11701,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11726,7 +11711,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11738,24 +11723,9 @@
       <c r="AG91" t="b">
         <v>0</v>
       </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL91" t="inlineStr">
-        <is>
-          <t>Klen gran i område med många fallna granar</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen gran i område med många fallna granar</t>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>Sluttning med tallskog</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11773,10 +11743,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121231792</v>
+        <v>121231793</v>
       </c>
       <c r="B92" t="n">
-        <v>94620</v>
+        <v>94716</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11789,24 +11759,33 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
@@ -11905,10 +11884,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121231782</v>
+        <v>121231765</v>
       </c>
       <c r="B93" t="n">
-        <v>57370</v>
+        <v>100364</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11917,43 +11896,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>693709</v>
+        <v>693309</v>
       </c>
       <c r="R93" t="n">
-        <v>6553983</v>
+        <v>6553789</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11985,7 +11959,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11995,12 +11969,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Födosökshack vid basen av stående död tall.</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12027,10 +11996,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121231794</v>
+        <v>121231771</v>
       </c>
       <c r="B94" t="n">
-        <v>94620</v>
+        <v>4775</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12043,21 +12012,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2818</v>
+        <v>102306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12067,10 +12036,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>693674</v>
+        <v>693494</v>
       </c>
       <c r="R94" t="n">
-        <v>6553897</v>
+        <v>6553917</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12102,7 +12071,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12112,7 +12081,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12136,12 +12105,12 @@
       </c>
       <c r="AL94" t="inlineStr">
         <is>
-          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+          <t>Äldre grov gran</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+          <t>Picea abies # Äldre grov gran</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12152,17 +12121,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121231765</v>
+        <v>121231764</v>
       </c>
       <c r="B95" t="n">
-        <v>100364</v>
+        <v>5192</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12175,21 +12144,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12199,10 +12168,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>693309</v>
+        <v>693261</v>
       </c>
       <c r="R95" t="n">
-        <v>6553789</v>
+        <v>6553742</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12234,7 +12203,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12244,7 +12213,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12255,6 +12224,26 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL95" t="inlineStr">
+        <is>
+          <t>Klen gran i område med många fallna granar</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen gran i område med många fallna granar</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -12271,10 +12260,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121231767</v>
+        <v>121231792</v>
       </c>
       <c r="B96" t="n">
-        <v>94716</v>
+        <v>94620</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12287,43 +12276,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>693436</v>
+        <v>693674</v>
       </c>
       <c r="R96" t="n">
-        <v>6553861</v>
+        <v>6553894</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12355,7 +12335,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12365,7 +12345,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12389,12 +12369,12 @@
       </c>
       <c r="AL96" t="inlineStr">
         <is>
-          <t>Kraftigt nedbruten grov granlåga</t>
+          <t>Kraftigt nedbruten granlåga</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftigt nedbruten grov granlåga</t>
+          <t>Picea abies # Kraftigt nedbruten granlåga</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12405,17 +12385,17 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121231762</v>
+        <v>121231794</v>
       </c>
       <c r="B97" t="n">
-        <v>110235</v>
+        <v>94620</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12428,21 +12408,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>219711</v>
+        <v>2818</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -12452,10 +12432,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>693313</v>
+        <v>693674</v>
       </c>
       <c r="R97" t="n">
-        <v>6553812</v>
+        <v>6553897</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12487,7 +12467,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12497,7 +12477,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12508,6 +12488,26 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL97" t="inlineStr">
+        <is>
+          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -12656,10 +12656,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121231786</v>
+        <v>121231768</v>
       </c>
       <c r="B99" t="n">
-        <v>94106</v>
+        <v>94716</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12672,38 +12672,43 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2362</v>
+        <v>210</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blek stjärnmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Mnium stellare</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>693670</v>
+        <v>693478</v>
       </c>
       <c r="R99" t="n">
-        <v>6553974</v>
+        <v>6553857</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12735,7 +12740,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12745,7 +12750,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12754,13 +12759,27 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL99" t="inlineStr">
+        <is>
+          <t>Granlåga i blockig sluttning</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>Vid basen av lodvägg</t>
+          <t>Picea abies # Granlåga i blockig sluttning</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -12778,10 +12797,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121231788</v>
+        <v>121231776</v>
       </c>
       <c r="B100" t="n">
-        <v>94599</v>
+        <v>94620</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12794,21 +12813,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2667</v>
+        <v>2818</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -12818,10 +12837,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>693670</v>
+        <v>693581</v>
       </c>
       <c r="R100" t="n">
-        <v>6553974</v>
+        <v>6553897</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12853,7 +12872,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12863,7 +12882,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12874,11 +12893,6 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Vid basen av lodvägg</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -12895,10 +12909,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121231776</v>
+        <v>121231786</v>
       </c>
       <c r="B101" t="n">
-        <v>94620</v>
+        <v>94106</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12911,34 +12925,38 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2818</v>
+        <v>2362</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>693581</v>
+        <v>693670</v>
       </c>
       <c r="R101" t="n">
-        <v>6553897</v>
+        <v>6553974</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12970,7 +12988,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12980,7 +12998,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12989,8 +13007,14 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Vid basen av lodvägg</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -13124,10 +13148,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121231768</v>
+        <v>121231788</v>
       </c>
       <c r="B103" t="n">
-        <v>94716</v>
+        <v>94599</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13140,43 +13164,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>210</v>
+        <v>2667</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>693478</v>
+        <v>693670</v>
       </c>
       <c r="R103" t="n">
-        <v>6553857</v>
+        <v>6553974</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13208,7 +13223,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13218,7 +13233,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13230,24 +13245,9 @@
       <c r="AG103" t="b">
         <v>0</v>
       </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL103" t="inlineStr">
-        <is>
-          <t>Granlåga i blockig sluttning</t>
-        </is>
-      </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga i blockig sluttning</t>
+          <t>Vid basen av lodvägg</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -9865,10 +9865,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121224119</v>
+        <v>121224447</v>
       </c>
       <c r="B77" t="n">
-        <v>97052</v>
+        <v>100370</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9881,21 +9881,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9909,13 +9909,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>693407</v>
+        <v>693195</v>
       </c>
       <c r="R77" t="n">
-        <v>6553843</v>
+        <v>6553768</v>
       </c>
       <c r="S77" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9981,10 +9981,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121224447</v>
+        <v>121224119</v>
       </c>
       <c r="B78" t="n">
-        <v>100364</v>
+        <v>97058</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9997,21 +9997,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10025,13 +10025,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>693195</v>
+        <v>693407</v>
       </c>
       <c r="R78" t="n">
-        <v>6553768</v>
+        <v>6553843</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10097,10 +10097,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121224002</v>
+        <v>121224726</v>
       </c>
       <c r="B79" t="n">
-        <v>5192</v>
+        <v>97058</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10113,37 +10113,41 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>105930</v>
+        <v>221945</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Sandkärr, Sandkärr, Srm</t>
+          <t>Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>693430</v>
+        <v>693312</v>
       </c>
       <c r="R79" t="n">
-        <v>6553864</v>
+        <v>6553808</v>
       </c>
       <c r="S79" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10172,7 +10176,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10182,7 +10186,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10197,22 +10201,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121224726</v>
+        <v>121221017</v>
       </c>
       <c r="B80" t="n">
-        <v>97052</v>
+        <v>57371</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10221,45 +10225,46 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Sandkärr, Srm</t>
+          <t>Kolnäsviken, Kolnäsviken, Srm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>693312</v>
+        <v>693644</v>
       </c>
       <c r="R80" t="n">
-        <v>6553808</v>
+        <v>6554031</v>
       </c>
       <c r="S80" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10288,7 +10293,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10298,7 +10303,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10313,22 +10318,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121221017</v>
+        <v>121224002</v>
       </c>
       <c r="B81" t="n">
-        <v>57370</v>
+        <v>5192</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10337,20 +10342,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -10359,24 +10364,19 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kolnäsviken, Kolnäsviken, Srm</t>
+          <t>Sandkärr, Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>693644</v>
+        <v>693430</v>
       </c>
       <c r="R81" t="n">
-        <v>6554031</v>
+        <v>6553864</v>
       </c>
       <c r="S81" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10442,10 +10442,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121231762</v>
+        <v>121231774</v>
       </c>
       <c r="B82" t="n">
-        <v>110235</v>
+        <v>105170</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10454,38 +10454,47 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219711</v>
+        <v>340</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>693313</v>
+        <v>693495</v>
       </c>
       <c r="R82" t="n">
-        <v>6553812</v>
+        <v>6553900</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10517,7 +10526,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10527,7 +10536,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Två av skotten hade frökapslar.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10538,6 +10552,11 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Sluttning med tallskog</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10557,7 +10576,7 @@
         <v>121231795</v>
       </c>
       <c r="B83" t="n">
-        <v>94716</v>
+        <v>94722</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10695,10 +10714,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121231782</v>
+        <v>121231762</v>
       </c>
       <c r="B84" t="n">
-        <v>57370</v>
+        <v>110241</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10707,43 +10726,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>693709</v>
+        <v>693313</v>
       </c>
       <c r="R84" t="n">
-        <v>6553983</v>
+        <v>6553812</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10775,7 +10789,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10785,12 +10799,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Födosökshack vid basen av stående död tall.</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10817,10 +10826,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121231789</v>
+        <v>121231793</v>
       </c>
       <c r="B85" t="n">
-        <v>91118</v>
+        <v>94722</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10833,34 +10842,43 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5420</v>
+        <v>210</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>693670</v>
+        <v>693674</v>
       </c>
       <c r="R85" t="n">
-        <v>6553974</v>
+        <v>6553894</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10892,7 +10910,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10902,7 +10920,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10916,22 +10934,22 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL85" t="inlineStr">
         <is>
-          <t>Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
+          <t>Kraftigt nedbruten granlåga</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
+          <t>Picea abies # Kraftigt nedbruten granlåga</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10942,17 +10960,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121231775</v>
+        <v>121231781</v>
       </c>
       <c r="B86" t="n">
-        <v>8435</v>
+        <v>5192</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10965,27 +10983,27 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -10994,10 +11012,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>693555</v>
+        <v>693639</v>
       </c>
       <c r="R86" t="n">
-        <v>6553905</v>
+        <v>6553969</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11029,7 +11047,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11039,7 +11057,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11053,17 +11071,17 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11081,10 +11099,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121231774</v>
+        <v>121231771</v>
       </c>
       <c r="B87" t="n">
-        <v>105164</v>
+        <v>4775</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11093,47 +11111,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>340</v>
+        <v>102306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>693495</v>
+        <v>693494</v>
       </c>
       <c r="R87" t="n">
-        <v>6553900</v>
+        <v>6553917</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11165,7 +11174,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11175,12 +11184,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Två av skotten hade frökapslar.</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11192,9 +11196,24 @@
       <c r="AG87" t="b">
         <v>0</v>
       </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>Sluttning med tallskog</t>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL87" t="inlineStr">
+        <is>
+          <t>Äldre grov gran</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grov gran</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11212,10 +11231,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121231767</v>
+        <v>121231782</v>
       </c>
       <c r="B88" t="n">
-        <v>94716</v>
+        <v>57371</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11224,35 +11243,31 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -11261,10 +11276,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>693436</v>
+        <v>693709</v>
       </c>
       <c r="R88" t="n">
-        <v>6553861</v>
+        <v>6553983</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11296,7 +11311,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11306,7 +11321,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Födosökshack vid basen av stående död tall.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11317,26 +11337,6 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL88" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten grov granlåga</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Picea abies # Kraftigt nedbruten grov granlåga</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -11353,10 +11353,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121231785</v>
+        <v>121231765</v>
       </c>
       <c r="B89" t="n">
-        <v>90733</v>
+        <v>100370</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11365,25 +11365,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>693675</v>
+        <v>693309</v>
       </c>
       <c r="R89" t="n">
-        <v>6553972</v>
+        <v>6553789</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11428,7 +11428,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11449,26 +11449,6 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL89" t="inlineStr">
-        <is>
-          <t>Äldre tall</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Äldre tall</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -11485,10 +11465,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121231781</v>
+        <v>121231767</v>
       </c>
       <c r="B90" t="n">
-        <v>5192</v>
+        <v>94722</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11501,27 +11481,31 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>105930</v>
+        <v>210</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -11530,10 +11514,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>693639</v>
+        <v>693436</v>
       </c>
       <c r="R90" t="n">
-        <v>6553969</v>
+        <v>6553861</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11565,7 +11549,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11575,7 +11559,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11597,9 +11581,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL90" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten grov granlåga</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Kraftigt nedbruten grov granlåga</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11617,10 +11606,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121231773</v>
+        <v>121231775</v>
       </c>
       <c r="B91" t="n">
-        <v>98098</v>
+        <v>8435</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11629,35 +11618,31 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -11666,10 +11651,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>693495</v>
+        <v>693555</v>
       </c>
       <c r="R91" t="n">
-        <v>6553900</v>
+        <v>6553905</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11701,7 +11686,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11711,7 +11696,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11723,9 +11708,19 @@
       <c r="AG91" t="b">
         <v>0</v>
       </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>Sluttning med tallskog</t>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11743,10 +11738,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121231793</v>
+        <v>121231764</v>
       </c>
       <c r="B92" t="n">
-        <v>94716</v>
+        <v>5192</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11759,43 +11754,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>210</v>
+        <v>105930</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>693674</v>
+        <v>693261</v>
       </c>
       <c r="R92" t="n">
-        <v>6553894</v>
+        <v>6553742</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11827,7 +11813,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11837,7 +11823,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11861,12 +11847,12 @@
       </c>
       <c r="AL92" t="inlineStr">
         <is>
-          <t>Kraftigt nedbruten granlåga</t>
+          <t>Klen gran i område med många fallna granar</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftigt nedbruten granlåga</t>
+          <t>Picea abies # Klen gran i område med många fallna granar</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11877,17 +11863,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121231765</v>
+        <v>121231785</v>
       </c>
       <c r="B93" t="n">
-        <v>100364</v>
+        <v>90739</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11896,25 +11882,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11924,10 +11910,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>693309</v>
+        <v>693675</v>
       </c>
       <c r="R93" t="n">
-        <v>6553789</v>
+        <v>6553972</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11959,7 +11945,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11969,7 +11955,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11980,6 +11966,26 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL93" t="inlineStr">
+        <is>
+          <t>Äldre tall</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Äldre tall</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11996,10 +12002,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121231771</v>
+        <v>121231789</v>
       </c>
       <c r="B94" t="n">
-        <v>4775</v>
+        <v>91124</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12012,21 +12018,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>102306</v>
+        <v>5420</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12036,10 +12042,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>693494</v>
+        <v>693670</v>
       </c>
       <c r="R94" t="n">
-        <v>6553917</v>
+        <v>6553974</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12071,7 +12077,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12081,7 +12087,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12095,22 +12101,22 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL94" t="inlineStr">
         <is>
-          <t>Äldre grov gran</t>
+          <t>Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grov gran</t>
+          <t>Pinus sylvestris # Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12128,10 +12134,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121231764</v>
+        <v>121231773</v>
       </c>
       <c r="B95" t="n">
-        <v>5192</v>
+        <v>98104</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12140,38 +12146,47 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>693261</v>
+        <v>693495</v>
       </c>
       <c r="R95" t="n">
-        <v>6553742</v>
+        <v>6553900</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12203,7 +12218,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12213,7 +12228,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12225,24 +12240,9 @@
       <c r="AG95" t="b">
         <v>0</v>
       </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL95" t="inlineStr">
-        <is>
-          <t>Klen gran i område med många fallna granar</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen gran i område med många fallna granar</t>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>Sluttning med tallskog</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12260,10 +12260,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121231792</v>
+        <v>121231794</v>
       </c>
       <c r="B96" t="n">
-        <v>94620</v>
+        <v>94626</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>693674</v>
       </c>
       <c r="R96" t="n">
-        <v>6553894</v>
+        <v>6553897</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12335,7 +12335,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12345,7 +12345,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12369,12 +12369,12 @@
       </c>
       <c r="AL96" t="inlineStr">
         <is>
-          <t>Kraftigt nedbruten granlåga</t>
+          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftigt nedbruten granlåga</t>
+          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12392,10 +12392,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121231794</v>
+        <v>121231792</v>
       </c>
       <c r="B97" t="n">
-        <v>94620</v>
+        <v>94626</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>693674</v>
       </c>
       <c r="R97" t="n">
-        <v>6553897</v>
+        <v>6553894</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12467,7 +12467,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+          <t>Kraftigt nedbruten granlåga</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+          <t>Picea abies # Kraftigt nedbruten granlåga</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -12527,7 +12527,7 @@
         <v>121231766</v>
       </c>
       <c r="B98" t="n">
-        <v>94620</v>
+        <v>94626</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>121231768</v>
       </c>
       <c r="B99" t="n">
-        <v>94716</v>
+        <v>94722</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12797,10 +12797,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121231776</v>
+        <v>121231788</v>
       </c>
       <c r="B100" t="n">
-        <v>94620</v>
+        <v>94605</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12813,21 +12813,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2818</v>
+        <v>2667</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -12837,10 +12837,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>693581</v>
+        <v>693670</v>
       </c>
       <c r="R100" t="n">
-        <v>6553897</v>
+        <v>6553974</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12872,7 +12872,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12893,6 +12893,11 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Vid basen av lodvägg</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -12909,10 +12914,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121231786</v>
+        <v>121231787</v>
       </c>
       <c r="B101" t="n">
-        <v>94106</v>
+        <v>94399</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12925,28 +12930,24 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2362</v>
+        <v>2779</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blek stjärnmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Mnium stellare</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
@@ -13007,7 +13008,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -13031,10 +13031,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121231787</v>
+        <v>121231776</v>
       </c>
       <c r="B102" t="n">
-        <v>94393</v>
+        <v>94626</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13047,21 +13047,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2779</v>
+        <v>2818</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -13071,10 +13071,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>693670</v>
+        <v>693581</v>
       </c>
       <c r="R102" t="n">
-        <v>6553974</v>
+        <v>6553897</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13106,7 +13106,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13127,11 +13127,6 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Vid basen av lodvägg</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -13148,10 +13143,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121231788</v>
+        <v>121231786</v>
       </c>
       <c r="B103" t="n">
-        <v>94599</v>
+        <v>94112</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13164,24 +13159,28 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2667</v>
+        <v>2362</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
@@ -13242,6 +13241,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -13268,7 +13268,7 @@
         <v>121330721</v>
       </c>
       <c r="B104" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>121231778</v>
       </c>
       <c r="B105" t="n">
-        <v>95684</v>
+        <v>95690</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
         <v>121231770</v>
       </c>
       <c r="B106" t="n">
-        <v>95961</v>
+        <v>95967</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -9744,10 +9744,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121222341</v>
+        <v>121224119</v>
       </c>
       <c r="B76" t="n">
-        <v>8424</v>
+        <v>97059</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9760,43 +9760,38 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Breviksnäs, Srm</t>
+          <t>Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>693587</v>
+        <v>693407</v>
       </c>
       <c r="R76" t="n">
-        <v>6553902</v>
+        <v>6553843</v>
       </c>
       <c r="S76" t="n">
         <v>13</v>
@@ -9828,7 +9823,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9838,7 +9833,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9865,10 +9860,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121224447</v>
+        <v>121224002</v>
       </c>
       <c r="B77" t="n">
-        <v>100370</v>
+        <v>5192</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9881,41 +9876,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sandkärr, Srm</t>
+          <t>Sandkärr, Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>693195</v>
+        <v>693430</v>
       </c>
       <c r="R77" t="n">
-        <v>6553768</v>
+        <v>6553864</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9944,7 +9935,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9954,7 +9945,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9969,22 +9960,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121224119</v>
+        <v>121222341</v>
       </c>
       <c r="B78" t="n">
-        <v>97058</v>
+        <v>8424</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9997,38 +9988,43 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>106554</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sandkärr, Srm</t>
+          <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>693407</v>
+        <v>693587</v>
       </c>
       <c r="R78" t="n">
-        <v>6553843</v>
+        <v>6553902</v>
       </c>
       <c r="S78" t="n">
         <v>13</v>
@@ -10060,7 +10056,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10070,7 +10066,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10097,10 +10093,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121224726</v>
+        <v>121224447</v>
       </c>
       <c r="B79" t="n">
-        <v>97058</v>
+        <v>100371</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10113,21 +10109,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10141,13 +10137,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>693312</v>
+        <v>693195</v>
       </c>
       <c r="R79" t="n">
-        <v>6553808</v>
+        <v>6553768</v>
       </c>
       <c r="S79" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10176,7 +10172,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10186,7 +10182,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10216,7 +10212,7 @@
         <v>121221017</v>
       </c>
       <c r="B80" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10330,10 +10326,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121224002</v>
+        <v>121224726</v>
       </c>
       <c r="B81" t="n">
-        <v>5192</v>
+        <v>97059</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10346,37 +10342,41 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>105930</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sandkärr, Sandkärr, Srm</t>
+          <t>Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>693430</v>
+        <v>693312</v>
       </c>
       <c r="R81" t="n">
-        <v>6553864</v>
+        <v>6553808</v>
       </c>
       <c r="S81" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10430,22 +10430,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121231774</v>
+        <v>121231773</v>
       </c>
       <c r="B82" t="n">
-        <v>105170</v>
+        <v>98105</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10454,35 +10454,35 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>340</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -10537,11 +10537,6 @@
       <c r="AB82" t="inlineStr">
         <is>
           <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Två av skotten hade frökapslar.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10573,10 +10568,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121231795</v>
+        <v>121231793</v>
       </c>
       <c r="B83" t="n">
-        <v>94722</v>
+        <v>94723</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10608,7 +10603,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10625,7 +10620,7 @@
         <v>693674</v>
       </c>
       <c r="R83" t="n">
-        <v>6553897</v>
+        <v>6553894</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10657,7 +10652,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10667,7 +10662,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10691,12 +10686,12 @@
       </c>
       <c r="AL83" t="inlineStr">
         <is>
-          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+          <t>Kraftigt nedbruten granlåga</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+          <t>Picea abies # Kraftigt nedbruten granlåga</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10714,10 +10709,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121231762</v>
+        <v>121231794</v>
       </c>
       <c r="B84" t="n">
-        <v>110241</v>
+        <v>94627</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10730,21 +10725,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>219711</v>
+        <v>2818</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10754,10 +10749,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>693313</v>
+        <v>693674</v>
       </c>
       <c r="R84" t="n">
-        <v>6553812</v>
+        <v>6553897</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10789,7 +10784,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10799,7 +10794,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10810,6 +10805,26 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL84" t="inlineStr">
+        <is>
+          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10819,17 +10834,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121231793</v>
+        <v>121231792</v>
       </c>
       <c r="B85" t="n">
-        <v>94722</v>
+        <v>94627</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10842,33 +10857,24 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
@@ -10967,10 +10973,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121231781</v>
+        <v>121231775</v>
       </c>
       <c r="B86" t="n">
-        <v>5192</v>
+        <v>8435</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10983,27 +10989,27 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -11012,10 +11018,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>693639</v>
+        <v>693555</v>
       </c>
       <c r="R86" t="n">
-        <v>6553969</v>
+        <v>6553905</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11047,7 +11053,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11057,7 +11063,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11071,17 +11077,17 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11099,10 +11105,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121231771</v>
+        <v>121231789</v>
       </c>
       <c r="B87" t="n">
-        <v>4775</v>
+        <v>91125</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11115,21 +11121,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>102306</v>
+        <v>5420</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -11139,10 +11145,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>693494</v>
+        <v>693670</v>
       </c>
       <c r="R87" t="n">
-        <v>6553917</v>
+        <v>6553974</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11174,7 +11180,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11184,7 +11190,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11198,22 +11204,22 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>Äldre grov gran</t>
+          <t>Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grov gran</t>
+          <t>Pinus sylvestris # Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11231,10 +11237,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121231782</v>
+        <v>121231774</v>
       </c>
       <c r="B88" t="n">
-        <v>57371</v>
+        <v>105171</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11243,31 +11249,35 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>340</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -11276,10 +11286,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>693709</v>
+        <v>693495</v>
       </c>
       <c r="R88" t="n">
-        <v>6553983</v>
+        <v>6553900</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11311,7 +11321,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11321,12 +11331,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Födosökshack vid basen av stående död tall.</t>
+          <t>Två av skotten hade frökapslar.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11337,6 +11347,11 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>Sluttning med tallskog</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -11353,10 +11368,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121231765</v>
+        <v>121231767</v>
       </c>
       <c r="B89" t="n">
-        <v>100370</v>
+        <v>94723</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11369,34 +11384,43 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>693309</v>
+        <v>693436</v>
       </c>
       <c r="R89" t="n">
-        <v>6553789</v>
+        <v>6553861</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11428,7 +11452,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11438,7 +11462,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11449,6 +11473,26 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL89" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten grov granlåga</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Picea abies # Kraftigt nedbruten grov granlåga</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -11465,10 +11509,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121231767</v>
+        <v>121231781</v>
       </c>
       <c r="B90" t="n">
-        <v>94722</v>
+        <v>5192</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11481,31 +11525,27 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>210</v>
+        <v>105930</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -11514,10 +11554,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>693436</v>
+        <v>693639</v>
       </c>
       <c r="R90" t="n">
-        <v>6553861</v>
+        <v>6553969</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11549,7 +11589,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11559,7 +11599,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11581,14 +11621,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL90" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten grov granlåga</t>
-        </is>
-      </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftigt nedbruten grov granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11606,10 +11641,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121231775</v>
+        <v>121231765</v>
       </c>
       <c r="B91" t="n">
-        <v>8435</v>
+        <v>100371</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11622,39 +11657,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>106545</v>
+        <v>222498</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>693555</v>
+        <v>693309</v>
       </c>
       <c r="R91" t="n">
-        <v>6553905</v>
+        <v>6553789</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11686,7 +11716,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11696,7 +11726,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11707,21 +11737,6 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -11738,10 +11753,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121231764</v>
+        <v>121231762</v>
       </c>
       <c r="B92" t="n">
-        <v>5192</v>
+        <v>110242</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11754,21 +11769,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>105930</v>
+        <v>219711</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11778,10 +11793,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>693261</v>
+        <v>693313</v>
       </c>
       <c r="R92" t="n">
-        <v>6553742</v>
+        <v>6553812</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11813,7 +11828,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11823,7 +11838,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11834,26 +11849,6 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL92" t="inlineStr">
-        <is>
-          <t>Klen gran i område med många fallna granar</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen gran i område med många fallna granar</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -11870,10 +11865,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121231785</v>
+        <v>121231771</v>
       </c>
       <c r="B93" t="n">
-        <v>90739</v>
+        <v>4775</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11882,25 +11877,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11910,10 +11905,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>693675</v>
+        <v>693494</v>
       </c>
       <c r="R93" t="n">
-        <v>6553972</v>
+        <v>6553917</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11945,7 +11940,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11955,7 +11950,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11969,22 +11964,22 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL93" t="inlineStr">
         <is>
-          <t>Äldre tall</t>
+          <t>Äldre grov gran</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Äldre tall</t>
+          <t>Picea abies # Äldre grov gran</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12002,10 +11997,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121231789</v>
+        <v>121231785</v>
       </c>
       <c r="B94" t="n">
-        <v>91124</v>
+        <v>90740</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12014,25 +12009,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12042,10 +12037,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>693670</v>
+        <v>693675</v>
       </c>
       <c r="R94" t="n">
-        <v>6553974</v>
+        <v>6553972</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12077,7 +12072,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12087,7 +12082,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12111,12 +12106,12 @@
       </c>
       <c r="AL94" t="inlineStr">
         <is>
-          <t>Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
+          <t>Äldre tall</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
+          <t>Pinus sylvestris # Äldre tall</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12134,10 +12129,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121231773</v>
+        <v>121231782</v>
       </c>
       <c r="B95" t="n">
-        <v>98104</v>
+        <v>57372</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12146,35 +12141,31 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -12183,10 +12174,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>693495</v>
+        <v>693709</v>
       </c>
       <c r="R95" t="n">
-        <v>6553900</v>
+        <v>6553983</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12218,7 +12209,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12228,7 +12219,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Födosökshack vid basen av stående död tall.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12239,11 +12235,6 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>Sluttning med tallskog</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -12260,10 +12251,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121231794</v>
+        <v>121231764</v>
       </c>
       <c r="B96" t="n">
-        <v>94626</v>
+        <v>5192</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12276,21 +12267,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2818</v>
+        <v>105930</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -12300,10 +12291,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>693674</v>
+        <v>693261</v>
       </c>
       <c r="R96" t="n">
-        <v>6553897</v>
+        <v>6553742</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12335,7 +12326,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12345,7 +12336,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12369,12 +12360,12 @@
       </c>
       <c r="AL96" t="inlineStr">
         <is>
-          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+          <t>Klen gran i område med många fallna granar</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+          <t>Picea abies # Klen gran i område med många fallna granar</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12385,17 +12376,17 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121231792</v>
+        <v>121231795</v>
       </c>
       <c r="B97" t="n">
-        <v>94626</v>
+        <v>94723</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12408,24 +12399,33 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
@@ -12435,7 +12435,7 @@
         <v>693674</v>
       </c>
       <c r="R97" t="n">
-        <v>6553894</v>
+        <v>6553897</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12467,7 +12467,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>Kraftigt nedbruten granlåga</t>
+          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftigt nedbruten granlåga</t>
+          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -12527,7 +12527,7 @@
         <v>121231766</v>
       </c>
       <c r="B98" t="n">
-        <v>94626</v>
+        <v>94627</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12656,10 +12656,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121231768</v>
+        <v>121231786</v>
       </c>
       <c r="B99" t="n">
-        <v>94722</v>
+        <v>94113</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12672,43 +12672,38 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>210</v>
+        <v>2362</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>693478</v>
+        <v>693670</v>
       </c>
       <c r="R99" t="n">
-        <v>6553857</v>
+        <v>6553974</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12740,7 +12735,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12750,7 +12745,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12759,27 +12754,13 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL99" t="inlineStr">
-        <is>
-          <t>Granlåga i blockig sluttning</t>
-        </is>
-      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga i blockig sluttning</t>
+          <t>Vid basen av lodvägg</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -12797,10 +12778,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121231788</v>
+        <v>121231787</v>
       </c>
       <c r="B100" t="n">
-        <v>94605</v>
+        <v>94400</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12813,21 +12794,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -12914,10 +12895,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121231787</v>
+        <v>121231768</v>
       </c>
       <c r="B101" t="n">
-        <v>94399</v>
+        <v>94723</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12930,34 +12911,43 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2779</v>
+        <v>210</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>693670</v>
+        <v>693478</v>
       </c>
       <c r="R101" t="n">
-        <v>6553974</v>
+        <v>6553857</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12989,7 +12979,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12999,7 +12989,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13011,9 +13001,24 @@
       <c r="AG101" t="b">
         <v>0</v>
       </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL101" t="inlineStr">
+        <is>
+          <t>Granlåga i blockig sluttning</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Vid basen av lodvägg</t>
+          <t>Picea abies # Granlåga i blockig sluttning</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13031,10 +13036,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121231776</v>
+        <v>121231788</v>
       </c>
       <c r="B102" t="n">
-        <v>94626</v>
+        <v>94606</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13047,21 +13052,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2818</v>
+        <v>2667</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -13071,10 +13076,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>693581</v>
+        <v>693670</v>
       </c>
       <c r="R102" t="n">
-        <v>6553897</v>
+        <v>6553974</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13106,7 +13111,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13116,7 +13121,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13127,6 +13132,11 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Vid basen av lodvägg</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -13143,10 +13153,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121231786</v>
+        <v>121231776</v>
       </c>
       <c r="B103" t="n">
-        <v>94112</v>
+        <v>94627</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13159,38 +13169,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2362</v>
+        <v>2818</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Blek stjärnmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Mnium stellare</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>693670</v>
+        <v>693581</v>
       </c>
       <c r="R103" t="n">
-        <v>6553974</v>
+        <v>6553897</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13222,7 +13228,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13232,7 +13238,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13241,14 +13247,8 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Vid basen av lodvägg</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -13268,7 +13268,7 @@
         <v>121330721</v>
       </c>
       <c r="B104" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>121231778</v>
       </c>
       <c r="B105" t="n">
-        <v>95690</v>
+        <v>95691</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
         <v>121231770</v>
       </c>
       <c r="B106" t="n">
-        <v>95967</v>
+        <v>95968</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -9744,7 +9744,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121224119</v>
+        <v>121224726</v>
       </c>
       <c r="B76" t="n">
         <v>97059</v>
@@ -9788,10 +9788,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>693407</v>
+        <v>693312</v>
       </c>
       <c r="R76" t="n">
-        <v>6553843</v>
+        <v>6553808</v>
       </c>
       <c r="S76" t="n">
         <v>13</v>
@@ -9823,7 +9823,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9860,10 +9860,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121224002</v>
+        <v>121224447</v>
       </c>
       <c r="B77" t="n">
-        <v>5192</v>
+        <v>100371</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9876,37 +9876,41 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sandkärr, Sandkärr, Srm</t>
+          <t>Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>693430</v>
+        <v>693195</v>
       </c>
       <c r="R77" t="n">
-        <v>6553864</v>
+        <v>6553768</v>
       </c>
       <c r="S77" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9935,7 +9939,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9945,7 +9949,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9960,22 +9964,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121222341</v>
+        <v>121224002</v>
       </c>
       <c r="B78" t="n">
-        <v>8424</v>
+        <v>5192</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9988,46 +9992,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Breviksnäs, Srm</t>
+          <t>Sandkärr, Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>693587</v>
+        <v>693430</v>
       </c>
       <c r="R78" t="n">
-        <v>6553902</v>
+        <v>6553864</v>
       </c>
       <c r="S78" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10056,7 +10051,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10066,7 +10061,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10081,22 +10076,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121224447</v>
+        <v>121222341</v>
       </c>
       <c r="B79" t="n">
-        <v>100371</v>
+        <v>8424</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10109,41 +10104,46 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Sandkärr, Srm</t>
+          <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>693195</v>
+        <v>693587</v>
       </c>
       <c r="R79" t="n">
-        <v>6553768</v>
+        <v>6553902</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10209,10 +10209,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121221017</v>
+        <v>121224119</v>
       </c>
       <c r="B80" t="n">
-        <v>57372</v>
+        <v>97059</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10221,46 +10221,45 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kolnäsviken, Kolnäsviken, Srm</t>
+          <t>Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>693644</v>
+        <v>693407</v>
       </c>
       <c r="R80" t="n">
-        <v>6554031</v>
+        <v>6553843</v>
       </c>
       <c r="S80" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10289,7 +10288,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10299,7 +10298,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10314,22 +10313,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121224726</v>
+        <v>121221017</v>
       </c>
       <c r="B81" t="n">
-        <v>97059</v>
+        <v>57372</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10338,45 +10337,46 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sandkärr, Srm</t>
+          <t>Kolnäsviken, Kolnäsviken, Srm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>693312</v>
+        <v>693644</v>
       </c>
       <c r="R81" t="n">
-        <v>6553808</v>
+        <v>6554031</v>
       </c>
       <c r="S81" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10430,22 +10430,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121231773</v>
+        <v>121231781</v>
       </c>
       <c r="B82" t="n">
-        <v>98105</v>
+        <v>5192</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10454,35 +10454,31 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -10491,10 +10487,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>693495</v>
+        <v>693639</v>
       </c>
       <c r="R82" t="n">
-        <v>6553900</v>
+        <v>6553969</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10526,7 +10522,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10536,7 +10532,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10548,9 +10544,19 @@
       <c r="AG82" t="b">
         <v>0</v>
       </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>Sluttning med tallskog</t>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10568,10 +10574,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121231793</v>
+        <v>121231785</v>
       </c>
       <c r="B83" t="n">
-        <v>94723</v>
+        <v>90740</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10580,47 +10586,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>210</v>
+        <v>5442</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>693674</v>
+        <v>693675</v>
       </c>
       <c r="R83" t="n">
-        <v>6553894</v>
+        <v>6553972</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10652,7 +10649,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10662,7 +10659,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10676,22 +10673,22 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL83" t="inlineStr">
         <is>
-          <t>Kraftigt nedbruten granlåga</t>
+          <t>Äldre tall</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftigt nedbruten granlåga</t>
+          <t>Pinus sylvestris # Äldre tall</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10702,17 +10699,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121231794</v>
+        <v>121231774</v>
       </c>
       <c r="B84" t="n">
-        <v>94627</v>
+        <v>105171</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10721,38 +10718,47 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2818</v>
+        <v>340</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>693674</v>
+        <v>693495</v>
       </c>
       <c r="R84" t="n">
-        <v>6553897</v>
+        <v>6553900</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10784,7 +10790,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10794,7 +10800,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Två av skotten hade frökapslar.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10806,24 +10817,9 @@
       <c r="AG84" t="b">
         <v>0</v>
       </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL84" t="inlineStr">
-        <is>
-          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>Sluttning med tallskog</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10834,17 +10830,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121231792</v>
+        <v>121231793</v>
       </c>
       <c r="B85" t="n">
-        <v>94627</v>
+        <v>94723</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10857,24 +10853,33 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
@@ -11105,10 +11110,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121231789</v>
+        <v>121231794</v>
       </c>
       <c r="B87" t="n">
-        <v>91125</v>
+        <v>94627</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11121,21 +11126,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5420</v>
+        <v>2818</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -11145,10 +11150,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>693670</v>
+        <v>693674</v>
       </c>
       <c r="R87" t="n">
-        <v>6553974</v>
+        <v>6553897</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11180,7 +11185,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11190,7 +11195,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11204,22 +11209,22 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
+          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
+          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11230,17 +11235,17 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121231774</v>
+        <v>121231789</v>
       </c>
       <c r="B88" t="n">
-        <v>105171</v>
+        <v>91125</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11249,47 +11254,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>340</v>
+        <v>5420</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>693495</v>
+        <v>693670</v>
       </c>
       <c r="R88" t="n">
-        <v>6553900</v>
+        <v>6553974</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11321,7 +11317,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11331,12 +11327,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Två av skotten hade frökapslar.</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11348,9 +11339,24 @@
       <c r="AG88" t="b">
         <v>0</v>
       </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>Sluttning med tallskog</t>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL88" t="inlineStr">
+        <is>
+          <t>Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11368,10 +11374,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121231767</v>
+        <v>121231771</v>
       </c>
       <c r="B89" t="n">
-        <v>94723</v>
+        <v>4775</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11384,43 +11390,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>210</v>
+        <v>102306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>693436</v>
+        <v>693494</v>
       </c>
       <c r="R89" t="n">
-        <v>6553861</v>
+        <v>6553917</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11452,7 +11449,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11462,7 +11459,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11486,12 +11483,12 @@
       </c>
       <c r="AL89" t="inlineStr">
         <is>
-          <t>Kraftigt nedbruten grov granlåga</t>
+          <t>Äldre grov gran</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftigt nedbruten grov granlåga</t>
+          <t>Picea abies # Äldre grov gran</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11509,10 +11506,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121231781</v>
+        <v>121231795</v>
       </c>
       <c r="B90" t="n">
-        <v>5192</v>
+        <v>94723</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11525,27 +11522,31 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>105930</v>
+        <v>210</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -11554,10 +11555,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>693639</v>
+        <v>693674</v>
       </c>
       <c r="R90" t="n">
-        <v>6553969</v>
+        <v>6553897</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11589,7 +11590,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11599,7 +11600,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11621,9 +11622,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL90" t="inlineStr">
+        <is>
+          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11634,7 +11640,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -11753,10 +11759,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121231762</v>
+        <v>121231782</v>
       </c>
       <c r="B92" t="n">
-        <v>110242</v>
+        <v>57372</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11765,38 +11771,43 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>693313</v>
+        <v>693709</v>
       </c>
       <c r="R92" t="n">
-        <v>6553812</v>
+        <v>6553983</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11828,7 +11839,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11838,7 +11849,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Födosökshack vid basen av stående död tall.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11865,10 +11881,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121231771</v>
+        <v>121231764</v>
       </c>
       <c r="B93" t="n">
-        <v>4775</v>
+        <v>5192</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11881,21 +11897,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11905,10 +11921,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>693494</v>
+        <v>693261</v>
       </c>
       <c r="R93" t="n">
-        <v>6553917</v>
+        <v>6553742</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11940,7 +11956,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11950,7 +11966,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11974,12 +11990,12 @@
       </c>
       <c r="AL93" t="inlineStr">
         <is>
-          <t>Äldre grov gran</t>
+          <t>Klen gran i område med många fallna granar</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grov gran</t>
+          <t>Picea abies # Klen gran i område med många fallna granar</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11997,10 +12013,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121231785</v>
+        <v>121231792</v>
       </c>
       <c r="B94" t="n">
-        <v>90740</v>
+        <v>94627</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12009,25 +12025,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5442</v>
+        <v>2818</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12037,10 +12053,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>693675</v>
+        <v>693674</v>
       </c>
       <c r="R94" t="n">
-        <v>6553972</v>
+        <v>6553894</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12072,7 +12088,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12082,7 +12098,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12096,22 +12112,22 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL94" t="inlineStr">
         <is>
-          <t>Äldre tall</t>
+          <t>Kraftigt nedbruten granlåga</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Äldre tall</t>
+          <t>Picea abies # Kraftigt nedbruten granlåga</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12122,17 +12138,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121231782</v>
+        <v>121231773</v>
       </c>
       <c r="B95" t="n">
-        <v>57372</v>
+        <v>98105</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12141,31 +12157,35 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -12174,10 +12194,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>693709</v>
+        <v>693495</v>
       </c>
       <c r="R95" t="n">
-        <v>6553983</v>
+        <v>6553900</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12209,7 +12229,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12219,12 +12239,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Födosökshack vid basen av stående död tall.</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12235,6 +12250,11 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>Sluttning med tallskog</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -12251,10 +12271,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121231764</v>
+        <v>121231767</v>
       </c>
       <c r="B96" t="n">
-        <v>5192</v>
+        <v>94723</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12267,34 +12287,43 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>105930</v>
+        <v>210</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>693261</v>
+        <v>693436</v>
       </c>
       <c r="R96" t="n">
-        <v>6553742</v>
+        <v>6553861</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12326,7 +12355,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12336,7 +12365,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12360,12 +12389,12 @@
       </c>
       <c r="AL96" t="inlineStr">
         <is>
-          <t>Klen gran i område med många fallna granar</t>
+          <t>Kraftigt nedbruten grov granlåga</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>Picea abies # Klen gran i område med många fallna granar</t>
+          <t>Picea abies # Kraftigt nedbruten grov granlåga</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12383,10 +12412,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121231795</v>
+        <v>121231762</v>
       </c>
       <c r="B97" t="n">
-        <v>94723</v>
+        <v>110242</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12399,43 +12428,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>210</v>
+        <v>219711</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>693674</v>
+        <v>693313</v>
       </c>
       <c r="R97" t="n">
-        <v>6553897</v>
+        <v>6553812</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12467,7 +12487,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12477,7 +12497,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12488,26 +12508,6 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL97" t="inlineStr">
-        <is>
-          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -12656,10 +12656,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121231786</v>
+        <v>121231788</v>
       </c>
       <c r="B99" t="n">
-        <v>94113</v>
+        <v>94606</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12672,28 +12672,24 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2362</v>
+        <v>2667</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blek stjärnmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Mnium stellare</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
@@ -12754,7 +12750,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -12778,10 +12773,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121231787</v>
+        <v>121231776</v>
       </c>
       <c r="B100" t="n">
-        <v>94400</v>
+        <v>94627</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12794,21 +12789,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2779</v>
+        <v>2818</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -12818,10 +12813,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>693670</v>
+        <v>693581</v>
       </c>
       <c r="R100" t="n">
-        <v>6553974</v>
+        <v>6553897</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12853,7 +12848,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12863,7 +12858,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12874,11 +12869,6 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Vid basen av lodvägg</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -12895,10 +12885,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121231768</v>
+        <v>121231786</v>
       </c>
       <c r="B101" t="n">
-        <v>94723</v>
+        <v>94113</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12911,43 +12901,38 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>210</v>
+        <v>2362</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>693478</v>
+        <v>693670</v>
       </c>
       <c r="R101" t="n">
-        <v>6553857</v>
+        <v>6553974</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12979,7 +12964,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12989,7 +12974,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12998,27 +12983,13 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL101" t="inlineStr">
-        <is>
-          <t>Granlåga i blockig sluttning</t>
-        </is>
-      </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga i blockig sluttning</t>
+          <t>Vid basen av lodvägg</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13036,10 +13007,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121231788</v>
+        <v>121231768</v>
       </c>
       <c r="B102" t="n">
-        <v>94606</v>
+        <v>94723</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13052,34 +13023,43 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2667</v>
+        <v>210</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>693670</v>
+        <v>693478</v>
       </c>
       <c r="R102" t="n">
-        <v>6553974</v>
+        <v>6553857</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13111,7 +13091,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13121,7 +13101,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13133,9 +13113,24 @@
       <c r="AG102" t="b">
         <v>0</v>
       </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL102" t="inlineStr">
+        <is>
+          <t>Granlåga i blockig sluttning</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Vid basen av lodvägg</t>
+          <t>Picea abies # Granlåga i blockig sluttning</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13153,10 +13148,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121231776</v>
+        <v>121231787</v>
       </c>
       <c r="B103" t="n">
-        <v>94627</v>
+        <v>94400</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13169,21 +13164,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2818</v>
+        <v>2779</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -13193,10 +13188,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>693581</v>
+        <v>693670</v>
       </c>
       <c r="R103" t="n">
-        <v>6553897</v>
+        <v>6553974</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13228,7 +13223,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13238,7 +13233,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13249,6 +13244,11 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Vid basen av lodvägg</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -9744,10 +9744,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121224726</v>
+        <v>121224002</v>
       </c>
       <c r="B76" t="n">
-        <v>97059</v>
+        <v>5192</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9760,41 +9760,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221945</v>
+        <v>105930</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Sandkärr, Srm</t>
+          <t>Sandkärr, Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>693312</v>
+        <v>693430</v>
       </c>
       <c r="R76" t="n">
-        <v>6553808</v>
+        <v>6553864</v>
       </c>
       <c r="S76" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9823,7 +9819,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9833,7 +9829,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9848,22 +9844,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121224447</v>
+        <v>121224119</v>
       </c>
       <c r="B77" t="n">
-        <v>100371</v>
+        <v>97059</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9876,21 +9872,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9904,13 +9900,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>693195</v>
+        <v>693407</v>
       </c>
       <c r="R77" t="n">
-        <v>6553768</v>
+        <v>6553843</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9939,7 +9935,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9949,7 +9945,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9976,10 +9972,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121224002</v>
+        <v>121224726</v>
       </c>
       <c r="B78" t="n">
-        <v>5192</v>
+        <v>97059</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9992,37 +9988,41 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>105930</v>
+        <v>221945</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sandkärr, Sandkärr, Srm</t>
+          <t>Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>693430</v>
+        <v>693312</v>
       </c>
       <c r="R78" t="n">
-        <v>6553864</v>
+        <v>6553808</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10076,22 +10076,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121222341</v>
+        <v>121221017</v>
       </c>
       <c r="B79" t="n">
-        <v>8424</v>
+        <v>57372</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10100,50 +10100,46 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Breviksnäs, Srm</t>
+          <t>Kolnäsviken, Kolnäsviken, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>693587</v>
+        <v>693644</v>
       </c>
       <c r="R79" t="n">
-        <v>6553902</v>
+        <v>6554031</v>
       </c>
       <c r="S79" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10172,7 +10168,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10182,7 +10178,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10197,22 +10193,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121224119</v>
+        <v>121222341</v>
       </c>
       <c r="B80" t="n">
-        <v>97059</v>
+        <v>8424</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10225,38 +10221,43 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>106554</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Sandkärr, Srm</t>
+          <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>693407</v>
+        <v>693587</v>
       </c>
       <c r="R80" t="n">
-        <v>6553843</v>
+        <v>6553902</v>
       </c>
       <c r="S80" t="n">
         <v>13</v>
@@ -10288,7 +10289,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10298,7 +10299,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10325,10 +10326,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121221017</v>
+        <v>121224447</v>
       </c>
       <c r="B81" t="n">
-        <v>57372</v>
+        <v>100371</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10337,46 +10338,45 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kolnäsviken, Kolnäsviken, Srm</t>
+          <t>Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>693644</v>
+        <v>693195</v>
       </c>
       <c r="R81" t="n">
-        <v>6554031</v>
+        <v>6553768</v>
       </c>
       <c r="S81" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10430,22 +10430,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121231781</v>
+        <v>121231792</v>
       </c>
       <c r="B82" t="n">
-        <v>5192</v>
+        <v>94627</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10458,39 +10458,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>105930</v>
+        <v>2818</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>693639</v>
+        <v>693674</v>
       </c>
       <c r="R82" t="n">
-        <v>6553969</v>
+        <v>6553894</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10522,7 +10517,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10532,7 +10527,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10554,9 +10549,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL82" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten granlåga</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Kraftigt nedbruten granlåga</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10567,17 +10567,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121231785</v>
+        <v>121231789</v>
       </c>
       <c r="B83" t="n">
-        <v>90740</v>
+        <v>91125</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10586,25 +10586,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10614,10 +10614,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>693675</v>
+        <v>693670</v>
       </c>
       <c r="R83" t="n">
-        <v>6553972</v>
+        <v>6553974</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10659,7 +10659,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10683,12 +10683,12 @@
       </c>
       <c r="AL83" t="inlineStr">
         <is>
-          <t>Äldre tall</t>
+          <t>Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Äldre tall</t>
+          <t>Pinus sylvestris # Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10706,10 +10706,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121231774</v>
+        <v>121231793</v>
       </c>
       <c r="B84" t="n">
-        <v>105171</v>
+        <v>94723</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10718,35 +10718,35 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>340</v>
+        <v>210</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10755,10 +10755,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>693495</v>
+        <v>693674</v>
       </c>
       <c r="R84" t="n">
-        <v>6553900</v>
+        <v>6553894</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10790,7 +10790,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10800,12 +10800,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Två av skotten hade frökapslar.</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10817,9 +10812,24 @@
       <c r="AG84" t="b">
         <v>0</v>
       </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>Sluttning med tallskog</t>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL84" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten granlåga</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Picea abies # Kraftigt nedbruten granlåga</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10830,17 +10840,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121231793</v>
+        <v>121231762</v>
       </c>
       <c r="B85" t="n">
-        <v>94723</v>
+        <v>110242</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10853,43 +10863,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>210</v>
+        <v>219711</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>693674</v>
+        <v>693313</v>
       </c>
       <c r="R85" t="n">
-        <v>6553894</v>
+        <v>6553812</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10921,7 +10922,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10931,7 +10932,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10942,26 +10943,6 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL85" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten granlåga</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Picea abies # Kraftigt nedbruten granlåga</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10971,17 +10952,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121231775</v>
+        <v>121231795</v>
       </c>
       <c r="B86" t="n">
-        <v>8435</v>
+        <v>94723</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10994,27 +10975,31 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>210</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -11023,10 +11008,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>693555</v>
+        <v>693674</v>
       </c>
       <c r="R86" t="n">
-        <v>6553905</v>
+        <v>6553897</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11058,7 +11043,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11068,7 +11053,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11082,17 +11067,22 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL86" t="inlineStr">
+        <is>
+          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11103,17 +11093,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121231794</v>
+        <v>121231781</v>
       </c>
       <c r="B87" t="n">
-        <v>94627</v>
+        <v>5192</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11126,34 +11116,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2818</v>
+        <v>105930</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>693674</v>
+        <v>693639</v>
       </c>
       <c r="R87" t="n">
-        <v>6553897</v>
+        <v>6553969</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11185,7 +11180,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11195,7 +11190,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11217,14 +11212,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL87" t="inlineStr">
-        <is>
-          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
-        </is>
-      </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11235,17 +11225,17 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121231789</v>
+        <v>121231773</v>
       </c>
       <c r="B88" t="n">
-        <v>91125</v>
+        <v>98105</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11254,38 +11244,47 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>693670</v>
+        <v>693495</v>
       </c>
       <c r="R88" t="n">
-        <v>6553974</v>
+        <v>6553900</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11317,7 +11316,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11327,7 +11326,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11339,24 +11338,9 @@
       <c r="AG88" t="b">
         <v>0</v>
       </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL88" t="inlineStr">
-        <is>
-          <t>Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>Sluttning med tallskog</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11374,10 +11358,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121231771</v>
+        <v>121231782</v>
       </c>
       <c r="B89" t="n">
-        <v>4775</v>
+        <v>57372</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11386,38 +11370,43 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>693494</v>
+        <v>693709</v>
       </c>
       <c r="R89" t="n">
-        <v>6553917</v>
+        <v>6553983</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11449,7 +11438,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11459,7 +11448,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Födosökshack vid basen av stående död tall.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11470,26 +11464,6 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL89" t="inlineStr">
-        <is>
-          <t>Äldre grov gran</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre grov gran</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -11506,10 +11480,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121231795</v>
+        <v>121231775</v>
       </c>
       <c r="B90" t="n">
-        <v>94723</v>
+        <v>8435</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11522,31 +11496,27 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>210</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -11555,10 +11525,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>693674</v>
+        <v>693555</v>
       </c>
       <c r="R90" t="n">
-        <v>6553897</v>
+        <v>6553905</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11590,7 +11560,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11600,7 +11570,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11614,22 +11584,17 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL90" t="inlineStr">
-        <is>
-          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11640,17 +11605,17 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121231765</v>
+        <v>121231774</v>
       </c>
       <c r="B91" t="n">
-        <v>100371</v>
+        <v>105171</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11659,38 +11624,47 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>222498</v>
+        <v>340</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>693309</v>
+        <v>693495</v>
       </c>
       <c r="R91" t="n">
-        <v>6553789</v>
+        <v>6553900</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11722,7 +11696,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11732,7 +11706,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Två av skotten hade frökapslar.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11743,6 +11722,11 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>Sluttning med tallskog</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -11759,10 +11743,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121231782</v>
+        <v>121231767</v>
       </c>
       <c r="B92" t="n">
-        <v>57372</v>
+        <v>94723</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11771,31 +11755,35 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -11804,10 +11792,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>693709</v>
+        <v>693436</v>
       </c>
       <c r="R92" t="n">
-        <v>6553983</v>
+        <v>6553861</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11839,7 +11827,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11849,12 +11837,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Födosökshack vid basen av stående död tall.</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11865,6 +11848,26 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL92" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten grov granlåga</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Picea abies # Kraftigt nedbruten grov granlåga</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -12013,7 +12016,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121231792</v>
+        <v>121231794</v>
       </c>
       <c r="B94" t="n">
         <v>94627</v>
@@ -12056,7 +12059,7 @@
         <v>693674</v>
       </c>
       <c r="R94" t="n">
-        <v>6553894</v>
+        <v>6553897</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12088,7 +12091,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12098,7 +12101,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12122,12 +12125,12 @@
       </c>
       <c r="AL94" t="inlineStr">
         <is>
-          <t>Kraftigt nedbruten granlåga</t>
+          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftigt nedbruten granlåga</t>
+          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12145,10 +12148,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121231773</v>
+        <v>121231771</v>
       </c>
       <c r="B95" t="n">
-        <v>98105</v>
+        <v>4775</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12157,47 +12160,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>693495</v>
+        <v>693494</v>
       </c>
       <c r="R95" t="n">
-        <v>6553900</v>
+        <v>6553917</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12229,7 +12223,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12239,7 +12233,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12251,9 +12245,24 @@
       <c r="AG95" t="b">
         <v>0</v>
       </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>Sluttning med tallskog</t>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL95" t="inlineStr">
+        <is>
+          <t>Äldre grov gran</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grov gran</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12271,10 +12280,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121231767</v>
+        <v>121231765</v>
       </c>
       <c r="B96" t="n">
-        <v>94723</v>
+        <v>100371</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12287,43 +12296,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>693436</v>
+        <v>693309</v>
       </c>
       <c r="R96" t="n">
-        <v>6553861</v>
+        <v>6553789</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12376,26 +12376,6 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL96" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten grov granlåga</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Picea abies # Kraftigt nedbruten grov granlåga</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -12412,10 +12392,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121231762</v>
+        <v>121231785</v>
       </c>
       <c r="B97" t="n">
-        <v>110242</v>
+        <v>90740</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12424,25 +12404,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>219711</v>
+        <v>5442</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -12452,10 +12432,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>693313</v>
+        <v>693675</v>
       </c>
       <c r="R97" t="n">
-        <v>6553812</v>
+        <v>6553972</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12487,7 +12467,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12497,7 +12477,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12508,6 +12488,26 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL97" t="inlineStr">
+        <is>
+          <t>Äldre tall</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Äldre tall</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -12656,10 +12656,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121231788</v>
+        <v>121231787</v>
       </c>
       <c r="B99" t="n">
-        <v>94606</v>
+        <v>94400</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12672,21 +12672,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -12773,10 +12773,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121231776</v>
+        <v>121231788</v>
       </c>
       <c r="B100" t="n">
-        <v>94627</v>
+        <v>94606</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12789,21 +12789,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2818</v>
+        <v>2667</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -12813,10 +12813,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>693581</v>
+        <v>693670</v>
       </c>
       <c r="R100" t="n">
-        <v>6553897</v>
+        <v>6553974</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12848,7 +12848,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12858,7 +12858,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12869,6 +12869,11 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Vid basen av lodvägg</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -13007,10 +13012,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121231768</v>
+        <v>121231776</v>
       </c>
       <c r="B102" t="n">
-        <v>94723</v>
+        <v>94627</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13023,43 +13028,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>693478</v>
+        <v>693581</v>
       </c>
       <c r="R102" t="n">
-        <v>6553857</v>
+        <v>6553897</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13091,7 +13087,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13101,7 +13097,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13112,26 +13108,6 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL102" t="inlineStr">
-        <is>
-          <t>Granlåga i blockig sluttning</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga i blockig sluttning</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -13148,10 +13124,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121231787</v>
+        <v>121231768</v>
       </c>
       <c r="B103" t="n">
-        <v>94400</v>
+        <v>94723</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13164,34 +13140,43 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2779</v>
+        <v>210</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>693670</v>
+        <v>693478</v>
       </c>
       <c r="R103" t="n">
-        <v>6553974</v>
+        <v>6553857</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13223,7 +13208,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13233,7 +13218,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13245,9 +13230,24 @@
       <c r="AG103" t="b">
         <v>0</v>
       </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL103" t="inlineStr">
+        <is>
+          <t>Granlåga i blockig sluttning</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>Vid basen av lodvägg</t>
+          <t>Picea abies # Granlåga i blockig sluttning</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -10442,10 +10442,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121231792</v>
+        <v>121231771</v>
       </c>
       <c r="B82" t="n">
-        <v>94627</v>
+        <v>4775</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10458,21 +10458,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2818</v>
+        <v>102306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10482,10 +10482,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>693674</v>
+        <v>693494</v>
       </c>
       <c r="R82" t="n">
-        <v>6553894</v>
+        <v>6553917</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10517,7 +10517,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10527,7 +10527,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="AL82" t="inlineStr">
         <is>
-          <t>Kraftigt nedbruten granlåga</t>
+          <t>Äldre grov gran</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftigt nedbruten granlåga</t>
+          <t>Picea abies # Äldre grov gran</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10567,7 +10567,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -10706,10 +10706,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121231793</v>
+        <v>121231774</v>
       </c>
       <c r="B84" t="n">
-        <v>94723</v>
+        <v>105171</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10718,35 +10718,35 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>210</v>
+        <v>340</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) W. P. C. Barton</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10755,10 +10755,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>693674</v>
+        <v>693495</v>
       </c>
       <c r="R84" t="n">
-        <v>6553894</v>
+        <v>6553900</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10790,7 +10790,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10800,7 +10800,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Två av skotten hade frökapslar.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10812,24 +10817,9 @@
       <c r="AG84" t="b">
         <v>0</v>
       </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL84" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten granlåga</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Picea abies # Kraftigt nedbruten granlåga</t>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>Sluttning med tallskog</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10840,17 +10830,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121231762</v>
+        <v>121231775</v>
       </c>
       <c r="B85" t="n">
-        <v>110242</v>
+        <v>8435</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10863,34 +10853,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>219711</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>693313</v>
+        <v>693555</v>
       </c>
       <c r="R85" t="n">
-        <v>6553812</v>
+        <v>6553905</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10922,7 +10917,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10932,7 +10927,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10943,6 +10938,21 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10959,10 +10969,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121231795</v>
+        <v>121231794</v>
       </c>
       <c r="B86" t="n">
-        <v>94723</v>
+        <v>94627</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10975,33 +10985,24 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
@@ -11100,10 +11101,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121231781</v>
+        <v>121231795</v>
       </c>
       <c r="B87" t="n">
-        <v>5192</v>
+        <v>94723</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11116,27 +11117,31 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>105930</v>
+        <v>210</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -11145,10 +11150,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>693639</v>
+        <v>693674</v>
       </c>
       <c r="R87" t="n">
-        <v>6553969</v>
+        <v>6553897</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11180,7 +11185,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11190,7 +11195,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11212,9 +11217,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL87" t="inlineStr">
+        <is>
+          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11225,7 +11235,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -11358,10 +11368,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121231782</v>
+        <v>121231792</v>
       </c>
       <c r="B89" t="n">
-        <v>57372</v>
+        <v>94627</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11370,43 +11380,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>693709</v>
+        <v>693674</v>
       </c>
       <c r="R89" t="n">
-        <v>6553983</v>
+        <v>6553894</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11438,7 +11443,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11448,12 +11453,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Födosökshack vid basen av stående död tall.</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11464,6 +11464,26 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL89" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten granlåga</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Picea abies # Kraftigt nedbruten granlåga</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -11473,17 +11493,17 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121231775</v>
+        <v>121231767</v>
       </c>
       <c r="B90" t="n">
-        <v>8435</v>
+        <v>94723</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11496,27 +11516,31 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>210</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -11525,10 +11549,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>693555</v>
+        <v>693436</v>
       </c>
       <c r="R90" t="n">
-        <v>6553905</v>
+        <v>6553861</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11560,7 +11584,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11570,7 +11594,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11584,17 +11608,22 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL90" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten grov granlåga</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies # Kraftigt nedbruten grov granlåga</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11612,10 +11641,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121231774</v>
+        <v>121231762</v>
       </c>
       <c r="B91" t="n">
-        <v>105171</v>
+        <v>110242</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11624,47 +11653,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>340</v>
+        <v>219711</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>693495</v>
+        <v>693313</v>
       </c>
       <c r="R91" t="n">
-        <v>6553900</v>
+        <v>6553812</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11696,7 +11716,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11706,12 +11726,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Två av skotten hade frökapslar.</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11722,11 +11737,6 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>Sluttning med tallskog</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -11743,10 +11753,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121231767</v>
+        <v>121231764</v>
       </c>
       <c r="B92" t="n">
-        <v>94723</v>
+        <v>5192</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11759,43 +11769,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>210</v>
+        <v>105930</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>693436</v>
+        <v>693261</v>
       </c>
       <c r="R92" t="n">
-        <v>6553861</v>
+        <v>6553742</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11827,7 +11828,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11837,7 +11838,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11861,12 +11862,12 @@
       </c>
       <c r="AL92" t="inlineStr">
         <is>
-          <t>Kraftigt nedbruten grov granlåga</t>
+          <t>Klen gran i område med många fallna granar</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftigt nedbruten grov granlåga</t>
+          <t>Picea abies # Klen gran i område med många fallna granar</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11884,10 +11885,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121231764</v>
+        <v>121231782</v>
       </c>
       <c r="B93" t="n">
-        <v>5192</v>
+        <v>57372</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11896,20 +11897,20 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -11918,16 +11919,21 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>693261</v>
+        <v>693709</v>
       </c>
       <c r="R93" t="n">
-        <v>6553742</v>
+        <v>6553983</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11959,7 +11965,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11969,7 +11975,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Födosökshack vid basen av stående död tall.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11980,26 +11991,6 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL93" t="inlineStr">
-        <is>
-          <t>Klen gran i område med många fallna granar</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen gran i område med många fallna granar</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -12016,10 +12007,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121231794</v>
+        <v>121231765</v>
       </c>
       <c r="B94" t="n">
-        <v>94627</v>
+        <v>100371</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12032,21 +12023,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12056,10 +12047,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>693674</v>
+        <v>693309</v>
       </c>
       <c r="R94" t="n">
-        <v>6553897</v>
+        <v>6553789</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12091,7 +12082,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12101,7 +12092,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12112,26 +12103,6 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL94" t="inlineStr">
-        <is>
-          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -12141,17 +12112,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121231771</v>
+        <v>121231785</v>
       </c>
       <c r="B95" t="n">
-        <v>4775</v>
+        <v>90740</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12160,25 +12131,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12188,10 +12159,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>693494</v>
+        <v>693675</v>
       </c>
       <c r="R95" t="n">
-        <v>6553917</v>
+        <v>6553972</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12223,7 +12194,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12233,7 +12204,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12247,22 +12218,22 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL95" t="inlineStr">
         <is>
-          <t>Äldre grov gran</t>
+          <t>Äldre tall</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grov gran</t>
+          <t>Pinus sylvestris # Äldre tall</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12280,10 +12251,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121231765</v>
+        <v>121231793</v>
       </c>
       <c r="B96" t="n">
-        <v>100371</v>
+        <v>94723</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12296,34 +12267,43 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>693309</v>
+        <v>693674</v>
       </c>
       <c r="R96" t="n">
-        <v>6553789</v>
+        <v>6553894</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12355,7 +12335,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12365,7 +12345,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12376,6 +12356,26 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL96" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten granlåga</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Picea abies # Kraftigt nedbruten granlåga</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -12385,17 +12385,17 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121231785</v>
+        <v>121231781</v>
       </c>
       <c r="B97" t="n">
-        <v>90740</v>
+        <v>5192</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12404,38 +12404,43 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5442</v>
+        <v>105930</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>693675</v>
+        <v>693639</v>
       </c>
       <c r="R97" t="n">
-        <v>6553972</v>
+        <v>6553969</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12467,7 +12472,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12477,7 +12482,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12491,22 +12496,17 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL97" t="inlineStr">
-        <is>
-          <t>Äldre tall</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Äldre tall</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -12656,10 +12656,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121231787</v>
+        <v>121231786</v>
       </c>
       <c r="B99" t="n">
-        <v>94400</v>
+        <v>94113</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12672,24 +12672,28 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2779</v>
+        <v>2362</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
@@ -12750,6 +12754,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -12773,10 +12778,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121231788</v>
+        <v>121231768</v>
       </c>
       <c r="B100" t="n">
-        <v>94606</v>
+        <v>94723</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12789,34 +12794,43 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2667</v>
+        <v>210</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>693670</v>
+        <v>693478</v>
       </c>
       <c r="R100" t="n">
-        <v>6553974</v>
+        <v>6553857</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12848,7 +12862,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12858,7 +12872,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12870,9 +12884,24 @@
       <c r="AG100" t="b">
         <v>0</v>
       </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL100" t="inlineStr">
+        <is>
+          <t>Granlåga i blockig sluttning</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>Vid basen av lodvägg</t>
+          <t>Picea abies # Granlåga i blockig sluttning</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -12890,10 +12919,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121231786</v>
+        <v>121231788</v>
       </c>
       <c r="B101" t="n">
-        <v>94113</v>
+        <v>94606</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12906,28 +12935,24 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2362</v>
+        <v>2667</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blek stjärnmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Mnium stellare</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
@@ -12988,7 +13013,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -13012,10 +13036,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121231776</v>
+        <v>121231787</v>
       </c>
       <c r="B102" t="n">
-        <v>94627</v>
+        <v>94400</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13028,21 +13052,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2818</v>
+        <v>2779</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -13052,10 +13076,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>693581</v>
+        <v>693670</v>
       </c>
       <c r="R102" t="n">
-        <v>6553897</v>
+        <v>6553974</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13087,7 +13111,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13097,7 +13121,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13108,6 +13132,11 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Vid basen av lodvägg</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -13124,10 +13153,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121231768</v>
+        <v>121231776</v>
       </c>
       <c r="B103" t="n">
-        <v>94723</v>
+        <v>94627</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13140,43 +13169,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>693478</v>
+        <v>693581</v>
       </c>
       <c r="R103" t="n">
-        <v>6553857</v>
+        <v>6553897</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13208,7 +13228,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13218,7 +13238,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13229,26 +13249,6 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL103" t="inlineStr">
-        <is>
-          <t>Granlåga i blockig sluttning</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga i blockig sluttning</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -13390,37 +13390,37 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121231778</v>
+        <v>121231770</v>
       </c>
       <c r="B105" t="n">
-        <v>95691</v>
+        <v>95968</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2590</v>
+        <v>990</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -13434,10 +13434,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>693588</v>
+        <v>693478</v>
       </c>
       <c r="R105" t="n">
-        <v>6553885</v>
+        <v>6553857</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13469,7 +13469,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13479,7 +13479,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13494,22 +13494,22 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr">
         <is>
-          <t>Tallåga i kärr</t>
+          <t>Granlåga i blockig sluttning</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Tallåga i kärr</t>
+          <t>Picea abies # Granlåga i blockig sluttning</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -13527,37 +13527,37 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121231770</v>
+        <v>121231778</v>
       </c>
       <c r="B106" t="n">
-        <v>95968</v>
+        <v>95691</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>990</v>
+        <v>2590</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -13571,10 +13571,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>693478</v>
+        <v>693588</v>
       </c>
       <c r="R106" t="n">
-        <v>6553857</v>
+        <v>6553885</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13606,7 +13606,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13631,22 +13631,22 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL106" t="inlineStr">
         <is>
-          <t>Granlåga i blockig sluttning</t>
+          <t>Tallåga i kärr</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga i blockig sluttning</t>
+          <t>Pinus sylvestris # Tallåga i kärr</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -13268,7 +13268,7 @@
         <v>121330721</v>
       </c>
       <c r="B104" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13390,37 +13390,37 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121231770</v>
+        <v>121231778</v>
       </c>
       <c r="B105" t="n">
-        <v>95968</v>
+        <v>95699</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>990</v>
+        <v>2590</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -13434,10 +13434,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>693478</v>
+        <v>693588</v>
       </c>
       <c r="R105" t="n">
-        <v>6553857</v>
+        <v>6553885</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13469,7 +13469,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13479,7 +13479,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13494,22 +13494,22 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr">
         <is>
-          <t>Granlåga i blockig sluttning</t>
+          <t>Tallåga i kärr</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga i blockig sluttning</t>
+          <t>Pinus sylvestris # Tallåga i kärr</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -13527,37 +13527,37 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121231778</v>
+        <v>121231770</v>
       </c>
       <c r="B106" t="n">
-        <v>95691</v>
+        <v>95976</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2590</v>
+        <v>990</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -13571,10 +13571,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>693588</v>
+        <v>693478</v>
       </c>
       <c r="R106" t="n">
-        <v>6553885</v>
+        <v>6553857</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13606,7 +13606,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13631,22 +13631,22 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL106" t="inlineStr">
         <is>
-          <t>Tallåga i kärr</t>
+          <t>Granlåga i blockig sluttning</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Tallåga i kärr</t>
+          <t>Picea abies # Granlåga i blockig sluttning</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY106"/>
+  <dimension ref="A1:AY105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1541,10 +1541,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97354291</v>
+        <v>97354603</v>
       </c>
       <c r="B9" t="n">
-        <v>95511</v>
+        <v>5113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1557,27 +1557,32 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221944</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1585,10 +1590,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>693426.5487788982</v>
+        <v>693311.9534352284</v>
       </c>
       <c r="R9" t="n">
-        <v>6553884.71708205</v>
+        <v>6554029.261892134</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1631,11 +1636,6 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Litet bestånd.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1663,7 +1663,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97354603</v>
+        <v>97354229</v>
       </c>
       <c r="B10" t="n">
         <v>5113</v>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>693311.9534352284</v>
+        <v>693478.6312425468</v>
       </c>
       <c r="R10" t="n">
-        <v>6554029.261892134</v>
+        <v>6553854.400347623</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97354229</v>
+        <v>97353544</v>
       </c>
       <c r="B11" t="n">
-        <v>5113</v>
+        <v>4711</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1801,21 +1801,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1824,7 +1824,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>693478.6312425468</v>
+        <v>693541.24329969</v>
       </c>
       <c r="R11" t="n">
-        <v>6553854.400347623</v>
+        <v>6553667.057662671</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1880,6 +1880,11 @@
       <c r="AB11" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gnagspår på död gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1907,10 +1912,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97353544</v>
+        <v>97354632</v>
       </c>
       <c r="B12" t="n">
-        <v>4711</v>
+        <v>90676</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1919,36 +1924,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100299</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1956,10 +1963,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>693541.24329969</v>
+        <v>693370.9503446445</v>
       </c>
       <c r="R12" t="n">
-        <v>6553667.057662671</v>
+        <v>6554106.899837079</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2002,11 +2009,6 @@
       <c r="AB12" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gnagspår på död gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2034,10 +2036,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97354632</v>
+        <v>97354154</v>
       </c>
       <c r="B13" t="n">
-        <v>90676</v>
+        <v>93235</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2046,38 +2048,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>210</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2085,10 +2088,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>693370.9503446445</v>
+        <v>693469.6977268271</v>
       </c>
       <c r="R13" t="n">
-        <v>6554106.899837079</v>
+        <v>6553867.85005971</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2131,6 +2134,11 @@
       <c r="AB13" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Två gröna fina sporkapslar vid roten av gammal starkt rötangripen granlåga.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2158,10 +2166,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97354154</v>
+        <v>97354790</v>
       </c>
       <c r="B14" t="n">
-        <v>93235</v>
+        <v>108194</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2174,33 +2182,25 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>210</v>
+        <v>219711</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>693469.6977268271</v>
+        <v>693695.1425051668</v>
       </c>
       <c r="R14" t="n">
-        <v>6553867.85005971</v>
+        <v>6553968.855639989</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2256,11 +2256,6 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Två gröna fina sporkapslar vid roten av gammal starkt rötangripen granlåga.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2288,10 +2283,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>97354790</v>
+        <v>97353710</v>
       </c>
       <c r="B15" t="n">
-        <v>108194</v>
+        <v>89412</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2300,31 +2295,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219711</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2332,10 +2326,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>693695.1425051668</v>
+        <v>693435.4104886684</v>
       </c>
       <c r="R15" t="n">
-        <v>6553968.855639989</v>
+        <v>6553658.611758322</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2405,10 +2399,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>97353710</v>
+        <v>97353704</v>
       </c>
       <c r="B16" t="n">
-        <v>89412</v>
+        <v>93132</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2417,30 +2411,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2448,10 +2443,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>693435.4104886684</v>
+        <v>693433.2277447049</v>
       </c>
       <c r="R16" t="n">
-        <v>6553658.611758322</v>
+        <v>6553650.777658764</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2494,6 +2489,11 @@
       <c r="AB16" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På block.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2521,10 +2521,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>97353704</v>
+        <v>97354275</v>
       </c>
       <c r="B17" t="n">
-        <v>93132</v>
+        <v>92939</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2537,21 +2537,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>693433.2277447049</v>
+        <v>693424.2829751407</v>
       </c>
       <c r="R17" t="n">
-        <v>6553650.777658764</v>
+        <v>6553888.72146775</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På block.</t>
+          <t>På lodyta. Blockig sluttning i anslutning till höga bergbranter med mossbeklädda lodytor.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2643,10 +2643,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>97354275</v>
+        <v>98155245</v>
       </c>
       <c r="B18" t="n">
-        <v>92939</v>
+        <v>108194</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2659,41 +2659,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2779</v>
+        <v>219711</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Breviksnäs, Ornö, Srm</t>
+          <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>693424.2829751407</v>
+        <v>693712.9448109742</v>
       </c>
       <c r="R18" t="n">
-        <v>6553888.72146775</v>
+        <v>6553922.904037611</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2717,27 +2715,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-11-29</t>
+          <t>2022-01-16</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-11-29</t>
+          <t>2022-01-16</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På lodyta. Blockig sluttning i anslutning till höga bergbranter med mossbeklädda lodytor.</t>
+          <t>Spridd över stort område</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2746,29 +2744,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson</t>
+          <t>Thomas Strid, Tiina Laantee, Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>98155245</v>
+        <v>98158262</v>
       </c>
       <c r="B19" t="n">
-        <v>108194</v>
+        <v>93235</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2781,24 +2778,33 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219711</v>
+        <v>210</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2807,13 +2813,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>693712.9448109742</v>
+        <v>693464.6461807546</v>
       </c>
       <c r="R19" t="n">
-        <v>6553922.904037611</v>
+        <v>6553886.130126562</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2842,7 +2848,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2852,12 +2858,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Spridd över stort område</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2884,49 +2885,40 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>98158262</v>
+        <v>98156324</v>
       </c>
       <c r="B20" t="n">
-        <v>93235</v>
+        <v>103226</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>210</v>
+        <v>340</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2935,13 +2927,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>693464.6461807546</v>
+        <v>693431.769816168</v>
       </c>
       <c r="R20" t="n">
-        <v>6553886.130126562</v>
+        <v>6554087.323701127</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2970,7 +2962,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2980,7 +2972,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3007,10 +2999,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>98156324</v>
+        <v>98157189</v>
       </c>
       <c r="B21" t="n">
-        <v>103226</v>
+        <v>96334</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3019,43 +3011,53 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>340</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>693431.769816168</v>
+        <v>693386.6176347288</v>
       </c>
       <c r="R21" t="n">
-        <v>6554087.323701127</v>
+        <v>6554103.058824784</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3084,7 +3086,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3094,7 +3096,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Nedanför liten snitslad tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3103,6 +3110,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3121,7 +3129,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>98157189</v>
+        <v>98156759</v>
       </c>
       <c r="B22" t="n">
         <v>96334</v>
@@ -3154,29 +3162,19 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>693386.6176347288</v>
+        <v>693395.9920624756</v>
       </c>
       <c r="R22" t="n">
-        <v>6554103.058824784</v>
+        <v>6554080.879655682</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3221,18 +3219,12 @@
           <t>13:05</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Nedanför liten snitslad tall</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3251,7 +3243,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>98156759</v>
+        <v>98156997</v>
       </c>
       <c r="B23" t="n">
         <v>96334</v>
@@ -3284,7 +3276,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -3293,10 +3289,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>693395.9920624756</v>
+        <v>693381.8680259516</v>
       </c>
       <c r="R23" t="n">
-        <v>6554080.879655682</v>
+        <v>6554084.798739863</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3365,7 +3361,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>98156997</v>
+        <v>98156914</v>
       </c>
       <c r="B24" t="n">
         <v>96334</v>
@@ -3398,11 +3394,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3411,13 +3403,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>693381.8680259516</v>
+        <v>693399.1099701935</v>
       </c>
       <c r="R24" t="n">
-        <v>6554084.798739863</v>
+        <v>6554070.225480206</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3457,6 +3449,11 @@
       <c r="AB24" t="inlineStr">
         <is>
           <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>11 + 4</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3483,55 +3480,61 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>98156914</v>
+        <v>99462539</v>
       </c>
       <c r="B25" t="n">
-        <v>96334</v>
+        <v>93235</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>693399.1099701935</v>
+        <v>693450.6253118357</v>
       </c>
       <c r="R25" t="n">
-        <v>6554070.225480206</v>
+        <v>6553887.994953271</v>
       </c>
       <c r="S25" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3555,27 +3558,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-01-16</t>
+          <t>2022-03-26</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-01-16</t>
+          <t>2022-03-26</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>11 + 4</t>
+          <t>Finns lite överallt i denna underbara naturligt fuktiga sänka!</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3584,28 +3587,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Leonard Brunner</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Thomas Strid, Tiina Laantee, Ulf Johansson, Bodil Ravn</t>
+          <t>Leonard Brunner, Kristina Bäck</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>99462539</v>
+        <v>99456502</v>
       </c>
       <c r="B26" t="n">
-        <v>93235</v>
+        <v>56411</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3614,49 +3618,44 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Breviksnäs, Srm</t>
+          <t>Haninge, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>693450.6253118357</v>
+        <v>693606.9893747875</v>
       </c>
       <c r="R26" t="n">
-        <v>6553887.994953271</v>
+        <v>6554008.668507322</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3685,7 +3684,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3695,12 +3694,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Finns lite överallt i denna underbara naturligt fuktiga sänka!</t>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3709,29 +3708,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Leonard Brunner</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Leonard Brunner, Kristina Bäck</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>99456502</v>
+        <v>99462632</v>
       </c>
       <c r="B27" t="n">
-        <v>56411</v>
+        <v>93235</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3740,44 +3738,49 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Haninge, Srm</t>
+          <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>693606.9893747875</v>
+        <v>693435.1340831907</v>
       </c>
       <c r="R27" t="n">
-        <v>6554008.668507322</v>
+        <v>6553847.565104425</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3806,7 +3809,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3816,12 +3819,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Spår</t>
+          <t>En magisk plats med mycket död ved!</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3830,28 +3833,29 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Leonard Brunner</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Leonard Brunner, Kristina Bäck</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>99462632</v>
+        <v>99505852</v>
       </c>
       <c r="B28" t="n">
-        <v>93235</v>
+        <v>78098</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3860,49 +3864,48 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>210</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Breviksnäs, Srm</t>
+          <t>Breviksnäs, Mörbyfjärden, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>693435.1340831907</v>
+        <v>693450.6253118357</v>
       </c>
       <c r="R28" t="n">
-        <v>6553847.565104425</v>
+        <v>6553887.994953271</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3931,7 +3934,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3941,12 +3944,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>En magisk plats med mycket död ved!</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3959,25 +3957,55 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Naturskog, hällmark</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Växer på silverved</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Växer på silverved</t>
+        </is>
+      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Leonard Brunner</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Leonard Brunner, Kristina Bäck</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>99505852</v>
+        <v>104335875</v>
       </c>
       <c r="B29" t="n">
-        <v>78098</v>
+        <v>103226</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3986,48 +4014,50 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>340</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Breviksnäs, Mörbyfjärden, Ornö, Srm</t>
+          <t>Breviksnässkogen, Ornö, Haninge, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>693450.6253118357</v>
+        <v>693432.8140939354</v>
       </c>
       <c r="R29" t="n">
-        <v>6553887.994953271</v>
+        <v>6554107.455752393</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4051,22 +4081,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4075,59 +4105,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Naturskog, hällmark</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL29" t="inlineStr">
-        <is>
-          <t>Växer på silverved</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Växer på silverved</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Tiina Laantee</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Tiina Laantee</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>104335875</v>
+        <v>104336481</v>
       </c>
       <c r="B30" t="n">
-        <v>103226</v>
+        <v>96334</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4136,35 +4135,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>340</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4173,13 +4168,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>693432.8140939354</v>
+        <v>693389.2106263841</v>
       </c>
       <c r="R30" t="n">
-        <v>6554107.455752393</v>
+        <v>6554062.001798894</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4208,7 +4203,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4218,7 +4213,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4245,10 +4240,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>104336481</v>
+        <v>120944668</v>
       </c>
       <c r="B31" t="n">
-        <v>96334</v>
+        <v>43707</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4257,46 +4252,46 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>101735</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Breviksnässkogen, Ornö, Haninge, Srm</t>
+          <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>693389.2106263841</v>
+        <v>693684</v>
       </c>
       <c r="R31" t="n">
-        <v>6554062.001798894</v>
+        <v>6553982</v>
       </c>
       <c r="S31" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4320,22 +4315,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4346,26 +4341,46 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>Fnöskticka på björk</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius # Fnöskticka på björk</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Tiina Laantee</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Tiina Laantee</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120944668</v>
+        <v>120944652</v>
       </c>
       <c r="B32" t="n">
-        <v>43707</v>
+        <v>5189</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4378,21 +4393,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>101735</v>
+        <v>105930</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4407,10 +4422,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>693684</v>
+        <v>693267</v>
       </c>
       <c r="R32" t="n">
-        <v>6553982</v>
+        <v>6553784</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4442,7 +4457,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4452,7 +4467,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4463,26 +4478,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>Fnöskticka på björk</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius # Fnöskticka på björk</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4499,10 +4494,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120944652</v>
+        <v>120944670</v>
       </c>
       <c r="B33" t="n">
-        <v>5189</v>
+        <v>83177</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4515,39 +4510,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>105930</v>
+        <v>1444</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sarcoscypha coccinea s.lat.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Jacq.:Fr.) Lambotte</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>693267</v>
+        <v>693691</v>
       </c>
       <c r="R33" t="n">
-        <v>6553784</v>
+        <v>6553897</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4579,7 +4572,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4589,7 +4582,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4598,6 +4591,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4616,10 +4610,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120944670</v>
+        <v>120944647</v>
       </c>
       <c r="B34" t="n">
-        <v>83177</v>
+        <v>91102</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4632,37 +4626,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1444</v>
+        <v>5420</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Scharlakansvårskål agg.</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcoscypha coccinea s.lat.</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Jacq.:Fr.) Lambotte</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>693691</v>
+        <v>693266</v>
       </c>
       <c r="R34" t="n">
-        <v>6553897</v>
+        <v>6553907</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4694,7 +4685,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4704,7 +4695,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4713,7 +4704,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4732,10 +4722,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120944647</v>
+        <v>120944676</v>
       </c>
       <c r="B35" t="n">
-        <v>91102</v>
+        <v>5189</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4748,21 +4738,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5420</v>
+        <v>105930</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4772,10 +4762,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>693266</v>
+        <v>693463</v>
       </c>
       <c r="R35" t="n">
-        <v>6553907</v>
+        <v>6553650</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4807,7 +4797,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4817,7 +4807,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4828,6 +4818,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>Klen granlåga</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen granlåga</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4844,10 +4854,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120944676</v>
+        <v>120944644</v>
       </c>
       <c r="B36" t="n">
-        <v>5189</v>
+        <v>98081</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4856,25 +4866,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4884,10 +4894,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>693463</v>
+        <v>693429</v>
       </c>
       <c r="R36" t="n">
-        <v>6553650</v>
+        <v>6554092</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4919,7 +4929,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4929,7 +4939,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4940,26 +4950,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL36" t="inlineStr">
-        <is>
-          <t>Klen granlåga</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen granlåga</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4976,10 +4966,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120944644</v>
+        <v>120944660</v>
       </c>
       <c r="B37" t="n">
-        <v>98081</v>
+        <v>100347</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4988,25 +4978,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5016,10 +5006,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>693429</v>
+        <v>693463</v>
       </c>
       <c r="R37" t="n">
-        <v>6554092</v>
+        <v>6553888</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5051,7 +5041,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5061,7 +5051,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5088,10 +5078,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120944660</v>
+        <v>120944662</v>
       </c>
       <c r="B38" t="n">
-        <v>100347</v>
+        <v>90717</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5100,25 +5090,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5128,10 +5118,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>693463</v>
+        <v>693541</v>
       </c>
       <c r="R38" t="n">
-        <v>6553888</v>
+        <v>6553901</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5163,7 +5153,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5173,7 +5163,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5184,6 +5174,21 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5200,10 +5205,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120944662</v>
+        <v>120944669</v>
       </c>
       <c r="B39" t="n">
-        <v>90717</v>
+        <v>110218</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5212,25 +5217,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>219711</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5240,10 +5245,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>693541</v>
+        <v>693696</v>
       </c>
       <c r="R39" t="n">
-        <v>6553901</v>
+        <v>6553895</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5275,7 +5280,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5285,7 +5290,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5296,21 +5301,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5327,10 +5317,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120944669</v>
+        <v>120944663</v>
       </c>
       <c r="B40" t="n">
-        <v>110218</v>
+        <v>8432</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5343,34 +5333,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219711</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>693696</v>
+        <v>693555</v>
       </c>
       <c r="R40" t="n">
-        <v>6553895</v>
+        <v>6553910</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5402,7 +5397,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5412,7 +5407,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5423,6 +5418,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>Äldre tallåga</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Äldre tallåga</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5439,10 +5454,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120944663</v>
+        <v>120944651</v>
       </c>
       <c r="B41" t="n">
-        <v>8432</v>
+        <v>100347</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5455,39 +5470,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>693555</v>
+        <v>693262</v>
       </c>
       <c r="R41" t="n">
-        <v>6553910</v>
+        <v>6553782</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5519,7 +5529,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5529,7 +5539,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5540,26 +5550,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>Äldre tallåga</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Äldre tallåga</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5576,10 +5566,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120944651</v>
+        <v>120944659</v>
       </c>
       <c r="B42" t="n">
-        <v>100347</v>
+        <v>110218</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5592,21 +5582,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5616,10 +5606,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>693262</v>
+        <v>693460</v>
       </c>
       <c r="R42" t="n">
-        <v>6553782</v>
+        <v>6553882</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5651,7 +5641,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5661,7 +5651,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5688,10 +5678,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120944659</v>
+        <v>120944646</v>
       </c>
       <c r="B43" t="n">
-        <v>110218</v>
+        <v>98081</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5700,25 +5690,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219711</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5728,10 +5718,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>693460</v>
+        <v>693387</v>
       </c>
       <c r="R43" t="n">
-        <v>6553882</v>
+        <v>6554088</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5763,7 +5753,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5773,7 +5763,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5800,7 +5790,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120944646</v>
+        <v>120944645</v>
       </c>
       <c r="B44" t="n">
         <v>98081</v>
@@ -5840,10 +5830,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>693387</v>
+        <v>693400</v>
       </c>
       <c r="R44" t="n">
-        <v>6554088</v>
+        <v>6554080</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5875,7 +5865,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5885,7 +5875,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5912,10 +5902,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120944645</v>
+        <v>120944649</v>
       </c>
       <c r="B45" t="n">
-        <v>98081</v>
+        <v>109853</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5924,25 +5914,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>222776</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5952,10 +5942,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>693400</v>
+        <v>693290</v>
       </c>
       <c r="R45" t="n">
-        <v>6554080</v>
+        <v>6553793</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5987,7 +5977,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5997,7 +5987,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6024,10 +6014,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120944649</v>
+        <v>120944654</v>
       </c>
       <c r="B46" t="n">
-        <v>109853</v>
+        <v>94604</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6036,25 +6026,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222776</v>
+        <v>2818</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6064,10 +6054,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>693290</v>
+        <v>693326</v>
       </c>
       <c r="R46" t="n">
-        <v>6553793</v>
+        <v>6553834</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6099,7 +6089,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6109,7 +6099,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6136,10 +6126,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120944654</v>
+        <v>120944672</v>
       </c>
       <c r="B47" t="n">
-        <v>94604</v>
+        <v>57370</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6152,34 +6142,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2818</v>
+        <v>102977</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>693326</v>
+        <v>693659</v>
       </c>
       <c r="R47" t="n">
-        <v>6553834</v>
+        <v>6553831</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6211,7 +6206,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6221,7 +6216,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6248,10 +6243,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120944672</v>
+        <v>120944675</v>
       </c>
       <c r="B48" t="n">
-        <v>57370</v>
+        <v>5169</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6264,27 +6259,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102977</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6293,10 +6288,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>693659</v>
+        <v>693463</v>
       </c>
       <c r="R48" t="n">
-        <v>6553831</v>
+        <v>6553650</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6328,7 +6323,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6338,7 +6333,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6349,6 +6344,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>Klen granlåga</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen granlåga</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6365,10 +6380,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120944675</v>
+        <v>120944653</v>
       </c>
       <c r="B49" t="n">
-        <v>5169</v>
+        <v>109853</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6377,31 +6392,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100526</v>
+        <v>222776</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6410,10 +6425,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>693463</v>
+        <v>693271</v>
       </c>
       <c r="R49" t="n">
-        <v>6553650</v>
+        <v>6553781</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6445,7 +6460,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6455,7 +6470,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6466,26 +6481,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL49" t="inlineStr">
-        <is>
-          <t>Klen granlåga</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen granlåga</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6502,55 +6497,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120944653</v>
+        <v>120944657</v>
       </c>
       <c r="B50" t="n">
-        <v>109853</v>
+        <v>94617</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222776</v>
+        <v>2818</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>693271</v>
+        <v>693433</v>
       </c>
       <c r="R50" t="n">
-        <v>6553781</v>
+        <v>6553866</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6582,7 +6572,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6592,7 +6582,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6619,37 +6609,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120944657</v>
+        <v>121124060</v>
       </c>
       <c r="B51" t="n">
-        <v>94617</v>
+        <v>57370</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6659,10 +6649,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>693433</v>
+        <v>693507</v>
       </c>
       <c r="R51" t="n">
-        <v>6553866</v>
+        <v>6553745</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6689,22 +6679,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6724,17 +6714,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Per Flodby, Nina Tadsen, Jennica Andersson, Mattias Bernhardsson, Nette Bygren, Roja Kirkeby</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121124060</v>
+        <v>121124065</v>
       </c>
       <c r="B52" t="n">
-        <v>57370</v>
+        <v>5171</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6747,34 +6737,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>102204</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>693507</v>
+        <v>693560</v>
       </c>
       <c r="R52" t="n">
-        <v>6553745</v>
+        <v>6553691</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6806,7 +6801,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6816,7 +6811,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6827,6 +6822,26 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t>Klen granlåga</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen granlåga</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6843,10 +6858,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121124065</v>
+        <v>121124055</v>
       </c>
       <c r="B53" t="n">
-        <v>5171</v>
+        <v>92024</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6859,39 +6874,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>102204</v>
+        <v>5966</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>693560</v>
+        <v>693466</v>
       </c>
       <c r="R53" t="n">
-        <v>6553691</v>
+        <v>6553741</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6923,7 +6933,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6933,7 +6943,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6944,26 +6954,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL53" t="inlineStr">
-        <is>
-          <t>Klen granlåga</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen granlåga</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6980,10 +6970,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121124055</v>
+        <v>121124058</v>
       </c>
       <c r="B54" t="n">
-        <v>92024</v>
+        <v>94870</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6992,25 +6982,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7020,10 +7010,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>693466</v>
+        <v>693480</v>
       </c>
       <c r="R54" t="n">
-        <v>6553741</v>
+        <v>6553749</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7055,7 +7045,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7065,7 +7055,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7092,10 +7082,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121124058</v>
+        <v>121124082</v>
       </c>
       <c r="B55" t="n">
-        <v>94870</v>
+        <v>89764</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7104,25 +7094,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2180</v>
+        <v>1962</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7132,10 +7122,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>693480</v>
+        <v>693411</v>
       </c>
       <c r="R55" t="n">
-        <v>6553749</v>
+        <v>6553549</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7167,7 +7157,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7177,7 +7167,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7188,6 +7178,26 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>På undersidan av tallved.</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # På undersidan av tallved.</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7204,10 +7214,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121124082</v>
+        <v>121124045</v>
       </c>
       <c r="B56" t="n">
-        <v>89764</v>
+        <v>110235</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7216,25 +7226,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1962</v>
+        <v>219711</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7244,10 +7254,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>693411</v>
+        <v>693689</v>
       </c>
       <c r="R56" t="n">
-        <v>6553549</v>
+        <v>6553935</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7279,7 +7289,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7289,7 +7299,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Mycket rikligt.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7300,26 +7315,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL56" t="inlineStr">
-        <is>
-          <t>På undersidan av tallved.</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # På undersidan av tallved.</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7336,7 +7331,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121124045</v>
+        <v>121124048</v>
       </c>
       <c r="B57" t="n">
         <v>110235</v>
@@ -7376,10 +7371,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>693689</v>
+        <v>693677</v>
       </c>
       <c r="R57" t="n">
-        <v>6553935</v>
+        <v>6553911</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7411,7 +7406,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7421,12 +7416,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Mycket rikligt.</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7453,10 +7443,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121124048</v>
+        <v>121124061</v>
       </c>
       <c r="B58" t="n">
-        <v>110235</v>
+        <v>94870</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7469,21 +7459,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219711</v>
+        <v>2180</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7493,10 +7483,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>693677</v>
+        <v>693526</v>
       </c>
       <c r="R58" t="n">
-        <v>6553911</v>
+        <v>6553740</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7528,7 +7518,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7538,7 +7528,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7565,10 +7555,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121124061</v>
+        <v>121124053</v>
       </c>
       <c r="B59" t="n">
-        <v>94870</v>
+        <v>91396</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7581,21 +7571,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2180</v>
+        <v>3298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7605,10 +7595,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>693526</v>
+        <v>693628</v>
       </c>
       <c r="R59" t="n">
-        <v>6553740</v>
+        <v>6553797</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7640,7 +7630,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7650,7 +7640,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7661,6 +7651,26 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL59" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död gran.</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7677,10 +7687,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121124053</v>
+        <v>121124059</v>
       </c>
       <c r="B60" t="n">
-        <v>91396</v>
+        <v>89764</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7689,25 +7699,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3298</v>
+        <v>1962</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7717,10 +7727,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>693628</v>
+        <v>693491</v>
       </c>
       <c r="R60" t="n">
-        <v>6553797</v>
+        <v>6553751</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7752,7 +7762,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7762,7 +7772,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7776,22 +7786,17 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL60" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död gran.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7809,10 +7814,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121124059</v>
+        <v>121124077</v>
       </c>
       <c r="B61" t="n">
-        <v>89764</v>
+        <v>5171</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7825,34 +7830,43 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1962</v>
+        <v>102204</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>693491</v>
+        <v>693453</v>
       </c>
       <c r="R61" t="n">
-        <v>6553751</v>
+        <v>6553587</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7884,7 +7898,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7894,7 +7908,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7903,22 +7917,28 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>Klen granlåga</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies # Klen granlåga</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7936,10 +7956,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121124077</v>
+        <v>121124067</v>
       </c>
       <c r="B62" t="n">
-        <v>5171</v>
+        <v>94620</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7948,47 +7968,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>102204</v>
+        <v>2818</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>693453</v>
+        <v>693537</v>
       </c>
       <c r="R62" t="n">
-        <v>6553587</v>
+        <v>6553673</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8020,7 +8031,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8030,7 +8041,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8039,29 +8050,8 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL62" t="inlineStr">
-        <is>
-          <t>Klen granlåga</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen granlåga</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -8078,10 +8068,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121124067</v>
+        <v>121124066</v>
       </c>
       <c r="B63" t="n">
-        <v>94620</v>
+        <v>4769</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8094,34 +8084,43 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2818</v>
+        <v>100299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>693537</v>
+        <v>693536</v>
       </c>
       <c r="R63" t="n">
-        <v>6553673</v>
+        <v>6553680</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8153,7 +8152,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8163,7 +8162,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8172,8 +8171,29 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL63" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död gran.</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -8190,10 +8210,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121124066</v>
+        <v>121124081</v>
       </c>
       <c r="B64" t="n">
-        <v>4769</v>
+        <v>5171</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8202,47 +8222,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100299</v>
+        <v>102204</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>693536</v>
+        <v>693426</v>
       </c>
       <c r="R64" t="n">
-        <v>6553680</v>
+        <v>6553560</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8274,7 +8290,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8284,7 +8300,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8293,7 +8309,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8309,12 +8324,12 @@
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>Stående död gran.</t>
+          <t>Klen låga.</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död gran.</t>
+          <t>Picea abies # Klen låga.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8332,7 +8347,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121124081</v>
+        <v>121124074</v>
       </c>
       <c r="B65" t="n">
         <v>5171</v>
@@ -8377,10 +8392,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>693426</v>
+        <v>693455</v>
       </c>
       <c r="R65" t="n">
-        <v>6553560</v>
+        <v>6553651</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8412,7 +8427,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8422,7 +8437,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8446,12 +8461,12 @@
       </c>
       <c r="AL65" t="inlineStr">
         <is>
-          <t>Klen låga.</t>
+          <t>Gren långt ner på gammal tall.</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Picea abies # Klen låga.</t>
+          <t>Picea abies # Gren långt ner på gammal tall.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8469,10 +8484,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121124074</v>
+        <v>121124056</v>
       </c>
       <c r="B66" t="n">
-        <v>5171</v>
+        <v>94870</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8481,43 +8496,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>102204</v>
+        <v>2180</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>693455</v>
+        <v>693482</v>
       </c>
       <c r="R66" t="n">
-        <v>6553651</v>
+        <v>6553750</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8549,7 +8559,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8559,7 +8569,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8570,26 +8580,6 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL66" t="inlineStr">
-        <is>
-          <t>Gren långt ner på gammal tall.</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Picea abies # Gren långt ner på gammal tall.</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8606,10 +8596,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121124056</v>
+        <v>121124071</v>
       </c>
       <c r="B67" t="n">
-        <v>94870</v>
+        <v>94620</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8622,21 +8612,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2180</v>
+        <v>2818</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8646,10 +8636,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>693482</v>
+        <v>693461</v>
       </c>
       <c r="R67" t="n">
-        <v>6553750</v>
+        <v>6553671</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8681,7 +8671,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8691,7 +8681,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8702,6 +8692,26 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL67" t="inlineStr">
+        <is>
+          <t>Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Picea abies # Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8718,10 +8728,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121124071</v>
+        <v>121124070</v>
       </c>
       <c r="B68" t="n">
-        <v>94620</v>
+        <v>94716</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8734,21 +8744,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8850,10 +8860,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121124070</v>
+        <v>121124073</v>
       </c>
       <c r="B69" t="n">
-        <v>94716</v>
+        <v>90678</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8866,21 +8876,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>210</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8890,10 +8900,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>693461</v>
+        <v>693439</v>
       </c>
       <c r="R69" t="n">
-        <v>6553671</v>
+        <v>6553651</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8925,7 +8935,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8935,7 +8945,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8946,26 +8956,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL69" t="inlineStr">
-        <is>
-          <t>Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Picea abies # Kraftig nedbruten granlåga på mark som eventuellt är översvämmad delar av året.</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8982,10 +8972,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121124073</v>
+        <v>121124047</v>
       </c>
       <c r="B70" t="n">
-        <v>90678</v>
+        <v>110235</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8998,21 +8988,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>219711</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9022,10 +9012,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>693439</v>
+        <v>693691</v>
       </c>
       <c r="R70" t="n">
-        <v>6553651</v>
+        <v>6553924</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9057,7 +9047,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9067,7 +9057,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9094,10 +9084,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121124047</v>
+        <v>121124080</v>
       </c>
       <c r="B71" t="n">
-        <v>110235</v>
+        <v>5172</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9110,34 +9100,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219711</v>
+        <v>100526</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>693691</v>
+        <v>693426</v>
       </c>
       <c r="R71" t="n">
-        <v>6553924</v>
+        <v>6553560</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9169,7 +9164,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9179,7 +9174,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9190,6 +9185,26 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL71" t="inlineStr">
+        <is>
+          <t>Klen låga.</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen låga.</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9206,10 +9221,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121124080</v>
+        <v>121124079</v>
       </c>
       <c r="B72" t="n">
-        <v>5172</v>
+        <v>5192</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9222,21 +9237,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9251,10 +9266,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>693426</v>
+        <v>693431</v>
       </c>
       <c r="R72" t="n">
-        <v>6553560</v>
+        <v>6553573</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9286,7 +9301,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9296,7 +9311,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9343,14 +9358,14 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121124079</v>
+        <v>121124052</v>
       </c>
       <c r="B73" t="n">
-        <v>5192</v>
+        <v>94716</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9359,39 +9374,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>105930</v>
+        <v>210</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>693431</v>
+        <v>693673</v>
       </c>
       <c r="R73" t="n">
-        <v>6553573</v>
+        <v>6553885</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9423,7 +9433,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9433,7 +9443,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9457,12 +9467,12 @@
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>Klen låga.</t>
+          <t>Kraftigt nedbruten granlåga.</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Picea abies # Klen låga.</t>
+          <t>Picea abies # Kraftigt nedbruten granlåga.</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9480,10 +9490,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121124052</v>
+        <v>121124051</v>
       </c>
       <c r="B74" t="n">
-        <v>94716</v>
+        <v>94620</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9496,21 +9506,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9612,14 +9622,14 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121124051</v>
+        <v>121224002</v>
       </c>
       <c r="B75" t="n">
-        <v>94620</v>
+        <v>5192</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9628,37 +9638,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2818</v>
+        <v>105930</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Breviksnäs, Srm</t>
+          <t>Sandkärr, Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>693673</v>
+        <v>693430</v>
       </c>
       <c r="R75" t="n">
-        <v>6553885</v>
+        <v>6553864</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9682,22 +9692,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9708,46 +9718,26 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL75" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten granlåga.</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Picea abies # Kraftigt nedbruten granlåga.</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Per Flodby, Nina Tadsen, Jennica Andersson, Mattias Bernhardsson, Nette Bygren, Roja Kirkeby</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121224002</v>
+        <v>121224119</v>
       </c>
       <c r="B76" t="n">
-        <v>5192</v>
+        <v>97059</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9760,37 +9750,41 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>105930</v>
+        <v>221945</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Sandkärr, Sandkärr, Srm</t>
+          <t>Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>693430</v>
+        <v>693407</v>
       </c>
       <c r="R76" t="n">
-        <v>6553864</v>
+        <v>6553843</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9819,7 +9813,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9829,7 +9823,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9844,19 +9838,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121224119</v>
+        <v>121224726</v>
       </c>
       <c r="B77" t="n">
         <v>97059</v>
@@ -9900,10 +9894,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>693407</v>
+        <v>693312</v>
       </c>
       <c r="R77" t="n">
-        <v>6553843</v>
+        <v>6553808</v>
       </c>
       <c r="S77" t="n">
         <v>13</v>
@@ -9935,7 +9929,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9945,7 +9939,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9972,10 +9966,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121224726</v>
+        <v>121221017</v>
       </c>
       <c r="B78" t="n">
-        <v>97059</v>
+        <v>57372</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9984,45 +9978,46 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sandkärr, Srm</t>
+          <t>Kolnäsviken, Kolnäsviken, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>693312</v>
+        <v>693644</v>
       </c>
       <c r="R78" t="n">
-        <v>6553808</v>
+        <v>6554031</v>
       </c>
       <c r="S78" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10051,7 +10046,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10061,7 +10056,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10076,22 +10071,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121221017</v>
+        <v>121222341</v>
       </c>
       <c r="B79" t="n">
-        <v>57372</v>
+        <v>8424</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10100,46 +10095,50 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kolnäsviken, Kolnäsviken, Srm</t>
+          <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>693644</v>
+        <v>693587</v>
       </c>
       <c r="R79" t="n">
-        <v>6554031</v>
+        <v>6553902</v>
       </c>
       <c r="S79" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10168,7 +10167,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10178,7 +10177,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10193,22 +10192,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121222341</v>
+        <v>121224447</v>
       </c>
       <c r="B80" t="n">
-        <v>8424</v>
+        <v>100371</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10221,46 +10220,41 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106554</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Breviksnäs, Srm</t>
+          <t>Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>693587</v>
+        <v>693195</v>
       </c>
       <c r="R80" t="n">
-        <v>6553902</v>
+        <v>6553768</v>
       </c>
       <c r="S80" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10289,7 +10283,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10299,7 +10293,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10326,10 +10320,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121224447</v>
+        <v>121231771</v>
       </c>
       <c r="B81" t="n">
-        <v>100371</v>
+        <v>4775</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10342,38 +10336,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sandkärr, Srm</t>
+          <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>693195</v>
+        <v>693494</v>
       </c>
       <c r="R81" t="n">
-        <v>6553768</v>
+        <v>6553917</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10405,7 +10395,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10415,7 +10405,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10426,26 +10416,46 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL81" t="inlineStr">
+        <is>
+          <t>Äldre grov gran</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grov gran</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121231771</v>
+        <v>121231789</v>
       </c>
       <c r="B82" t="n">
-        <v>4775</v>
+        <v>91125</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10458,21 +10468,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>102306</v>
+        <v>5420</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10482,10 +10492,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>693494</v>
+        <v>693670</v>
       </c>
       <c r="R82" t="n">
-        <v>6553917</v>
+        <v>6553974</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10517,7 +10527,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10527,7 +10537,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10541,22 +10551,22 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL82" t="inlineStr">
         <is>
-          <t>Äldre grov gran</t>
+          <t>Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre grov gran</t>
+          <t>Pinus sylvestris # Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10574,10 +10584,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121231789</v>
+        <v>121231774</v>
       </c>
       <c r="B83" t="n">
-        <v>91125</v>
+        <v>105171</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10586,38 +10596,47 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5420</v>
+        <v>340</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>693670</v>
+        <v>693495</v>
       </c>
       <c r="R83" t="n">
-        <v>6553974</v>
+        <v>6553900</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10649,7 +10668,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10659,7 +10678,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Två av skotten hade frökapslar.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10671,24 +10695,9 @@
       <c r="AG83" t="b">
         <v>0</v>
       </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL83" t="inlineStr">
-        <is>
-          <t>Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Vid basen av gammal tall på klippavsats. En fruktkropp hade fallit ned från avsatsen.</t>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>Sluttning med tallskog</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10706,10 +10715,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121231774</v>
+        <v>121231775</v>
       </c>
       <c r="B84" t="n">
-        <v>105171</v>
+        <v>8435</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10718,35 +10727,31 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>340</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10755,10 +10760,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>693495</v>
+        <v>693555</v>
       </c>
       <c r="R84" t="n">
-        <v>6553900</v>
+        <v>6553905</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10790,7 +10795,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10800,12 +10805,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Två av skotten hade frökapslar.</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10817,9 +10817,19 @@
       <c r="AG84" t="b">
         <v>0</v>
       </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>Sluttning med tallskog</t>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10837,10 +10847,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121231775</v>
+        <v>121231794</v>
       </c>
       <c r="B85" t="n">
-        <v>8435</v>
+        <v>94627</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10853,39 +10863,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>2818</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>693555</v>
+        <v>693674</v>
       </c>
       <c r="R85" t="n">
-        <v>6553905</v>
+        <v>6553897</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10917,7 +10922,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10927,7 +10932,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10941,17 +10946,22 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL85" t="inlineStr">
+        <is>
+          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10962,17 +10972,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121231794</v>
+        <v>121231795</v>
       </c>
       <c r="B86" t="n">
-        <v>94627</v>
+        <v>94723</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10985,24 +10995,33 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
@@ -11101,10 +11120,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121231795</v>
+        <v>121231773</v>
       </c>
       <c r="B87" t="n">
-        <v>94723</v>
+        <v>98105</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11113,25 +11132,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -11141,7 +11160,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -11150,10 +11169,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>693674</v>
+        <v>693495</v>
       </c>
       <c r="R87" t="n">
-        <v>6553897</v>
+        <v>6553900</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11185,7 +11204,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11195,7 +11214,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11207,24 +11226,9 @@
       <c r="AG87" t="b">
         <v>0</v>
       </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL87" t="inlineStr">
-        <is>
-          <t>Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Picea abies # Relativt klen granlåga där ena änden hade markkontakt och därför var mer nedbruten än resten av lågan.</t>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>Sluttning med tallskog</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11235,17 +11239,17 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121231773</v>
+        <v>121231792</v>
       </c>
       <c r="B88" t="n">
-        <v>98105</v>
+        <v>94627</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11254,47 +11258,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>2818</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>693495</v>
+        <v>693674</v>
       </c>
       <c r="R88" t="n">
-        <v>6553900</v>
+        <v>6553894</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11326,7 +11321,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11336,7 +11331,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11348,9 +11343,24 @@
       <c r="AG88" t="b">
         <v>0</v>
       </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>Sluttning med tallskog</t>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL88" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten granlåga</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Picea abies # Kraftigt nedbruten granlåga</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11361,17 +11371,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121231792</v>
+        <v>121231767</v>
       </c>
       <c r="B89" t="n">
-        <v>94627</v>
+        <v>94723</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11384,34 +11394,43 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>693674</v>
+        <v>693436</v>
       </c>
       <c r="R89" t="n">
-        <v>6553894</v>
+        <v>6553861</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11443,7 +11462,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11453,7 +11472,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11477,12 +11496,12 @@
       </c>
       <c r="AL89" t="inlineStr">
         <is>
-          <t>Kraftigt nedbruten granlåga</t>
+          <t>Kraftigt nedbruten grov granlåga</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftigt nedbruten granlåga</t>
+          <t>Picea abies # Kraftigt nedbruten grov granlåga</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11493,17 +11512,17 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121231767</v>
+        <v>121231762</v>
       </c>
       <c r="B90" t="n">
-        <v>94723</v>
+        <v>110242</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11516,43 +11535,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>210</v>
+        <v>219711</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>693436</v>
+        <v>693313</v>
       </c>
       <c r="R90" t="n">
-        <v>6553861</v>
+        <v>6553812</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11584,7 +11594,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11594,7 +11604,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11605,26 +11615,6 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL90" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten grov granlåga</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Picea abies # Kraftigt nedbruten grov granlåga</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -11641,10 +11631,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121231762</v>
+        <v>121231764</v>
       </c>
       <c r="B91" t="n">
-        <v>110242</v>
+        <v>5192</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11657,21 +11647,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219711</v>
+        <v>105930</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11681,10 +11671,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>693313</v>
+        <v>693261</v>
       </c>
       <c r="R91" t="n">
-        <v>6553812</v>
+        <v>6553742</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11716,7 +11706,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11726,7 +11716,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11737,6 +11727,26 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL91" t="inlineStr">
+        <is>
+          <t>Klen gran i område med många fallna granar</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen gran i område med många fallna granar</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -11753,10 +11763,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121231764</v>
+        <v>121231782</v>
       </c>
       <c r="B92" t="n">
-        <v>5192</v>
+        <v>57372</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11765,20 +11775,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -11787,16 +11797,21 @@
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>693261</v>
+        <v>693709</v>
       </c>
       <c r="R92" t="n">
-        <v>6553742</v>
+        <v>6553983</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11828,7 +11843,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11838,7 +11853,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Födosökshack vid basen av stående död tall.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11849,26 +11869,6 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL92" t="inlineStr">
-        <is>
-          <t>Klen gran i område med många fallna granar</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen gran i område med många fallna granar</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -11885,10 +11885,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121231782</v>
+        <v>121231765</v>
       </c>
       <c r="B93" t="n">
-        <v>57372</v>
+        <v>100371</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11897,43 +11897,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>693709</v>
+        <v>693309</v>
       </c>
       <c r="R93" t="n">
-        <v>6553983</v>
+        <v>6553789</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11965,7 +11960,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11975,12 +11970,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Födosökshack vid basen av stående död tall.</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12007,10 +11997,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121231765</v>
+        <v>121231785</v>
       </c>
       <c r="B94" t="n">
-        <v>100371</v>
+        <v>90740</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12019,25 +12009,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12047,10 +12037,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>693309</v>
+        <v>693675</v>
       </c>
       <c r="R94" t="n">
-        <v>6553789</v>
+        <v>6553972</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12082,7 +12072,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12092,7 +12082,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12103,6 +12093,26 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL94" t="inlineStr">
+        <is>
+          <t>Äldre tall</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Äldre tall</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -12119,10 +12129,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121231785</v>
+        <v>121231793</v>
       </c>
       <c r="B95" t="n">
-        <v>90740</v>
+        <v>94723</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12131,38 +12141,47 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5442</v>
+        <v>210</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>693675</v>
+        <v>693674</v>
       </c>
       <c r="R95" t="n">
-        <v>6553972</v>
+        <v>6553894</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12194,7 +12213,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12204,7 +12223,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12218,22 +12237,22 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL95" t="inlineStr">
         <is>
-          <t>Äldre tall</t>
+          <t>Kraftigt nedbruten granlåga</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Äldre tall</t>
+          <t>Picea abies # Kraftigt nedbruten granlåga</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12244,17 +12263,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121231793</v>
+        <v>121231781</v>
       </c>
       <c r="B96" t="n">
-        <v>94723</v>
+        <v>5192</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12267,31 +12286,27 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>210</v>
+        <v>105930</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -12300,10 +12315,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>693674</v>
+        <v>693639</v>
       </c>
       <c r="R96" t="n">
-        <v>6553894</v>
+        <v>6553969</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12335,7 +12350,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12345,7 +12360,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12367,14 +12382,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL96" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten granlåga</t>
-        </is>
-      </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftigt nedbruten granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12385,21 +12395,21 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby, Cecilia Gottfries</t>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121231781</v>
+        <v>121231766</v>
       </c>
       <c r="B97" t="n">
-        <v>5192</v>
+        <v>94627</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12408,39 +12418,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>105930</v>
+        <v>2818</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>693639</v>
+        <v>693436</v>
       </c>
       <c r="R97" t="n">
-        <v>6553969</v>
+        <v>6553861</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12472,7 +12477,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12482,7 +12487,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12504,9 +12509,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL97" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten grov granlåga</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Kraftigt nedbruten grov granlåga</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -12524,10 +12534,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121231766</v>
+        <v>121231786</v>
       </c>
       <c r="B98" t="n">
-        <v>94627</v>
+        <v>94113</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12540,34 +12550,38 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2818</v>
+        <v>2362</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>693436</v>
+        <v>693670</v>
       </c>
       <c r="R98" t="n">
-        <v>6553861</v>
+        <v>6553974</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12599,7 +12613,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12609,7 +12623,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12618,27 +12632,13 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL98" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten grov granlåga</t>
-        </is>
-      </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Picea abies # Kraftigt nedbruten grov granlåga</t>
+          <t>Vid basen av lodvägg</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -12656,10 +12656,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121231786</v>
+        <v>121231768</v>
       </c>
       <c r="B99" t="n">
-        <v>94113</v>
+        <v>94723</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12672,38 +12672,43 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2362</v>
+        <v>210</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blek stjärnmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Mnium stellare</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>693670</v>
+        <v>693478</v>
       </c>
       <c r="R99" t="n">
-        <v>6553974</v>
+        <v>6553857</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12735,7 +12740,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12745,7 +12750,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12754,13 +12759,27 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL99" t="inlineStr">
+        <is>
+          <t>Granlåga i blockig sluttning</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>Vid basen av lodvägg</t>
+          <t>Picea abies # Granlåga i blockig sluttning</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -12778,10 +12797,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121231768</v>
+        <v>121231788</v>
       </c>
       <c r="B100" t="n">
-        <v>94723</v>
+        <v>94606</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12794,43 +12813,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>210</v>
+        <v>2667</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>693478</v>
+        <v>693670</v>
       </c>
       <c r="R100" t="n">
-        <v>6553857</v>
+        <v>6553974</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12862,7 +12872,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12872,7 +12882,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12884,24 +12894,9 @@
       <c r="AG100" t="b">
         <v>0</v>
       </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL100" t="inlineStr">
-        <is>
-          <t>Granlåga i blockig sluttning</t>
-        </is>
-      </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga i blockig sluttning</t>
+          <t>Vid basen av lodvägg</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -12919,10 +12914,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121231788</v>
+        <v>121231787</v>
       </c>
       <c r="B101" t="n">
-        <v>94606</v>
+        <v>94400</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12935,21 +12930,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -13036,10 +13031,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121231787</v>
+        <v>121231776</v>
       </c>
       <c r="B102" t="n">
-        <v>94400</v>
+        <v>94627</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13052,21 +13047,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2779</v>
+        <v>2818</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -13076,10 +13071,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>693670</v>
+        <v>693581</v>
       </c>
       <c r="R102" t="n">
-        <v>6553974</v>
+        <v>6553897</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13111,7 +13106,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13121,7 +13116,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13132,11 +13127,6 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Vid basen av lodvägg</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -13153,50 +13143,59 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121231776</v>
+        <v>121330721</v>
       </c>
       <c r="B103" t="n">
-        <v>94627</v>
+        <v>98113</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2818</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Breviksnäs, Ornö, Srm</t>
+          <t>Breviksnäs, Ornö 2 (*knärot* /stjälk/), Srm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>693581</v>
+        <v>693430</v>
       </c>
       <c r="R103" t="n">
-        <v>6553897</v>
+        <v>6554092</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13221,24 +13220,24 @@
           <t>Ornö</t>
         </is>
       </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>AB-Han-0263</t>
+        </is>
+      </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Obskoord: 6554026/1647371/10 m (Avst fr FV-lokal: 49 m). // Ej räknad.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13253,71 +13252,70 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
-        </is>
-      </c>
-      <c r="AY103" t="inlineStr"/>
+          <t>Per Flodby, Emilia Blixt, Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121330721</v>
+        <v>121231778</v>
       </c>
       <c r="B104" t="n">
-        <v>98113</v>
+        <v>95699</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Breviksnäs, Ornö 2 (*knärot* /stjälk/), Srm</t>
+          <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>693430</v>
+        <v>693588</v>
       </c>
       <c r="R104" t="n">
-        <v>6554092</v>
+        <v>6553885</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13342,24 +13340,24 @@
           <t>Ornö</t>
         </is>
       </c>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t>AB-Han-0263</t>
-        </is>
-      </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Obskoord: 6554026/1647371/10 m (Avst fr FV-lokal: 49 m). // Ej räknad.</t>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13368,59 +13366,76 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL104" t="inlineStr">
+        <is>
+          <t>Tallåga i kärr</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallåga i kärr</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Per Flodby, Emilia Blixt, Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY104" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121231778</v>
+        <v>121231770</v>
       </c>
       <c r="B105" t="n">
-        <v>95699</v>
+        <v>95976</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2590</v>
+        <v>990</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -13434,10 +13449,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>693588</v>
+        <v>693478</v>
       </c>
       <c r="R105" t="n">
-        <v>6553885</v>
+        <v>6553857</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13469,7 +13484,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13479,7 +13494,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13494,22 +13509,22 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr">
         <is>
-          <t>Tallåga i kärr</t>
+          <t>Granlåga i blockig sluttning</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Tallåga i kärr</t>
+          <t>Picea abies # Granlåga i blockig sluttning</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -13524,143 +13539,6 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>121231770</v>
-      </c>
-      <c r="B106" t="n">
-        <v>95976</v>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E106" t="n">
-        <v>990</v>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Liten hornflikmossa</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Lophozia ascendens</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>(Warnst.) R.M.Schust.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="P106" t="inlineStr">
-        <is>
-          <t>Breviksnäs, Ornö, Srm</t>
-        </is>
-      </c>
-      <c r="Q106" t="n">
-        <v>693478</v>
-      </c>
-      <c r="R106" t="n">
-        <v>6553857</v>
-      </c>
-      <c r="S106" t="n">
-        <v>10</v>
-      </c>
-      <c r="T106" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>Haninge</t>
-        </is>
-      </c>
-      <c r="V106" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W106" t="inlineStr">
-        <is>
-          <t>Ornö</t>
-        </is>
-      </c>
-      <c r="Y106" t="inlineStr">
-        <is>
-          <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AA106" t="inlineStr">
-        <is>
-          <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AD106" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE106" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF106" t="inlineStr"/>
-      <c r="AG106" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL106" t="inlineStr">
-        <is>
-          <t>Granlåga i blockig sluttning</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga i blockig sluttning</t>
-        </is>
-      </c>
-      <c r="AT106" t="inlineStr"/>
-      <c r="AW106" t="inlineStr">
-        <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>Klas Magnusson, Emilia Blixt, Per Flodby</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY105"/>
+  <dimension ref="A1:AY106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13540,6 +13540,132 @@
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>124182917</v>
+      </c>
+      <c r="B106" t="n">
+        <v>91010</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>693537</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6553906</v>
+      </c>
+      <c r="S106" t="n">
+        <v>2</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Cecilia Gottfries</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Cecilia Gottfries</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY106"/>
+  <dimension ref="A1:AY110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13666,6 +13666,434 @@
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>126551299</v>
+      </c>
+      <c r="B107" t="n">
+        <v>102590</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>693270</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6553841</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>23:34</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>23:34</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>126551316</v>
+      </c>
+      <c r="B108" t="n">
+        <v>58516</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>693280</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6553820</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>23:11</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>23:11</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>126551318</v>
+      </c>
+      <c r="B109" t="n">
+        <v>95693</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>693344</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6553877</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>19:14</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>19:14</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>126551287</v>
+      </c>
+      <c r="B110" t="n">
+        <v>95487</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>693424</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6553895</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY110"/>
+  <dimension ref="A1:AY121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14094,6 +14094,1215 @@
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>126604714</v>
+      </c>
+      <c r="B111" t="n">
+        <v>79598</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>693492</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6553652</v>
+      </c>
+      <c r="S111" t="n">
+        <v>1</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>126610277</v>
+      </c>
+      <c r="B112" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>693557</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6553923</v>
+      </c>
+      <c r="S112" t="n">
+        <v>1</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>126609883</v>
+      </c>
+      <c r="B113" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>693570</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6553929</v>
+      </c>
+      <c r="S113" t="n">
+        <v>1</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>126609812</v>
+      </c>
+      <c r="B114" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>693550</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6553922</v>
+      </c>
+      <c r="S114" t="n">
+        <v>1</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>126603803</v>
+      </c>
+      <c r="B115" t="n">
+        <v>79598</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>693427</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6553558</v>
+      </c>
+      <c r="S115" t="n">
+        <v>36</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>126609998</v>
+      </c>
+      <c r="B116" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>693549</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6553923</v>
+      </c>
+      <c r="S116" t="n">
+        <v>1</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>126607356</v>
+      </c>
+      <c r="B117" t="n">
+        <v>97239</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Sandkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>693251</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6553764</v>
+      </c>
+      <c r="S117" t="n">
+        <v>16</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>126610157</v>
+      </c>
+      <c r="B118" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>693536</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6553895</v>
+      </c>
+      <c r="S118" t="n">
+        <v>1</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>126610206</v>
+      </c>
+      <c r="B119" t="n">
+        <v>91265</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>693534</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6553890</v>
+      </c>
+      <c r="S119" t="n">
+        <v>1</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>126610096</v>
+      </c>
+      <c r="B120" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>693536</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6553915</v>
+      </c>
+      <c r="S120" t="n">
+        <v>1</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>126607980</v>
+      </c>
+      <c r="B121" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Sandkärr, Sandkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>693317</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6553855</v>
+      </c>
+      <c r="S121" t="n">
+        <v>1</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -14758,52 +14758,52 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126607356</v>
+        <v>126610157</v>
       </c>
       <c r="B117" t="n">
-        <v>97239</v>
+        <v>98361</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Sandkärr, Srm</t>
+          <t>Breviksnäs, Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>693251</v>
+        <v>693536</v>
       </c>
       <c r="R117" t="n">
-        <v>6553764</v>
+        <v>6553895</v>
       </c>
       <c r="S117" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14842,7 +14842,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14857,64 +14857,64 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126610157</v>
+        <v>126607356</v>
       </c>
       <c r="B118" t="n">
-        <v>98361</v>
+        <v>97239</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Breviksnäs, Breviksnäs, Srm</t>
+          <t>Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>693536</v>
+        <v>693251</v>
       </c>
       <c r="R118" t="n">
-        <v>6553895</v>
+        <v>6553764</v>
       </c>
       <c r="S118" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -14953,7 +14953,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14968,12 +14968,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -13671,7 +13671,7 @@
         <v>126551299</v>
       </c>
       <c r="B107" t="n">
-        <v>102590</v>
+        <v>102665</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>126551318</v>
       </c>
       <c r="B109" t="n">
-        <v>95693</v>
+        <v>95768</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>126551287</v>
       </c>
       <c r="B110" t="n">
-        <v>95487</v>
+        <v>95562</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>126604714</v>
       </c>
       <c r="B111" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>126610277</v>
       </c>
       <c r="B112" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>126609883</v>
       </c>
       <c r="B113" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>126609812</v>
       </c>
       <c r="B114" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>126603803</v>
       </c>
       <c r="B115" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>126609998</v>
       </c>
       <c r="B116" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14758,52 +14758,52 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126607356</v>
+        <v>126610157</v>
       </c>
       <c r="B117" t="n">
-        <v>97239</v>
+        <v>98436</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Sandkärr, Srm</t>
+          <t>Breviksnäs, Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>693251</v>
+        <v>693536</v>
       </c>
       <c r="R117" t="n">
-        <v>6553764</v>
+        <v>6553895</v>
       </c>
       <c r="S117" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14842,7 +14842,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14857,64 +14857,64 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126610157</v>
+        <v>126607356</v>
       </c>
       <c r="B118" t="n">
-        <v>98361</v>
+        <v>97314</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Breviksnäs, Breviksnäs, Srm</t>
+          <t>Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>693536</v>
+        <v>693251</v>
       </c>
       <c r="R118" t="n">
-        <v>6553895</v>
+        <v>6553764</v>
       </c>
       <c r="S118" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -14953,7 +14953,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14968,12 +14968,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -14983,7 +14983,7 @@
         <v>126610206</v>
       </c>
       <c r="B119" t="n">
-        <v>91265</v>
+        <v>91339</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15090,7 +15090,7 @@
         <v>126610096</v>
       </c>
       <c r="B120" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>126753764</v>
       </c>
       <c r="B122" t="n">
-        <v>95964</v>
+        <v>96039</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>126753771</v>
       </c>
       <c r="B124" t="n">
-        <v>95714</v>
+        <v>95789</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>126753763</v>
       </c>
       <c r="B126" t="n">
-        <v>95200</v>
+        <v>95275</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>126753773</v>
       </c>
       <c r="B128" t="n">
-        <v>103429</v>
+        <v>103504</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>126753784</v>
       </c>
       <c r="B129" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>126753772</v>
       </c>
       <c r="B130" t="n">
-        <v>95714</v>
+        <v>95789</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -13671,7 +13671,7 @@
         <v>126551299</v>
       </c>
       <c r="B107" t="n">
-        <v>102665</v>
+        <v>102671</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>126551318</v>
       </c>
       <c r="B109" t="n">
-        <v>95768</v>
+        <v>95774</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>126551287</v>
       </c>
       <c r="B110" t="n">
-        <v>95562</v>
+        <v>95568</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>126604714</v>
       </c>
       <c r="B111" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>126610277</v>
       </c>
       <c r="B112" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>126609883</v>
       </c>
       <c r="B113" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>126609812</v>
       </c>
       <c r="B114" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>126603803</v>
       </c>
       <c r="B115" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>126609998</v>
       </c>
       <c r="B116" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>126610157</v>
       </c>
       <c r="B117" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>126607356</v>
       </c>
       <c r="B118" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>126610206</v>
       </c>
       <c r="B119" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15090,7 +15090,7 @@
         <v>126610096</v>
       </c>
       <c r="B120" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>126753764</v>
       </c>
       <c r="B122" t="n">
-        <v>96039</v>
+        <v>96045</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>126753771</v>
       </c>
       <c r="B124" t="n">
-        <v>95789</v>
+        <v>95795</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>126753763</v>
       </c>
       <c r="B126" t="n">
-        <v>95275</v>
+        <v>95281</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>126753773</v>
       </c>
       <c r="B128" t="n">
-        <v>103504</v>
+        <v>103510</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>126753784</v>
       </c>
       <c r="B129" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>126753772</v>
       </c>
       <c r="B130" t="n">
-        <v>95789</v>
+        <v>95795</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -15529,10 +15529,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126753771</v>
+        <v>126753786</v>
       </c>
       <c r="B124" t="n">
-        <v>95795</v>
+        <v>4772</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15540,34 +15540,39 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2818</v>
+        <v>100299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>693329</v>
+        <v>693484</v>
       </c>
       <c r="R124" t="n">
-        <v>6553838</v>
+        <v>6553659</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15599,7 +15604,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15609,7 +15614,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15620,6 +15625,26 @@
       </c>
       <c r="AG124" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL124" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
@@ -15636,10 +15661,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126753786</v>
+        <v>126753771</v>
       </c>
       <c r="B125" t="n">
-        <v>4772</v>
+        <v>95795</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15647,39 +15672,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100299</v>
+        <v>2818</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>693484</v>
+        <v>693329</v>
       </c>
       <c r="R125" t="n">
-        <v>6553659</v>
+        <v>6553838</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15711,7 +15731,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15721,7 +15741,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15732,26 +15752,6 @@
       </c>
       <c r="AG125" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL125" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -15308,7 +15308,7 @@
         <v>126753764</v>
       </c>
       <c r="B122" t="n">
-        <v>96045</v>
+        <v>96046</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15529,10 +15529,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126753786</v>
+        <v>126753771</v>
       </c>
       <c r="B124" t="n">
-        <v>4772</v>
+        <v>95796</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15540,39 +15540,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100299</v>
+        <v>2818</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>693484</v>
+        <v>693329</v>
       </c>
       <c r="R124" t="n">
-        <v>6553659</v>
+        <v>6553838</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15604,7 +15599,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15614,7 +15609,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15625,26 +15620,6 @@
       </c>
       <c r="AG124" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL124" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
@@ -15661,10 +15636,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126753771</v>
+        <v>126753786</v>
       </c>
       <c r="B125" t="n">
-        <v>95795</v>
+        <v>4772</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15672,34 +15647,39 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2818</v>
+        <v>100299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>693329</v>
+        <v>693484</v>
       </c>
       <c r="R125" t="n">
-        <v>6553838</v>
+        <v>6553659</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15731,7 +15711,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15741,7 +15721,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15752,6 +15732,26 @@
       </c>
       <c r="AG125" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL125" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
@@ -15771,7 +15771,7 @@
         <v>126753763</v>
       </c>
       <c r="B126" t="n">
-        <v>95281</v>
+        <v>95282</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>126753773</v>
       </c>
       <c r="B128" t="n">
-        <v>103510</v>
+        <v>103511</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>126753784</v>
       </c>
       <c r="B129" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>126753772</v>
       </c>
       <c r="B130" t="n">
-        <v>95795</v>
+        <v>95796</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -15308,7 +15308,7 @@
         <v>126753764</v>
       </c>
       <c r="B122" t="n">
-        <v>96046</v>
+        <v>96050</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>126753788</v>
       </c>
       <c r="B123" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>126753771</v>
       </c>
       <c r="B124" t="n">
-        <v>95796</v>
+        <v>95800</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>126753786</v>
       </c>
       <c r="B125" t="n">
-        <v>4772</v>
+        <v>4773</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>126753763</v>
       </c>
       <c r="B126" t="n">
-        <v>95282</v>
+        <v>95286</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>126753790</v>
       </c>
       <c r="B127" t="n">
-        <v>4772</v>
+        <v>4773</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>126753773</v>
       </c>
       <c r="B128" t="n">
-        <v>103511</v>
+        <v>103516</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>126753784</v>
       </c>
       <c r="B129" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>126753772</v>
       </c>
       <c r="B130" t="n">
-        <v>95796</v>
+        <v>95800</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>126753768</v>
       </c>
       <c r="B131" t="n">
-        <v>4772</v>
+        <v>4773</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY131"/>
+  <dimension ref="A1:AY136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16463,6 +16463,602 @@
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>128279306</v>
+      </c>
+      <c r="B132" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>693569</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6553921</v>
+      </c>
+      <c r="S132" t="n">
+        <v>2</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Ett 20-tal plantor varav 6 överblommade stjälkar.</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Cecilia Gottfries</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Cecilia Gottfries</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>128278597</v>
+      </c>
+      <c r="B133" t="n">
+        <v>92654</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>693472</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6553862</v>
+      </c>
+      <c r="S133" t="n">
+        <v>1</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>128280496</v>
+      </c>
+      <c r="B134" t="n">
+        <v>92287</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Sandkärr, Sandkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>693433</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6553885</v>
+      </c>
+      <c r="S134" t="n">
+        <v>2</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Cecilia Gottfries</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Cecilia Gottfries</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>128274696</v>
+      </c>
+      <c r="B135" t="n">
+        <v>58531</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>693430</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6553691</v>
+      </c>
+      <c r="S135" t="n">
+        <v>2</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Cecilia Gottfries</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Cecilia Gottfries</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>128280607</v>
+      </c>
+      <c r="B136" t="n">
+        <v>92287</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Sandkärr, Sandkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>693421</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6553893</v>
+      </c>
+      <c r="S136" t="n">
+        <v>3</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Cecilia Gottfries</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Cecilia Gottfries</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY136"/>
+  <dimension ref="A1:AY150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17059,6 +17059,1678 @@
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>128365718</v>
+      </c>
+      <c r="B137" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>693618</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6553945</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL137" t="inlineStr">
+        <is>
+          <t>Äldre grovbarkig gran.</t>
+        </is>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grovbarkig gran.</t>
+        </is>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Ulrika Karlsson, Cecilia Gottfries, Sara Järver, Roja Kirkeby, Birgitta Tulin</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>128365728</v>
+      </c>
+      <c r="B138" t="n">
+        <v>92290</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>693461</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6553891</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Ulrika Karlsson, Cecilia Gottfries, Sara Järver, Roja Kirkeby, Birgitta Tulin</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>128365726</v>
+      </c>
+      <c r="B139" t="n">
+        <v>92290</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>693442</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6553883</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Ulrika Karlsson, Cecilia Gottfries, Sara Järver, Roja Kirkeby, Birgitta Tulin</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>128365747</v>
+      </c>
+      <c r="B140" t="n">
+        <v>98473</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>693476</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6553676</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Cirka 10 stänglar med frökapslar och cirka 100 bladrosetter.</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Ulrika Karlsson, Cecilia Gottfries, Sara Järver, Roja Kirkeby, Birgitta Tulin</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>128365740</v>
+      </c>
+      <c r="B141" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>693549</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6553711</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL141" t="inlineStr">
+        <is>
+          <t>Klen stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen stående död gran.</t>
+        </is>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Ulrika Karlsson, Cecilia Gottfries, Sara Järver, Roja Kirkeby, Birgitta Tulin</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>128365741</v>
+      </c>
+      <c r="B142" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>693549</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6553711</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL142" t="inlineStr">
+        <is>
+          <t>Klen stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen stående död gran.</t>
+        </is>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Ulrika Karlsson, Cecilia Gottfries, Sara Järver, Roja Kirkeby, Birgitta Tulin</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>128365742</v>
+      </c>
+      <c r="B143" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>693549</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6553711</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL143" t="inlineStr">
+        <is>
+          <t>Klen stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen stående död gran.</t>
+        </is>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Ulrika Karlsson, Cecilia Gottfries, Sara Järver, Roja Kirkeby, Birgitta Tulin</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>128365743</v>
+      </c>
+      <c r="B144" t="n">
+        <v>96075</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>693486</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6553746</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Ulrika Karlsson, Cecilia Gottfries, Sara Järver, Roja Kirkeby, Birgitta Tulin</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>128365727</v>
+      </c>
+      <c r="B145" t="n">
+        <v>92679</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>693461</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6553891</v>
+      </c>
+      <c r="S145" t="n">
+        <v>10</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF145" t="inlineStr"/>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Ulrika Karlsson, Cecilia Gottfries, Sara Järver, Roja Kirkeby, Birgitta Tulin</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>128365753</v>
+      </c>
+      <c r="B146" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>693407</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6553551</v>
+      </c>
+      <c r="S146" t="n">
+        <v>10</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Ulrika Karlsson, Cecilia Gottfries, Sara Järver, Roja Kirkeby, Birgitta Tulin</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>128365729</v>
+      </c>
+      <c r="B147" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>693679</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6554041</v>
+      </c>
+      <c r="S147" t="n">
+        <v>10</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL147" t="inlineStr">
+        <is>
+          <t>Nedfallen tallgren.</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Nedfallen tallgren.</t>
+        </is>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Ulrika Karlsson, Cecilia Gottfries, Sara Järver, Roja Kirkeby, Birgitta Tulin</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>128365739</v>
+      </c>
+      <c r="B148" t="n">
+        <v>92052</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>693631</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6553794</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL148" t="inlineStr">
+        <is>
+          <t>På rötterna till stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>Picea abies # På rötterna till stående död gran.</t>
+        </is>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Ulrika Karlsson, Cecilia Gottfries, Sara Järver, Roja Kirkeby, Birgitta Tulin</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>128365744</v>
+      </c>
+      <c r="B149" t="n">
+        <v>92659</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>693556</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6553690</v>
+      </c>
+      <c r="S149" t="n">
+        <v>10</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Ulrika Karlsson, Cecilia Gottfries, Sara Järver, Roja Kirkeby, Birgitta Tulin</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>128365722</v>
+      </c>
+      <c r="B150" t="n">
+        <v>92657</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>693388</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6553877</v>
+      </c>
+      <c r="S150" t="n">
+        <v>10</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Ulrika Karlsson, Cecilia Gottfries, Sara Järver, Roja Kirkeby, Birgitta Tulin</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -16468,7 +16468,7 @@
         <v>128279306</v>
       </c>
       <c r="B132" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>128278597</v>
       </c>
       <c r="B133" t="n">
-        <v>92654</v>
+        <v>92662</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>128280496</v>
       </c>
       <c r="B134" t="n">
-        <v>92287</v>
+        <v>92295</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>128274696</v>
       </c>
       <c r="B135" t="n">
-        <v>58531</v>
+        <v>58532</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>128280607</v>
       </c>
       <c r="B136" t="n">
-        <v>92287</v>
+        <v>92295</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>128365728</v>
       </c>
       <c r="B138" t="n">
-        <v>92290</v>
+        <v>92295</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>128365726</v>
       </c>
       <c r="B139" t="n">
-        <v>92290</v>
+        <v>92295</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>128365747</v>
       </c>
       <c r="B140" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17922,7 +17922,7 @@
         <v>128365743</v>
       </c>
       <c r="B144" t="n">
-        <v>96075</v>
+        <v>96080</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18026,10 +18026,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128365727</v>
+        <v>128365729</v>
       </c>
       <c r="B145" t="n">
-        <v>92679</v>
+        <v>8450</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18037,37 +18037,39 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5964</v>
+        <v>106545</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>693461</v>
+        <v>693679</v>
       </c>
       <c r="R145" t="n">
-        <v>6553891</v>
+        <v>6554041</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -18099,7 +18101,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -18109,7 +18111,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18118,9 +18120,28 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL145" t="inlineStr">
+        <is>
+          <t>Nedfallen tallgren.</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Nedfallen tallgren.</t>
+        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
@@ -18264,10 +18285,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128365729</v>
+        <v>128365739</v>
       </c>
       <c r="B147" t="n">
-        <v>8450</v>
+        <v>92057</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18275,39 +18296,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>106545</v>
+        <v>3298</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>693679</v>
+        <v>693631</v>
       </c>
       <c r="R147" t="n">
-        <v>6554041</v>
+        <v>6553794</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -18339,7 +18355,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -18349,7 +18365,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18363,22 +18379,22 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL147" t="inlineStr">
         <is>
-          <t>Nedfallen tallgren.</t>
+          <t>På rötterna till stående död gran.</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Nedfallen tallgren.</t>
+          <t>Picea abies # På rötterna till stående död gran.</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
@@ -18396,10 +18412,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128365739</v>
+        <v>128365727</v>
       </c>
       <c r="B148" t="n">
-        <v>92052</v>
+        <v>92684</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18407,34 +18423,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>3298</v>
+        <v>5964</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>693631</v>
+        <v>693461</v>
       </c>
       <c r="R148" t="n">
-        <v>6553794</v>
+        <v>6553891</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -18466,7 +18485,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -18476,7 +18495,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18485,28 +18504,9 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ148" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK148" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL148" t="inlineStr">
-        <is>
-          <t>På rötterna till stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO148" t="inlineStr">
-        <is>
-          <t>Picea abies # På rötterna till stående död gran.</t>
-        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
@@ -18526,7 +18526,7 @@
         <v>128365744</v>
       </c>
       <c r="B149" t="n">
-        <v>92659</v>
+        <v>92664</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>128365722</v>
       </c>
       <c r="B150" t="n">
-        <v>92657</v>
+        <v>92662</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -18026,10 +18026,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128365729</v>
+        <v>128365739</v>
       </c>
       <c r="B145" t="n">
-        <v>8450</v>
+        <v>92057</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18037,39 +18037,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>106545</v>
+        <v>3298</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>693679</v>
+        <v>693631</v>
       </c>
       <c r="R145" t="n">
-        <v>6554041</v>
+        <v>6553794</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -18101,7 +18096,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -18111,7 +18106,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18125,22 +18120,22 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL145" t="inlineStr">
         <is>
-          <t>Nedfallen tallgren.</t>
+          <t>På rötterna till stående död gran.</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Nedfallen tallgren.</t>
+          <t>Picea abies # På rötterna till stående död gran.</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -18158,10 +18153,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128365753</v>
+        <v>128365727</v>
       </c>
       <c r="B146" t="n">
-        <v>8450</v>
+        <v>92684</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18169,39 +18164,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>106545</v>
+        <v>5964</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>693407</v>
+        <v>693461</v>
       </c>
       <c r="R146" t="n">
-        <v>6553551</v>
+        <v>6553891</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -18233,7 +18226,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -18243,7 +18236,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18252,23 +18245,9 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ146" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK146" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO146" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
@@ -18285,10 +18264,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128365739</v>
+        <v>128365729</v>
       </c>
       <c r="B147" t="n">
-        <v>92057</v>
+        <v>8450</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18296,34 +18275,39 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3298</v>
+        <v>106545</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>693631</v>
+        <v>693679</v>
       </c>
       <c r="R147" t="n">
-        <v>6553794</v>
+        <v>6554041</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -18355,7 +18339,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -18365,7 +18349,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18379,22 +18363,22 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL147" t="inlineStr">
         <is>
-          <t>På rötterna till stående död gran.</t>
+          <t>Nedfallen tallgren.</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>Picea abies # På rötterna till stående död gran.</t>
+          <t>Pinus sylvestris # Nedfallen tallgren.</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
@@ -18412,10 +18396,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128365727</v>
+        <v>128365753</v>
       </c>
       <c r="B148" t="n">
-        <v>92684</v>
+        <v>8450</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18423,37 +18407,39 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>5964</v>
+        <v>106545</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>693461</v>
+        <v>693407</v>
       </c>
       <c r="R148" t="n">
-        <v>6553891</v>
+        <v>6553551</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -18485,7 +18471,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -18495,7 +18481,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18504,9 +18490,23 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY150"/>
+  <dimension ref="A1:AY152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16468,7 +16468,7 @@
         <v>128279306</v>
       </c>
       <c r="B132" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>128278597</v>
       </c>
       <c r="B133" t="n">
-        <v>92662</v>
+        <v>92754</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>128280496</v>
       </c>
       <c r="B134" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>128274696</v>
       </c>
       <c r="B135" t="n">
-        <v>58532</v>
+        <v>58544</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>128280607</v>
       </c>
       <c r="B136" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>128365728</v>
       </c>
       <c r="B138" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>128365726</v>
       </c>
       <c r="B139" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>128365747</v>
       </c>
       <c r="B140" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17922,7 +17922,7 @@
         <v>128365743</v>
       </c>
       <c r="B144" t="n">
-        <v>96080</v>
+        <v>96173</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>128365739</v>
       </c>
       <c r="B145" t="n">
-        <v>92057</v>
+        <v>92149</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>128365727</v>
       </c>
       <c r="B146" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18526,7 +18526,7 @@
         <v>128365744</v>
       </c>
       <c r="B149" t="n">
-        <v>92664</v>
+        <v>92756</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>128365722</v>
       </c>
       <c r="B150" t="n">
-        <v>92662</v>
+        <v>92754</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18730,6 +18730,208 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>128538845</v>
+      </c>
+      <c r="B151" t="n">
+        <v>91871</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Breviksnäs Udden, Srm</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>693350</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6553870</v>
+      </c>
+      <c r="S151" t="n">
+        <v>10</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF151" t="inlineStr"/>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Roja Kirkeby</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Roja Kirkeby</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>128539518</v>
+      </c>
+      <c r="B152" t="n">
+        <v>91572</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>3277</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Luddfingersvamp</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Alloclavaria purpurea</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Breviksnäs Udden, Srm</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>693336</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6553883</v>
+      </c>
+      <c r="S152" t="n">
+        <v>10</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF152" t="inlineStr"/>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Roja Kirkeby</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Roja Kirkeby</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -17523,10 +17523,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128365740</v>
+        <v>128365741</v>
       </c>
       <c r="B141" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17534,21 +17534,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -17655,10 +17655,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128365741</v>
+        <v>128365740</v>
       </c>
       <c r="B142" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17666,21 +17666,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -18026,10 +18026,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128365739</v>
+        <v>128365753</v>
       </c>
       <c r="B145" t="n">
-        <v>92149</v>
+        <v>8450</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18037,34 +18037,39 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3298</v>
+        <v>106545</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>693631</v>
+        <v>693407</v>
       </c>
       <c r="R145" t="n">
-        <v>6553794</v>
+        <v>6553551</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -18096,7 +18101,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -18106,7 +18111,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18120,22 +18125,17 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL145" t="inlineStr">
-        <is>
-          <t>På rötterna till stående död gran.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>Picea abies # På rötterna till stående död gran.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -18153,10 +18153,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128365727</v>
+        <v>128365739</v>
       </c>
       <c r="B146" t="n">
-        <v>92776</v>
+        <v>92149</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18164,37 +18164,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5964</v>
+        <v>3298</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>693461</v>
+        <v>693631</v>
       </c>
       <c r="R146" t="n">
-        <v>6553891</v>
+        <v>6553794</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -18226,7 +18223,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -18236,7 +18233,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18245,9 +18242,28 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL146" t="inlineStr">
+        <is>
+          <t>På rötterna till stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>Picea abies # På rötterna till stående död gran.</t>
+        </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
@@ -18264,10 +18280,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128365729</v>
+        <v>128365727</v>
       </c>
       <c r="B147" t="n">
-        <v>8450</v>
+        <v>92776</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18275,39 +18291,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>106545</v>
+        <v>5964</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>693679</v>
+        <v>693461</v>
       </c>
       <c r="R147" t="n">
-        <v>6554041</v>
+        <v>6553891</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -18339,7 +18353,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -18349,7 +18363,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18358,28 +18372,9 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL147" t="inlineStr">
-        <is>
-          <t>Nedfallen tallgren.</t>
-        </is>
-      </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Nedfallen tallgren.</t>
-        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
@@ -18396,7 +18391,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128365753</v>
+        <v>128365729</v>
       </c>
       <c r="B148" t="n">
         <v>8450</v>
@@ -18436,10 +18431,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>693407</v>
+        <v>693679</v>
       </c>
       <c r="R148" t="n">
-        <v>6553551</v>
+        <v>6554041</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -18471,7 +18466,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -18481,7 +18476,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18503,9 +18498,14 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
+      <c r="AL148" t="inlineStr">
+        <is>
+          <t>Nedfallen tallgren.</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Pinus sylvestris # Nedfallen tallgren.</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr"/>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -17523,10 +17523,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128365741</v>
+        <v>128365740</v>
       </c>
       <c r="B141" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17534,21 +17534,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -17655,10 +17655,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128365740</v>
+        <v>128365741</v>
       </c>
       <c r="B142" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17666,21 +17666,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -18026,7 +18026,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128365753</v>
+        <v>128365729</v>
       </c>
       <c r="B145" t="n">
         <v>8450</v>
@@ -18066,10 +18066,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>693407</v>
+        <v>693679</v>
       </c>
       <c r="R145" t="n">
-        <v>6553551</v>
+        <v>6554041</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -18101,7 +18101,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -18111,7 +18111,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18133,9 +18133,14 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
+      <c r="AL145" t="inlineStr">
+        <is>
+          <t>Nedfallen tallgren.</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Pinus sylvestris # Nedfallen tallgren.</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -18153,10 +18158,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128365739</v>
+        <v>128365753</v>
       </c>
       <c r="B146" t="n">
-        <v>92149</v>
+        <v>8450</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18164,34 +18169,39 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>3298</v>
+        <v>106545</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>693631</v>
+        <v>693407</v>
       </c>
       <c r="R146" t="n">
-        <v>6553794</v>
+        <v>6553551</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -18223,7 +18233,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -18233,7 +18243,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18247,22 +18257,17 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL146" t="inlineStr">
-        <is>
-          <t>På rötterna till stående död gran.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>Picea abies # På rötterna till stående död gran.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
@@ -18280,10 +18285,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128365727</v>
+        <v>128365739</v>
       </c>
       <c r="B147" t="n">
-        <v>92776</v>
+        <v>92149</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18291,37 +18296,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5964</v>
+        <v>3298</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>693461</v>
+        <v>693631</v>
       </c>
       <c r="R147" t="n">
-        <v>6553891</v>
+        <v>6553794</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -18353,7 +18355,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -18363,7 +18365,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18372,9 +18374,28 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL147" t="inlineStr">
+        <is>
+          <t>På rötterna till stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>Picea abies # På rötterna till stående död gran.</t>
+        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
@@ -18391,10 +18412,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128365729</v>
+        <v>128365727</v>
       </c>
       <c r="B148" t="n">
-        <v>8450</v>
+        <v>92776</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18402,39 +18423,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>106545</v>
+        <v>5964</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>693679</v>
+        <v>693461</v>
       </c>
       <c r="R148" t="n">
-        <v>6554041</v>
+        <v>6553891</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -18466,7 +18485,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -18476,7 +18495,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18485,28 +18504,9 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ148" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK148" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL148" t="inlineStr">
-        <is>
-          <t>Nedfallen tallgren.</t>
-        </is>
-      </c>
-      <c r="AO148" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Nedfallen tallgren.</t>
-        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
@@ -18736,7 +18736,7 @@
         <v>128538845</v>
       </c>
       <c r="B151" t="n">
-        <v>91871</v>
+        <v>91877</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>128539518</v>
       </c>
       <c r="B152" t="n">
-        <v>91572</v>
+        <v>91578</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -16468,7 +16468,7 @@
         <v>128279306</v>
       </c>
       <c r="B132" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>128278597</v>
       </c>
       <c r="B133" t="n">
-        <v>92754</v>
+        <v>92766</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>128280496</v>
       </c>
       <c r="B134" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>128274696</v>
       </c>
       <c r="B135" t="n">
-        <v>58544</v>
+        <v>58548</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>128280607</v>
       </c>
       <c r="B136" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>128365728</v>
       </c>
       <c r="B138" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>128365726</v>
       </c>
       <c r="B139" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>128365747</v>
       </c>
       <c r="B140" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17922,7 +17922,7 @@
         <v>128365743</v>
       </c>
       <c r="B144" t="n">
-        <v>96173</v>
+        <v>96185</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18026,10 +18026,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128365729</v>
+        <v>128365739</v>
       </c>
       <c r="B145" t="n">
-        <v>8450</v>
+        <v>92161</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18037,39 +18037,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>106545</v>
+        <v>3298</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>693679</v>
+        <v>693631</v>
       </c>
       <c r="R145" t="n">
-        <v>6554041</v>
+        <v>6553794</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -18101,7 +18096,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -18111,7 +18106,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18125,22 +18120,22 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL145" t="inlineStr">
         <is>
-          <t>Nedfallen tallgren.</t>
+          <t>På rötterna till stående död gran.</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Nedfallen tallgren.</t>
+          <t>Picea abies # På rötterna till stående död gran.</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -18158,10 +18153,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128365753</v>
+        <v>128365727</v>
       </c>
       <c r="B146" t="n">
-        <v>8450</v>
+        <v>92788</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18169,39 +18164,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>106545</v>
+        <v>5964</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>693407</v>
+        <v>693461</v>
       </c>
       <c r="R146" t="n">
-        <v>6553551</v>
+        <v>6553891</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -18233,7 +18226,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -18243,7 +18236,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18252,23 +18245,9 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ146" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK146" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO146" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
@@ -18285,10 +18264,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128365739</v>
+        <v>128365729</v>
       </c>
       <c r="B147" t="n">
-        <v>92149</v>
+        <v>8450</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18296,34 +18275,39 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3298</v>
+        <v>106545</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>693631</v>
+        <v>693679</v>
       </c>
       <c r="R147" t="n">
-        <v>6553794</v>
+        <v>6554041</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -18355,7 +18339,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -18365,7 +18349,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18379,22 +18363,22 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL147" t="inlineStr">
         <is>
-          <t>På rötterna till stående död gran.</t>
+          <t>Nedfallen tallgren.</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>Picea abies # På rötterna till stående död gran.</t>
+          <t>Pinus sylvestris # Nedfallen tallgren.</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
@@ -18412,10 +18396,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128365727</v>
+        <v>128365753</v>
       </c>
       <c r="B148" t="n">
-        <v>92776</v>
+        <v>8450</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18423,37 +18407,39 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>5964</v>
+        <v>106545</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>693461</v>
+        <v>693407</v>
       </c>
       <c r="R148" t="n">
-        <v>6553891</v>
+        <v>6553551</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -18485,7 +18471,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -18495,7 +18481,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18504,9 +18490,23 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
@@ -18526,7 +18526,7 @@
         <v>128365744</v>
       </c>
       <c r="B149" t="n">
-        <v>92756</v>
+        <v>92768</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>128365722</v>
       </c>
       <c r="B150" t="n">
-        <v>92754</v>
+        <v>92766</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>128538845</v>
       </c>
       <c r="B151" t="n">
-        <v>91877</v>
+        <v>91883</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>128539518</v>
       </c>
       <c r="B152" t="n">
-        <v>91578</v>
+        <v>91584</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -16468,7 +16468,7 @@
         <v>128279306</v>
       </c>
       <c r="B132" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>128278597</v>
       </c>
       <c r="B133" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>128280496</v>
       </c>
       <c r="B134" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>128280607</v>
       </c>
       <c r="B136" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>128365728</v>
       </c>
       <c r="B138" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>128365726</v>
       </c>
       <c r="B139" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>128365747</v>
       </c>
       <c r="B140" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17922,7 +17922,7 @@
         <v>128365743</v>
       </c>
       <c r="B144" t="n">
-        <v>96185</v>
+        <v>96187</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18026,10 +18026,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128365739</v>
+        <v>128365727</v>
       </c>
       <c r="B145" t="n">
-        <v>92161</v>
+        <v>92790</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18037,34 +18037,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3298</v>
+        <v>5964</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>693631</v>
+        <v>693461</v>
       </c>
       <c r="R145" t="n">
-        <v>6553794</v>
+        <v>6553891</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -18096,7 +18099,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -18106,7 +18109,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18115,28 +18118,9 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL145" t="inlineStr">
-        <is>
-          <t>På rötterna till stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO145" t="inlineStr">
-        <is>
-          <t>Picea abies # På rötterna till stående död gran.</t>
-        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
@@ -18153,10 +18137,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128365727</v>
+        <v>128365739</v>
       </c>
       <c r="B146" t="n">
-        <v>92788</v>
+        <v>92163</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18164,37 +18148,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5964</v>
+        <v>3298</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>693461</v>
+        <v>693631</v>
       </c>
       <c r="R146" t="n">
-        <v>6553891</v>
+        <v>6553794</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -18226,7 +18207,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -18236,7 +18217,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18245,9 +18226,28 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL146" t="inlineStr">
+        <is>
+          <t>På rötterna till stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>Picea abies # På rötterna till stående död gran.</t>
+        </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
@@ -18526,7 +18526,7 @@
         <v>128365744</v>
       </c>
       <c r="B149" t="n">
-        <v>92768</v>
+        <v>92770</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>128365722</v>
       </c>
       <c r="B150" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>128538845</v>
       </c>
       <c r="B151" t="n">
-        <v>91883</v>
+        <v>91885</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>128539518</v>
       </c>
       <c r="B152" t="n">
-        <v>91584</v>
+        <v>91586</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -16468,7 +16468,7 @@
         <v>128279306</v>
       </c>
       <c r="B132" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>128365747</v>
       </c>
       <c r="B140" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -18026,10 +18026,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128365727</v>
+        <v>128365739</v>
       </c>
       <c r="B145" t="n">
-        <v>92790</v>
+        <v>92163</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18037,37 +18037,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5964</v>
+        <v>3298</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>693461</v>
+        <v>693631</v>
       </c>
       <c r="R145" t="n">
-        <v>6553891</v>
+        <v>6553794</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -18099,7 +18096,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -18109,7 +18106,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18118,9 +18115,28 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL145" t="inlineStr">
+        <is>
+          <t>På rötterna till stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>Picea abies # På rötterna till stående död gran.</t>
+        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
@@ -18137,10 +18153,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128365739</v>
+        <v>128365727</v>
       </c>
       <c r="B146" t="n">
-        <v>92163</v>
+        <v>92790</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18148,34 +18164,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>3298</v>
+        <v>5964</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>693631</v>
+        <v>693461</v>
       </c>
       <c r="R146" t="n">
-        <v>6553794</v>
+        <v>6553891</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -18207,7 +18226,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -18217,7 +18236,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18226,28 +18245,9 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ146" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK146" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL146" t="inlineStr">
-        <is>
-          <t>På rötterna till stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO146" t="inlineStr">
-        <is>
-          <t>Picea abies # På rötterna till stående död gran.</t>
-        </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -18026,10 +18026,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128365739</v>
+        <v>128365727</v>
       </c>
       <c r="B145" t="n">
-        <v>92163</v>
+        <v>92790</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18037,34 +18037,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3298</v>
+        <v>5964</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>693631</v>
+        <v>693461</v>
       </c>
       <c r="R145" t="n">
-        <v>6553794</v>
+        <v>6553891</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -18096,7 +18099,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -18106,7 +18109,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18115,28 +18118,9 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL145" t="inlineStr">
-        <is>
-          <t>På rötterna till stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO145" t="inlineStr">
-        <is>
-          <t>Picea abies # På rötterna till stående död gran.</t>
-        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
@@ -18153,10 +18137,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128365727</v>
+        <v>128365729</v>
       </c>
       <c r="B146" t="n">
-        <v>92790</v>
+        <v>8450</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18164,37 +18148,39 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5964</v>
+        <v>106545</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>693461</v>
+        <v>693679</v>
       </c>
       <c r="R146" t="n">
-        <v>6553891</v>
+        <v>6554041</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -18226,7 +18212,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -18236,7 +18222,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18245,9 +18231,28 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL146" t="inlineStr">
+        <is>
+          <t>Nedfallen tallgren.</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Nedfallen tallgren.</t>
+        </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
@@ -18264,7 +18269,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128365729</v>
+        <v>128365753</v>
       </c>
       <c r="B147" t="n">
         <v>8450</v>
@@ -18304,10 +18309,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>693679</v>
+        <v>693407</v>
       </c>
       <c r="R147" t="n">
-        <v>6554041</v>
+        <v>6553551</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -18339,7 +18344,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -18349,7 +18354,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18371,14 +18376,9 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
-      <c r="AL147" t="inlineStr">
-        <is>
-          <t>Nedfallen tallgren.</t>
-        </is>
-      </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Nedfallen tallgren.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
@@ -18396,10 +18396,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128365753</v>
+        <v>128365739</v>
       </c>
       <c r="B148" t="n">
-        <v>8450</v>
+        <v>92163</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18407,39 +18407,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>106545</v>
+        <v>3298</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>693407</v>
+        <v>693631</v>
       </c>
       <c r="R148" t="n">
-        <v>6553551</v>
+        <v>6553794</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -18471,7 +18466,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -18481,7 +18476,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18495,17 +18490,22 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL148" t="inlineStr">
+        <is>
+          <t>På rötterna till stående död gran.</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies # På rötterna till stående död gran.</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr"/>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -16468,7 +16468,7 @@
         <v>128279306</v>
       </c>
       <c r="B132" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>128278597</v>
       </c>
       <c r="B133" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>128280496</v>
       </c>
       <c r="B134" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>128280607</v>
       </c>
       <c r="B136" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>128365728</v>
       </c>
       <c r="B138" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>128365726</v>
       </c>
       <c r="B139" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>128365747</v>
       </c>
       <c r="B140" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17523,10 +17523,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128365740</v>
+        <v>128365741</v>
       </c>
       <c r="B141" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17534,21 +17534,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -17655,10 +17655,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128365741</v>
+        <v>128365740</v>
       </c>
       <c r="B142" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17666,21 +17666,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -17922,7 +17922,7 @@
         <v>128365743</v>
       </c>
       <c r="B144" t="n">
-        <v>96187</v>
+        <v>96188</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>128365727</v>
       </c>
       <c r="B145" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18137,10 +18137,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128365729</v>
+        <v>128365739</v>
       </c>
       <c r="B146" t="n">
-        <v>8450</v>
+        <v>92164</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18148,39 +18148,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>106545</v>
+        <v>3298</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>693679</v>
+        <v>693631</v>
       </c>
       <c r="R146" t="n">
-        <v>6554041</v>
+        <v>6553794</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -18212,7 +18207,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -18222,7 +18217,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18236,22 +18231,22 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL146" t="inlineStr">
         <is>
-          <t>Nedfallen tallgren.</t>
+          <t>På rötterna till stående död gran.</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Nedfallen tallgren.</t>
+          <t>Picea abies # På rötterna till stående död gran.</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
@@ -18269,7 +18264,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128365753</v>
+        <v>128365729</v>
       </c>
       <c r="B147" t="n">
         <v>8450</v>
@@ -18309,10 +18304,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>693407</v>
+        <v>693679</v>
       </c>
       <c r="R147" t="n">
-        <v>6553551</v>
+        <v>6554041</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -18344,7 +18339,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -18354,7 +18349,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18376,9 +18371,14 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
+      <c r="AL147" t="inlineStr">
+        <is>
+          <t>Nedfallen tallgren.</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Pinus sylvestris # Nedfallen tallgren.</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
@@ -18396,10 +18396,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128365739</v>
+        <v>128365753</v>
       </c>
       <c r="B148" t="n">
-        <v>92163</v>
+        <v>8450</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18407,34 +18407,39 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>3298</v>
+        <v>106545</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>693631</v>
+        <v>693407</v>
       </c>
       <c r="R148" t="n">
-        <v>6553794</v>
+        <v>6553551</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -18466,7 +18471,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -18476,7 +18481,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18490,22 +18495,17 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL148" t="inlineStr">
-        <is>
-          <t>På rötterna till stående död gran.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>Picea abies # På rötterna till stående död gran.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr"/>
@@ -18526,7 +18526,7 @@
         <v>128365744</v>
       </c>
       <c r="B149" t="n">
-        <v>92770</v>
+        <v>92771</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>128365722</v>
       </c>
       <c r="B150" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>128538845</v>
       </c>
       <c r="B151" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>128539518</v>
       </c>
       <c r="B152" t="n">
-        <v>91586</v>
+        <v>91587</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -18026,10 +18026,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128365727</v>
+        <v>128365739</v>
       </c>
       <c r="B145" t="n">
-        <v>92791</v>
+        <v>92164</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18037,37 +18037,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5964</v>
+        <v>3298</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>693461</v>
+        <v>693631</v>
       </c>
       <c r="R145" t="n">
-        <v>6553891</v>
+        <v>6553794</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -18099,7 +18096,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -18109,7 +18106,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18118,9 +18115,28 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL145" t="inlineStr">
+        <is>
+          <t>På rötterna till stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>Picea abies # På rötterna till stående död gran.</t>
+        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
@@ -18137,10 +18153,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128365739</v>
+        <v>128365727</v>
       </c>
       <c r="B146" t="n">
-        <v>92164</v>
+        <v>92791</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18148,34 +18164,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>3298</v>
+        <v>5964</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>693631</v>
+        <v>693461</v>
       </c>
       <c r="R146" t="n">
-        <v>6553794</v>
+        <v>6553891</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -18207,7 +18226,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -18217,7 +18236,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18226,28 +18245,9 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ146" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK146" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL146" t="inlineStr">
-        <is>
-          <t>På rötterna till stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO146" t="inlineStr">
-        <is>
-          <t>Picea abies # På rötterna till stående död gran.</t>
-        </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
@@ -18736,7 +18736,7 @@
         <v>128538845</v>
       </c>
       <c r="B151" t="n">
-        <v>91886</v>
+        <v>91913</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>128539518</v>
       </c>
       <c r="B152" t="n">
-        <v>91587</v>
+        <v>91614</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -16468,7 +16468,7 @@
         <v>128279306</v>
       </c>
       <c r="B132" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>128278597</v>
       </c>
       <c r="B133" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>128280496</v>
       </c>
       <c r="B134" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>128274696</v>
       </c>
       <c r="B135" t="n">
-        <v>58548</v>
+        <v>58575</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>128280607</v>
       </c>
       <c r="B136" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>128365728</v>
       </c>
       <c r="B138" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>128365726</v>
       </c>
       <c r="B139" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>128365747</v>
       </c>
       <c r="B140" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17922,7 +17922,7 @@
         <v>128365743</v>
       </c>
       <c r="B144" t="n">
-        <v>96188</v>
+        <v>96215</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18026,10 +18026,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128365739</v>
+        <v>128365727</v>
       </c>
       <c r="B145" t="n">
-        <v>92164</v>
+        <v>92818</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18037,34 +18037,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3298</v>
+        <v>5964</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>693631</v>
+        <v>693461</v>
       </c>
       <c r="R145" t="n">
-        <v>6553794</v>
+        <v>6553891</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -18096,7 +18099,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -18106,7 +18109,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18115,28 +18118,9 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL145" t="inlineStr">
-        <is>
-          <t>På rötterna till stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO145" t="inlineStr">
-        <is>
-          <t>Picea abies # På rötterna till stående död gran.</t>
-        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
@@ -18153,10 +18137,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128365727</v>
+        <v>128365739</v>
       </c>
       <c r="B146" t="n">
-        <v>92791</v>
+        <v>92191</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18164,37 +18148,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5964</v>
+        <v>3298</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>693461</v>
+        <v>693631</v>
       </c>
       <c r="R146" t="n">
-        <v>6553891</v>
+        <v>6553794</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -18226,7 +18207,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -18236,7 +18217,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18245,9 +18226,28 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL146" t="inlineStr">
+        <is>
+          <t>På rötterna till stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>Picea abies # På rötterna till stående död gran.</t>
+        </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
@@ -18526,7 +18526,7 @@
         <v>128365744</v>
       </c>
       <c r="B149" t="n">
-        <v>92771</v>
+        <v>92798</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>128365722</v>
       </c>
       <c r="B150" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -17523,10 +17523,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128365741</v>
+        <v>128365740</v>
       </c>
       <c r="B141" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17534,21 +17534,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -17655,10 +17655,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128365740</v>
+        <v>128365741</v>
       </c>
       <c r="B142" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17666,21 +17666,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -18736,7 +18736,7 @@
         <v>128538845</v>
       </c>
       <c r="B151" t="n">
-        <v>91913</v>
+        <v>91918</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>128539518</v>
       </c>
       <c r="B152" t="n">
-        <v>91614</v>
+        <v>91619</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -16468,7 +16468,7 @@
         <v>128279306</v>
       </c>
       <c r="B132" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>128278597</v>
       </c>
       <c r="B133" t="n">
-        <v>92796</v>
+        <v>92806</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>128280496</v>
       </c>
       <c r="B134" t="n">
-        <v>92429</v>
+        <v>92439</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>128280607</v>
       </c>
       <c r="B136" t="n">
-        <v>92429</v>
+        <v>92439</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>128365728</v>
       </c>
       <c r="B138" t="n">
-        <v>92429</v>
+        <v>92439</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>128365726</v>
       </c>
       <c r="B139" t="n">
-        <v>92429</v>
+        <v>92439</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>128365747</v>
       </c>
       <c r="B140" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17922,7 +17922,7 @@
         <v>128365743</v>
       </c>
       <c r="B144" t="n">
-        <v>96215</v>
+        <v>96228</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18026,10 +18026,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128365727</v>
+        <v>128365729</v>
       </c>
       <c r="B145" t="n">
-        <v>92818</v>
+        <v>8450</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18037,37 +18037,39 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5964</v>
+        <v>106545</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>693461</v>
+        <v>693679</v>
       </c>
       <c r="R145" t="n">
-        <v>6553891</v>
+        <v>6554041</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -18099,7 +18101,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -18109,7 +18111,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18118,9 +18120,28 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL145" t="inlineStr">
+        <is>
+          <t>Nedfallen tallgren.</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Nedfallen tallgren.</t>
+        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
@@ -18137,10 +18158,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128365739</v>
+        <v>128365753</v>
       </c>
       <c r="B146" t="n">
-        <v>92191</v>
+        <v>8450</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18148,34 +18169,39 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>3298</v>
+        <v>106545</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>693631</v>
+        <v>693407</v>
       </c>
       <c r="R146" t="n">
-        <v>6553794</v>
+        <v>6553551</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -18207,7 +18233,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -18217,7 +18243,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18231,22 +18257,17 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL146" t="inlineStr">
-        <is>
-          <t>På rötterna till stående död gran.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>Picea abies # På rötterna till stående död gran.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
@@ -18264,10 +18285,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128365729</v>
+        <v>128365727</v>
       </c>
       <c r="B147" t="n">
-        <v>8450</v>
+        <v>92830</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18275,39 +18296,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>106545</v>
+        <v>5964</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>693679</v>
+        <v>693461</v>
       </c>
       <c r="R147" t="n">
-        <v>6554041</v>
+        <v>6553891</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -18339,7 +18358,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -18349,7 +18368,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18358,28 +18377,9 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL147" t="inlineStr">
-        <is>
-          <t>Nedfallen tallgren.</t>
-        </is>
-      </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Nedfallen tallgren.</t>
-        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
@@ -18396,10 +18396,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128365753</v>
+        <v>128365739</v>
       </c>
       <c r="B148" t="n">
-        <v>8450</v>
+        <v>92201</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18407,39 +18407,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>106545</v>
+        <v>3298</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>693407</v>
+        <v>693631</v>
       </c>
       <c r="R148" t="n">
-        <v>6553551</v>
+        <v>6553794</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -18471,7 +18466,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -18481,7 +18476,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18495,17 +18490,22 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL148" t="inlineStr">
+        <is>
+          <t>På rötterna till stående död gran.</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies # På rötterna till stående död gran.</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr"/>
@@ -18526,7 +18526,7 @@
         <v>128365744</v>
       </c>
       <c r="B149" t="n">
-        <v>92798</v>
+        <v>92808</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>128365722</v>
       </c>
       <c r="B150" t="n">
-        <v>92796</v>
+        <v>92806</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>128538845</v>
       </c>
       <c r="B151" t="n">
-        <v>91918</v>
+        <v>91923</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>128539518</v>
       </c>
       <c r="B152" t="n">
-        <v>91619</v>
+        <v>91624</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -18026,10 +18026,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128365729</v>
+        <v>128365739</v>
       </c>
       <c r="B145" t="n">
-        <v>8450</v>
+        <v>92201</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18037,39 +18037,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>106545</v>
+        <v>3298</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>693679</v>
+        <v>693631</v>
       </c>
       <c r="R145" t="n">
-        <v>6554041</v>
+        <v>6553794</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -18101,7 +18096,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -18111,7 +18106,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18125,22 +18120,22 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL145" t="inlineStr">
         <is>
-          <t>Nedfallen tallgren.</t>
+          <t>På rötterna till stående död gran.</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Nedfallen tallgren.</t>
+          <t>Picea abies # På rötterna till stående död gran.</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -18158,7 +18153,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128365753</v>
+        <v>128365729</v>
       </c>
       <c r="B146" t="n">
         <v>8450</v>
@@ -18198,10 +18193,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>693407</v>
+        <v>693679</v>
       </c>
       <c r="R146" t="n">
-        <v>6553551</v>
+        <v>6554041</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -18233,7 +18228,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -18243,7 +18238,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18265,9 +18260,14 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
+      <c r="AL146" t="inlineStr">
+        <is>
+          <t>Nedfallen tallgren.</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Pinus sylvestris # Nedfallen tallgren.</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
@@ -18285,10 +18285,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128365727</v>
+        <v>128365753</v>
       </c>
       <c r="B147" t="n">
-        <v>92830</v>
+        <v>8450</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18296,37 +18296,39 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5964</v>
+        <v>106545</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>693461</v>
+        <v>693407</v>
       </c>
       <c r="R147" t="n">
-        <v>6553891</v>
+        <v>6553551</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -18358,7 +18360,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -18368,7 +18370,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18377,9 +18379,23 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
@@ -18396,10 +18412,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128365739</v>
+        <v>128365727</v>
       </c>
       <c r="B148" t="n">
-        <v>92201</v>
+        <v>92830</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18407,34 +18423,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>3298</v>
+        <v>5964</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>693631</v>
+        <v>693461</v>
       </c>
       <c r="R148" t="n">
-        <v>6553794</v>
+        <v>6553891</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -18466,7 +18485,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -18476,7 +18495,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18485,28 +18504,9 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ148" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK148" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL148" t="inlineStr">
-        <is>
-          <t>På rötterna till stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO148" t="inlineStr">
-        <is>
-          <t>Picea abies # På rötterna till stående död gran.</t>
-        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -18153,10 +18153,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128365729</v>
+        <v>128365727</v>
       </c>
       <c r="B146" t="n">
-        <v>8450</v>
+        <v>92830</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18164,39 +18164,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>106545</v>
+        <v>5964</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>693679</v>
+        <v>693461</v>
       </c>
       <c r="R146" t="n">
-        <v>6554041</v>
+        <v>6553891</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -18228,7 +18226,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -18238,7 +18236,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18247,28 +18245,9 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ146" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK146" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL146" t="inlineStr">
-        <is>
-          <t>Nedfallen tallgren.</t>
-        </is>
-      </c>
-      <c r="AO146" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Nedfallen tallgren.</t>
-        </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
@@ -18285,7 +18264,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128365753</v>
+        <v>128365729</v>
       </c>
       <c r="B147" t="n">
         <v>8450</v>
@@ -18325,10 +18304,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>693407</v>
+        <v>693679</v>
       </c>
       <c r="R147" t="n">
-        <v>6553551</v>
+        <v>6554041</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -18360,7 +18339,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -18370,7 +18349,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18392,9 +18371,14 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
+      <c r="AL147" t="inlineStr">
+        <is>
+          <t>Nedfallen tallgren.</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Pinus sylvestris # Nedfallen tallgren.</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
@@ -18412,10 +18396,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128365727</v>
+        <v>128365753</v>
       </c>
       <c r="B148" t="n">
-        <v>92830</v>
+        <v>8450</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18423,37 +18407,39 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>5964</v>
+        <v>106545</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>693461</v>
+        <v>693407</v>
       </c>
       <c r="R148" t="n">
-        <v>6553891</v>
+        <v>6553551</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -18485,7 +18471,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -18495,7 +18481,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18504,9 +18490,23 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -17523,10 +17523,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128365740</v>
+        <v>128365741</v>
       </c>
       <c r="B141" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17534,21 +17534,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -17655,10 +17655,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128365741</v>
+        <v>128365740</v>
       </c>
       <c r="B142" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17666,21 +17666,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -18026,10 +18026,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128365739</v>
+        <v>128365729</v>
       </c>
       <c r="B145" t="n">
-        <v>92201</v>
+        <v>8450</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18037,34 +18037,39 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3298</v>
+        <v>106545</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>693631</v>
+        <v>693679</v>
       </c>
       <c r="R145" t="n">
-        <v>6553794</v>
+        <v>6554041</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -18096,7 +18101,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -18106,7 +18111,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18120,22 +18125,22 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL145" t="inlineStr">
         <is>
-          <t>På rötterna till stående död gran.</t>
+          <t>Nedfallen tallgren.</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>Picea abies # På rötterna till stående död gran.</t>
+          <t>Pinus sylvestris # Nedfallen tallgren.</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -18153,10 +18158,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128365727</v>
+        <v>128365753</v>
       </c>
       <c r="B146" t="n">
-        <v>92830</v>
+        <v>8450</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18164,37 +18169,39 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5964</v>
+        <v>106545</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>693461</v>
+        <v>693407</v>
       </c>
       <c r="R146" t="n">
-        <v>6553891</v>
+        <v>6553551</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -18226,7 +18233,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -18236,7 +18243,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18245,9 +18252,23 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
@@ -18264,10 +18285,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128365729</v>
+        <v>128365739</v>
       </c>
       <c r="B147" t="n">
-        <v>8450</v>
+        <v>92201</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18275,39 +18296,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>106545</v>
+        <v>3298</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>693679</v>
+        <v>693631</v>
       </c>
       <c r="R147" t="n">
-        <v>6554041</v>
+        <v>6553794</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -18339,7 +18355,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -18349,7 +18365,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18363,22 +18379,22 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL147" t="inlineStr">
         <is>
-          <t>Nedfallen tallgren.</t>
+          <t>På rötterna till stående död gran.</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Nedfallen tallgren.</t>
+          <t>Picea abies # På rötterna till stående död gran.</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
@@ -18396,10 +18412,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128365753</v>
+        <v>128365727</v>
       </c>
       <c r="B148" t="n">
-        <v>8450</v>
+        <v>92830</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18407,39 +18423,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>106545</v>
+        <v>5964</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>693407</v>
+        <v>693461</v>
       </c>
       <c r="R148" t="n">
-        <v>6553551</v>
+        <v>6553891</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -18471,7 +18485,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -18481,7 +18495,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18490,23 +18504,9 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ148" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK148" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO148" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
@@ -18736,7 +18736,7 @@
         <v>128538845</v>
       </c>
       <c r="B151" t="n">
-        <v>91923</v>
+        <v>91927</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>128539518</v>
       </c>
       <c r="B152" t="n">
-        <v>91624</v>
+        <v>91628</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -17191,7 +17191,7 @@
         <v>128365728</v>
       </c>
       <c r="B138" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>128365726</v>
       </c>
       <c r="B139" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>128365747</v>
       </c>
       <c r="B140" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17922,7 +17922,7 @@
         <v>128365743</v>
       </c>
       <c r="B144" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -18026,10 +18026,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128365729</v>
+        <v>128365739</v>
       </c>
       <c r="B145" t="n">
-        <v>8450</v>
+        <v>92205</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18037,39 +18037,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>106545</v>
+        <v>3298</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>693679</v>
+        <v>693631</v>
       </c>
       <c r="R145" t="n">
-        <v>6554041</v>
+        <v>6553794</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -18101,7 +18096,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -18111,7 +18106,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18125,22 +18120,22 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL145" t="inlineStr">
         <is>
-          <t>Nedfallen tallgren.</t>
+          <t>På rötterna till stående död gran.</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Nedfallen tallgren.</t>
+          <t>Picea abies # På rötterna till stående död gran.</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -18158,10 +18153,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128365753</v>
+        <v>128365727</v>
       </c>
       <c r="B146" t="n">
-        <v>8450</v>
+        <v>92834</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18169,39 +18164,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>106545</v>
+        <v>5964</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>693407</v>
+        <v>693461</v>
       </c>
       <c r="R146" t="n">
-        <v>6553551</v>
+        <v>6553891</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -18233,7 +18226,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -18243,7 +18236,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18252,23 +18245,9 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ146" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK146" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO146" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
@@ -18285,10 +18264,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128365739</v>
+        <v>128365729</v>
       </c>
       <c r="B147" t="n">
-        <v>92201</v>
+        <v>8450</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18296,34 +18275,39 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3298</v>
+        <v>106545</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>693631</v>
+        <v>693679</v>
       </c>
       <c r="R147" t="n">
-        <v>6553794</v>
+        <v>6554041</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -18355,7 +18339,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -18365,7 +18349,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18379,22 +18363,22 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL147" t="inlineStr">
         <is>
-          <t>På rötterna till stående död gran.</t>
+          <t>Nedfallen tallgren.</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>Picea abies # På rötterna till stående död gran.</t>
+          <t>Pinus sylvestris # Nedfallen tallgren.</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
@@ -18412,10 +18396,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128365727</v>
+        <v>128365753</v>
       </c>
       <c r="B148" t="n">
-        <v>92830</v>
+        <v>8450</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18423,37 +18407,39 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>5964</v>
+        <v>106545</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>693461</v>
+        <v>693407</v>
       </c>
       <c r="R148" t="n">
-        <v>6553891</v>
+        <v>6553551</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -18485,7 +18471,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -18495,7 +18481,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18504,9 +18490,23 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
@@ -18526,7 +18526,7 @@
         <v>128365744</v>
       </c>
       <c r="B149" t="n">
-        <v>92808</v>
+        <v>92812</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>128365722</v>
       </c>
       <c r="B150" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -17523,10 +17523,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128365741</v>
+        <v>128365740</v>
       </c>
       <c r="B141" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17534,21 +17534,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -17655,10 +17655,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128365740</v>
+        <v>128365741</v>
       </c>
       <c r="B142" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17666,21 +17666,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -18026,10 +18026,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128365739</v>
+        <v>128365727</v>
       </c>
       <c r="B145" t="n">
-        <v>92205</v>
+        <v>92834</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -18037,34 +18037,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3298</v>
+        <v>5964</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>693631</v>
+        <v>693461</v>
       </c>
       <c r="R145" t="n">
-        <v>6553794</v>
+        <v>6553891</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -18096,7 +18099,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -18106,7 +18109,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -18115,28 +18118,9 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL145" t="inlineStr">
-        <is>
-          <t>På rötterna till stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO145" t="inlineStr">
-        <is>
-          <t>Picea abies # På rötterna till stående död gran.</t>
-        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
@@ -18153,10 +18137,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128365727</v>
+        <v>128365729</v>
       </c>
       <c r="B146" t="n">
-        <v>92834</v>
+        <v>8450</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -18164,37 +18148,39 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5964</v>
+        <v>106545</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>693461</v>
+        <v>693679</v>
       </c>
       <c r="R146" t="n">
-        <v>6553891</v>
+        <v>6554041</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -18226,7 +18212,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -18236,7 +18222,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18245,9 +18231,28 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL146" t="inlineStr">
+        <is>
+          <t>Nedfallen tallgren.</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Nedfallen tallgren.</t>
+        </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
@@ -18264,7 +18269,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128365729</v>
+        <v>128365753</v>
       </c>
       <c r="B147" t="n">
         <v>8450</v>
@@ -18304,10 +18309,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>693679</v>
+        <v>693407</v>
       </c>
       <c r="R147" t="n">
-        <v>6554041</v>
+        <v>6553551</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -18339,7 +18344,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -18349,7 +18354,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18371,14 +18376,9 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
-      <c r="AL147" t="inlineStr">
-        <is>
-          <t>Nedfallen tallgren.</t>
-        </is>
-      </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Nedfallen tallgren.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
@@ -18396,10 +18396,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128365753</v>
+        <v>128365739</v>
       </c>
       <c r="B148" t="n">
-        <v>8450</v>
+        <v>92205</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18407,39 +18407,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>106545</v>
+        <v>3298</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>693407</v>
+        <v>693631</v>
       </c>
       <c r="R148" t="n">
-        <v>6553551</v>
+        <v>6553794</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -18471,7 +18466,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -18481,7 +18476,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18495,17 +18490,22 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL148" t="inlineStr">
+        <is>
+          <t>På rötterna till stående död gran.</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies # På rötterna till stående död gran.</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr"/>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -18736,7 +18736,7 @@
         <v>128538845</v>
       </c>
       <c r="B151" t="n">
-        <v>91927</v>
+        <v>91932</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>128539518</v>
       </c>
       <c r="B152" t="n">
-        <v>91628</v>
+        <v>91633</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -18736,7 +18736,7 @@
         <v>128538845</v>
       </c>
       <c r="B151" t="n">
-        <v>91935</v>
+        <v>91940</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>128539518</v>
       </c>
       <c r="B152" t="n">
-        <v>91635</v>
+        <v>91640</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -18736,7 +18736,7 @@
         <v>128538845</v>
       </c>
       <c r="B151" t="n">
-        <v>91940</v>
+        <v>91946</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>128539518</v>
       </c>
       <c r="B152" t="n">
-        <v>91640</v>
+        <v>91646</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY152"/>
+  <dimension ref="A1:AY154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18933,6 +18933,240 @@
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>129518152</v>
+      </c>
+      <c r="B153" t="n">
+        <v>58097</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Mörbyfjärden, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>693294</v>
+      </c>
+      <c r="R153" t="n">
+        <v>6554029</v>
+      </c>
+      <c r="S153" t="n">
+        <v>10</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Per Flodby</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Per Flodby</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>129517893</v>
+      </c>
+      <c r="B154" t="n">
+        <v>58097</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Mörbyfjärden, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>693614</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6553916</v>
+      </c>
+      <c r="S154" t="n">
+        <v>10</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Per Flodby</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Per Flodby</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY154"/>
+  <dimension ref="A1:AY156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19167,6 +19167,216 @@
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>129667335</v>
+      </c>
+      <c r="B155" t="n">
+        <v>91574</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>693435</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6553848</v>
+      </c>
+      <c r="S155" t="n">
+        <v>1</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF155" t="inlineStr"/>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Leonard Brunner</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Leonard Brunner</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>129667428</v>
+      </c>
+      <c r="B156" t="n">
+        <v>92873</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>693435</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6553848</v>
+      </c>
+      <c r="S156" t="n">
+        <v>1</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF156" t="inlineStr"/>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Leonard Brunner</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Leonard Brunner</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -18938,7 +18938,7 @@
         <v>129518152</v>
       </c>
       <c r="B153" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>129517893</v>
       </c>
       <c r="B154" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>129667335</v>
       </c>
       <c r="B155" t="n">
-        <v>91574</v>
+        <v>91602</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>129667428</v>
       </c>
       <c r="B156" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -18938,7 +18938,7 @@
         <v>129518152</v>
       </c>
       <c r="B153" t="n">
-        <v>58100</v>
+        <v>58105</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>129517893</v>
       </c>
       <c r="B154" t="n">
-        <v>58100</v>
+        <v>58105</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>129667335</v>
       </c>
       <c r="B155" t="n">
-        <v>91602</v>
+        <v>91608</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>129667428</v>
       </c>
       <c r="B156" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -18938,7 +18938,7 @@
         <v>129518152</v>
       </c>
       <c r="B153" t="n">
-        <v>58105</v>
+        <v>58106</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>129517893</v>
       </c>
       <c r="B154" t="n">
-        <v>58105</v>
+        <v>58106</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>129667335</v>
       </c>
       <c r="B155" t="n">
-        <v>91608</v>
+        <v>91609</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>129667428</v>
       </c>
       <c r="B156" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -19172,7 +19172,7 @@
         <v>129667335</v>
       </c>
       <c r="B155" t="n">
-        <v>91609</v>
+        <v>91614</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>129667428</v>
       </c>
       <c r="B156" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -19172,7 +19172,7 @@
         <v>129667335</v>
       </c>
       <c r="B155" t="n">
-        <v>91614</v>
+        <v>91618</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>129667428</v>
       </c>
       <c r="B156" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -19172,7 +19172,7 @@
         <v>129667335</v>
       </c>
       <c r="B155" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>129667428</v>
       </c>
       <c r="B156" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY156"/>
+  <dimension ref="A1:AY162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19377,6 +19377,690 @@
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>129910966</v>
+      </c>
+      <c r="B157" t="n">
+        <v>96131</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>693478</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6553857</v>
+      </c>
+      <c r="S157" t="n">
+        <v>10</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF157" t="inlineStr"/>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL157" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Leonard Brunner, Birgitta Tulin, Roja Kirkeby</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>129910883</v>
+      </c>
+      <c r="B158" t="n">
+        <v>98785</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>693592</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6553948</v>
+      </c>
+      <c r="S158" t="n">
+        <v>10</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Leonard Brunner, Birgitta Tulin, Roja Kirkeby</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>129910890</v>
+      </c>
+      <c r="B159" t="n">
+        <v>85013</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>3518</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Smal svampklubba</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Tolypocladium ophioglossoides</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>693470</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6553669</v>
+      </c>
+      <c r="S159" t="n">
+        <v>10</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Leonard Brunner, Birgitta Tulin, Roja Kirkeby</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>129910885</v>
+      </c>
+      <c r="B160" t="n">
+        <v>98785</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>693560</v>
+      </c>
+      <c r="R160" t="n">
+        <v>6553891</v>
+      </c>
+      <c r="S160" t="n">
+        <v>10</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Leonard Brunner, Birgitta Tulin, Roja Kirkeby</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>129910884</v>
+      </c>
+      <c r="B161" t="n">
+        <v>98785</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>693584</v>
+      </c>
+      <c r="R161" t="n">
+        <v>6553936</v>
+      </c>
+      <c r="S161" t="n">
+        <v>10</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Leonard Brunner, Birgitta Tulin, Roja Kirkeby</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>129910879</v>
+      </c>
+      <c r="B162" t="n">
+        <v>88847</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>4405</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Diskvaxskivling</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Hygrophorus discoideus</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>693454</v>
+      </c>
+      <c r="R162" t="n">
+        <v>6553884</v>
+      </c>
+      <c r="S162" t="n">
+        <v>10</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -19382,7 +19382,7 @@
         <v>129910966</v>
       </c>
       <c r="B157" t="n">
-        <v>96131</v>
+        <v>96136</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>129910883</v>
       </c>
       <c r="B158" t="n">
-        <v>98785</v>
+        <v>98790</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19617,45 +19617,54 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129910890</v>
+        <v>129910884</v>
       </c>
       <c r="B159" t="n">
-        <v>85013</v>
+        <v>98790</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>3518</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>693470</v>
+        <v>693584</v>
       </c>
       <c r="R159" t="n">
-        <v>6553669</v>
+        <v>6553936</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -19687,7 +19696,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19697,7 +19706,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19727,7 +19736,7 @@
         <v>129910885</v>
       </c>
       <c r="B160" t="n">
-        <v>98785</v>
+        <v>98790</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19840,54 +19849,45 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129910884</v>
+        <v>129910890</v>
       </c>
       <c r="B161" t="n">
-        <v>98785</v>
+        <v>85013</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>3518</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>693584</v>
+        <v>693470</v>
       </c>
       <c r="R161" t="n">
-        <v>6553936</v>
+        <v>6553669</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19919,7 +19919,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD161" t="b">

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -19617,54 +19617,45 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129910884</v>
+        <v>129910890</v>
       </c>
       <c r="B159" t="n">
-        <v>98790</v>
+        <v>85013</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220787</v>
+        <v>3518</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>693584</v>
+        <v>693470</v>
       </c>
       <c r="R159" t="n">
-        <v>6553936</v>
+        <v>6553669</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -19696,7 +19687,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19706,7 +19697,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19733,7 +19724,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129910885</v>
+        <v>129910884</v>
       </c>
       <c r="B160" t="n">
         <v>98790</v>
@@ -19763,7 +19754,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -19777,10 +19768,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>693560</v>
+        <v>693584</v>
       </c>
       <c r="R160" t="n">
-        <v>6553891</v>
+        <v>6553936</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -19812,7 +19803,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19822,7 +19813,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19849,45 +19840,54 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129910890</v>
+        <v>129910885</v>
       </c>
       <c r="B161" t="n">
-        <v>85013</v>
+        <v>98790</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>3518</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>693470</v>
+        <v>693560</v>
       </c>
       <c r="R161" t="n">
-        <v>6553669</v>
+        <v>6553891</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19919,7 +19919,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD161" t="b">

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -19382,7 +19382,7 @@
         <v>129910966</v>
       </c>
       <c r="B157" t="n">
-        <v>96136</v>
+        <v>96140</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Leonard Brunner, Birgitta Tulin, Roja Kirkeby</t>
+          <t>Klas Magnusson, Roja Kirkeby, Birgitta Tulin, Leonard Brunner, Emilia Blixt, Per Flodby</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -19504,7 +19504,7 @@
         <v>129910883</v>
       </c>
       <c r="B158" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19617,45 +19617,54 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129910890</v>
+        <v>129910884</v>
       </c>
       <c r="B159" t="n">
-        <v>85013</v>
+        <v>98794</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>3518</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>693470</v>
+        <v>693584</v>
       </c>
       <c r="R159" t="n">
-        <v>6553669</v>
+        <v>6553936</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -19687,7 +19696,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19697,7 +19706,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19724,10 +19733,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129910884</v>
+        <v>129910885</v>
       </c>
       <c r="B160" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19754,7 +19763,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -19768,10 +19777,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>693584</v>
+        <v>693560</v>
       </c>
       <c r="R160" t="n">
-        <v>6553936</v>
+        <v>6553891</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -19803,7 +19812,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19813,7 +19822,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19840,54 +19849,45 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129910885</v>
+        <v>129910890</v>
       </c>
       <c r="B161" t="n">
-        <v>98790</v>
+        <v>85016</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>3518</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>693560</v>
+        <v>693470</v>
       </c>
       <c r="R161" t="n">
-        <v>6553891</v>
+        <v>6553669</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19919,7 +19919,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19959,7 +19959,7 @@
         <v>129910879</v>
       </c>
       <c r="B162" t="n">
-        <v>88847</v>
+        <v>88850</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -19172,7 +19172,7 @@
         <v>129667335</v>
       </c>
       <c r="B155" t="n">
-        <v>91620</v>
+        <v>91623</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>129667428</v>
       </c>
       <c r="B156" t="n">
-        <v>92919</v>
+        <v>92922</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Roja Kirkeby, Birgitta Tulin, Leonard Brunner, Emilia Blixt, Per Flodby</t>
+          <t>Klas Magnusson, Per Flodby, Emilia Blixt, Leonard Brunner, Birgitta Tulin, Roja Kirkeby</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -19617,54 +19617,45 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129910884</v>
+        <v>129910890</v>
       </c>
       <c r="B159" t="n">
-        <v>98794</v>
+        <v>85016</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220787</v>
+        <v>3518</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>693584</v>
+        <v>693470</v>
       </c>
       <c r="R159" t="n">
-        <v>6553936</v>
+        <v>6553669</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -19696,7 +19687,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19706,7 +19697,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19733,7 +19724,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129910885</v>
+        <v>129910884</v>
       </c>
       <c r="B160" t="n">
         <v>98794</v>
@@ -19763,7 +19754,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -19777,10 +19768,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>693560</v>
+        <v>693584</v>
       </c>
       <c r="R160" t="n">
-        <v>6553891</v>
+        <v>6553936</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -19812,7 +19803,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19822,7 +19813,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19849,45 +19840,54 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129910890</v>
+        <v>129910885</v>
       </c>
       <c r="B161" t="n">
-        <v>85016</v>
+        <v>98794</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>3518</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>693470</v>
+        <v>693560</v>
       </c>
       <c r="R161" t="n">
-        <v>6553669</v>
+        <v>6553891</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19919,7 +19919,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD161" t="b">

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -19172,7 +19172,7 @@
         <v>129667335</v>
       </c>
       <c r="B155" t="n">
-        <v>91623</v>
+        <v>91626</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>129667428</v>
       </c>
       <c r="B156" t="n">
-        <v>92922</v>
+        <v>92925</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>129910966</v>
       </c>
       <c r="B157" t="n">
-        <v>96140</v>
+        <v>96143</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>129910883</v>
       </c>
       <c r="B158" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19617,45 +19617,54 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129910890</v>
+        <v>129910884</v>
       </c>
       <c r="B159" t="n">
-        <v>85016</v>
+        <v>98797</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>3518</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>693470</v>
+        <v>693584</v>
       </c>
       <c r="R159" t="n">
-        <v>6553669</v>
+        <v>6553936</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -19687,7 +19696,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19697,7 +19706,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19724,10 +19733,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129910884</v>
+        <v>129910885</v>
       </c>
       <c r="B160" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19754,7 +19763,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -19768,10 +19777,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>693584</v>
+        <v>693560</v>
       </c>
       <c r="R160" t="n">
-        <v>6553936</v>
+        <v>6553891</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -19803,7 +19812,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19813,7 +19822,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19840,54 +19849,45 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129910885</v>
+        <v>129910890</v>
       </c>
       <c r="B161" t="n">
-        <v>98794</v>
+        <v>85019</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>3518</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>693560</v>
+        <v>693470</v>
       </c>
       <c r="R161" t="n">
-        <v>6553891</v>
+        <v>6553669</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19919,7 +19919,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19959,7 +19959,7 @@
         <v>129910879</v>
       </c>
       <c r="B162" t="n">
-        <v>88850</v>
+        <v>88853</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -19617,54 +19617,45 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129910884</v>
+        <v>129910890</v>
       </c>
       <c r="B159" t="n">
-        <v>98797</v>
+        <v>85019</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220787</v>
+        <v>3518</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>693584</v>
+        <v>693470</v>
       </c>
       <c r="R159" t="n">
-        <v>6553936</v>
+        <v>6553669</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -19696,7 +19687,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19706,7 +19697,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19733,7 +19724,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129910885</v>
+        <v>129910884</v>
       </c>
       <c r="B160" t="n">
         <v>98797</v>
@@ -19763,7 +19754,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -19777,10 +19768,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>693560</v>
+        <v>693584</v>
       </c>
       <c r="R160" t="n">
-        <v>6553891</v>
+        <v>6553936</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -19812,7 +19803,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19822,7 +19813,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19849,45 +19840,54 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129910890</v>
+        <v>129910885</v>
       </c>
       <c r="B161" t="n">
-        <v>85019</v>
+        <v>98797</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>3518</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>693470</v>
+        <v>693560</v>
       </c>
       <c r="R161" t="n">
-        <v>6553669</v>
+        <v>6553891</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19919,7 +19919,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD161" t="b">

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -19172,7 +19172,7 @@
         <v>129667335</v>
       </c>
       <c r="B155" t="n">
-        <v>91626</v>
+        <v>91627</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>129667428</v>
       </c>
       <c r="B156" t="n">
-        <v>92925</v>
+        <v>92926</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>129910966</v>
       </c>
       <c r="B157" t="n">
-        <v>96143</v>
+        <v>96144</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>129910883</v>
       </c>
       <c r="B158" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>129910890</v>
       </c>
       <c r="B159" t="n">
-        <v>85019</v>
+        <v>85020</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>129910884</v>
       </c>
       <c r="B160" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>129910885</v>
       </c>
       <c r="B161" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>129910879</v>
       </c>
       <c r="B162" t="n">
-        <v>88853</v>
+        <v>88854</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -19617,45 +19617,54 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129910890</v>
+        <v>129910884</v>
       </c>
       <c r="B159" t="n">
-        <v>85020</v>
+        <v>98798</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>3518</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>693470</v>
+        <v>693584</v>
       </c>
       <c r="R159" t="n">
-        <v>6553669</v>
+        <v>6553936</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -19687,7 +19696,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19697,7 +19706,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19724,7 +19733,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129910884</v>
+        <v>129910885</v>
       </c>
       <c r="B160" t="n">
         <v>98798</v>
@@ -19754,7 +19763,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -19768,10 +19777,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>693584</v>
+        <v>693560</v>
       </c>
       <c r="R160" t="n">
-        <v>6553936</v>
+        <v>6553891</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -19803,7 +19812,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19813,7 +19822,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19840,54 +19849,45 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129910885</v>
+        <v>129910890</v>
       </c>
       <c r="B161" t="n">
-        <v>98798</v>
+        <v>85020</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>3518</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>693560</v>
+        <v>693470</v>
       </c>
       <c r="R161" t="n">
-        <v>6553891</v>
+        <v>6553669</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19919,7 +19919,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD161" t="b">

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -19617,54 +19617,45 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129910884</v>
+        <v>129910890</v>
       </c>
       <c r="B159" t="n">
-        <v>98798</v>
+        <v>85020</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220787</v>
+        <v>3518</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>693584</v>
+        <v>693470</v>
       </c>
       <c r="R159" t="n">
-        <v>6553936</v>
+        <v>6553669</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -19696,7 +19687,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19706,7 +19697,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19733,7 +19724,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129910885</v>
+        <v>129910884</v>
       </c>
       <c r="B160" t="n">
         <v>98798</v>
@@ -19763,7 +19754,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -19777,10 +19768,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>693560</v>
+        <v>693584</v>
       </c>
       <c r="R160" t="n">
-        <v>6553891</v>
+        <v>6553936</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -19812,7 +19803,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19822,7 +19813,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19849,45 +19840,54 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129910890</v>
+        <v>129910885</v>
       </c>
       <c r="B161" t="n">
-        <v>85020</v>
+        <v>98798</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>3518</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>693470</v>
+        <v>693560</v>
       </c>
       <c r="R161" t="n">
-        <v>6553669</v>
+        <v>6553891</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19919,7 +19919,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD161" t="b">

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -19382,7 +19382,7 @@
         <v>129910966</v>
       </c>
       <c r="B157" t="n">
-        <v>96144</v>
+        <v>96161</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>129910883</v>
       </c>
       <c r="B158" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19617,45 +19617,54 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129910890</v>
+        <v>129910884</v>
       </c>
       <c r="B159" t="n">
-        <v>85020</v>
+        <v>98815</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>3518</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>693470</v>
+        <v>693584</v>
       </c>
       <c r="R159" t="n">
-        <v>6553669</v>
+        <v>6553936</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -19687,7 +19696,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19697,7 +19706,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19724,10 +19733,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129910884</v>
+        <v>129910885</v>
       </c>
       <c r="B160" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19754,7 +19763,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -19768,10 +19777,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>693584</v>
+        <v>693560</v>
       </c>
       <c r="R160" t="n">
-        <v>6553936</v>
+        <v>6553891</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -19803,7 +19812,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19813,7 +19822,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19840,54 +19849,45 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129910885</v>
+        <v>129910890</v>
       </c>
       <c r="B161" t="n">
-        <v>98798</v>
+        <v>85024</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>3518</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>693560</v>
+        <v>693470</v>
       </c>
       <c r="R161" t="n">
-        <v>6553891</v>
+        <v>6553669</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19919,7 +19919,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19959,7 +19959,7 @@
         <v>129910879</v>
       </c>
       <c r="B162" t="n">
-        <v>88854</v>
+        <v>88871</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -19617,54 +19617,45 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129910885</v>
+        <v>129910890</v>
       </c>
       <c r="B159" t="n">
-        <v>98831</v>
+        <v>85032</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220787</v>
+        <v>3518</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>693560</v>
+        <v>693470</v>
       </c>
       <c r="R159" t="n">
-        <v>6553891</v>
+        <v>6553669</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -19696,7 +19687,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19706,7 +19697,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19733,45 +19724,54 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129910890</v>
+        <v>129910884</v>
       </c>
       <c r="B160" t="n">
-        <v>85032</v>
+        <v>98831</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>3518</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>693470</v>
+        <v>693584</v>
       </c>
       <c r="R160" t="n">
-        <v>6553669</v>
+        <v>6553936</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -19803,7 +19803,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19813,7 +19813,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19840,7 +19840,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129910884</v>
+        <v>129910885</v>
       </c>
       <c r="B161" t="n">
         <v>98831</v>
@@ -19870,7 +19870,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -19884,10 +19884,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>693584</v>
+        <v>693560</v>
       </c>
       <c r="R161" t="n">
-        <v>6553936</v>
+        <v>6553891</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19919,7 +19919,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD161" t="b">

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -19382,7 +19382,7 @@
         <v>129910966</v>
       </c>
       <c r="B157" t="n">
-        <v>96177</v>
+        <v>96179</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>129910883</v>
       </c>
       <c r="B158" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>129910884</v>
       </c>
       <c r="B160" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>129910885</v>
       </c>
       <c r="B161" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -13671,7 +13671,7 @@
         <v>126551299</v>
       </c>
       <c r="B107" t="n">
-        <v>102671</v>
+        <v>102665</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>126551318</v>
       </c>
       <c r="B109" t="n">
-        <v>95774</v>
+        <v>95768</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>126551287</v>
       </c>
       <c r="B110" t="n">
-        <v>95568</v>
+        <v>95562</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>126604714</v>
       </c>
       <c r="B111" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>126610277</v>
       </c>
       <c r="B112" t="n">
-        <v>98442</v>
+        <v>98436</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>126609883</v>
       </c>
       <c r="B113" t="n">
-        <v>98442</v>
+        <v>98436</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>126609812</v>
       </c>
       <c r="B114" t="n">
-        <v>98442</v>
+        <v>98436</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>126603803</v>
       </c>
       <c r="B115" t="n">
-        <v>79632</v>
+        <v>79629</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>126609998</v>
       </c>
       <c r="B116" t="n">
-        <v>98442</v>
+        <v>98436</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>126610157</v>
       </c>
       <c r="B117" t="n">
-        <v>98442</v>
+        <v>98436</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>126607356</v>
       </c>
       <c r="B118" t="n">
-        <v>97320</v>
+        <v>97314</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>126610206</v>
       </c>
       <c r="B119" t="n">
-        <v>91345</v>
+        <v>91339</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15090,7 +15090,7 @@
         <v>126610096</v>
       </c>
       <c r="B120" t="n">
-        <v>98442</v>
+        <v>98436</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>126753764</v>
       </c>
       <c r="B122" t="n">
-        <v>96050</v>
+        <v>96039</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>126753788</v>
       </c>
       <c r="B123" t="n">
-        <v>57658</v>
+        <v>57654</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>126753771</v>
       </c>
       <c r="B124" t="n">
-        <v>95800</v>
+        <v>95789</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>126753786</v>
       </c>
       <c r="B125" t="n">
-        <v>4773</v>
+        <v>4772</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>126753763</v>
       </c>
       <c r="B126" t="n">
-        <v>95286</v>
+        <v>95275</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>126753790</v>
       </c>
       <c r="B127" t="n">
-        <v>4773</v>
+        <v>4772</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>126753773</v>
       </c>
       <c r="B128" t="n">
-        <v>103516</v>
+        <v>103504</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>126753784</v>
       </c>
       <c r="B129" t="n">
-        <v>98447</v>
+        <v>98436</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>126753772</v>
       </c>
       <c r="B130" t="n">
-        <v>95800</v>
+        <v>95789</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>126753768</v>
       </c>
       <c r="B131" t="n">
-        <v>4773</v>
+        <v>4772</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>129910966</v>
       </c>
       <c r="B157" t="n">
-        <v>96179</v>
+        <v>96266</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>129910883</v>
       </c>
       <c r="B158" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19617,45 +19617,54 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129910890</v>
+        <v>129910884</v>
       </c>
       <c r="B159" t="n">
-        <v>85032</v>
+        <v>98920</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>3518</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>693470</v>
+        <v>693584</v>
       </c>
       <c r="R159" t="n">
-        <v>6553669</v>
+        <v>6553936</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -19687,7 +19696,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19697,7 +19706,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19724,10 +19733,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129910884</v>
+        <v>129910885</v>
       </c>
       <c r="B160" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19754,7 +19763,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -19768,10 +19777,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>693584</v>
+        <v>693560</v>
       </c>
       <c r="R160" t="n">
-        <v>6553936</v>
+        <v>6553891</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -19803,7 +19812,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19813,7 +19822,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19840,54 +19849,45 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129910885</v>
+        <v>129910890</v>
       </c>
       <c r="B161" t="n">
-        <v>98833</v>
+        <v>85119</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>3518</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>693560</v>
+        <v>693470</v>
       </c>
       <c r="R161" t="n">
-        <v>6553891</v>
+        <v>6553669</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19919,7 +19919,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19959,7 +19959,7 @@
         <v>129910879</v>
       </c>
       <c r="B162" t="n">
-        <v>88887</v>
+        <v>88974</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -19617,7 +19617,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129910884</v>
+        <v>129910885</v>
       </c>
       <c r="B159" t="n">
         <v>98920</v>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -19661,10 +19661,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>693584</v>
+        <v>693560</v>
       </c>
       <c r="R159" t="n">
-        <v>6553936</v>
+        <v>6553891</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -19696,7 +19696,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19706,7 +19706,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19733,54 +19733,45 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129910885</v>
+        <v>129910890</v>
       </c>
       <c r="B160" t="n">
-        <v>98920</v>
+        <v>85119</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220787</v>
+        <v>3518</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>693560</v>
+        <v>693470</v>
       </c>
       <c r="R160" t="n">
-        <v>6553891</v>
+        <v>6553669</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -19812,7 +19803,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19822,7 +19813,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19849,45 +19840,54 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129910890</v>
+        <v>129910884</v>
       </c>
       <c r="B161" t="n">
-        <v>85119</v>
+        <v>98920</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>3518</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>693470</v>
+        <v>693584</v>
       </c>
       <c r="R161" t="n">
-        <v>6553669</v>
+        <v>6553936</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19919,7 +19919,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD161" t="b">

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -19617,7 +19617,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129910885</v>
+        <v>129910884</v>
       </c>
       <c r="B159" t="n">
         <v>98920</v>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -19661,10 +19661,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>693560</v>
+        <v>693584</v>
       </c>
       <c r="R159" t="n">
-        <v>6553891</v>
+        <v>6553936</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -19696,7 +19696,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19706,7 +19706,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19733,45 +19733,54 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129910890</v>
+        <v>129910885</v>
       </c>
       <c r="B160" t="n">
-        <v>85119</v>
+        <v>98920</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>3518</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>693470</v>
+        <v>693560</v>
       </c>
       <c r="R160" t="n">
-        <v>6553669</v>
+        <v>6553891</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -19803,7 +19812,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19813,7 +19822,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19840,54 +19849,45 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129910884</v>
+        <v>129910890</v>
       </c>
       <c r="B161" t="n">
-        <v>98920</v>
+        <v>85119</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>3518</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>693584</v>
+        <v>693470</v>
       </c>
       <c r="R161" t="n">
-        <v>6553936</v>
+        <v>6553669</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19919,7 +19919,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD161" t="b">

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -13671,7 +13671,7 @@
         <v>126551299</v>
       </c>
       <c r="B107" t="n">
-        <v>102665</v>
+        <v>102671</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>126551318</v>
       </c>
       <c r="B109" t="n">
-        <v>95768</v>
+        <v>95774</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>126551287</v>
       </c>
       <c r="B110" t="n">
-        <v>95562</v>
+        <v>95568</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>126604714</v>
       </c>
       <c r="B111" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>126610277</v>
       </c>
       <c r="B112" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>126609883</v>
       </c>
       <c r="B113" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>126609812</v>
       </c>
       <c r="B114" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>126603803</v>
       </c>
       <c r="B115" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>126609998</v>
       </c>
       <c r="B116" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>126610157</v>
       </c>
       <c r="B117" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>126607356</v>
       </c>
       <c r="B118" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>126610206</v>
       </c>
       <c r="B119" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15090,7 +15090,7 @@
         <v>126610096</v>
       </c>
       <c r="B120" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>126753764</v>
       </c>
       <c r="B122" t="n">
-        <v>96039</v>
+        <v>96050</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>126753788</v>
       </c>
       <c r="B123" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>126753771</v>
       </c>
       <c r="B124" t="n">
-        <v>95789</v>
+        <v>95800</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>126753786</v>
       </c>
       <c r="B125" t="n">
-        <v>4772</v>
+        <v>4773</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>126753763</v>
       </c>
       <c r="B126" t="n">
-        <v>95275</v>
+        <v>95286</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>126753790</v>
       </c>
       <c r="B127" t="n">
-        <v>4772</v>
+        <v>4773</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>126753773</v>
       </c>
       <c r="B128" t="n">
-        <v>103504</v>
+        <v>103516</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>126753784</v>
       </c>
       <c r="B129" t="n">
-        <v>98436</v>
+        <v>98447</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>126753772</v>
       </c>
       <c r="B130" t="n">
-        <v>95789</v>
+        <v>95800</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>126753768</v>
       </c>
       <c r="B131" t="n">
-        <v>4772</v>
+        <v>4773</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>0</v>
       </c>
       <c r="AE149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG149" t="b">
         <v>0</v>
@@ -19382,7 +19382,7 @@
         <v>129910966</v>
       </c>
       <c r="B157" t="n">
-        <v>96266</v>
+        <v>96179</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>129910883</v>
       </c>
       <c r="B158" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19617,54 +19617,45 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129910884</v>
+        <v>129910890</v>
       </c>
       <c r="B159" t="n">
-        <v>98920</v>
+        <v>85032</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220787</v>
+        <v>3518</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>693584</v>
+        <v>693470</v>
       </c>
       <c r="R159" t="n">
-        <v>6553936</v>
+        <v>6553669</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -19696,7 +19687,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19706,7 +19697,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19733,10 +19724,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129910885</v>
+        <v>129910884</v>
       </c>
       <c r="B160" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19763,7 +19754,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -19777,10 +19768,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>693560</v>
+        <v>693584</v>
       </c>
       <c r="R160" t="n">
-        <v>6553891</v>
+        <v>6553936</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -19812,7 +19803,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19822,7 +19813,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19849,45 +19840,54 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129910890</v>
+        <v>129910885</v>
       </c>
       <c r="B161" t="n">
-        <v>85119</v>
+        <v>98833</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>3518</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>693470</v>
+        <v>693560</v>
       </c>
       <c r="R161" t="n">
-        <v>6553669</v>
+        <v>6553891</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19919,7 +19919,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19959,7 +19959,7 @@
         <v>129910879</v>
       </c>
       <c r="B162" t="n">
-        <v>88974</v>
+        <v>88887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -20305,48 +20305,53 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>131844576</v>
+        <v>131866840</v>
       </c>
       <c r="B165" t="n">
-        <v>84135</v>
+        <v>57945</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1444</v>
+        <v>100049</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Scharlakansvårskål agg.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Sarcoscypha coccinea s.lat.</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Jacq.:Fr.) Lambotte</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Kolnäsviken, Kolnäsviken, Srm</t>
+          <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>693703</v>
+        <v>693287</v>
       </c>
       <c r="R165" t="n">
-        <v>6553911</v>
+        <v>6553954</v>
       </c>
       <c r="S165" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -20373,9 +20378,19 @@
           <t>2026-03-22</t>
         </is>
       </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -20390,65 +20405,60 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Kalle Skarin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Kalle Skarin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>131866840</v>
+        <v>131844576</v>
       </c>
       <c r="B166" t="n">
-        <v>57945</v>
+        <v>84137</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100049</v>
+        <v>1444</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcoscypha coccinea s.lat.</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Jacq.:Fr.) Lambotte</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Breviksnäs, Srm</t>
+          <t>Kolnäsviken, Kolnäsviken, Srm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>693287</v>
+        <v>693703</v>
       </c>
       <c r="R166" t="n">
-        <v>6553954</v>
+        <v>6553911</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -20475,19 +20485,9 @@
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -20502,19 +20502,19 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Kalle Skarin</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Kalle Skarin</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>131866857</v>
+        <v>131866844</v>
       </c>
       <c r="B167" t="n">
         <v>57945</v>
@@ -20545,7 +20545,7 @@
       <c r="I167" t="inlineStr"/>
       <c r="M167" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -20554,10 +20554,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>693611</v>
+        <v>693187</v>
       </c>
       <c r="R167" t="n">
-        <v>6553796</v>
+        <v>6553721</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -20589,7 +20589,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -20599,7 +20599,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -20626,7 +20626,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>131866844</v>
+        <v>131866857</v>
       </c>
       <c r="B168" t="n">
         <v>57945</v>
@@ -20657,7 +20657,7 @@
       <c r="I168" t="inlineStr"/>
       <c r="M168" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -20666,10 +20666,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>693187</v>
+        <v>693611</v>
       </c>
       <c r="R168" t="n">
-        <v>6553721</v>
+        <v>6553796</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -20701,7 +20701,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -20711,7 +20711,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -20741,7 +20741,7 @@
         <v>131853396</v>
       </c>
       <c r="B169" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>131866848</v>
+        <v>131866859</v>
       </c>
       <c r="B170" t="n">
         <v>57945</v>
@@ -20866,7 +20866,7 @@
       <c r="I170" t="inlineStr"/>
       <c r="M170" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -20875,10 +20875,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>693488</v>
+        <v>693659</v>
       </c>
       <c r="R170" t="n">
-        <v>6553663</v>
+        <v>6553854</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -20910,7 +20910,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -20920,7 +20920,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -20947,7 +20947,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>131866859</v>
+        <v>131866848</v>
       </c>
       <c r="B171" t="n">
         <v>57945</v>
@@ -20978,7 +20978,7 @@
       <c r="I171" t="inlineStr"/>
       <c r="M171" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -20987,10 +20987,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>693659</v>
+        <v>693488</v>
       </c>
       <c r="R171" t="n">
-        <v>6553854</v>
+        <v>6553663</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -21022,7 +21022,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -21032,7 +21032,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -21062,7 +21062,7 @@
         <v>131854006</v>
       </c>
       <c r="B172" t="n">
-        <v>96435</v>
+        <v>96438</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>131866854</v>
       </c>
       <c r="B174" t="n">
-        <v>96685</v>
+        <v>96688</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -21599,7 +21599,7 @@
         <v>131848310</v>
       </c>
       <c r="B177" t="n">
-        <v>96685</v>
+        <v>96688</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21693,45 +21693,50 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>131847315</v>
+        <v>131866845</v>
       </c>
       <c r="B178" t="n">
-        <v>96685</v>
+        <v>57945</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Breviksnäs, Breviksnäs, Srm</t>
+          <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>693575</v>
+        <v>693230</v>
       </c>
       <c r="R178" t="n">
-        <v>6553722</v>
+        <v>6553757</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -21761,9 +21766,19 @@
           <t>2026-03-22</t>
         </is>
       </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -21778,62 +21793,57 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>131866845</v>
+        <v>131847315</v>
       </c>
       <c r="B179" t="n">
-        <v>57945</v>
+        <v>96688</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Breviksnäs, Srm</t>
+          <t>Breviksnäs, Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>693230</v>
+        <v>693575</v>
       </c>
       <c r="R179" t="n">
-        <v>6553757</v>
+        <v>6553722</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -21863,19 +21873,9 @@
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>14:39</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>14:39</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -21890,69 +21890,65 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>131845274</v>
+        <v>131866838</v>
       </c>
       <c r="B180" t="n">
-        <v>96531</v>
+        <v>57945</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Kolnäsviken, Kolnäsviken, Srm</t>
+          <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>693703</v>
+        <v>693330</v>
       </c>
       <c r="R180" t="n">
-        <v>6553911</v>
+        <v>6553843</v>
       </c>
       <c r="S180" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -21979,9 +21975,19 @@
           <t>2026-03-22</t>
         </is>
       </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -21996,65 +22002,69 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Kalle Skarin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Kalle Skarin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>131866838</v>
+        <v>131845274</v>
       </c>
       <c r="B181" t="n">
-        <v>57945</v>
+        <v>96534</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Breviksnäs, Srm</t>
+          <t>Kolnäsviken, Kolnäsviken, Srm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>693330</v>
+        <v>693703</v>
       </c>
       <c r="R181" t="n">
-        <v>6553843</v>
+        <v>6553911</v>
       </c>
       <c r="S181" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -22081,19 +22091,9 @@
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>15:51</t>
-        </is>
-      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>15:51</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -22108,19 +22108,19 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Kalle Skarin</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Kalle Skarin</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>131866858</v>
+        <v>131866841</v>
       </c>
       <c r="B182" t="n">
         <v>57945</v>
@@ -22160,10 +22160,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>693646</v>
+        <v>693280</v>
       </c>
       <c r="R182" t="n">
-        <v>6553852</v>
+        <v>6553953</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -22195,7 +22195,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -22205,7 +22205,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -22232,7 +22232,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>131866841</v>
+        <v>131866858</v>
       </c>
       <c r="B183" t="n">
         <v>57945</v>
@@ -22272,10 +22272,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>693280</v>
+        <v>693646</v>
       </c>
       <c r="R183" t="n">
-        <v>6553953</v>
+        <v>6553852</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -22307,7 +22307,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -22317,7 +22317,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -22598,7 +22598,7 @@
         <v>131851419</v>
       </c>
       <c r="B186" t="n">
-        <v>96414</v>
+        <v>96417</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>131867113</v>
       </c>
       <c r="B188" t="n">
-        <v>58595</v>
+        <v>58597</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -21059,48 +21059,48 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>131854006</v>
+        <v>131852478</v>
       </c>
       <c r="B172" t="n">
-        <v>96438</v>
+        <v>5178</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>2818</v>
+        <v>102204</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Sandkärr, Sandkärr, Srm</t>
+          <t>Breviksnäs, Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>693193</v>
+        <v>693457</v>
       </c>
       <c r="R172" t="n">
-        <v>6553735</v>
+        <v>6553649</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -21144,60 +21144,60 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Kalle Skarin</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Kalle Skarin</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>131852478</v>
+        <v>131854006</v>
       </c>
       <c r="B173" t="n">
-        <v>5178</v>
+        <v>96438</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>102204</v>
+        <v>2818</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Breviksnäs, Breviksnäs, Srm</t>
+          <t>Sandkärr, Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>693457</v>
+        <v>693193</v>
       </c>
       <c r="R173" t="n">
-        <v>6553649</v>
+        <v>6553735</v>
       </c>
       <c r="S173" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -21241,12 +21241,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Kalle Skarin</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Kalle Skarin</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
@@ -21902,53 +21902,57 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>131866838</v>
+        <v>131845274</v>
       </c>
       <c r="B180" t="n">
-        <v>57945</v>
+        <v>96534</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Breviksnäs, Srm</t>
+          <t>Kolnäsviken, Kolnäsviken, Srm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>693330</v>
+        <v>693703</v>
       </c>
       <c r="R180" t="n">
-        <v>6553843</v>
+        <v>6553911</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -21975,19 +21979,9 @@
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="Z180" t="inlineStr">
-        <is>
-          <t>15:51</t>
-        </is>
-      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t>15:51</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -22002,69 +21996,65 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Kalle Skarin</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Kalle Skarin</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>131845274</v>
+        <v>131866838</v>
       </c>
       <c r="B181" t="n">
-        <v>96534</v>
+        <v>57945</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Kolnäsviken, Kolnäsviken, Srm</t>
+          <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>693703</v>
+        <v>693330</v>
       </c>
       <c r="R181" t="n">
-        <v>6553911</v>
+        <v>6553843</v>
       </c>
       <c r="S181" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -22091,9 +22081,19 @@
           <t>2026-03-22</t>
         </is>
       </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -22108,19 +22108,19 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Kalle Skarin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Kalle Skarin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>131866841</v>
+        <v>131866858</v>
       </c>
       <c r="B182" t="n">
         <v>57945</v>
@@ -22160,10 +22160,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>693280</v>
+        <v>693646</v>
       </c>
       <c r="R182" t="n">
-        <v>6553953</v>
+        <v>6553852</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -22195,7 +22195,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -22205,7 +22205,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -22232,7 +22232,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>131866858</v>
+        <v>131866841</v>
       </c>
       <c r="B183" t="n">
         <v>57945</v>
@@ -22272,10 +22272,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>693646</v>
+        <v>693280</v>
       </c>
       <c r="R183" t="n">
-        <v>6553852</v>
+        <v>6553953</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -22307,7 +22307,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -22317,7 +22317,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -22344,41 +22344,44 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>131866843</v>
+        <v>131866839</v>
       </c>
       <c r="B184" t="n">
-        <v>4775</v>
+        <v>57894</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100299</v>
+        <v>100067</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N184" t="inlineStr"/>
@@ -22388,10 +22391,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>693164</v>
+        <v>693301</v>
       </c>
       <c r="R184" t="n">
-        <v>6553708</v>
+        <v>6554003</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -22423,7 +22426,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -22433,7 +22436,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -22442,24 +22445,8 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
-      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ184" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK184" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO184" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
@@ -22476,44 +22463,41 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>131866839</v>
+        <v>131866843</v>
       </c>
       <c r="B185" t="n">
-        <v>57894</v>
+        <v>4775</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100067</v>
+        <v>100299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N185" t="inlineStr"/>
@@ -22523,10 +22507,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>693301</v>
+        <v>693164</v>
       </c>
       <c r="R185" t="n">
-        <v>6554003</v>
+        <v>6553708</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -22558,7 +22542,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -22568,7 +22552,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -22577,8 +22561,24 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
+      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO185" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -21059,48 +21059,48 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>131852478</v>
+        <v>131854006</v>
       </c>
       <c r="B172" t="n">
-        <v>5178</v>
+        <v>96438</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>102204</v>
+        <v>2818</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Breviksnäs, Breviksnäs, Srm</t>
+          <t>Sandkärr, Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>693457</v>
+        <v>693193</v>
       </c>
       <c r="R172" t="n">
-        <v>6553649</v>
+        <v>6553735</v>
       </c>
       <c r="S172" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -21144,60 +21144,60 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Kalle Skarin</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Kalle Skarin</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>131854006</v>
+        <v>131852478</v>
       </c>
       <c r="B173" t="n">
-        <v>96438</v>
+        <v>5178</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2818</v>
+        <v>102204</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Sandkärr, Sandkärr, Srm</t>
+          <t>Breviksnäs, Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>693193</v>
+        <v>693457</v>
       </c>
       <c r="R173" t="n">
-        <v>6553735</v>
+        <v>6553649</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -21241,12 +21241,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Kalle Skarin</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Kalle Skarin</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
@@ -21902,57 +21902,53 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>131845274</v>
+        <v>131866838</v>
       </c>
       <c r="B180" t="n">
-        <v>96534</v>
+        <v>57945</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Kolnäsviken, Kolnäsviken, Srm</t>
+          <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>693703</v>
+        <v>693330</v>
       </c>
       <c r="R180" t="n">
-        <v>6553911</v>
+        <v>6553843</v>
       </c>
       <c r="S180" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -21979,9 +21975,19 @@
           <t>2026-03-22</t>
         </is>
       </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -21996,65 +22002,69 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Kalle Skarin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Kalle Skarin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>131866838</v>
+        <v>131845274</v>
       </c>
       <c r="B181" t="n">
-        <v>57945</v>
+        <v>96534</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Breviksnäs, Srm</t>
+          <t>Kolnäsviken, Kolnäsviken, Srm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>693330</v>
+        <v>693703</v>
       </c>
       <c r="R181" t="n">
-        <v>6553843</v>
+        <v>6553911</v>
       </c>
       <c r="S181" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -22081,19 +22091,9 @@
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>15:51</t>
-        </is>
-      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>15:51</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -22108,12 +22108,12 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Kalle Skarin</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Kalle Skarin</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
@@ -22595,45 +22595,50 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>131851419</v>
+        <v>131866847</v>
       </c>
       <c r="B186" t="n">
-        <v>96417</v>
+        <v>57945</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>2667</v>
+        <v>100049</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Breviksnäs, Breviksnäs, Srm</t>
+          <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>693447</v>
+        <v>693465</v>
       </c>
       <c r="R186" t="n">
-        <v>6553658</v>
+        <v>6553656</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -22663,9 +22668,19 @@
           <t>2026-03-22</t>
         </is>
       </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -22680,62 +22695,57 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>131866847</v>
+        <v>131851419</v>
       </c>
       <c r="B187" t="n">
-        <v>57945</v>
+        <v>96417</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>100049</v>
+        <v>2667</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Breviksnäs, Srm</t>
+          <t>Breviksnäs, Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>693465</v>
+        <v>693447</v>
       </c>
       <c r="R187" t="n">
-        <v>6553656</v>
+        <v>6553658</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -22765,19 +22775,9 @@
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>14:06</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -22792,12 +22792,12 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -18151,7 +18151,7 @@
         <v>128365727</v>
       </c>
       <c r="B146" t="n">
-        <v>92834</v>
+        <v>93216</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>131866859</v>
+        <v>131866848</v>
       </c>
       <c r="B170" t="n">
         <v>57945</v>
@@ -20866,7 +20866,7 @@
       <c r="I170" t="inlineStr"/>
       <c r="M170" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -20875,10 +20875,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>693659</v>
+        <v>693488</v>
       </c>
       <c r="R170" t="n">
-        <v>6553854</v>
+        <v>6553663</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -20910,7 +20910,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -20920,7 +20920,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -20947,7 +20947,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>131866848</v>
+        <v>131866859</v>
       </c>
       <c r="B171" t="n">
         <v>57945</v>
@@ -20978,7 +20978,7 @@
       <c r="I171" t="inlineStr"/>
       <c r="M171" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -20987,10 +20987,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>693488</v>
+        <v>693659</v>
       </c>
       <c r="R171" t="n">
-        <v>6553663</v>
+        <v>6553854</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -21022,7 +21022,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -21032,7 +21032,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -21059,48 +21059,48 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>131854006</v>
+        <v>131852478</v>
       </c>
       <c r="B172" t="n">
-        <v>96438</v>
+        <v>5178</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>2818</v>
+        <v>102204</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Sandkärr, Sandkärr, Srm</t>
+          <t>Breviksnäs, Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>693193</v>
+        <v>693457</v>
       </c>
       <c r="R172" t="n">
-        <v>6553735</v>
+        <v>6553649</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -21144,60 +21144,60 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Kalle Skarin</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Kalle Skarin</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>131852478</v>
+        <v>131854006</v>
       </c>
       <c r="B173" t="n">
-        <v>5178</v>
+        <v>96438</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>102204</v>
+        <v>2818</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Breviksnäs, Breviksnäs, Srm</t>
+          <t>Sandkärr, Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>693457</v>
+        <v>693193</v>
       </c>
       <c r="R173" t="n">
-        <v>6553649</v>
+        <v>6553735</v>
       </c>
       <c r="S173" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -21241,12 +21241,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Kalle Skarin</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Kalle Skarin</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -21693,50 +21693,45 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>131866845</v>
+        <v>131847315</v>
       </c>
       <c r="B178" t="n">
-        <v>57945</v>
+        <v>96688</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Breviksnäs, Srm</t>
+          <t>Breviksnäs, Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>693230</v>
+        <v>693575</v>
       </c>
       <c r="R178" t="n">
-        <v>6553757</v>
+        <v>6553722</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -21766,19 +21761,9 @@
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="Z178" t="inlineStr">
-        <is>
-          <t>14:39</t>
-        </is>
-      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="AB178" t="inlineStr">
-        <is>
-          <t>14:39</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -21793,57 +21778,62 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>131847315</v>
+        <v>131866845</v>
       </c>
       <c r="B179" t="n">
-        <v>96688</v>
+        <v>57945</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Breviksnäs, Breviksnäs, Srm</t>
+          <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>693575</v>
+        <v>693230</v>
       </c>
       <c r="R179" t="n">
-        <v>6553722</v>
+        <v>6553757</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -21873,9 +21863,19 @@
           <t>2026-03-22</t>
         </is>
       </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -21890,12 +21890,12 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -20514,7 +20514,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>131866844</v>
+        <v>131866857</v>
       </c>
       <c r="B167" t="n">
         <v>57945</v>
@@ -20545,7 +20545,7 @@
       <c r="I167" t="inlineStr"/>
       <c r="M167" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -20554,10 +20554,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>693187</v>
+        <v>693611</v>
       </c>
       <c r="R167" t="n">
-        <v>6553721</v>
+        <v>6553796</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -20589,7 +20589,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -20599,7 +20599,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -20626,50 +20626,45 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>131866857</v>
+        <v>131853396</v>
       </c>
       <c r="B168" t="n">
-        <v>57945</v>
+        <v>101304</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Breviksnäs, Srm</t>
+          <t>Sandkärr, Sandkärr, Srm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>693611</v>
+        <v>693268</v>
       </c>
       <c r="R168" t="n">
-        <v>6553796</v>
+        <v>6553763</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -20699,19 +20694,9 @@
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -20726,57 +20711,62 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>131853396</v>
+        <v>131866844</v>
       </c>
       <c r="B169" t="n">
-        <v>101304</v>
+        <v>57945</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Sandkärr, Sandkärr, Srm</t>
+          <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>693268</v>
+        <v>693187</v>
       </c>
       <c r="R169" t="n">
-        <v>6553763</v>
+        <v>6553721</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -20806,9 +20796,19 @@
           <t>2026-03-22</t>
         </is>
       </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20823,12 +20823,12 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
@@ -21693,45 +21693,50 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>131847315</v>
+        <v>131866845</v>
       </c>
       <c r="B178" t="n">
-        <v>96688</v>
+        <v>57945</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Breviksnäs, Breviksnäs, Srm</t>
+          <t>Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>693575</v>
+        <v>693230</v>
       </c>
       <c r="R178" t="n">
-        <v>6553722</v>
+        <v>6553757</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -21761,9 +21766,19 @@
           <t>2026-03-22</t>
         </is>
       </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -21778,62 +21793,57 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>131866845</v>
+        <v>131847315</v>
       </c>
       <c r="B179" t="n">
-        <v>57945</v>
+        <v>96688</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Breviksnäs, Srm</t>
+          <t>Breviksnäs, Breviksnäs, Srm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>693230</v>
+        <v>693575</v>
       </c>
       <c r="R179" t="n">
-        <v>6553757</v>
+        <v>6553722</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -21863,19 +21873,9 @@
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>14:39</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>14:39</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -21890,12 +21890,12 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -18151,7 +18151,7 @@
         <v>128365727</v>
       </c>
       <c r="B146" t="n">
-        <v>93216</v>
+        <v>93222</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>131867113</v>
       </c>
       <c r="B188" t="n">
-        <v>58597</v>
+        <v>58598</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>132336524</v>
       </c>
       <c r="B189" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>132336525</v>
       </c>
       <c r="B190" t="n">
-        <v>56830</v>
+        <v>56831</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         <v>132336526</v>
       </c>
       <c r="B191" t="n">
-        <v>56832</v>
+        <v>56833</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -18151,7 +18151,7 @@
         <v>128365727</v>
       </c>
       <c r="B146" t="n">
-        <v>93222</v>
+        <v>93232</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>132336524</v>
       </c>
       <c r="B189" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>132336525</v>
       </c>
       <c r="B190" t="n">
-        <v>56831</v>
+        <v>56835</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         <v>132336526</v>
       </c>
       <c r="B191" t="n">
-        <v>56833</v>
+        <v>56837</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -18151,7 +18151,7 @@
         <v>128365727</v>
       </c>
       <c r="B146" t="n">
-        <v>93232</v>
+        <v>93233</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -23373,32 +23373,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>132336526</v>
+        <v>133328062</v>
       </c>
       <c r="B193" t="n">
-        <v>56839</v>
+        <v>56837</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -23409,17 +23409,17 @@
       <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Kolnäsviken, Ornö, Srm</t>
+          <t>Sandkärr, Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>693687</v>
+        <v>693257</v>
       </c>
       <c r="R193" t="n">
-        <v>6553908</v>
+        <v>6553857</v>
       </c>
       <c r="S193" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -23443,22 +23443,22 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>22:25</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>22:25</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -23472,7 +23472,7 @@
       </c>
       <c r="AI193" t="inlineStr">
         <is>
-          <t>Dalgång med halvöppen lövskog omgiven av barrskog intill vik.</t>
+          <t>Klibbalsremsa med bladvass utanför och barrskog innanför.</t>
         </is>
       </c>
       <c r="AT193" t="inlineStr"/>
@@ -23490,32 +23490,32 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>133328062</v>
+        <v>132336526</v>
       </c>
       <c r="B194" t="n">
-        <v>56837</v>
+        <v>56839</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -23526,17 +23526,17 @@
       <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Sandkärr, Breviksnäs, Ornö, Srm</t>
+          <t>Kolnäsviken, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>693257</v>
+        <v>693687</v>
       </c>
       <c r="R194" t="n">
-        <v>6553857</v>
+        <v>6553908</v>
       </c>
       <c r="S194" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -23560,22 +23560,22 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="AI194" t="inlineStr">
         <is>
-          <t>Klibbalsremsa med bladvass utanför och barrskog innanför.</t>
+          <t>Dalgång med halvöppen lövskog omgiven av barrskog intill vik.</t>
         </is>
       </c>
       <c r="AT194" t="inlineStr"/>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -23373,32 +23373,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>133328062</v>
+        <v>132336526</v>
       </c>
       <c r="B193" t="n">
-        <v>56837</v>
+        <v>56839</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -23409,17 +23409,17 @@
       <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Sandkärr, Breviksnäs, Ornö, Srm</t>
+          <t>Kolnäsviken, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>693257</v>
+        <v>693687</v>
       </c>
       <c r="R193" t="n">
-        <v>6553857</v>
+        <v>6553908</v>
       </c>
       <c r="S193" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -23443,22 +23443,22 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -23472,7 +23472,7 @@
       </c>
       <c r="AI193" t="inlineStr">
         <is>
-          <t>Klibbalsremsa med bladvass utanför och barrskog innanför.</t>
+          <t>Dalgång med halvöppen lövskog omgiven av barrskog intill vik.</t>
         </is>
       </c>
       <c r="AT193" t="inlineStr"/>
@@ -23490,32 +23490,32 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>132336526</v>
+        <v>133328062</v>
       </c>
       <c r="B194" t="n">
-        <v>56839</v>
+        <v>56837</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -23526,17 +23526,17 @@
       <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Kolnäsviken, Ornö, Srm</t>
+          <t>Sandkärr, Breviksnäs, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>693687</v>
+        <v>693257</v>
       </c>
       <c r="R194" t="n">
-        <v>6553908</v>
+        <v>6553857</v>
       </c>
       <c r="S194" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -23560,22 +23560,22 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>22:25</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>22:25</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="AI194" t="inlineStr">
         <is>
-          <t>Dalgång med halvöppen lövskog omgiven av barrskog intill vik.</t>
+          <t>Klibbalsremsa med bladvass utanför och barrskog innanför.</t>
         </is>
       </c>
       <c r="AT194" t="inlineStr"/>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY194"/>
+  <dimension ref="A1:AY225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23605,6 +23605,3478 @@
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>133637963</v>
+      </c>
+      <c r="B195" t="n">
+        <v>58393</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>693635</v>
+      </c>
+      <c r="R195" t="n">
+        <v>6554041</v>
+      </c>
+      <c r="S195" t="n">
+        <v>25</v>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="AD195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT195" t="inlineStr"/>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>133637976</v>
+      </c>
+      <c r="B196" t="n">
+        <v>58641</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>693635</v>
+      </c>
+      <c r="R196" t="n">
+        <v>6554041</v>
+      </c>
+      <c r="S196" t="n">
+        <v>25</v>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="AD196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT196" t="inlineStr"/>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>133637887</v>
+      </c>
+      <c r="B197" t="n">
+        <v>57971</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>693465</v>
+      </c>
+      <c r="R197" t="n">
+        <v>6554079</v>
+      </c>
+      <c r="S197" t="n">
+        <v>25</v>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AD197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT197" t="inlineStr"/>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>133637913</v>
+      </c>
+      <c r="B198" t="n">
+        <v>58393</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>693430</v>
+      </c>
+      <c r="R198" t="n">
+        <v>6553676</v>
+      </c>
+      <c r="S198" t="n">
+        <v>25</v>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="AD198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT198" t="inlineStr"/>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>133637938</v>
+      </c>
+      <c r="B199" t="n">
+        <v>58393</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>693333</v>
+      </c>
+      <c r="R199" t="n">
+        <v>6553773</v>
+      </c>
+      <c r="S199" t="n">
+        <v>25</v>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AD199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT199" t="inlineStr"/>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX199" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>133637863</v>
+      </c>
+      <c r="B200" t="n">
+        <v>58332</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>693502</v>
+      </c>
+      <c r="R200" t="n">
+        <v>6553871</v>
+      </c>
+      <c r="S200" t="n">
+        <v>25</v>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="AD200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT200" t="inlineStr"/>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>133637912</v>
+      </c>
+      <c r="B201" t="n">
+        <v>57300</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>102950</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Strandskata</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Haematopus ostralegus</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q201" t="n">
+        <v>693430</v>
+      </c>
+      <c r="R201" t="n">
+        <v>6553676</v>
+      </c>
+      <c r="S201" t="n">
+        <v>25</v>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="AD201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT201" t="inlineStr"/>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>133637926</v>
+      </c>
+      <c r="B202" t="n">
+        <v>58641</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q202" t="n">
+        <v>693430</v>
+      </c>
+      <c r="R202" t="n">
+        <v>6553676</v>
+      </c>
+      <c r="S202" t="n">
+        <v>25</v>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT202" t="inlineStr"/>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>133637936</v>
+      </c>
+      <c r="B203" t="n">
+        <v>57300</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>102950</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Strandskata</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Haematopus ostralegus</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q203" t="n">
+        <v>693333</v>
+      </c>
+      <c r="R203" t="n">
+        <v>6553773</v>
+      </c>
+      <c r="S203" t="n">
+        <v>25</v>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AD203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT203" t="inlineStr"/>
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX203" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>133637868</v>
+      </c>
+      <c r="B204" t="n">
+        <v>58641</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q204" t="n">
+        <v>693502</v>
+      </c>
+      <c r="R204" t="n">
+        <v>6553871</v>
+      </c>
+      <c r="S204" t="n">
+        <v>25</v>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT204" t="inlineStr"/>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX204" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>133637969</v>
+      </c>
+      <c r="B205" t="n">
+        <v>58332</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q205" t="n">
+        <v>693635</v>
+      </c>
+      <c r="R205" t="n">
+        <v>6554041</v>
+      </c>
+      <c r="S205" t="n">
+        <v>25</v>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="AD205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT205" t="inlineStr"/>
+      <c r="AW205" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX205" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>133637918</v>
+      </c>
+      <c r="B206" t="n">
+        <v>58332</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q206" t="n">
+        <v>693430</v>
+      </c>
+      <c r="R206" t="n">
+        <v>6553676</v>
+      </c>
+      <c r="S206" t="n">
+        <v>25</v>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="AD206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT206" t="inlineStr"/>
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX206" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>133637881</v>
+      </c>
+      <c r="B207" t="n">
+        <v>56928</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>100045</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Sångsvan</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Cygnus cygnus</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q207" t="n">
+        <v>693465</v>
+      </c>
+      <c r="R207" t="n">
+        <v>6554079</v>
+      </c>
+      <c r="S207" t="n">
+        <v>25</v>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>01:20</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>01:20</t>
+        </is>
+      </c>
+      <c r="AD207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT207" t="inlineStr"/>
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX207" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>133637928</v>
+      </c>
+      <c r="B208" t="n">
+        <v>58090</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q208" t="n">
+        <v>693430</v>
+      </c>
+      <c r="R208" t="n">
+        <v>6553676</v>
+      </c>
+      <c r="S208" t="n">
+        <v>25</v>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT208" t="inlineStr"/>
+      <c r="AW208" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX208" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>133637952</v>
+      </c>
+      <c r="B209" t="n">
+        <v>58641</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr"/>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q209" t="n">
+        <v>693333</v>
+      </c>
+      <c r="R209" t="n">
+        <v>6553773</v>
+      </c>
+      <c r="S209" t="n">
+        <v>25</v>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT209" t="inlineStr"/>
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX209" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>133637899</v>
+      </c>
+      <c r="B210" t="n">
+        <v>58117</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q210" t="n">
+        <v>693465</v>
+      </c>
+      <c r="R210" t="n">
+        <v>6554079</v>
+      </c>
+      <c r="S210" t="n">
+        <v>25</v>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="AD210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT210" t="inlineStr"/>
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX210" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>133637943</v>
+      </c>
+      <c r="B211" t="n">
+        <v>58332</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr"/>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q211" t="n">
+        <v>693333</v>
+      </c>
+      <c r="R211" t="n">
+        <v>6553773</v>
+      </c>
+      <c r="S211" t="n">
+        <v>25</v>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT211" t="inlineStr"/>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>133637885</v>
+      </c>
+      <c r="B212" t="n">
+        <v>58393</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q212" t="n">
+        <v>693465</v>
+      </c>
+      <c r="R212" t="n">
+        <v>6554079</v>
+      </c>
+      <c r="S212" t="n">
+        <v>25</v>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="AD212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT212" t="inlineStr"/>
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX212" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>133637927</v>
+      </c>
+      <c r="B213" t="n">
+        <v>58607</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q213" t="n">
+        <v>693430</v>
+      </c>
+      <c r="R213" t="n">
+        <v>6553676</v>
+      </c>
+      <c r="S213" t="n">
+        <v>25</v>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="AD213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT213" t="inlineStr"/>
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX213" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>133637896</v>
+      </c>
+      <c r="B214" t="n">
+        <v>58090</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q214" t="n">
+        <v>693465</v>
+      </c>
+      <c r="R214" t="n">
+        <v>6554079</v>
+      </c>
+      <c r="S214" t="n">
+        <v>25</v>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT214" t="inlineStr"/>
+      <c r="AW214" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX214" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>133637884</v>
+      </c>
+      <c r="B215" t="n">
+        <v>57551</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>102963</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Skrattmås</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Chroicocephalus ridibundus</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr"/>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q215" t="n">
+        <v>693465</v>
+      </c>
+      <c r="R215" t="n">
+        <v>6554079</v>
+      </c>
+      <c r="S215" t="n">
+        <v>25</v>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="AD215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT215" t="inlineStr"/>
+      <c r="AW215" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX215" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>133637858</v>
+      </c>
+      <c r="B216" t="n">
+        <v>58393</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr"/>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q216" t="n">
+        <v>693502</v>
+      </c>
+      <c r="R216" t="n">
+        <v>6553871</v>
+      </c>
+      <c r="S216" t="n">
+        <v>25</v>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="AD216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT216" t="inlineStr"/>
+      <c r="AW216" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX216" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>133637869</v>
+      </c>
+      <c r="B217" t="n">
+        <v>58090</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q217" t="n">
+        <v>693502</v>
+      </c>
+      <c r="R217" t="n">
+        <v>6553871</v>
+      </c>
+      <c r="S217" t="n">
+        <v>25</v>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT217" t="inlineStr"/>
+      <c r="AW217" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX217" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>133637978</v>
+      </c>
+      <c r="B218" t="n">
+        <v>58607</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr"/>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q218" t="n">
+        <v>693635</v>
+      </c>
+      <c r="R218" t="n">
+        <v>6554041</v>
+      </c>
+      <c r="S218" t="n">
+        <v>25</v>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT218" t="inlineStr"/>
+      <c r="AW218" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX218" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>133637908</v>
+      </c>
+      <c r="B219" t="n">
+        <v>58119</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q219" t="n">
+        <v>693430</v>
+      </c>
+      <c r="R219" t="n">
+        <v>6553676</v>
+      </c>
+      <c r="S219" t="n">
+        <v>25</v>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AD219" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE219" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG219" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT219" t="inlineStr"/>
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX219" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>133637977</v>
+      </c>
+      <c r="B220" t="n">
+        <v>57952</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q220" t="n">
+        <v>693635</v>
+      </c>
+      <c r="R220" t="n">
+        <v>6554041</v>
+      </c>
+      <c r="S220" t="n">
+        <v>25</v>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="AB220" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="AD220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT220" t="inlineStr"/>
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX220" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>133637852</v>
+      </c>
+      <c r="B221" t="n">
+        <v>58119</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q221" t="n">
+        <v>693502</v>
+      </c>
+      <c r="R221" t="n">
+        <v>6553871</v>
+      </c>
+      <c r="S221" t="n">
+        <v>25</v>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AD221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT221" t="inlineStr"/>
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX221" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>133637985</v>
+      </c>
+      <c r="B222" t="n">
+        <v>58398</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q222" t="n">
+        <v>693635</v>
+      </c>
+      <c r="R222" t="n">
+        <v>6554041</v>
+      </c>
+      <c r="S222" t="n">
+        <v>25</v>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>05:41</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>05:41</t>
+        </is>
+      </c>
+      <c r="AD222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT222" t="inlineStr"/>
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX222" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>133637888</v>
+      </c>
+      <c r="B223" t="n">
+        <v>58332</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q223" t="n">
+        <v>693465</v>
+      </c>
+      <c r="R223" t="n">
+        <v>6554079</v>
+      </c>
+      <c r="S223" t="n">
+        <v>25</v>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AD223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG223" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT223" t="inlineStr"/>
+      <c r="AW223" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX223" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>133637937</v>
+      </c>
+      <c r="B224" t="n">
+        <v>57551</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>102963</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Skrattmås</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Chroicocephalus ridibundus</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr"/>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q224" t="n">
+        <v>693333</v>
+      </c>
+      <c r="R224" t="n">
+        <v>6553773</v>
+      </c>
+      <c r="S224" t="n">
+        <v>25</v>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AD224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT224" t="inlineStr"/>
+      <c r="AW224" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX224" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>133637856</v>
+      </c>
+      <c r="B225" t="n">
+        <v>57300</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>102950</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Strandskata</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Haematopus ostralegus</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>Breviksnäs, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q225" t="n">
+        <v>693502</v>
+      </c>
+      <c r="R225" t="n">
+        <v>6553871</v>
+      </c>
+      <c r="S225" t="n">
+        <v>25</v>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>04:36</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="AB225" t="inlineStr">
+        <is>
+          <t>04:36</t>
+        </is>
+      </c>
+      <c r="AD225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT225" t="inlineStr"/>
+      <c r="AW225" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX225" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -24055,32 +24055,32 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>133637938</v>
+        <v>133637926</v>
       </c>
       <c r="B199" t="n">
-        <v>58410</v>
+        <v>58658</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>103001</v>
+        <v>103044</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -24095,10 +24095,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>693333</v>
+        <v>693430</v>
       </c>
       <c r="R199" t="n">
-        <v>6553773</v>
+        <v>6553676</v>
       </c>
       <c r="S199" t="n">
         <v>25</v>
@@ -24125,22 +24125,22 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -24167,10 +24167,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>133637926</v>
+        <v>133637863</v>
       </c>
       <c r="B200" t="n">
-        <v>58658</v>
+        <v>58349</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -24178,16 +24178,16 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -24207,10 +24207,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>693430</v>
+        <v>693502</v>
       </c>
       <c r="R200" t="n">
-        <v>6553676</v>
+        <v>6553871</v>
       </c>
       <c r="S200" t="n">
         <v>25</v>
@@ -24237,22 +24237,22 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -24279,10 +24279,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>133637912</v>
+        <v>133637938</v>
       </c>
       <c r="B201" t="n">
-        <v>57317</v>
+        <v>58410</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24290,21 +24290,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>102950</v>
+        <v>103001</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Strandskata</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Haematopus ostralegus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -24319,10 +24319,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>693430</v>
+        <v>693333</v>
       </c>
       <c r="R201" t="n">
-        <v>6553676</v>
+        <v>6553773</v>
       </c>
       <c r="S201" t="n">
         <v>25</v>
@@ -24349,22 +24349,22 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -24391,32 +24391,32 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>133637863</v>
+        <v>133637912</v>
       </c>
       <c r="B202" t="n">
-        <v>58349</v>
+        <v>57317</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>103015</v>
+        <v>102950</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Strandskata</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Haematopus ostralegus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -24431,10 +24431,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>693502</v>
+        <v>693430</v>
       </c>
       <c r="R202" t="n">
-        <v>6553871</v>
+        <v>6553676</v>
       </c>
       <c r="S202" t="n">
         <v>25</v>
@@ -24461,22 +24461,22 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -24503,32 +24503,32 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>133637868</v>
+        <v>133637936</v>
       </c>
       <c r="B203" t="n">
-        <v>58658</v>
+        <v>57317</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>103044</v>
+        <v>102950</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Strandskata</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Haematopus ostralegus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -24543,10 +24543,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>693502</v>
+        <v>693333</v>
       </c>
       <c r="R203" t="n">
-        <v>6553871</v>
+        <v>6553773</v>
       </c>
       <c r="S203" t="n">
         <v>25</v>
@@ -24573,22 +24573,22 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -24615,32 +24615,32 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>133637936</v>
+        <v>133637969</v>
       </c>
       <c r="B204" t="n">
-        <v>57317</v>
+        <v>58349</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>102950</v>
+        <v>103015</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Strandskata</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Haematopus ostralegus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -24655,10 +24655,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>693333</v>
+        <v>693635</v>
       </c>
       <c r="R204" t="n">
-        <v>6553773</v>
+        <v>6554041</v>
       </c>
       <c r="S204" t="n">
         <v>25</v>
@@ -24685,22 +24685,22 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -24727,10 +24727,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>133637969</v>
+        <v>133637868</v>
       </c>
       <c r="B205" t="n">
-        <v>58349</v>
+        <v>58658</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24738,16 +24738,16 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -24767,10 +24767,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>693635</v>
+        <v>693502</v>
       </c>
       <c r="R205" t="n">
-        <v>6554041</v>
+        <v>6553871</v>
       </c>
       <c r="S205" t="n">
         <v>25</v>
@@ -24797,22 +24797,22 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -24839,10 +24839,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>133637881</v>
+        <v>133637918</v>
       </c>
       <c r="B206" t="n">
-        <v>56945</v>
+        <v>58349</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24850,16 +24850,16 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>100045</v>
+        <v>103015</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -24879,10 +24879,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>693465</v>
+        <v>693430</v>
       </c>
       <c r="R206" t="n">
-        <v>6554079</v>
+        <v>6553676</v>
       </c>
       <c r="S206" t="n">
         <v>25</v>
@@ -24909,22 +24909,22 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>01:20</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>01:20</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -24951,10 +24951,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>133637918</v>
+        <v>133637881</v>
       </c>
       <c r="B207" t="n">
-        <v>58349</v>
+        <v>56945</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24962,16 +24962,16 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>103015</v>
+        <v>100045</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -24991,10 +24991,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>693430</v>
+        <v>693465</v>
       </c>
       <c r="R207" t="n">
-        <v>6553676</v>
+        <v>6554079</v>
       </c>
       <c r="S207" t="n">
         <v>25</v>
@@ -25021,22 +25021,22 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>01:20</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>01:20</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -25063,10 +25063,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>133637885</v>
+        <v>133637928</v>
       </c>
       <c r="B208" t="n">
-        <v>58410</v>
+        <v>58107</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -25074,21 +25074,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>103001</v>
+        <v>205976</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -25103,10 +25103,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>693465</v>
+        <v>693430</v>
       </c>
       <c r="R208" t="n">
-        <v>6554079</v>
+        <v>6553676</v>
       </c>
       <c r="S208" t="n">
         <v>25</v>
@@ -25133,22 +25133,22 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -25175,32 +25175,32 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>133637928</v>
+        <v>133637952</v>
       </c>
       <c r="B209" t="n">
-        <v>58107</v>
+        <v>58658</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>205976</v>
+        <v>103044</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -25215,10 +25215,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>693430</v>
+        <v>693333</v>
       </c>
       <c r="R209" t="n">
-        <v>6553676</v>
+        <v>6553773</v>
       </c>
       <c r="S209" t="n">
         <v>25</v>
@@ -25245,22 +25245,22 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -25287,27 +25287,27 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>133637943</v>
+        <v>133637899</v>
       </c>
       <c r="B210" t="n">
-        <v>58349</v>
+        <v>58134</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -25327,10 +25327,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>693333</v>
+        <v>693465</v>
       </c>
       <c r="R210" t="n">
-        <v>6553773</v>
+        <v>6554079</v>
       </c>
       <c r="S210" t="n">
         <v>25</v>
@@ -25357,22 +25357,22 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -25399,27 +25399,27 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>133637899</v>
+        <v>133637943</v>
       </c>
       <c r="B211" t="n">
-        <v>58134</v>
+        <v>58349</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -25439,10 +25439,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>693465</v>
+        <v>693333</v>
       </c>
       <c r="R211" t="n">
-        <v>6554079</v>
+        <v>6553773</v>
       </c>
       <c r="S211" t="n">
         <v>25</v>
@@ -25469,22 +25469,22 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -25511,32 +25511,32 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>133637952</v>
+        <v>133637885</v>
       </c>
       <c r="B212" t="n">
-        <v>58658</v>
+        <v>58410</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>103044</v>
+        <v>103001</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -25551,10 +25551,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>693333</v>
+        <v>693465</v>
       </c>
       <c r="R212" t="n">
-        <v>6553773</v>
+        <v>6554079</v>
       </c>
       <c r="S212" t="n">
         <v>25</v>
@@ -25586,7 +25586,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -25596,7 +25596,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -25623,32 +25623,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>133637896</v>
+        <v>133637927</v>
       </c>
       <c r="B213" t="n">
-        <v>58107</v>
+        <v>58624</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>205976</v>
+        <v>103042</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -25663,10 +25663,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>693465</v>
+        <v>693430</v>
       </c>
       <c r="R213" t="n">
-        <v>6554079</v>
+        <v>6553676</v>
       </c>
       <c r="S213" t="n">
         <v>25</v>
@@ -25698,7 +25698,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -25708,7 +25708,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -25735,32 +25735,32 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>133637927</v>
+        <v>133637896</v>
       </c>
       <c r="B214" t="n">
-        <v>58624</v>
+        <v>58107</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>103042</v>
+        <v>205976</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -25775,10 +25775,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>693430</v>
+        <v>693465</v>
       </c>
       <c r="R214" t="n">
-        <v>6553676</v>
+        <v>6554079</v>
       </c>
       <c r="S214" t="n">
         <v>25</v>
@@ -25810,7 +25810,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -25820,7 +25820,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -26071,32 +26071,32 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>133637908</v>
+        <v>133637978</v>
       </c>
       <c r="B217" t="n">
-        <v>58136</v>
+        <v>58624</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>103021</v>
+        <v>103042</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -26111,10 +26111,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>693430</v>
+        <v>693635</v>
       </c>
       <c r="R217" t="n">
-        <v>6553676</v>
+        <v>6554041</v>
       </c>
       <c r="S217" t="n">
         <v>25</v>
@@ -26141,22 +26141,22 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -26183,32 +26183,32 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>133637978</v>
+        <v>133637908</v>
       </c>
       <c r="B218" t="n">
-        <v>58624</v>
+        <v>58136</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>103042</v>
+        <v>103021</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -26223,10 +26223,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>693635</v>
+        <v>693430</v>
       </c>
       <c r="R218" t="n">
-        <v>6554041</v>
+        <v>6553676</v>
       </c>
       <c r="S218" t="n">
         <v>25</v>
@@ -26253,22 +26253,22 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD218" t="b">

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -24167,32 +24167,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>133637863</v>
+        <v>133637938</v>
       </c>
       <c r="B200" t="n">
-        <v>58349</v>
+        <v>58410</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -24207,10 +24207,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>693502</v>
+        <v>693333</v>
       </c>
       <c r="R200" t="n">
-        <v>6553871</v>
+        <v>6553773</v>
       </c>
       <c r="S200" t="n">
         <v>25</v>
@@ -24237,22 +24237,22 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -24279,10 +24279,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>133637938</v>
+        <v>133637912</v>
       </c>
       <c r="B201" t="n">
-        <v>58410</v>
+        <v>57317</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24290,21 +24290,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>103001</v>
+        <v>102950</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Strandskata</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Haematopus ostralegus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -24319,10 +24319,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>693333</v>
+        <v>693430</v>
       </c>
       <c r="R201" t="n">
-        <v>6553773</v>
+        <v>6553676</v>
       </c>
       <c r="S201" t="n">
         <v>25</v>
@@ -24349,22 +24349,22 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -24391,32 +24391,32 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>133637912</v>
+        <v>133637863</v>
       </c>
       <c r="B202" t="n">
-        <v>57317</v>
+        <v>58349</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>102950</v>
+        <v>103015</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Strandskata</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Haematopus ostralegus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -24431,10 +24431,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>693430</v>
+        <v>693502</v>
       </c>
       <c r="R202" t="n">
-        <v>6553676</v>
+        <v>6553871</v>
       </c>
       <c r="S202" t="n">
         <v>25</v>
@@ -24461,22 +24461,22 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -24503,32 +24503,32 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>133637936</v>
+        <v>133637969</v>
       </c>
       <c r="B203" t="n">
-        <v>57317</v>
+        <v>58349</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>102950</v>
+        <v>103015</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Strandskata</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Haematopus ostralegus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -24543,10 +24543,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>693333</v>
+        <v>693635</v>
       </c>
       <c r="R203" t="n">
-        <v>6553773</v>
+        <v>6554041</v>
       </c>
       <c r="S203" t="n">
         <v>25</v>
@@ -24573,22 +24573,22 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -24615,10 +24615,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>133637969</v>
+        <v>133637868</v>
       </c>
       <c r="B204" t="n">
-        <v>58349</v>
+        <v>58658</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24626,16 +24626,16 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -24655,10 +24655,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>693635</v>
+        <v>693502</v>
       </c>
       <c r="R204" t="n">
-        <v>6554041</v>
+        <v>6553871</v>
       </c>
       <c r="S204" t="n">
         <v>25</v>
@@ -24685,22 +24685,22 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -24727,32 +24727,32 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>133637868</v>
+        <v>133637936</v>
       </c>
       <c r="B205" t="n">
-        <v>58658</v>
+        <v>57317</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>103044</v>
+        <v>102950</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Strandskata</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Haematopus ostralegus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -24767,10 +24767,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>693502</v>
+        <v>693333</v>
       </c>
       <c r="R205" t="n">
-        <v>6553871</v>
+        <v>6553773</v>
       </c>
       <c r="S205" t="n">
         <v>25</v>
@@ -24797,22 +24797,22 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -24839,10 +24839,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>133637918</v>
+        <v>133637881</v>
       </c>
       <c r="B206" t="n">
-        <v>58349</v>
+        <v>56945</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24850,16 +24850,16 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>103015</v>
+        <v>100045</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -24879,10 +24879,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>693430</v>
+        <v>693465</v>
       </c>
       <c r="R206" t="n">
-        <v>6553676</v>
+        <v>6554079</v>
       </c>
       <c r="S206" t="n">
         <v>25</v>
@@ -24909,22 +24909,22 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>01:20</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>01:20</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -24951,10 +24951,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>133637881</v>
+        <v>133637918</v>
       </c>
       <c r="B207" t="n">
-        <v>56945</v>
+        <v>58349</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24962,16 +24962,16 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100045</v>
+        <v>103015</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -24991,10 +24991,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>693465</v>
+        <v>693430</v>
       </c>
       <c r="R207" t="n">
-        <v>6554079</v>
+        <v>6553676</v>
       </c>
       <c r="S207" t="n">
         <v>25</v>
@@ -25021,22 +25021,22 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>01:20</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>01:20</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -25063,32 +25063,32 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>133637928</v>
+        <v>133637943</v>
       </c>
       <c r="B208" t="n">
-        <v>58107</v>
+        <v>58349</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>205976</v>
+        <v>103015</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -25103,10 +25103,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>693430</v>
+        <v>693333</v>
       </c>
       <c r="R208" t="n">
-        <v>6553676</v>
+        <v>6553773</v>
       </c>
       <c r="S208" t="n">
         <v>25</v>
@@ -25133,22 +25133,22 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -25175,32 +25175,32 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>133637952</v>
+        <v>133637928</v>
       </c>
       <c r="B209" t="n">
-        <v>58658</v>
+        <v>58107</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>103044</v>
+        <v>205976</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -25215,10 +25215,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>693333</v>
+        <v>693430</v>
       </c>
       <c r="R209" t="n">
-        <v>6553773</v>
+        <v>6553676</v>
       </c>
       <c r="S209" t="n">
         <v>25</v>
@@ -25245,22 +25245,22 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -25287,10 +25287,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>133637899</v>
+        <v>133637885</v>
       </c>
       <c r="B210" t="n">
-        <v>58134</v>
+        <v>58410</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25298,21 +25298,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>103020</v>
+        <v>103001</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -25357,22 +25357,22 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -25399,27 +25399,27 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>133637943</v>
+        <v>133637899</v>
       </c>
       <c r="B211" t="n">
-        <v>58349</v>
+        <v>58134</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -25439,10 +25439,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>693333</v>
+        <v>693465</v>
       </c>
       <c r="R211" t="n">
-        <v>6553773</v>
+        <v>6554079</v>
       </c>
       <c r="S211" t="n">
         <v>25</v>
@@ -25469,22 +25469,22 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -25511,32 +25511,32 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>133637885</v>
+        <v>133637952</v>
       </c>
       <c r="B212" t="n">
-        <v>58410</v>
+        <v>58658</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>103001</v>
+        <v>103044</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -25551,10 +25551,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>693465</v>
+        <v>693333</v>
       </c>
       <c r="R212" t="n">
-        <v>6554079</v>
+        <v>6553773</v>
       </c>
       <c r="S212" t="n">
         <v>25</v>
@@ -25586,7 +25586,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -25596,7 +25596,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -26071,32 +26071,32 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>133637978</v>
+        <v>133637908</v>
       </c>
       <c r="B217" t="n">
-        <v>58624</v>
+        <v>58136</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>103042</v>
+        <v>103021</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -26111,10 +26111,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>693635</v>
+        <v>693430</v>
       </c>
       <c r="R217" t="n">
-        <v>6554041</v>
+        <v>6553676</v>
       </c>
       <c r="S217" t="n">
         <v>25</v>
@@ -26141,22 +26141,22 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -26183,10 +26183,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>133637908</v>
+        <v>133637869</v>
       </c>
       <c r="B218" t="n">
-        <v>58136</v>
+        <v>58107</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -26194,21 +26194,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>103021</v>
+        <v>205976</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -26223,10 +26223,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>693430</v>
+        <v>693502</v>
       </c>
       <c r="R218" t="n">
-        <v>6553676</v>
+        <v>6553871</v>
       </c>
       <c r="S218" t="n">
         <v>25</v>
@@ -26253,22 +26253,22 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -26295,32 +26295,32 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>133637869</v>
+        <v>133637978</v>
       </c>
       <c r="B219" t="n">
-        <v>58107</v>
+        <v>58624</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>205976</v>
+        <v>103042</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -26335,10 +26335,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>693502</v>
+        <v>693635</v>
       </c>
       <c r="R219" t="n">
-        <v>6553871</v>
+        <v>6554041</v>
       </c>
       <c r="S219" t="n">
         <v>25</v>
@@ -26365,22 +26365,22 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -26407,32 +26407,32 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>133637977</v>
+        <v>133637852</v>
       </c>
       <c r="B220" t="n">
-        <v>57969</v>
+        <v>58136</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -26447,10 +26447,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>693635</v>
+        <v>693502</v>
       </c>
       <c r="R220" t="n">
-        <v>6554041</v>
+        <v>6553871</v>
       </c>
       <c r="S220" t="n">
         <v>25</v>
@@ -26477,22 +26477,22 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -26519,32 +26519,32 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>133637852</v>
+        <v>133637977</v>
       </c>
       <c r="B221" t="n">
-        <v>58136</v>
+        <v>57969</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -26559,10 +26559,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>693502</v>
+        <v>693635</v>
       </c>
       <c r="R221" t="n">
-        <v>6553871</v>
+        <v>6554041</v>
       </c>
       <c r="S221" t="n">
         <v>25</v>
@@ -26589,22 +26589,22 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="AD221" t="b">

--- a/artfynd/A 66380-2021 artfynd.xlsx
+++ b/artfynd/A 66380-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY296"/>
+  <dimension ref="A1:AZ296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354154</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98158262</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99458021</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1134,6 +1154,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99462539</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1245,6 +1270,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99462632</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1372,6 +1402,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124052</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1499,6 +1534,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124070</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1635,6 +1675,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231767</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1771,6 +1816,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231768</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1907,6 +1957,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231793</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2043,6 +2098,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231795</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2170,6 +2230,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365737</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2276,6 +2341,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131845274</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2377,6 +2447,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131845470</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2483,6 +2558,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131847129</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2598,6 +2678,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354716</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2726,6 +2811,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97371838</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2835,6 +2925,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98156324</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2951,6 +3046,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104335875</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3077,6 +3177,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231774</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3209,6 +3314,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231770</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3315,6 +3425,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97353845</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3426,6 +3541,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944670</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3523,6 +3643,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131844576</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3645,6 +3770,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124059</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3772,6 +3902,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124064</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3899,6 +4034,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124082</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4001,6 +4141,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97355018</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4108,6 +4253,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124056</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4215,6 +4365,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124058</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4322,6 +4477,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124061</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4437,6 +4597,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126603393</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4544,6 +4709,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753764</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4651,6 +4821,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365743</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4758,6 +4933,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910886</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4855,6 +5035,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131847315</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4952,6 +5137,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131848310</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5059,6 +5249,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866851</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5166,6 +5361,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866854</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5283,6 +5483,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231786</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5395,6 +5600,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753763</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5488,6 +5698,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131844464</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5620,6 +5835,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231778</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5732,6 +5952,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231788</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5839,6 +6064,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126551318</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5951,6 +6181,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910892</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6048,6 +6283,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131851419</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6155,6 +6395,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97353704</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6262,6 +6507,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354362</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6369,6 +6619,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354275</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6481,6 +6736,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231787</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6588,6 +6848,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126551287</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6700,6 +6965,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910891</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6807,6 +7077,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866861</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6914,6 +7189,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944654</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7021,6 +7301,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944657</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7148,6 +7433,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124051</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7255,6 +7545,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124067</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7382,6 +7677,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124071</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7509,6 +7809,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231766</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7616,6 +7921,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231776</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7743,6 +8053,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231792</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7870,6 +8185,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231794</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7977,6 +8297,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753771</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8084,6 +8409,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753772</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8211,6 +8541,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365738</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8333,6 +8668,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910966</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8430,6 +8770,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131854006</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8531,6 +8876,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128539518</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8658,6 +9008,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124053</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8785,6 +9140,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365739</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8892,6 +9252,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910890</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9018,6 +9383,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128274021</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9125,6 +9495,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128278597</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9232,6 +9607,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365722</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9339,6 +9719,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365746</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9446,6 +9831,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365751</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9553,6 +9943,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910879</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9674,6 +10069,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128280496</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9795,6 +10195,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128280607</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9902,6 +10307,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365726</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10009,6 +10419,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365728</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10116,6 +10531,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944647</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10243,6 +10663,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231789</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10344,6 +10769,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128538845</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10451,6 +10881,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866855</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10552,6 +10987,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97353710</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10653,6 +11093,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97353721</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10775,6 +11220,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944662</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10897,6 +11347,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944684</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11024,6 +11479,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124084</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11131,6 +11591,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121221411</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11245,6 +11710,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121221425</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11372,6 +11842,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231785</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11493,6 +11968,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124182917</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11614,6 +12094,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124185384</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11721,6 +12206,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126610206</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11848,6 +12338,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753792</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11945,6 +12440,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129516556</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12050,6 +12550,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129667335</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12177,6 +12682,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910887</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12304,6 +12814,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910895</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12411,6 +12926,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124073</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12522,6 +13042,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365727</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12631,6 +13156,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354632</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12738,6 +13268,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124055</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12843,6 +13378,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129667428</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12950,6 +13490,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910888</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13062,6 +13607,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98984020</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13172,6 +13722,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99458070</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13269,6 +13824,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99477052</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13414,6 +13974,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99505825</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13559,6 +14124,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99505852</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13681,6 +14251,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944683</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13796,6 +14371,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126603618</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13906,6 +14486,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126603803</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -14013,6 +14598,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126604714</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14123,6 +14713,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126608100</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14233,6 +14828,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126608423</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14343,6 +14943,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126609668</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14470,6 +15075,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753791</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14567,6 +15177,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131848306</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14687,6 +15302,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131696846</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14799,6 +15419,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637881</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14923,6 +15548,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866860</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -15035,6 +15665,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637887</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15150,6 +15785,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99456502</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15252,6 +15892,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99477054</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15354,6 +15999,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99477055</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15461,6 +16111,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124060</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15578,6 +16233,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124075</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15690,6 +16350,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121221017</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15807,6 +16472,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231782</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15914,6 +16584,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126607980</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -16031,6 +16706,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753788</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -16143,6 +16823,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866838</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16255,6 +16940,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866840</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16367,6 +17057,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866841</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16479,6 +17174,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866842</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16591,6 +17291,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866844</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16703,6 +17408,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866845</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16815,6 +17525,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866847</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16927,6 +17642,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866848</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -17039,6 +17759,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866856</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -17151,6 +17876,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866857</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17263,6 +17993,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866858</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17375,6 +18110,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866859</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17472,6 +18212,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131888523</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17591,6 +18336,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866839</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17703,6 +18453,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97353544</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17840,6 +18595,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124066</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17967,6 +18727,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124072</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -18099,6 +18864,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124078</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -18226,6 +18996,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753768</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18358,6 +19133,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753779</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18490,6 +19270,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753786</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18617,6 +19402,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753789</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18744,6 +19534,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753790</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18876,6 +19671,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365742</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -19008,6 +19808,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131866843</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -19115,6 +19920,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354229</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -19222,6 +20032,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354603</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -19354,6 +20169,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944675</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -19486,6 +20306,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124080</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19618,6 +20443,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365740</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19715,6 +20545,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131852103</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19847,6 +20682,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753769</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19959,6 +20799,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354788</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -20071,6 +20916,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354834</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -20203,6 +21053,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944668</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -20335,6 +21190,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124065</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -20467,6 +21327,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124074</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -20604,6 +21469,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124077</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -20736,6 +21606,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124081</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -20833,6 +21708,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131852478</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20960,6 +21840,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231771</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -21087,6 +21972,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365718</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -21199,6 +22089,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637856</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -21311,6 +22206,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637912</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -21423,6 +22323,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637936</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -21535,6 +22440,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637884</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -21647,6 +22557,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637937</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -21757,6 +22672,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354555</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21869,6 +22789,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944672</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21981,6 +22906,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637977</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -22093,6 +23023,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637985</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -22205,6 +23140,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637858</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -22317,6 +23257,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637885</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -22429,6 +23374,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637913</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -22541,6 +23491,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637938</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -22653,6 +23608,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637963</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -22767,6 +23727,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98158609</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -22879,6 +23844,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944643</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -22994,6 +23964,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129517893</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -23113,6 +24088,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129518152</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -23225,6 +24205,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637863</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -23337,6 +24322,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637888</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -23449,6 +24439,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637918</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -23561,6 +24556,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637943</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -23673,6 +24673,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637969</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -23785,6 +24790,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637899</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -23897,6 +24907,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637852</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -24009,6 +25024,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637908</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -24121,6 +25141,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637851</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -24233,6 +25258,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637878</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -24345,6 +25375,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637905</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -24457,6 +25492,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637933</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -24569,6 +25609,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637959</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -24674,6 +25719,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131867113</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -24786,6 +25836,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637927</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -24898,6 +25953,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637978</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -25010,6 +26070,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637868</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -25122,6 +26187,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637926</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -25234,6 +26304,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637952</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -25346,6 +26421,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637976</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -25453,6 +26533,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354607</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -25565,6 +26650,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944652</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -25692,6 +26782,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944676</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -25824,6 +26919,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124079</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -25931,6 +27031,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121224002</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -26058,6 +27163,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231764</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -26185,6 +27295,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231781</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -26317,6 +27432,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365741</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -26414,6 +27534,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131851479</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -26546,6 +27671,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944663</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -26678,6 +27808,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124063</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -26805,6 +27940,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231775</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -26921,6 +28061,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126608030</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -27053,6 +28198,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365729</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -27180,6 +28330,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365753</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -27302,6 +28457,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910897</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -27434,6 +28594,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124083</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -27550,6 +28715,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121222341</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -27682,6 +28852,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910893</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -27794,6 +28969,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637869</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -27906,6 +29086,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637896</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -28018,6 +29203,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133637928</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -28135,6 +29325,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133328061</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -28252,6 +29447,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132336525</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -28369,6 +29569,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133328062</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -28482,6 +29687,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132336524</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -28599,6 +29809,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132336526</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -28716,6 +29931,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133328063</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -28821,6 +30041,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129667342</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -28928,6 +30153,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126551316</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -29049,6 +30279,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128274696</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -29151,6 +30386,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354790</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -29265,6 +30505,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98155245</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -29372,6 +30617,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944659</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -29479,6 +30729,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944669</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -29591,6 +30846,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124045</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -29698,6 +30958,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124047</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -29805,6 +31070,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124048</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -29912,6 +31182,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231762</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -30009,6 +31284,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131851241</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -30118,6 +31398,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98156759</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -30232,6 +31517,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98156914</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -30345,6 +31635,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98156997</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -30470,6 +31765,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98157189</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -30594,6 +31894,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99462175</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -30706,6 +32011,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104336481</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -30813,6 +32123,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944644</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -30920,6 +32235,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944645</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -31027,6 +32347,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944646</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -31148,6 +32473,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231773</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -31268,6 +32598,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121330721</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -31380,6 +32715,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126605219</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -31492,6 +32832,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126609812</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -31603,6 +32948,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126609883</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -31714,6 +33064,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126609998</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -31825,6 +33180,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126610096</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -31936,6 +33296,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126610157</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -32047,6 +33412,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126610277</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -32159,6 +33529,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753784</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -32285,6 +33660,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128279306</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -32406,6 +33786,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365747</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -32522,6 +33907,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910883</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -32638,6 +34028,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910884</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -32754,6 +34149,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910885</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -32870,6 +34270,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910889</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -32973,6 +34378,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97354291</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -33084,6 +34494,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121224119</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -33195,6 +34610,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121224726</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -33306,6 +34726,11 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126607356</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -33418,6 +34843,11 @@
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753773</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -33525,6 +34955,11 @@
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944651</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -33632,6 +35067,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944660</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -33743,6 +35183,11 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121224447</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -33850,6 +35295,11 @@
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121231765</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -33947,6 +35397,11 @@
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131853396</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -34054,6 +35509,11 @@
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944649</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -34166,6 +35626,11 @@
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120944653</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -34273,6 +35738,11 @@
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126551299</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -34376,6 +35846,11 @@
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365744</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -34487,8 +35962,310 @@
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131765108</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http:/